--- a/final_template/output/doosan_fuel_cell_large_RR_renewable_resources_alternative_energy_2025_v7_2/Doosan_Fuel_Cell_2025_EBX_Q_consultant_safe_v7_2_KO.xlsx
+++ b/final_template/output/doosan_fuel_cell_large_RR_renewable_resources_alternative_energy_2025_v7_2/Doosan_Fuel_Cell_2025_EBX_Q_consultant_safe_v7_2_KO.xlsx
@@ -1,70 +1,137 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="consultant_safe_v7_2" sheetId="1" r:id="R17172ad996c644ec"/>
-  </x:sheets>
-</x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="consultant_safe_v7_2" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="3">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF174A5A"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border/>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="7">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF174A5A"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -259,59 +326,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="14.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="41.25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="65" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="45" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="57.5" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="90" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="5" t="str">
-        <x:v>EBX Indicator</x:v>
-      </x:c>
-      <x:c r="B1" s="5" t="str">
-        <x:v>Field</x:v>
-      </x:c>
-      <x:c r="C1" s="5" t="str">
-        <x:v>Original Answer</x:v>
-      </x:c>
-      <x:c r="D1" s="5" t="str">
-        <x:v>Original Answer Metadata</x:v>
-      </x:c>
-      <x:c r="E1" s="5" t="str">
-        <x:v>Style Template Applied</x:v>
-      </x:c>
-      <x:c r="F1" s="5" t="str">
-        <x:v>Final Answer</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="6" t="str">
-        <x:v>EBX-Q-001</x:v>
-      </x:c>
-      <x:c r="B2" s="6" t="str">
-        <x:v>일반 / 전략 (Strategy) / ESG 비전 및 중장기 전략</x:v>
-      </x:c>
-      <x:c r="C2" s="6" t="str">
-        <x:v>[p.15] ESG 거버넌스 ESG 위원회 두산퓨얼셀은 회사의 지속가능성과 관련된 기회와 위험을 파악하고 영향을 분석해 대응방안을 마련하고 승인하는 최고 의사결정 기구로 ESG 위원회를 운영하고 있습니다. ESG 위원회는 CEO가 주관하고 전사 임원과 주요 팀장이 참석하며, 상·하반기 각 1회씩 개최됩니다. 상반기 위원회는 연간 ESG 과제와 목표 및 실행계획을 보고하고 승인받으며, 하반기 위원회는 한 해 동안의 ESG 성과를 보고하고 내년도 방향성을 설정하는 방식으로 운영됩니다. ESG 협의회 ESG 성과를 관리하고 실행력을 강화할 수 있도록 유관부서 실무자와 실무 책임자가 참여하는 ESG 협의회를 분기 별로 운영합니다. 1·3분기 협의회는 ESG팀이 주관하고, 2·4분기 협의회는 각 본부에서 주관함으로써 ESG가 각 현업부서에 내재화되도록 하고 있습니다. ESG 회의체 주요 활동 일자 활동 내역 2024.7.23 ’24년 상반기  ESG 활동 경과보고 •  중대 이슈보고 •   주요 ESG 과제 및 목표 보고 -  제품 전과정 친환경성 강화, 온실가스 감축, 오염물질/폐기물 감축,  공급망 ESG 관리, 사회공헌 활동 계획, 가족친화경영 인증 획득 등 2024.12.19 사외이사 ESG 교육 실시 •  지속가능성 공시제도 동향 2025.1.17 ’24년 ESG 주요 과제 및  성과 보고 •  기후변화 대응 활동 보고(시나리오 분석 결과, Scope 3 관리 체계 등) •  제품 전과정 친환경성 강화 과제 성과 보고 •  기후변화 외 사업장 환경성과 보고(폐기물, 오염물질, 환경사고 등) 이사회 ESG 활동 내역 일자 활동 내역 2024.3.22 ’24년 상반기  ESG 위원회 개최 •   ’24년 ESG 과제 추진 계획 보고 -  재생에너지 도입 방안 검토, 에너지/온실가스 감축, 공급망 ESG 평가 전문업체 선정, Scope 3 산정 방안, 자원순환 및 환경영향 저감 체계 구축, 인권영향평가 시행 방안 등 2024.12.20 ’24년 하반기  ESG 위원회 개최 •  ESG 평가 결과 및 외부 ESG 관련 수상 결과 보고 •   ’24년 ESG 과제 성과 보고 -  자원순환에 따른 폐기물 절감 및 원가 ...
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14.38000011444092" customWidth="1" min="1" max="1"/>
+    <col width="41.25" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="57.5" customWidth="1" min="5" max="5"/>
+    <col width="90" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>EBX Indicator</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Original Answer</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Original Answer Metadata</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Style Template Applied</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Final Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>일반 / 전략 (Strategy) / ESG 비전 및 중장기 전략</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>[p.15] ESG 거버넌스 ESG 위원회 두산퓨얼셀은 회사의 지속가능성과 관련된 기회와 위험을 파악하고 영향을 분석해 대응방안을 마련하고 승인하는 최고 의사결정 기구로 ESG 위원회를 운영하고 있습니다. ESG 위원회는 CEO가 주관하고 전사 임원과 주요 팀장이 참석하며, 상·하반기 각 1회씩 개최됩니다. 상반기 위원회는 연간 ESG 과제와 목표 및 실행계획을 보고하고 승인받으며, 하반기 위원회는 한 해 동안의 ESG 성과를 보고하고 내년도 방향성을 설정하는 방식으로 운영됩니다. ESG 협의회 ESG 성과를 관리하고 실행력을 강화할 수 있도록 유관부서 실무자와 실무 책임자가 참여하는 ESG 협의회를 분기 별로 운영합니다. 1·3분기 협의회는 ESG팀이 주관하고, 2·4분기 협의회는 각 본부에서 주관함으로써 ESG가 각 현업부서에 내재화되도록 하고 있습니다. ESG 회의체 주요 활동 일자 활동 내역 2024.7.23 ’24년 상반기  ESG 활동 경과보고 •  중대 이슈보고 •   주요 ESG 과제 및 목표 보고 -  제품 전과정 친환경성 강화, 온실가스 감축, 오염물질/폐기물 감축,  공급망 ESG 관리, 사회공헌 활동 계획, 가족친화경영 인증 획득 등 2024.12.19 사외이사 ESG 교육 실시 •  지속가능성 공시제도 동향 2025.1.17 ’24년 ESG 주요 과제 및  성과 보고 •  기후변화 대응 활동 보고(시나리오 분석 결과, Scope 3 관리 체계 등) •  제품 전과정 친환경성 강화 과제 성과 보고 •  기후변화 외 사업장 환경성과 보고(폐기물, 오염물질, 환경사고 등) 이사회 ESG 활동 내역 일자 활동 내역 2024.3.22 ’24년 상반기  ESG 위원회 개최 •   ’24년 ESG 과제 추진 계획 보고 -  재생에너지 도입 방안 검토, 에너지/온실가스 감축, 공급망 ESG 평가 전문업체 선정, Scope 3 산정 방안, 자원순환 및 환경영향 저감 체계 구축, 인권영향평가 시행 방안 등 2024.12.20 ’24년 하반기  ESG 위원회 개최 •  ESG 평가 결과 및 외부 ESG 관련 수상 결과 보고 •   ’24년 ESG 과제 성과 보고 -  자원순환에 따른 폐기물 절감 및 원가 ...
 [p.16] ESG 전략 두산퓨얼셀은 수소에너지 전문 기업으로서, 환경 친화적이고 지속가능한 성장의 의지를 담아 ESG 경영 전략을 수립했습니다. 두산퓨얼셀은 ESG 전략에 대한 최고 거버넌스 기구의 검토와 승인을 바탕으로 적극적이고 체계적인 ESG 활동을 추진해 나가고 있습니다. ESG 전략 방향 두산퓨얼셀은 비즈니스 연계성과 위험 및 기회 요소를 기준으로 과제별 전략 방향과 활동 방침을 설정했습니다. ESG 전략 체계 두산퓨얼셀의 ESG 전략 체계는 ESG Vision, 전략목표, 전략방향, 전략과제로 구성되어 있습니다. 환경·사회 측면에서는 3대 전략 목표 및 방향과 9대 전략 과제를, 거버넌스 측면에서는 전략 목표 및 방향과 3대 전략 과제를 선정하여 성과를 관리하고 있습니다. 기회 영역 이해관계자 소통 활성화: 장기적 관점에서 성장 기반으로 관리 친환경 경쟁력 강화 : 집중적인 강화/육성으로 경쟁사와 격차 확대 커뮤니케이션 강화 제품 전과정 환경영향 최소화 고객만족 강화 탄소중립 선언 및 온실가스 감축 지역사회 참여 확대 탄소중립 기여 제품군 강화 자원을 집중하고 성과 개선에 힘써야 할 과제 위험 영역 ESG 경영 내재화 : 필수 관리 요소로 변화관리 관점에서 접근 리스크 관리 : 리스크 관리 체계를 강화하고 실질적 성과 개선 인권 · 안전 · 윤리 기후변화 리스크 대응체계 구축 이사회 구성/운영 친환경 사업장 구축 변화관리 활동 촉진 공급망 ESG 관리 장기적 관점에서 추진하고 내재화 할 과제 비즈니스 연계성 높음낮음 글로벌 시장 진출 역량 연구 개발 능력 생산 능력 ESG Vision 두산퓨얼셀 “지속가능한 미래를 실현하는 친환경 에너지 기업” 비즈니스 연속성 강화전략목표 비재무리스크 관리 확대전략방향 ·  공급망 ESG 관리 강화 ·  기후변화 리스크  정보 공개 · 사업장 환경성과 개선 전략과제 ESG 경영 내재화전략목표 ESG 경영문화 조성전략방향 ·  이사회 구성과 ESG 역할 강화 · 인권·안전· 윤리경영 · 변화 관리 활동 촉진 전략과제 2050 Net-Zero전략목표 친환경 경쟁력 강화전략방향 · 사업장 온실가스 감축 · 탄소중립 제품군 확대 ·  제품 전과정 환경 영향 최소화 전략과제 지속적인 변화 추구전략목표 ...
 [p.17] ESG 전략 ESG 중장기 로드맵 두산퓨얼셀은 2030년까지 ‘지속가능한 미래를 실천하는 친환경 에너지 기업’이라는 ESG Vision을 달성하기 위하여 2023년2월, ESG 중장기 로드맵을 수립했습니다. 2023년은 첫 해로서 ESG 경영 전략을 바탕으로 성과관리 방안을 마련하고 환경, 사회, 지배구조 전 영역에 걸쳐 목표를 수립하고 활동했습니다. 그 결과 2023년에 한국ESG기준원 (KCGS) ESG 평가에서 종합 A 등급을 획득하는 등 목표를 일부 초과 달성했습니다. Phase 2에 접어든 2024년부터는 ESG 성과와 비즈니스 성과의 연계를 위한 전략과제를 수립/실행하고 있으며, 다가올 공시 의무화에 대비하기 위한 활동을 단계적으로 추진하고 있습니다. Phase 3인 2026년부터는 ESG 역량을 Global Standard 수준까지 끌어올리고 Best Practice를 개발하여 동종 산업군 내 ESG TOP Tier로 도약하는 것을 목표로 하고 있습니다. Phase 01Phase 01 Phase 02Phase 02 Phase 03Phase 03 ESG 전략 및 체계 수립/실행 ESG 체계, 로드맵 전략과제 수립 및 실행 ESG 실행 성숙기 ESG 과제 실행력 강화 및 보완 ESG 이행 활동 고도화 ESG Best Practice 개발 • ESG 전략 체계 수립/실행 • ESG 성과 관리 방안 마련/실행 • 중장기 온실가스 감축 목표 수립/실행 • 협력사 ESG 평가 체계 구축 및 협력사 대상 평가 실시 • ESG 과제 실행력 강화 및 보완 • C-Level ESG 성과 관리 • 온실가스 감축을 위한 재생에너지 도입 검토 • 협력사 ESG 평가 및 리스크 완화 활동 실행, 구매 제도 반영 • 고객만족 체계 구축/실행 • 제품 전 과정 친환경성 강화 Frame 구축 및 실행 • 공시의무화 대응 활동 시행(IRO 분석) • 택소노미 정보 공시 • 온실가스 Scope 3 배출량 산정 • ESG 경영 관리 고도화 및 플랫폼 구축 • 이사회 내 ESG 성과 관리 • 온실가스 추가 감축 수단 검토 및 도입 • 글로벌 공급망 리스크 관리를 위한 공시, 실행, 평가 • VOC DB 구축 및 활용 • ESG 정보공개 확대 및 공시 활성화 ...
-[p.19] ESG 성과 관리 성과관리 프로세스 두산퓨얼셀은 분기별로 실무 협의회를 운영하여 ESG 전략 과제를 관리하고 실천합니다. 1·3분기 협의회는 ESG팀이 주관하고, 2·4분기는 각 본부에서 주관하며 성과를 점검하고 실행력을 강화합니다. 또한 CEO가 주관하는 ESG 위원회를 개최하여 당해년도 ESG 목표와 성과, 실행 방안에 대한 의사결정을 진행하고 있습니다. 2024년 상반기 ESG 위원회 2025년 상반기 ESG 위원회 지속성장혁신위원회 지주 주관 과제 및 자회사 ESG 계획 공유 ESG 트렌드 강연 1 지속성장혁신위원회 당해년도  지주과제 실적 리뷰 차년도 그룹 과제 확정 2 정기이사회 보고서 발간 결과 주요 과제 추진 결과 2 정기이사회 위원회/지성위 결과 중대성평가 결과 및 주요추진 과제 보고 1 2월1월 3월 4월 5월 6월 7월 8월 9월 10월 11월 12월 퓨 얼 셀 ESG 팀 ESG 협의회 ESG 위원회 이사회 지주 ESG 위원회 당해 년도 과제별 달성 목표 및 실행 방안 강구 1 ESG 위원회 당해 년도 실적 보고 2 ESG 협의회  (본부 주관) 보고서 초안 검토 과제진행 사항 점검 2 ESG 협의회  (ESG팀 주관) 개선 과제 발굴 과제 진행 사항 점검 2 ESG 협의회  (본부 주관) 당해년도 실적 리뷰, 평가  결과 공유, 개선 방향 도출 2 KCGS / DJSI 평가 대응 평가 결과 공개 ESG 협의회  (ESG팀 주관) 당해 년도 과제별 달성 목표 및 실행 방안 강구 1 지속가능경영보고서 준비 및 발간 실적 리뷰 및 개선 과제 도출 당해 년도 목표/실행 계획 확정 및 지주 공유 Doosan Fuel Cell Sustainability Report 2025 Company Overview ESG Strategy Materiality ESG Performance Appendix ESG 거버넌스 ESG 전략 ESG 목표 및 성과 ESG 성과 관리 019</x:v>
-      </x:c>
-      <x:c r="D2" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.19] ESG 성과 관리 성과관리 프로세스 두산퓨얼셀은 분기별로 실무 협의회를 운영하여 ESG 전략 과제를 관리하고 실천합니다. 1·3분기 협의회는 ESG팀이 주관하고, 2·4분기는 각 본부에서 주관하며 성과를 점검하고 실행력을 강화합니다. 또한 CEO가 주관하는 ESG 위원회를 개최하여 당해년도 ESG 목표와 성과, 실행 방안에 대한 의사결정을 진행하고 있습니다. 2024년 상반기 ESG 위원회 2025년 상반기 ESG 위원회 지속성장혁신위원회 지주 주관 과제 및 자회사 ESG 계획 공유 ESG 트렌드 강연 1 지속성장혁신위원회 당해년도  지주과제 실적 리뷰 차년도 그룹 과제 확정 2 정기이사회 보고서 발간 결과 주요 과제 추진 결과 2 정기이사회 위원회/지성위 결과 중대성평가 결과 및 주요추진 과제 보고 1 2월1월 3월 4월 5월 6월 7월 8월 9월 10월 11월 12월 퓨 얼 셀 ESG 팀 ESG 협의회 ESG 위원회 이사회 지주 ESG 위원회 당해 년도 과제별 달성 목표 및 실행 방안 강구 1 ESG 위원회 당해 년도 실적 보고 2 ESG 협의회  (본부 주관) 보고서 초안 검토 과제진행 사항 점검 2 ESG 협의회  (ESG팀 주관) 개선 과제 발굴 과제 진행 사항 점검 2 ESG 협의회  (본부 주관) 당해년도 실적 리뷰, 평가  결과 공유, 개선 방향 도출 2 KCGS / DJSI 평가 대응 평가 결과 공개 ESG 협의회  (ESG팀 주관) 당해 년도 과제별 달성 목표 및 실행 방안 강구 1 지속가능경영보고서 준비 및 발간 실적 리뷰 및 개선 과제 도출 당해 년도 목표/실행 계획 확정 및 지주 공유 Doosan Fuel Cell Sustainability Report 2025 Company Overview ESG Strategy Materiality ESG Performance Appendix ESG 거버넌스 ESG 전략 ESG 목표 및 성과 ESG 성과 관리 019</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 15;16;17;19
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E2" s="6" t="str">
-        <x:v>Selected Style: narrative
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: narrative
 Preferred Style Source: template
 Answer Type: strategy-policy
 Answer Intent: Explain the policy or strategic direction first, then connect targets, governance, and execution evidence.
@@ -330,34 +423,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: Medium: prose must be natural, evidence-grounded, and non-repetitive.</x:v>
-      </x:c>
-      <x:c r="F2" s="6" t="str">
-        <x:v>ESG 거버넌스 ESG 위원회 두산퓨얼셀은 회사의 지속가능성과 관련된 기회와 위험을 파악하고 영향을 분석해 대응방안을 마련하고 승인하는 최고 의사결정 기구로 ESG 위원회를 운영하고 있습니다. ESG 전략 두산퓨얼셀은 수소에너지 전문 기업으로서, 환경 친화적이고 지속가능한 성장의 의지를 담아 ESG 경영 전략을 수립했습니다. 두산퓨얼셀은 ESG 전략에 대한 최고 거버넌스 기구의 검토와 승인을 바탕으로 적극적이고 체계적인 ESG 활동을 추진해 나가고 있습니다. 두산퓨얼셀는 ESG 비전 및 중장기 전략를 중장기 방향과 실행 과제에 연결해 지속가능경영의 방향성을 제시하고 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="6" t="str">
-        <x:v>EBX-Q-002</x:v>
-      </x:c>
-      <x:c r="B3" s="6" t="str">
-        <x:v>일반 / 거버넌스 (Governance) / ESG 거버넌스 및 의사결정 체계</x:v>
-      </x:c>
-      <x:c r="C3" s="6" t="str">
-        <x:v>[p.25] &gt; 최고 경영진의 역할과 책임 지배구조 두산퓨얼셀은 기후변화 관련 위험과 기회를 관리 및 감독하기 위하여 경영진 의사결정 기구인 ESG위원회를 중심으로 거버넌스를 구축하고 있습니다. ESG위원회는 연 2회 개최하며, 상반기에는 기후변화 관련 위험과 기회를 보고받고 대응 전략과 목표를 결정하며, 하반기에는 성과를 점검하고 차기 연도 방향성을 수립합니다. 또한, ESG를 총괄하는 경영지원본부장이 필요에 따라 수시로 기후변화 관련 위험 분석과 모니터링 및 대응 전략을 검토하고 있습니다. 한편, 기후변화 관련 주요 전략 및 과제는 연 1회 이상 이사회에 보고하고 있습니다. &gt; 기후변화 관련 위험과 기회를 의사결정에 고려하는 방법 정부는 탄소중립 이행을 위하여 정책적으로 수소산업을 육성하고 있습니다. 그 일환으로 일반수소발전 입찰시장(RPS)과 함께 2024년부터 청정수소발전 의무화제도(CHPS)를 운영하고 있으며, RPS와 CHPS 입찰 시장 규모를 합하면 2024년 기준 약 7,800GWh 규모입니다. 두산퓨얼셀은 수소발전 입찰시장이 커짐에 따라 사업기회가 확대될 것으로 기대하고 있습니다. 한편, CHPS의 도입으로 연료전지 사업자뿐만 아니라 석탄-암모니아 혼소, 수소전소터빈 등 신규 사업자와의 경쟁이 심화될 것으로 예상됩니다. 이에 따라 당사는 경쟁력 제고를 위해 제품 효율 개선을 통한 균등화발전원가(LCOE) 저감과 품질 개선을 통한 장기유지보수(LTSA) 비용 저감 등의 투자를 진행하고 있습니다. &gt; 경영진의 기후변화 감독을 지원하기 위한 통제 및 절차 두산퓨얼셀은 매년 중대성 평가 시, 기후변화와 관련된 영향, 위험 및 기회요인(IRO)을 도출하여 유관부서 실무자를  대상으로 설문조사를 실시하여 환경/사회적 영향과 재무적 영향의 규모, 범위, 발생 가능성을 파악합니다. 결과는 경영진 주관의 ESG위원회에 보고되어 대응 방안의 수립과 목표를 의사결정 받는데 활용됩니다. 특히, 최고전략책임자(CSO)를 겸하고 있는 CEO는 사업전략 수립에, ESG를 총괄하는 경영지원본부장은 사업장 환경 및 안전/보건 전략 수립에  기후변화에 따른 위험과 기회 분석 결과를 반영하고 있습니다. &gt; 최고 경영진 교육 현황 두산퓨얼셀은 법률, 재무/회계, ...
+QA Severity: Medium: prose must be natural, evidence-grounded, and non-repetitive.</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 회사의 지속가능성과 관련된 기회와 위험을 파악하고 영향을 분석해 대응방안을 마련하고 승인하는 최고 의사결정 기구로 ESG 위원회를 운영하고 있습니다. 두산퓨얼셀은 수소에너지 전문 기업으로서, 환경 친화적이고 지속가능한 성장의 의지를 담아 ESG 경영 전략을 수립했습니다. 두산퓨얼셀은 ESG 전략에 대한 최고 거버넌스 기구의 검토와 승인을 바탕으로 적극적이고 체계적인 ESG 활동을 추진해 나가고 있습니다. 두산퓨얼셀은 ESG 비전 및 중장기 전략을 중장기 방향과 실행 과제에 연결해 지속가능경영의 방향성을 제시하고 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>일반 / 거버넌스 (Governance) / ESG 거버넌스 및 의사결정 체계</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>[p.25] &gt; 최고 경영진의 역할과 책임 지배구조 두산퓨얼셀은 기후변화 관련 위험과 기회를 관리 및 감독하기 위하여 경영진 의사결정 기구인 ESG위원회를 중심으로 거버넌스를 구축하고 있습니다. ESG위원회는 연 2회 개최하며, 상반기에는 기후변화 관련 위험과 기회를 보고받고 대응 전략과 목표를 결정하며, 하반기에는 성과를 점검하고 차기 연도 방향성을 수립합니다. 또한, ESG를 총괄하는 경영지원본부장이 필요에 따라 수시로 기후변화 관련 위험 분석과 모니터링 및 대응 전략을 검토하고 있습니다. 한편, 기후변화 관련 주요 전략 및 과제는 연 1회 이상 이사회에 보고하고 있습니다. &gt; 기후변화 관련 위험과 기회를 의사결정에 고려하는 방법 정부는 탄소중립 이행을 위하여 정책적으로 수소산업을 육성하고 있습니다. 그 일환으로 일반수소발전 입찰시장(RPS)과 함께 2024년부터 청정수소발전 의무화제도(CHPS)를 운영하고 있으며, RPS와 CHPS 입찰 시장 규모를 합하면 2024년 기준 약 7,800GWh 규모입니다. 두산퓨얼셀은 수소발전 입찰시장이 커짐에 따라 사업기회가 확대될 것으로 기대하고 있습니다. 한편, CHPS의 도입으로 연료전지 사업자뿐만 아니라 석탄-암모니아 혼소, 수소전소터빈 등 신규 사업자와의 경쟁이 심화될 것으로 예상됩니다. 이에 따라 당사는 경쟁력 제고를 위해 제품 효율 개선을 통한 균등화발전원가(LCOE) 저감과 품질 개선을 통한 장기유지보수(LTSA) 비용 저감 등의 투자를 진행하고 있습니다. &gt; 경영진의 기후변화 감독을 지원하기 위한 통제 및 절차 두산퓨얼셀은 매년 중대성 평가 시, 기후변화와 관련된 영향, 위험 및 기회요인(IRO)을 도출하여 유관부서 실무자를  대상으로 설문조사를 실시하여 환경/사회적 영향과 재무적 영향의 규모, 범위, 발생 가능성을 파악합니다. 결과는 경영진 주관의 ESG위원회에 보고되어 대응 방안의 수립과 목표를 의사결정 받는데 활용됩니다. 특히, 최고전략책임자(CSO)를 겸하고 있는 CEO는 사업전략 수립에, ESG를 총괄하는 경영지원본부장은 사업장 환경 및 안전/보건 전략 수립에  기후변화에 따른 위험과 기회 분석 결과를 반영하고 있습니다. &gt; 최고 경영진 교육 현황 두산퓨얼셀은 법률, 재무/회계, ...
 [p.85] 지배구조 이사회 운영 체제 이사회는 회사의 주요 경영사항을 심의·의결하며 법령 또는 정관에 정한 사항, 주주총회로부터 위임받은 사항, 회사 경영의 기본 방침과 업무 집행에 관한 중요 사항을 의결하고 정관 변경을 위해서는 상법 제434조에 따라 주주총회의 승인이 필요합니다. 2024년 말 현재 당사의 이사회는 사내이사 2인 및 사외이사 4인으로 구성되어 있으며, 이사회 내 이사 가운데 다른 직책을 4개 이상 보유한 이사는 없습니다. 당사는 상법 제400조 2항의 이사 책임 감면제도를 도입하지 않고 있으므로 이사의 책임에는 제한이 없습니다. 이사회 의장 및 소집권자는 이두순 대표이사로, 업무 수행의 전문성과 이사회 운영의 효율성을 고려하여 이사회 의장으로 선임되었습니다. 이사회 내 위원회로는 전원 사외이사로 구성된 감사위원회, 사외이사후보추천위원회, 내부거래위원회 및 보상위원회가 설치되어 운영되고 있습니다. 이사의 임기는 취임 후 3년 내의 최종 결산기에 관한 정기주주총회 종결까지로, 통상 약 3년입니다. 2024년 말 기준으로 이사진의 평균 재임 기간은 약 31개월입니다. 이사회는 사업연도 개시일부터 매 3월에 1회 개최되는 정기이사회와 임시이사회로 구분되며, 임시이사회는 필요에 따라 수시로 개최할 수 있습니다. 이사회의 성립과 결의는 통상 이사 전원의 과반수 출석 및 출석 이사 과반수 찬성으로 진행하고 있으며, 특정 사항에 이해관계가 있는 이사의 의결권은 제한됩니다. 2024년 회사의 이사회는 총 9회 개최되었으며 이사진의 평균 참석률은 93%입니다. 이사회 내 사외이사 비율은 2022년 및 2023년 말 60%, 2024년 말 기준 67%입니다. 한편 여성이사는 아직 한 명도 선임하지 않았으며, 2024년 말 기준으로 이사회 구성원 모두 50세 초과 연령대에 해당됩니다. 이사회 소집은 1일 전에는 사전 통지 되도록 정관에 규정되어 있습니다. 출석률이 저조한(75% 미만) 사외이사는 없으며 동종 산업 경력이 있는 사외이사의 비율은 2022년 및 2023년 33%에서 2024년 말 기준 25%로 감소했습니다. 2024년 말 기준으로 사외이사가 반대 또는 수정의견을 제시한 안건 수는 없었으며, 최대주주 및 특수관계인을 제외 한 등기임원의 ...
 [p.86] 지배구조 구분 감사위원회 내부거래위원회 사외이사후보추천위원회 보상위원회 구성 사외이사 전원 사외이사 전원 사외이사 전원 사외이사 전원 역할 회사의 회계 및 업무감사 공정거래법상 내부거래 심사 및 승인 사외이사 후보 추천 임원 보상 관련 사항 심사 및 승인 활동내용 외부감사인 선정, 회계감사결과 보고 등 계열회사와의 거래 승인 등 사외이사 후보 추천 장기 성과급 지급 승인 등 개최횟수 7 3 1 2025년 신설 참석률 97% 92% 67% - 안건 감사결과 보고 등 13건 내부거래 변경 승인 등 3건 사외이사 후보 추천 1건 - 이사회 산하 위원회 운영 현황(’24년 기준) 겸직자 겸직회사 성명 직위 회사명 직위 상근여부 고창현 사외이사 HD현대삼호(주) 사외이사 비상근 박찬석 사외이사 한온시스템(주) 사외이사 비상근 이두순 대표이사 HyAxiom. Inc. 대표이사 상근 두산에이치투이노베이션 (주) 대표이사 상근 등기임원의 타회사 임원 겸직 현황 한편, 두산퓨얼셀은 2023년부터 이사회의 ESG 관리/감독 기능을 강화하기 위하여 이사회 규정을 개정하여 사외이사에 대한 전문인력 지원 규정을 명문화했고, 감사위원회 규정을 개정하여 감사위원회에 내부감사부서 책임자 임명동의권을 부여했습니다. 또한 매년 상/하반기에 정례적으로 주요 ESG 안건을 부의하여 목표와 성과를 보고하고 있습니다. 평가와 보상 이사의 보수는 주주총회에서 승인한 보수한도 내에서 당사 사규에 따라 집행됩니다. 사내이사의 보수는 ‘집행인원 인사관리 규정’에 따라 기본 연봉과 경영 성과를 반영한 성과급으로 구분하여 지급하며, 사외 이사에게는 기본 연봉만 지급하며 성과급 지급은 없습니다. 당사는 이사의 보수를 공정하고 투명하게 지급하고 관계 법령에 따라 이를 공개하고 있습니다. 경영진 보수 성과 평가는 규정에 따라 재무성과과제 및 전략성과과제 등의 계량적 지표(MBO)와 성장성, 포트폴리오 개선, 계획 수준의 적정성 등 비계량적 지표(정성평가)에 대한 평가결과에 따라 지급하고 있습니다. CEO의 보수는 매출액, 영업이익, 잉여현금흐름(FCF, Free Cash Flow), 부채비율의 지표에 따라 집행됩니다. 또한 CEO의 인센티브 중 단기 인센티브는 재무성과과제 등 계량적 지표( ...
-[p.87] 지배구조 이사회는 법령 및 내규에 의거하여 중요한 자산의 처분 및 양도, 대규모 재산의 차입 등 회사 경영의 중요한 사항을 의 결하고 있습니다. 2024년에는 총 9회의 이사회가 개최되어 제5기 재무제표 및 영업보고서 승인 등 총 30건의 보고 및 결의 안건을 상정하여 처리하였으며, 관련 내용은 사업보고서를 통해 투명하게 공시하고 있습니다. 이사회는 공시, IR 활동 등 다양한 소통 채널을 통하여 이해관계자와 대내외 커뮤니케이션을 하고 있습니다. 또한 신속하게 주주와 이해관계자에게 경영정보를 제공하고자 주주총회의 의사 결정 사항과 경영상 주요 결정 사항을 즉각 공시하고 있습니다. 2019년~2021년 결산 정기주주총회는 14일 전에 통지했으며, 2022년~2024년 결산 정기주주총회는 21일 전에 통지했습니다. 이해관계자 커뮤니케이션 이사회 주요 의결 사항 사외이사 다양성 두산퓨얼셀은 사외이사 선임 시 종교, 성별, 인종, 연령, 장애, 정치성향, 지역 및 국가에 대한 차별을 하지 않으며 다양성을 고려하여 이사회를 구성하고자 노력하고 있습니다. 사외이사 선임 절차와 기준 사외이사 후보자는 전원 사외이사로 구성된 사외이사후보추천위원회의 검토 및 추천을 통해 선정되며, 이 과정에서 후보자의 자격 요건, 독립성 여부 및 업무 분야의 전문성 등이 고려됩니다. 후보자 선정 이후에는 이사회와 주주총회의 승인을 통해 사외이사로 선임됩니다. 사외이사의 임기는 3년이며, 상법 542조의8 등 관계 법령에 따라 연임은 1회로 제한되고 있습니다. 한편, 당사는 사외이사 선임 시 상법 제382조에 따라 다음 각 호의 어느 하나에 해당하지 않도록 자격 요건을 검증하고 있습니다. ▲최근 2년 이내에 해당 회사의 상무에 종사한 이사 ㆍ 감사 ㆍ 집행임원 및 피용자 ▲최대주주가 자연인인 경우 본인과 그 배우자 및 직계 존속 ㆍ 비속 ▲이사 ㆍ 감사 ㆍ 집행임원의 배우자 및 직계 존속 ㆍ 비속 ▲회사와 거래관계 등 중요한 이해관계에 있는 법인의 이사 ㆍ 감사 ㆍ 집행임원 및 피용자 ▲회사의 이사 ㆍ 집행임원 및 피용자가 이사 ㆍ 집행임원으로 있는 다른 회사의 이사 ㆍ 감사 ㆍ 집행임원 및 피용자 전자투표제 및 서면투표제 두산퓨얼셀은 소액주주의 의결권 보호를 위하여 ...</x:v>
-      </x:c>
-      <x:c r="D3" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.87] 지배구조 이사회는 법령 및 내규에 의거하여 중요한 자산의 처분 및 양도, 대규모 재산의 차입 등 회사 경영의 중요한 사항을 의 결하고 있습니다. 2024년에는 총 9회의 이사회가 개최되어 제5기 재무제표 및 영업보고서 승인 등 총 30건의 보고 및 결의 안건을 상정하여 처리하였으며, 관련 내용은 사업보고서를 통해 투명하게 공시하고 있습니다. 이사회는 공시, IR 활동 등 다양한 소통 채널을 통하여 이해관계자와 대내외 커뮤니케이션을 하고 있습니다. 또한 신속하게 주주와 이해관계자에게 경영정보를 제공하고자 주주총회의 의사 결정 사항과 경영상 주요 결정 사항을 즉각 공시하고 있습니다. 2019년~2021년 결산 정기주주총회는 14일 전에 통지했으며, 2022년~2024년 결산 정기주주총회는 21일 전에 통지했습니다. 이해관계자 커뮤니케이션 이사회 주요 의결 사항 사외이사 다양성 두산퓨얼셀은 사외이사 선임 시 종교, 성별, 인종, 연령, 장애, 정치성향, 지역 및 국가에 대한 차별을 하지 않으며 다양성을 고려하여 이사회를 구성하고자 노력하고 있습니다. 사외이사 선임 절차와 기준 사외이사 후보자는 전원 사외이사로 구성된 사외이사후보추천위원회의 검토 및 추천을 통해 선정되며, 이 과정에서 후보자의 자격 요건, 독립성 여부 및 업무 분야의 전문성 등이 고려됩니다. 후보자 선정 이후에는 이사회와 주주총회의 승인을 통해 사외이사로 선임됩니다. 사외이사의 임기는 3년이며, 상법 542조의8 등 관계 법령에 따라 연임은 1회로 제한되고 있습니다. 한편, 당사는 사외이사 선임 시 상법 제382조에 따라 다음 각 호의 어느 하나에 해당하지 않도록 자격 요건을 검증하고 있습니다. ▲최근 2년 이내에 해당 회사의 상무에 종사한 이사 ㆍ 감사 ㆍ 집행임원 및 피용자 ▲최대주주가 자연인인 경우 본인과 그 배우자 및 직계 존속 ㆍ 비속 ▲이사 ㆍ 감사 ㆍ 집행임원의 배우자 및 직계 존속 ㆍ 비속 ▲회사와 거래관계 등 중요한 이해관계에 있는 법인의 이사 ㆍ 감사 ㆍ 집행임원 및 피용자 ▲회사의 이사 ㆍ 집행임원 및 피용자가 이사 ㆍ 집행임원으로 있는 다른 회사의 이사 ㆍ 감사 ㆍ 집행임원 및 피용자 전자투표제 및 서면투표제 두산퓨얼셀은 소액주주의 의결권 보호를 위하여 ...</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 25;85;86;87
 Evidence type: qualitative+quantitative
 Coverage status: SUFFICIENT
-Numeric support: 12 quantitative row(s) in data_dinh_luong.csv are linked to the same source page(s).</x:v>
-      </x:c>
-      <x:c r="E3" s="6" t="str">
-        <x:v>Selected Style: governance
+Numeric support: 12 quantitative row(s) in data_dinh_luong.csv are linked to the same source page(s).</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: governance
 Preferred Style Source: template
 Answer Type: governance-organization
 Answer Intent: Explain who is responsible, what they decide or oversee, and how reporting or escalation works.
@@ -376,34 +481,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: Medium: responsibility and decision flow must be clear.</x:v>
-      </x:c>
-      <x:c r="F3" s="6" t="str">
-        <x:v>ESG위원회는 연 2회 개최하며, 상반기에는 기후변화 관련 위험과 기회를 보고받고 대응 전략과 목표를 결정하며, 하반기에는 성과를 점검하고 차기 연도 방향성을 수립합니다. 또한, ESG를 총괄하는 경영지원본부장이 필요에 따라 수시로 기후변화 관련 위험 분석과 모니터링 및 대응 전략을 검토하고 있습니다. 지배구조 이사회 운영 체제 이사회는 회사의 주요 경영사항을 심의·의결하며 법령 또는 정관에 정한 사항, 주주총회로부터 위임받은 사항, 회사 경영의 기본 방침과 업무 집행에 관한 중요 사항을 의결하고 정관 변경을 위해서는 상법 제434조에 따라 주주총회의 승인이 필요합니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="6" t="str">
-        <x:v>EBX-Q-003</x:v>
-      </x:c>
-      <x:c r="B4" s="6" t="str">
-        <x:v>일반 / 위험 관리 (Risk Management) / ESG 리스크 식별 및 관리 체계</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="str">
-        <x:v>[p.21] 영향의 우선순위 지정 - 주제별 그룹화 - 임계값 정의 - 결과 보고 환경 · 사회적 영향도 평가 - 국제표준 검토 (GRI, UN SDGs, ISO 26000 등) - 미디어 리서치 - 동종업계 벤치마킹 분석 재무적 영향도 평가 - 기업 내부 전략 분석 - 국제표준 검토 (SASB, DJSI, MSCI 등) - 국내 법규 분석 중요도 평가 중대 이슈 세부화 이슈에 대한 Sub Topic 선정 - GRI 및 ESRS Topic Standards 기반 중대 이슈 IRO 도출 - ESG 평가지표 분석 - 동종업계 벤치마킹 - 법률 및 연구논문 분석 이중 중대성 평가 이중 중대성 평가 개념 GRI Standards 등 국제 ESG 공시 가이드라인은 지속가능경영의 보고 수 준을 고도화하고자 이중 중대성 개념을 적용하고 있습니다. 이중 중대성은 외부의 지속가능성 관련 요인이 기업의 재무 상태에 미치는 영향과 기업의 경영활동이 환경·사회에 미치는 영향, 즉 내부적 관점과 외부적 관점을 모두 고려하는 개념입니다. 이중 중대성 평가 프로세스 두산퓨얼셀은 GRI 2021 Standard 방법론에 따라 환경·사회적 영향도와 재무적 영향도를 종합적으로 고려하여 이중 중대성 평가를 실시하였습니다. 특히,  환경·사회적 영향도와 재무적 영향도 분석을 통해 도출된 상위 10개 이슈 중 중대 이슈 3가지를 선별하여 중요한 영향, 위험 및 기회(Impact, Risk and Opportunity, 이하 IRO)를 도출하였습니다. 중대 이슈와 관련된 부서를 대상으로 이해관계자 설문조사를 실시하여 IRO의 우선순위를 지정하는 과정을 통해 두산퓨얼셀이 집중 관리해야 할 IRO 요인을 식별했습니다. 이렇게 식별된 IRO 요인은 두산퓨얼셀의 ESG경영의 주요 전략을 추진하는 데 활용되었으며, 두산퓨 얼셀은 CEO가 참여하는 ESG 위원회를 통해 중대성 평가 결과를 보고하고 검토 및 승인 단계를 거쳐 중대 이슈를 체계적으로 관리하고 있습니다. 환경・사회적 중요성 Inside-out(외부적 관점)에서 기업의 경영 활동으로 인해  사회 및 환경에 끼칠 수 있는  긍 · 부정적 영향의 정도를 의미 재무적 중요성 Outside-in(내부적 관점)에서 외부의 지속가능성 관련 요 ...
+QA Severity: Medium: responsibility and decision flow must be clear.</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>ESG위원회는 연 2회 개최하며, 상반기에는 기후변화 관련 위험과 기회를 보고받고 대응 전략과 목표를 결정하며, 하반기에는 성과를 점검하고 차기 연도 방향성을 수립합니다. 결과는 경영진 주관의 ESG위원회에 보고되어 대응 방안의 수립과 목표를 의사결정 받는데 활용됩니다. 지배구조 이사회 운영 체제 이사회는 회사의 주요 경영사항을 심의·의결하며 법령 또는 정관에 정한 사항, 주주총회로부터 위임받은 사항, 회사 경영의 기본 방침과 업무 집행에 관한 중요 사항을 의결하고 정관 변경을 위해서는 상법 제434조에 따라 주주총회의 승인이 필요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-003</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>일반 / 위험 관리 (Risk Management) / ESG 리스크 식별 및 관리 체계</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>[p.21] 영향의 우선순위 지정 - 주제별 그룹화 - 임계값 정의 - 결과 보고 환경 · 사회적 영향도 평가 - 국제표준 검토 (GRI, UN SDGs, ISO 26000 등) - 미디어 리서치 - 동종업계 벤치마킹 분석 재무적 영향도 평가 - 기업 내부 전략 분석 - 국제표준 검토 (SASB, DJSI, MSCI 등) - 국내 법규 분석 중요도 평가 중대 이슈 세부화 이슈에 대한 Sub Topic 선정 - GRI 및 ESRS Topic Standards 기반 중대 이슈 IRO 도출 - ESG 평가지표 분석 - 동종업계 벤치마킹 - 법률 및 연구논문 분석 이중 중대성 평가 이중 중대성 평가 개념 GRI Standards 등 국제 ESG 공시 가이드라인은 지속가능경영의 보고 수 준을 고도화하고자 이중 중대성 개념을 적용하고 있습니다. 이중 중대성은 외부의 지속가능성 관련 요인이 기업의 재무 상태에 미치는 영향과 기업의 경영활동이 환경·사회에 미치는 영향, 즉 내부적 관점과 외부적 관점을 모두 고려하는 개념입니다. 이중 중대성 평가 프로세스 두산퓨얼셀은 GRI 2021 Standard 방법론에 따라 환경·사회적 영향도와 재무적 영향도를 종합적으로 고려하여 이중 중대성 평가를 실시하였습니다. 특히,  환경·사회적 영향도와 재무적 영향도 분석을 통해 도출된 상위 10개 이슈 중 중대 이슈 3가지를 선별하여 중요한 영향, 위험 및 기회(Impact, Risk and Opportunity, 이하 IRO)를 도출하였습니다. 중대 이슈와 관련된 부서를 대상으로 이해관계자 설문조사를 실시하여 IRO의 우선순위를 지정하는 과정을 통해 두산퓨얼셀이 집중 관리해야 할 IRO 요인을 식별했습니다. 이렇게 식별된 IRO 요인은 두산퓨얼셀의 ESG경영의 주요 전략을 추진하는 데 활용되었으며, 두산퓨 얼셀은 CEO가 참여하는 ESG 위원회를 통해 중대성 평가 결과를 보고하고 검토 및 승인 단계를 거쳐 중대 이슈를 체계적으로 관리하고 있습니다. 환경・사회적 중요성 Inside-out(외부적 관점)에서 기업의 경영 활동으로 인해  사회 및 환경에 끼칠 수 있는  긍 · 부정적 영향의 정도를 의미 재무적 중요성 Outside-in(내부적 관점)에서 외부의 지속가능성 관련 요 ...
 [p.29] 기후변화 대응 MATERIAL TOPIC #1. &gt; 기후변화 시나리오 분석을 통한 기후 회복력 평가 두산퓨얼셀은 기후변화가 당사에 미치는 영향을 평가하기 위하여 기후변화 시나리오 분석을 수행하였습니다.  기후리스크를 탄소중립 또는 탄소저감정책에 따른 비용 상승 등의 전환리스크와 급성 또는 만성적으로 영향을 미치는 이상기후현상 등의 물리적리스크로 구분하여 기후변화 시나리오 분석을 실시하고 해당 리스크가 두산퓨얼셀의 사업 활동 및 재무적으로 미치는 영향을 분석하였습니다. 기후변화 시나리오 분석은 2021년 말 대내 ㆍ 외 경영 환경을 기준으로 2050년까지의 영향을 분석하였으며, 전환리스크는 에너지 산업군에서 널리 활용하는 IEA(국제에너지기구)의 NZE2050 시나리오와 STEPS 시나리오를 활용하여 저탄소  경제로 전환하는 과정에서 발생하는 탄소 비용 증가, 수주 경쟁력 약화, 규제 대응 비용 증가 규모를 분석하였고,  물리적 리스크는 IPCC에서 제시하는 SSP 시나리오를 활용하여 이상기후현상에 따른 재무적 영향(영업이익)을 분석 하였습니다. &gt; 전환 리스크 시나리오 분석 두산퓨얼셀은 IEA의 기후변화 시나리오 가운데 2050년까지 전 세계가 순배출 제로 경로를 달성하고, 기온 상승폭을 1.5℃에서 유지하는 것을 전제로 하는 NZE2050 기후변화 시나리오와 각 부문 ㆍ 국가 ㆍ 지역에서 이미 추진하고 있는  정책과 조치에 더하여 현재까지 발표된 감축목표, 이미 확정된 계획 등을 기반으로 전망하는 STEPS 시나리오를 활용 하였습니다. 이는 현재 시장 형성 초기로서 정부 정책에 따라 수요 변동폭이 큰 수소연료전지 시장의 특성을 가장 적절 하게 반영하기 위해서입니다. NZE2050 시나리오에서는 탄소가격이 2030년 90USD에서 2040년 160USD, 2050년 200USD까지 상승하고, SPS 시나리오에서는 2030년까지 56USD, 2040년까지 73USD, 2050년까지 89USD까지 상승 할 것으로 예측되었습니다. 구분 시나리오 전환  리스크 물리적 리스크 급성 만성 폭염 호우 강수량 수자원 평균기온 상승 IEA NZE2050 1.5℃ 2050년 전 세계적으로 탄소중립을 달성하고 평균기온 상승폭을 1.5℃ 이하로 ...
 [p.33] &gt; 위험 관리 프로세스 위험 관리 지표와 목표 두산퓨얼셀은 시장 형성 초기인 수소산업의 특성상 설비 증설과 제품 생산량 증가 폭이 크기때문에 기준연도를 설정하고 절대량을 감축하는 목표 수립은 적절하지 않은 관계로 예상배출량 대비 감축 목표를 수립하였습니다. 또한, 전사 온실가스 배출량의 94%를 차지하는 익산공장을 대상으로 중장기 감축 목표를 수립하였습니다. 2025년부터는 최신화된 국가온실가스감축목표(NDC)를 반영하여 예상배출량 기준 감축 목표를 보완하기 위하여 매출액 또는 제품 생산량 한 단위당 온실가스 배출량 감축 목표를 제시하는 집약도 기준 목표를 수립할 예정입니다. &gt; 2030년 중장기 온실가스 배출량 감축 목표 두산퓨얼셀은 미디어, 고객 요구사항, 동종업계 사례, ESG 스탠다드, 내부 경영전략, ESG 평가기관 및 법률/제도 등을 분석하여 기후변화 리스크를 식별하고 TCFD 프레임워크에 따라 전환 리스크와 물리적 리스크로 구분합니다. 각각의 리스크는 시나리오 분석과 유관부서 담당자가 참여하는 구조화된 설문지를 활용한 평가를 통해 규모와 범위 및 발생 가능성을 평가하여 우선순위를 선정합니다. &gt; 기후 리스크 식별 및 평가 ESG위원회 점검 결과 미진한 부분은 차년도 과제에 반영되는 구조를 보유하고 있습니다. &gt; 기후 리스크 모니터링 및 보고 리스크는 과제화하여 대응 전략을 수립하고 추진 현황을 ESG협의회를 통해 점검하며, 경영진 및 ESG위원회에 최종 보고됩니다. &gt; 기후 리스크 대응 두산퓨얼셀은 기후 관련 위험을 식별 및 평가하고 우선순위 설정과 모니터링을 위하여 아래와 같은 프로세스를  보유하고 있습니다. 두산퓨얼셀은 기후변화 관련 위험과 기회를 체계적으로 관리하기 위하여 SASB 산업별 지표, IFRS S2, ESRS E1에  근거하여 에너지 사용량의 대부분을 차지하는 익산공장의 총 에너지 소비량과 온실가스 배출량 Scope 1&amp;2를 관리 지표로 선정하고 목표를 설정하여 성과를 모니터링하고 있습니다. 리스크 식별 기후변화 이슈 파악 리스크 평가 영향, 위험, 기회 요소 분석, 시나리오 분석, 우선순위 설정 리스크 대응  전략 수립 기후변화 관련 추진 과제 설정 리스크 관리 추진 과제 이행 및 확인 사후 관리 과 ...
-[p.98] 리스크 관리 리스크 관리 활동 두산퓨얼셀은 기업 경영과 전략에 영향을 미칠 수 있는 리스크 유형을 분류하고 리스크 관리 프로세스에 따라 연 1회 이상 리스크를 검토하고 식별된 리스크에 대한 대응활동을 체계적으로 진행하고 있습니다. 특히, 리스크 관리 문화 조성을 위 하여 모든 임원 및 사외이사를 대상으로 연 1회 이상 리스크 관리 교육을 실시하고 있습니다. 리스크 유형 예상 리스크 관리 활동 리스크 유형 예상 리스크 관리활동 사업 리스크 수주 계약 조건 및  계약 이행 관련 리스크 - 제반 계약 조건에 대한 유관부서 내부 검토 - 계열체결에 대한 경영진 보고와 품의 품질 리스크 품질/생산 및 서비스 관련 리스크 -  전사적인 품질 이슈 발굴 및 개선 제도 시행 -  사무실과 공장에 품질 게시판 신설 -  격월 생산과 품질부서 기술교류회 개최 외환 리스크 국제적 영업활동 영위에 따른 환율변동 위험에 노출 -  수출과 수입통화 대응을 통한 Hedge로 환율변동 노출금액 상쇄 -  환위험관리규정에 따라 선물환 등 파생산품 이용하여 환율변동위험 관리 -  환율 10% 인상/인하에 따른 민감도 분석 공급망 리스크 부품 협력사의 비즈니스  연속성 측면의 리스크 -  비즈니스 영향과 구매 위험에 따른 1차 부품 협력사 Grouping -  Group별 ESG 평가 지표 개발과 자가진단 및 현장 실사 실시 - 자가진단 결과에 따른 개선 지원 이자율 리스크 이자율 변동위험에 노출된 변동금리부 금융자산 및 부채 리스크 -  변동금리부 금융자산 및 금융부채의 이자율 100bp 변동시 세전순손익에 미치는 민감도 분석 정보 보안 리스크 정보 유출 위험 - IT 권한 모니터링 실시하여 업무별 권한 최소화 - 연 4회 정보유출 피해 예방 모의 훈련 실시 신용 리스크 금융상품의 당사자 중 일방이 의무를 이행하지 않아 발생하는 재무손실 -  신규 거래처 계약시 재무정보와 신용평가기관 정보를 이용해 신용도를 평가하고 신용거래한도를 결정하며 담보 또는 지급보증 제공 받음 -  주기적인 거래처 신용도 재평가 및 신용거래한도 재조정 인적 리스크 우수인재 확보와 유지 및  유출로 인한 위험 -  전사 사업전략과 연계하여 전략적 인력계획 수립 - ...</x:v>
-      </x:c>
-      <x:c r="D4" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.98] 리스크 관리 리스크 관리 활동 두산퓨얼셀은 기업 경영과 전략에 영향을 미칠 수 있는 리스크 유형을 분류하고 리스크 관리 프로세스에 따라 연 1회 이상 리스크를 검토하고 식별된 리스크에 대한 대응활동을 체계적으로 진행하고 있습니다. 특히, 리스크 관리 문화 조성을 위 하여 모든 임원 및 사외이사를 대상으로 연 1회 이상 리스크 관리 교육을 실시하고 있습니다. 리스크 유형 예상 리스크 관리 활동 리스크 유형 예상 리스크 관리활동 사업 리스크 수주 계약 조건 및  계약 이행 관련 리스크 - 제반 계약 조건에 대한 유관부서 내부 검토 - 계열체결에 대한 경영진 보고와 품의 품질 리스크 품질/생산 및 서비스 관련 리스크 -  전사적인 품질 이슈 발굴 및 개선 제도 시행 -  사무실과 공장에 품질 게시판 신설 -  격월 생산과 품질부서 기술교류회 개최 외환 리스크 국제적 영업활동 영위에 따른 환율변동 위험에 노출 -  수출과 수입통화 대응을 통한 Hedge로 환율변동 노출금액 상쇄 -  환위험관리규정에 따라 선물환 등 파생산품 이용하여 환율변동위험 관리 -  환율 10% 인상/인하에 따른 민감도 분석 공급망 리스크 부품 협력사의 비즈니스  연속성 측면의 리스크 -  비즈니스 영향과 구매 위험에 따른 1차 부품 협력사 Grouping -  Group별 ESG 평가 지표 개발과 자가진단 및 현장 실사 실시 - 자가진단 결과에 따른 개선 지원 이자율 리스크 이자율 변동위험에 노출된 변동금리부 금융자산 및 부채 리스크 -  변동금리부 금융자산 및 금융부채의 이자율 100bp 변동시 세전순손익에 미치는 민감도 분석 정보 보안 리스크 정보 유출 위험 - IT 권한 모니터링 실시하여 업무별 권한 최소화 - 연 4회 정보유출 피해 예방 모의 훈련 실시 신용 리스크 금융상품의 당사자 중 일방이 의무를 이행하지 않아 발생하는 재무손실 -  신규 거래처 계약시 재무정보와 신용평가기관 정보를 이용해 신용도를 평가하고 신용거래한도를 결정하며 담보 또는 지급보증 제공 받음 -  주기적인 거래처 신용도 재평가 및 신용거래한도 재조정 인적 리스크 우수인재 확보와 유지 및  유출로 인한 위험 -  전사 사업전략과 연계하여 전략적 인력계획 수립 - ...</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 21;29;33;98
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E4" s="6" t="str">
-        <x:v>Selected Style: risk-control
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: risk-control
 Preferred Style Source: template
 Answer Type: risk-control
 Answer Intent: Explain the risk/control scope, then prevention, monitoring, and follow-up actions.
@@ -422,34 +539,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: High: must include risk/control and monitoring evidence.</x:v>
-      </x:c>
-      <x:c r="F4" s="6" t="str">
-        <x:v>이렇게 식별된 IRO 요인은 두산퓨얼셀의 ESG경영의 주요 전략을 추진하는 데 활용되었으며, 두산퓨 얼셀은 CEO가 참여하는 ESG 위원회를 통해 중대성 평가 결과를 보고하고 검토 및 승인 단계를 거쳐 중대 이슈를 체계적으로 관리하고 있습니다.  기후리스크를 탄소중립 또는 탄소저감정책에 따른 비용 상승 등의 전환리스크와 급성 또는 만성적으로 영향을 미치는 이상기후현상 등의 물리적리스크로 구분하여 기후변화 시나리오 분석을 실시하고 해당 리스크가 두산퓨얼셀의 사업 활동 및 재무적으로 미치는 영향을 분석하였습니다. 따라서 ESG 리스크 식별 및 관리 체계 관련 공시는 단순한 선언보다 예방, 모니터링, 후속 조치의 연결성을 중심으로 해석할 수 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="6" t="str">
-        <x:v>EBX-Q-004</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="str">
-        <x:v>사회 / 전략 (Strategy) / 안전보건 정책 및 목표</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="str">
-        <x:v>[p.65] 안전보건 안전보건경영목표 안전보건 방침 안전보건 관리 시스템 안전보건경영전략 -  안전보건 관리체계 강화를 통한 법, 규제준수 및 중대재해 예방 -  경영진 주도의 안전보건점검, 회의 등 Leadership활동을 통하여, 강력한 안전보건중심운영 의지전달 및 임직원 안전의식 수준 제고 -  사업장 PSM(Process Safety Management) 운영을 통해 중대산업사고 예방 및 자율안전보건체제 구축 -  안전보건 규정을 제정하고 원칙을 준수하여 사고를 예방하고, 효과적인 위험성평가 제도 운영을 통한 중대위험 Risk 관리 -  안전보건 잠재요인의 적극적인 발굴, 개선을 통한 위험관리 운영 -  협력업체 안전보건관리 프로세스를 체계적으로 정립하고 운영하여 사업장 관리수준을 높이고, 안전보건 동반성장 실현 인간존중 이념을 바탕으로 함께 일하는 모든 사람들의 생명과 건강을 최우선 가치로 생각하며, 모든 임직원은 솔선수범의 자세로 안전보건 활동을 적극적으로 실천합니다. 안전보건경영체계를 구축하고 시스템의 관리수준을 지속적으로 개선하며, 관련 법규 및 당사의 제반 규정을 적극적으로 준수합니다. 전 임직원의 참여를 원칙으로 발생 가능한 위험요인을 효과적으로 식별·개선하여 안전사고를 근원적으로 예방합니다. 당사 및 협력업체 임직원을 대상으로 한 주기적인 안전보건교육과 비상대응활동을 통하여, 안전의식을 제고하고 위험관리 능력향상을 시킵니다. 안전보건에 대한 지속적인 투자와 개발을 통하여 최고로 안전한 작업환경과 시설운영 역량을 확보합니다. 정직과 투명성을 기반으로 이해관계자와 상하좌우의 열린 의사소통을 실천하며, 지역사회에 사회적 책임을 다합니다. 2023년 4월 3일 두산퓨얼셀㈜ CSHO 박준영 01 02 03 04 05 06 두산퓨얼셀은 안전하고 청결한 작업환경을 임직원, 가족, 사회에 대한 책임이자 핵심가치로 인식하고 있습니다. 이를 위해 안전보건경영시스템 (ISO 45001)를 구축하고, 안전보건경영 방침에 따라 부서별 세부 실행목표를 수립·이행하고 있습니다. 또한 중대재해처벌법, 산업안전보건법 등 관련 법규 준수를 통해 모든 임직원이 안전한 환경에서 근무할 수 있도록 관리하고 있습니다. 앞으로도 글로벌 기준에 부합하는 안전 ...
+QA Severity: High: must include risk/control and monitoring evidence.</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>식별된 IRO 요인은 두산퓨얼셀의 ESG경영의 주요 전략을 추진하는 데 활용되었으며, 두산퓨얼셀은 CEO가 참여하는 ESG 위원회를 통해 중대성 평가 결과를 보고하고 검토 및 승인 단계를 거쳐 중대 이슈를 체계적으로 관리하고 있습니다. 기후리스크를 탄소중립 또는 탄소저감정책에 따른 비용 상승 등의 전환리스크와 급성 또는 만성적으로 영향을 미치는 이상기후현상 등의 물리적 리스크로 구분하여 기후변화 시나리오 분석을 실시하고 해당 리스크가 두산퓨얼셀의 사업 활동 및 재무적으로 미치는 영향을 분석하였습니다. ESG 리스크 식별 및 관리 체계 관련 공시는 단순한 선언보다 예방, 모니터링, 후속 조치의 연결성을 중심으로 해석할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-004</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 전략 (Strategy) / 안전보건 정책 및 목표</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>[p.65] 안전보건 안전보건경영목표 안전보건 방침 안전보건 관리 시스템 안전보건경영전략 -  안전보건 관리체계 강화를 통한 법, 규제준수 및 중대재해 예방 -  경영진 주도의 안전보건점검, 회의 등 Leadership활동을 통하여, 강력한 안전보건중심운영 의지전달 및 임직원 안전의식 수준 제고 -  사업장 PSM(Process Safety Management) 운영을 통해 중대산업사고 예방 및 자율안전보건체제 구축 -  안전보건 규정을 제정하고 원칙을 준수하여 사고를 예방하고, 효과적인 위험성평가 제도 운영을 통한 중대위험 Risk 관리 -  안전보건 잠재요인의 적극적인 발굴, 개선을 통한 위험관리 운영 -  협력업체 안전보건관리 프로세스를 체계적으로 정립하고 운영하여 사업장 관리수준을 높이고, 안전보건 동반성장 실현 인간존중 이념을 바탕으로 함께 일하는 모든 사람들의 생명과 건강을 최우선 가치로 생각하며, 모든 임직원은 솔선수범의 자세로 안전보건 활동을 적극적으로 실천합니다. 안전보건경영체계를 구축하고 시스템의 관리수준을 지속적으로 개선하며, 관련 법규 및 당사의 제반 규정을 적극적으로 준수합니다. 전 임직원의 참여를 원칙으로 발생 가능한 위험요인을 효과적으로 식별·개선하여 안전사고를 근원적으로 예방합니다. 당사 및 협력업체 임직원을 대상으로 한 주기적인 안전보건교육과 비상대응활동을 통하여, 안전의식을 제고하고 위험관리 능력향상을 시킵니다. 안전보건에 대한 지속적인 투자와 개발을 통하여 최고로 안전한 작업환경과 시설운영 역량을 확보합니다. 정직과 투명성을 기반으로 이해관계자와 상하좌우의 열린 의사소통을 실천하며, 지역사회에 사회적 책임을 다합니다. 2023년 4월 3일 두산퓨얼셀㈜ CSHO 박준영 01 02 03 04 05 06 두산퓨얼셀은 안전하고 청결한 작업환경을 임직원, 가족, 사회에 대한 책임이자 핵심가치로 인식하고 있습니다. 이를 위해 안전보건경영시스템 (ISO 45001)를 구축하고, 안전보건경영 방침에 따라 부서별 세부 실행목표를 수립·이행하고 있습니다. 또한 중대재해처벌법, 산업안전보건법 등 관련 법규 준수를 통해 모든 임직원이 안전한 환경에서 근무할 수 있도록 관리하고 있습니다. 앞으로도 글로벌 기준에 부합하는 안전 ...
 [p.67] 안전보건 안전보건 관리 활동 두산퓨얼셀은 임직원과 협력사 근로자의 안전과 건강을 최우선으로 생각하며 인간 존중 경영을 실천하고 있습니다. EHS와 관련된 위험 요소를 사전에 파악하고 제거하거나 최소화하기 위해 다양한 평가, 점검 및 비상 대응체계를 운영하고 있습 니다. 특히 솔선수범하는 리더십을 바탕으로 임원과 리더 직급의 자율적인 안전보건 활동을 확산시키기 위해 지속적으로 노력하고 있습니다. 또한 매달 EHS 뉴스레터를 발행하여 일상생활에서 유용한 안전 및 건강 정보를 제공하고 있으며, 각 사업장별 이벤트를 통해 임직원의 EHS에 대한 관심과 참여를 유도하고 있습니다. &gt; 안전보건 조직 구축 및 목표 수립 &gt; 안전보건 리더십 활동 &gt; 고객서비스 안전보건관리 두산퓨얼셀은 EHS 방침을 기반으로 전사 및 사업장의 안전보건 목표를 설 정하고 이를 체계적으로 시행하고 있습니다. 또한 안전사고를 예방하고 각 조직의 안전보건 목표를 달성하기 위해 안전보건 전담 부서를 설치, 운영하 고 있습니다. 각 사이트별로 관리 감독자를 선임하고 안전보건 담당자를 지 정하여 효과적으로 운영하고 있습니다. &gt; 임직원 건강 증진 두산퓨얼셀은 임직원의 건강 증진과 직업성 질환 예방을 위해 정기적인 건 강검진을 실시하고 있습니다. 유소견자에 대해서는 지속적인 건강 상담과 추적 관리는 물론, 다양한 건강 증진 프로그램도 함께 운영하고 있습니다. 또한 임직원의 자발적인 건강 관리를 지원하기 위해 체력 측정 이벤트, 금연 프로그램 등도 함께 추진하고 있습니다. 두산퓨얼셀은 경영진의 안전보건 실천 의지를 표명하고 안전점검, 회의, 간담 회 등 다양한 활동을 통해 EHS 리더십을 적극 실천하고 있습니다. 또한 안전보건경영시스템 운영 및 관련 법규 준수 사항에 대해 근로자가 직 접 참여하는 EHS 협의기구를 운영하여, EHS 활동에 대한 책임과 권한을 부 여하고 있습니다. 이를 통해 임직원의 자주적인 안전 활동을 유도하고 안전의 식을 높여, 사업장 내 사고 예방과 지속 가능한 성장에 기여하고 있습니다. &gt; 외주공사 안전관리 및 협력관계 구축 두산퓨얼셀은 사업장에서 발생하는 외주공사 재해예방을 위한 관리규정을 제정하고, 사내 공사 및 유지보수 서비스 현장에 대한 안전관리 프로세 ...
 [p.75] 공급망 ESG 관리 &gt; 3. 안전 및 보건 3.1 산업안전 관리: 두산퓨얼셀의 협력회사는 물리적인 위험 요소를 사전에 제거하고 적절한 설계, 엔지니어링 및 행정적 통제, 예방 정비, 안전한 작업절차를 통해 예방조치를 취해야 합니다. 또한 근로자들이 잠재적 안전 위험 요소(예: 전기 및 기타 에너지원, 화재, 차량, 추락위험)에 노출되지 않도록 하여야 합니다. 이러한 수단으로 위험 요소들을 충분히 통제할 수 없는 경우에는 근로자에게 적절한 개인 보호 장비를 제공해야 합니다. 3.2 기계설비의 안전유지: 두산퓨얼셀의 생산 및 기계설비의 안전 위해 요소를 평가해야 합니다. 근로자가 설비로 인해 상해를 당할 위험이 있을 경우 협력회사는 안전장치, 방호벽, 긴급장치 등을 설치하고 근로자에게 안전 보호구를 지급하여야 합니다. 3.7 위험성 평가: 두산퓨얼셀의 협력회사는 위험 요인에 대한 근로자의 노출 가능성을 파악하고 위험을 사전에 차단하기 위해 위험성 평가를 정기적으로 실시해야 합니다. 평가 결과에 따라 안전한 공정의 설계, 기술적/행정적 통제, 예방정비, 작업절차서 내 안전 측면 반영, 지속적인 교육 등을 실시해야 하고, 필요한 개인보호구를 근로자에게 제공하며 대상 근로자는 반드시 착용하도록 관리 감독해야 합니다. 3.8 건강검진 및 사후관리: 두산퓨얼셀의 협력회사는 사업을 영위하는 국가별 건강검진 법률에 따라 임직원을 대상으로 일반건강검진 또는 특수건강검진 등을 정기적으로 실시하여야 하며, 건강검진 결과 필요한 경우 작업 장소 변경, 작업 전환, 근로 시간 단축 등의 조치를 실시해야 합니다. 3.9 신체부담 업무: 두산퓨얼셀의 협력회사는 근로자가 무거운 자재를 들어 올리거나 심하게 반복적인 작업, 장시간 서 있는 작업, 체력 소모가 심한 조립 작업 등의 육체적으로 힘든 작업에 노출되는 것을 파악하고 평가하며 통제해야 합니다. 3.10 위생, 식품 및 주거: 두산퓨얼셀의 협력회사는 근로자에게 청결한 화장실과 식수 시설, 위생적인 식품 조리/보관 시설과 식사할 수 있는 장소를 제공해야 합니다. 또한 근로자에게 제공되는 기숙사는 청결하고 안전을 유지해야 하며, 적절한 조명, 비상 탈출시설, 난방, 온수, 환기시설, 개인물품 보관시설 및 적절한 출 ...
-[p.80] 공급망 ESG 관리 동반성장 지원 프로그램 두산퓨얼셀은 협력사의 생산성 향상을 위해 필요한 일부 설비에 직접 투자하고, 신규 설비에 대한 기술 교육도 함께 지원하고 있습니다. &gt; 협력사 생산성 향상 지원 두산퓨얼셀은 제품 생산에 사용되는 수입 원자재 및 부품을 국내 협력사와의 협력을 통해 국산화함으로써, 공급망 안정화는 물론 국내 수소 산업 생태계 조성에도 기여하고 있습니다. &gt; 원자재/부품 이원화를 통한 수급 안정화 및 수소 산업 생태계 조성 연료전지 제작에 사용되는 불소점착제 테이프는 기존에 전량 수입에 의존하고 있었으나, 해외 공급 업체의 사업 철수로 인해 수급 안정성에 문제가 발생했습니다. 이에 두산퓨얼셀은 국내 업체를 발굴하여 다음과 같은 상생 협력 활동을 통해 공급망 안정화를 도모하고, 물류비 및 생산비 절감 효과를 거뒀습니다. &gt; Dyneon Tape(불소점착제 테이프) 국산화 전극 이원화/국산화 개발 지원 두산퓨얼셀은 기존에 전량 해외 업체를 통해 공급받던 연료전지의 핵심 부품인 전극 촉매의 국산화를 추진하여 공급망을 이원화하고, 이를 통해 수급 안정화 및 원가 절감 효과를 높였습니다. 또한 주요 부품의 국산화율을 제고하기 위해 국내 업체를 발굴하고 기술 개발을 지원했습니다. 이를 통해 해외 업체에 의존하던 자재의 수급 안정성을 개선하고, 국내 수소연료전지 핵심 부품의 국산화를 통해 수소 산업 생태계 구축에 기여했습니다. • 기술 이전 및 역량 강화  -  협력사에 테이프 제조 기술을 이전하여 해당 업체의 기술력이 크게 향상되었으며, 공동 연구 개발 프로젝트를 추진하여 테이프의 품질을 개선하고 생산 효율을 높였습니다. • 생산설비 및 인력지원  -  협력사에 신규 생산설비 도입을 지원하여 생산 능력을 강화했으며, 업체 직원을 대상으로 제조 관련 교육과 훈련을 제공하여 인적 역량 향상에 기여했습니다. • 상생협력 및 신뢰 구축  -  협력사의 생산품 품질을 유지하고 원활한 공급망 관리를 위해 노력한 결과, 양사 간의 신뢰 관계가 형성되었습니다. 좌측 3개 국산 대체품, 우측 기존품 국산화 제품 안전보건협의체 및 노사협동점검 두산퓨얼셀은 사내·외 협력업체와 정기적으로 안전보건 협의체를 운영하고 노사 합동 점검을 실 ...</x:v>
-      </x:c>
-      <x:c r="D5" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.80] 공급망 ESG 관리 동반성장 지원 프로그램 두산퓨얼셀은 협력사의 생산성 향상을 위해 필요한 일부 설비에 직접 투자하고, 신규 설비에 대한 기술 교육도 함께 지원하고 있습니다. &gt; 협력사 생산성 향상 지원 두산퓨얼셀은 제품 생산에 사용되는 수입 원자재 및 부품을 국내 협력사와의 협력을 통해 국산화함으로써, 공급망 안정화는 물론 국내 수소 산업 생태계 조성에도 기여하고 있습니다. &gt; 원자재/부품 이원화를 통한 수급 안정화 및 수소 산업 생태계 조성 연료전지 제작에 사용되는 불소점착제 테이프는 기존에 전량 수입에 의존하고 있었으나, 해외 공급 업체의 사업 철수로 인해 수급 안정성에 문제가 발생했습니다. 이에 두산퓨얼셀은 국내 업체를 발굴하여 다음과 같은 상생 협력 활동을 통해 공급망 안정화를 도모하고, 물류비 및 생산비 절감 효과를 거뒀습니다. &gt; Dyneon Tape(불소점착제 테이프) 국산화 전극 이원화/국산화 개발 지원 두산퓨얼셀은 기존에 전량 해외 업체를 통해 공급받던 연료전지의 핵심 부품인 전극 촉매의 국산화를 추진하여 공급망을 이원화하고, 이를 통해 수급 안정화 및 원가 절감 효과를 높였습니다. 또한 주요 부품의 국산화율을 제고하기 위해 국내 업체를 발굴하고 기술 개발을 지원했습니다. 이를 통해 해외 업체에 의존하던 자재의 수급 안정성을 개선하고, 국내 수소연료전지 핵심 부품의 국산화를 통해 수소 산업 생태계 구축에 기여했습니다. • 기술 이전 및 역량 강화  -  협력사에 테이프 제조 기술을 이전하여 해당 업체의 기술력이 크게 향상되었으며, 공동 연구 개발 프로젝트를 추진하여 테이프의 품질을 개선하고 생산 효율을 높였습니다. • 생산설비 및 인력지원  -  협력사에 신규 생산설비 도입을 지원하여 생산 능력을 강화했으며, 업체 직원을 대상으로 제조 관련 교육과 훈련을 제공하여 인적 역량 향상에 기여했습니다. • 상생협력 및 신뢰 구축  -  협력사의 생산품 품질을 유지하고 원활한 공급망 관리를 위해 노력한 결과, 양사 간의 신뢰 관계가 형성되었습니다. 좌측 3개 국산 대체품, 우측 기존품 국산화 제품 안전보건협의체 및 노사협동점검 두산퓨얼셀은 사내·외 협력업체와 정기적으로 안전보건 협의체를 운영하고 노사 합동 점검을 실 ...</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 65;67;75;80
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E5" s="6" t="str">
-        <x:v>Selected Style: balanced-policy
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: balanced-policy
 Preferred Style Source: template
 Answer Type: policy-management
 Answer Intent: Explain the standard or policy, then show implementation ownership and supporting performance facts.
@@ -468,34 +597,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: Medium: prose must be natural, evidence-grounded, and non-repetitive.</x:v>
-      </x:c>
-      <x:c r="F5" s="6" t="str">
-        <x:v>2023년 4월 3일 두산퓨얼셀㈜ CSHO 박준영 01 02 03 04 05 06 두산퓨얼셀은 안전하고 청결한 작업환경을 임직원, 가족, 사회에 대한 책임이자 핵심가치로 인식하고 있습니다. 안전보건 안전보건 관리 활동 두산퓨얼셀은 임직원과 협력사 근로자의 안전과 건강을 최우선으로 생각하며 인간 존중 경영을 실천하고 있습니다. 두산퓨얼셀은 경영진의 안전보건 실천 의지를 표명하고 안전점검, 회의, 간담 회 등 다양한 활동을 통해 EHS 리더십을 적극 실천하고 있습니다. 두산퓨얼셀는 안전보건 정책 및 목표에 대해 정책 기준과 운영 절차를 함께 제시하고 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="6" t="str">
-        <x:v>EBX-Q-005</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="str">
-        <x:v>사회 / 거버넌스 (Governance) / 안전보건 관리 조직 및 책임</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="str">
-        <x:v>[p.65] 안전보건 안전보건경영목표 안전보건 방침 안전보건 관리 시스템 안전보건경영전략 -  안전보건 관리체계 강화를 통한 법, 규제준수 및 중대재해 예방 -  경영진 주도의 안전보건점검, 회의 등 Leadership활동을 통하여, 강력한 안전보건중심운영 의지전달 및 임직원 안전의식 수준 제고 -  사업장 PSM(Process Safety Management) 운영을 통해 중대산업사고 예방 및 자율안전보건체제 구축 -  안전보건 규정을 제정하고 원칙을 준수하여 사고를 예방하고, 효과적인 위험성평가 제도 운영을 통한 중대위험 Risk 관리 -  안전보건 잠재요인의 적극적인 발굴, 개선을 통한 위험관리 운영 -  협력업체 안전보건관리 프로세스를 체계적으로 정립하고 운영하여 사업장 관리수준을 높이고, 안전보건 동반성장 실현 인간존중 이념을 바탕으로 함께 일하는 모든 사람들의 생명과 건강을 최우선 가치로 생각하며, 모든 임직원은 솔선수범의 자세로 안전보건 활동을 적극적으로 실천합니다. 안전보건경영체계를 구축하고 시스템의 관리수준을 지속적으로 개선하며, 관련 법규 및 당사의 제반 규정을 적극적으로 준수합니다. 전 임직원의 참여를 원칙으로 발생 가능한 위험요인을 효과적으로 식별·개선하여 안전사고를 근원적으로 예방합니다. 당사 및 협력업체 임직원을 대상으로 한 주기적인 안전보건교육과 비상대응활동을 통하여, 안전의식을 제고하고 위험관리 능력향상을 시킵니다. 안전보건에 대한 지속적인 투자와 개발을 통하여 최고로 안전한 작업환경과 시설운영 역량을 확보합니다. 정직과 투명성을 기반으로 이해관계자와 상하좌우의 열린 의사소통을 실천하며, 지역사회에 사회적 책임을 다합니다. 2023년 4월 3일 두산퓨얼셀㈜ CSHO 박준영 01 02 03 04 05 06 두산퓨얼셀은 안전하고 청결한 작업환경을 임직원, 가족, 사회에 대한 책임이자 핵심가치로 인식하고 있습니다. 이를 위해 안전보건경영시스템 (ISO 45001)를 구축하고, 안전보건경영 방침에 따라 부서별 세부 실행목표를 수립·이행하고 있습니다. 또한 중대재해처벌법, 산업안전보건법 등 관련 법규 준수를 통해 모든 임직원이 안전한 환경에서 근무할 수 있도록 관리하고 있습니다. 앞으로도 글로벌 기준에 부합하는 안전 ...
+QA Severity: Medium: prose must be natural, evidence-grounded, and non-repetitive.</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>당사 및 협력업체 임직원을 대상으로 한 주기적인 안전보건교육과 비상대응활동을 통하여, 안전의식을 제고하고 위험관리 능력 향상을 지원합니다. 두산퓨얼셀은 경영진의 안전보건 실천 의지를 표명하고 안전점검, 회의, 간담회 등 다양한 활동을 통해 EHS 리더십을 적극 실천하고 있습니다. 이에 두산퓨얼셀은 국내 업체를 발굴하여 다음과 같은 상생 협력 활동을 통해 공급망 안정화를 도모하고, 물류비 및 생산비 절감 효과를 거뒀습니다. 두산퓨얼셀은 안전보건 정책 및 목표에 대해 정책 기준과 운영 절차를 함께 제시하고 있습니다. 안전보건 정책 및 목표는 정책, 실행 주체, 성과 확인이 연결된 관리 항목으로 정리됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-005</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 거버넌스 (Governance) / 안전보건 관리 조직 및 책임</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>[p.65] 안전보건 안전보건경영목표 안전보건 방침 안전보건 관리 시스템 안전보건경영전략 -  안전보건 관리체계 강화를 통한 법, 규제준수 및 중대재해 예방 -  경영진 주도의 안전보건점검, 회의 등 Leadership활동을 통하여, 강력한 안전보건중심운영 의지전달 및 임직원 안전의식 수준 제고 -  사업장 PSM(Process Safety Management) 운영을 통해 중대산업사고 예방 및 자율안전보건체제 구축 -  안전보건 규정을 제정하고 원칙을 준수하여 사고를 예방하고, 효과적인 위험성평가 제도 운영을 통한 중대위험 Risk 관리 -  안전보건 잠재요인의 적극적인 발굴, 개선을 통한 위험관리 운영 -  협력업체 안전보건관리 프로세스를 체계적으로 정립하고 운영하여 사업장 관리수준을 높이고, 안전보건 동반성장 실현 인간존중 이념을 바탕으로 함께 일하는 모든 사람들의 생명과 건강을 최우선 가치로 생각하며, 모든 임직원은 솔선수범의 자세로 안전보건 활동을 적극적으로 실천합니다. 안전보건경영체계를 구축하고 시스템의 관리수준을 지속적으로 개선하며, 관련 법규 및 당사의 제반 규정을 적극적으로 준수합니다. 전 임직원의 참여를 원칙으로 발생 가능한 위험요인을 효과적으로 식별·개선하여 안전사고를 근원적으로 예방합니다. 당사 및 협력업체 임직원을 대상으로 한 주기적인 안전보건교육과 비상대응활동을 통하여, 안전의식을 제고하고 위험관리 능력향상을 시킵니다. 안전보건에 대한 지속적인 투자와 개발을 통하여 최고로 안전한 작업환경과 시설운영 역량을 확보합니다. 정직과 투명성을 기반으로 이해관계자와 상하좌우의 열린 의사소통을 실천하며, 지역사회에 사회적 책임을 다합니다. 2023년 4월 3일 두산퓨얼셀㈜ CSHO 박준영 01 02 03 04 05 06 두산퓨얼셀은 안전하고 청결한 작업환경을 임직원, 가족, 사회에 대한 책임이자 핵심가치로 인식하고 있습니다. 이를 위해 안전보건경영시스템 (ISO 45001)를 구축하고, 안전보건경영 방침에 따라 부서별 세부 실행목표를 수립·이행하고 있습니다. 또한 중대재해처벌법, 산업안전보건법 등 관련 법규 준수를 통해 모든 임직원이 안전한 환경에서 근무할 수 있도록 관리하고 있습니다. 앞으로도 글로벌 기준에 부합하는 안전 ...
 [p.66] 안전보건 안전보건관리 중장기 로드맵 수립 두산퓨얼셀은 안전과 보건을 최우선으로 생각하며, 모든 임직원과 지역사회의 안전을 보장하기 위해 최선을 다하고 있습니다. 두산퓨얼셀은 안전보건 중장기 로드맵을 기반으로 KPI(Key Performance Index)를 설정하고 연도별 안전보건추진계획을 수립하여 정기적인 모니터링을 통해 목표 달성 여부 및 실행 효과를 점검하고 있습니다. 2024년부터는 안전보건 Phase2 단계에 진입하여, 각 부서의 주도적인 EHS활동 실행력 강화와 더불어, 사내외 협력사의 EHS역량 및 관리 수준 향상을 위한 활동을 추진하고 있습니다. 두산퓨얼셀은 임직원 스스로 안전의 중요성을 인식하고 능동적으로 실천하는 안전보건 실행문화를 정착하기 위해 중장기적 관점에서 단계별 세부 목표를 설정하고 지속적으로 개선해나가겠습니다. &gt; DSRS 정량평가 수준 향상 2024년에는 협력업체 EHS 수준 강화와 EHS 모니터링 강화를 주요 과제로 삼고 다양한 활동을 실시한 결과 DSRS 수준 향상 성과를 인정받아 연말에 개최되는 그룹 EHS Fair에서 2년 연속 혁신상을 수상했습니다. 안전보건 단계별 추진 로드맵 '23년 '28년 '33년 인식 및 방향설정 지속적 개선 Quick WIN(’23년) ’24~28년 ’29~33년 Stagnant 국내 대기업 Global 기업 Golbal EHS선진사 Proactive Worldclass KPI 추진 계획 •  EHS R&amp;R 재정립 및 Site 주도의 EHS활동 실행력 강화 •  EHS평가 및 보상체계 확대(벌칙 포함) •  ISO 45001/DSRS운영수준 제고 및 내재화 •  사내·외 협력사 EHS역량 및 관리강화 •  근로자 Health Care program활성화 Mid-term Initiatives 현업 중심의 EHS실행문화 확립 •  행동중심 관찰기법의 활성화 •  EHS IT System 실행/효율성 확보(고도화) •  눈으로 보는 EHS 관리(Visual EHS) 강화 •  SMART EHS 강화(AI 등 선진안전기술 적용) •  EHS활동의 재무적 효과 평가기준 수립 •  팀 주도의 EHS실행 내재화 Long-term Initiatives EHS활동의 ...
 [p.67] 안전보건 안전보건 관리 활동 두산퓨얼셀은 임직원과 협력사 근로자의 안전과 건강을 최우선으로 생각하며 인간 존중 경영을 실천하고 있습니다. EHS와 관련된 위험 요소를 사전에 파악하고 제거하거나 최소화하기 위해 다양한 평가, 점검 및 비상 대응체계를 운영하고 있습 니다. 특히 솔선수범하는 리더십을 바탕으로 임원과 리더 직급의 자율적인 안전보건 활동을 확산시키기 위해 지속적으로 노력하고 있습니다. 또한 매달 EHS 뉴스레터를 발행하여 일상생활에서 유용한 안전 및 건강 정보를 제공하고 있으며, 각 사업장별 이벤트를 통해 임직원의 EHS에 대한 관심과 참여를 유도하고 있습니다. &gt; 안전보건 조직 구축 및 목표 수립 &gt; 안전보건 리더십 활동 &gt; 고객서비스 안전보건관리 두산퓨얼셀은 EHS 방침을 기반으로 전사 및 사업장의 안전보건 목표를 설 정하고 이를 체계적으로 시행하고 있습니다. 또한 안전사고를 예방하고 각 조직의 안전보건 목표를 달성하기 위해 안전보건 전담 부서를 설치, 운영하 고 있습니다. 각 사이트별로 관리 감독자를 선임하고 안전보건 담당자를 지 정하여 효과적으로 운영하고 있습니다. &gt; 임직원 건강 증진 두산퓨얼셀은 임직원의 건강 증진과 직업성 질환 예방을 위해 정기적인 건 강검진을 실시하고 있습니다. 유소견자에 대해서는 지속적인 건강 상담과 추적 관리는 물론, 다양한 건강 증진 프로그램도 함께 운영하고 있습니다. 또한 임직원의 자발적인 건강 관리를 지원하기 위해 체력 측정 이벤트, 금연 프로그램 등도 함께 추진하고 있습니다. 두산퓨얼셀은 경영진의 안전보건 실천 의지를 표명하고 안전점검, 회의, 간담 회 등 다양한 활동을 통해 EHS 리더십을 적극 실천하고 있습니다. 또한 안전보건경영시스템 운영 및 관련 법규 준수 사항에 대해 근로자가 직 접 참여하는 EHS 협의기구를 운영하여, EHS 활동에 대한 책임과 권한을 부 여하고 있습니다. 이를 통해 임직원의 자주적인 안전 활동을 유도하고 안전의 식을 높여, 사업장 내 사고 예방과 지속 가능한 성장에 기여하고 있습니다. &gt; 외주공사 안전관리 및 협력관계 구축 두산퓨얼셀은 사업장에서 발생하는 외주공사 재해예방을 위한 관리규정을 제정하고, 사내 공사 및 유지보수 서비스 현장에 대한 안전관리 프로세 ...
-[p.75] 공급망 ESG 관리 &gt; 3. 안전 및 보건 3.1 산업안전 관리: 두산퓨얼셀의 협력회사는 물리적인 위험 요소를 사전에 제거하고 적절한 설계, 엔지니어링 및 행정적 통제, 예방 정비, 안전한 작업절차를 통해 예방조치를 취해야 합니다. 또한 근로자들이 잠재적 안전 위험 요소(예: 전기 및 기타 에너지원, 화재, 차량, 추락위험)에 노출되지 않도록 하여야 합니다. 이러한 수단으로 위험 요소들을 충분히 통제할 수 없는 경우에는 근로자에게 적절한 개인 보호 장비를 제공해야 합니다. 3.2 기계설비의 안전유지: 두산퓨얼셀의 생산 및 기계설비의 안전 위해 요소를 평가해야 합니다. 근로자가 설비로 인해 상해를 당할 위험이 있을 경우 협력회사는 안전장치, 방호벽, 긴급장치 등을 설치하고 근로자에게 안전 보호구를 지급하여야 합니다. 3.7 위험성 평가: 두산퓨얼셀의 협력회사는 위험 요인에 대한 근로자의 노출 가능성을 파악하고 위험을 사전에 차단하기 위해 위험성 평가를 정기적으로 실시해야 합니다. 평가 결과에 따라 안전한 공정의 설계, 기술적/행정적 통제, 예방정비, 작업절차서 내 안전 측면 반영, 지속적인 교육 등을 실시해야 하고, 필요한 개인보호구를 근로자에게 제공하며 대상 근로자는 반드시 착용하도록 관리 감독해야 합니다. 3.8 건강검진 및 사후관리: 두산퓨얼셀의 협력회사는 사업을 영위하는 국가별 건강검진 법률에 따라 임직원을 대상으로 일반건강검진 또는 특수건강검진 등을 정기적으로 실시하여야 하며, 건강검진 결과 필요한 경우 작업 장소 변경, 작업 전환, 근로 시간 단축 등의 조치를 실시해야 합니다. 3.9 신체부담 업무: 두산퓨얼셀의 협력회사는 근로자가 무거운 자재를 들어 올리거나 심하게 반복적인 작업, 장시간 서 있는 작업, 체력 소모가 심한 조립 작업 등의 육체적으로 힘든 작업에 노출되는 것을 파악하고 평가하며 통제해야 합니다. 3.10 위생, 식품 및 주거: 두산퓨얼셀의 협력회사는 근로자에게 청결한 화장실과 식수 시설, 위생적인 식품 조리/보관 시설과 식사할 수 있는 장소를 제공해야 합니다. 또한 근로자에게 제공되는 기숙사는 청결하고 안전을 유지해야 하며, 적절한 조명, 비상 탈출시설, 난방, 온수, 환기시설, 개인물품 보관시설 및 적절한 출 ...</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.75] 공급망 ESG 관리 &gt; 3. 안전 및 보건 3.1 산업안전 관리: 두산퓨얼셀의 협력회사는 물리적인 위험 요소를 사전에 제거하고 적절한 설계, 엔지니어링 및 행정적 통제, 예방 정비, 안전한 작업절차를 통해 예방조치를 취해야 합니다. 또한 근로자들이 잠재적 안전 위험 요소(예: 전기 및 기타 에너지원, 화재, 차량, 추락위험)에 노출되지 않도록 하여야 합니다. 이러한 수단으로 위험 요소들을 충분히 통제할 수 없는 경우에는 근로자에게 적절한 개인 보호 장비를 제공해야 합니다. 3.2 기계설비의 안전유지: 두산퓨얼셀의 생산 및 기계설비의 안전 위해 요소를 평가해야 합니다. 근로자가 설비로 인해 상해를 당할 위험이 있을 경우 협력회사는 안전장치, 방호벽, 긴급장치 등을 설치하고 근로자에게 안전 보호구를 지급하여야 합니다. 3.7 위험성 평가: 두산퓨얼셀의 협력회사는 위험 요인에 대한 근로자의 노출 가능성을 파악하고 위험을 사전에 차단하기 위해 위험성 평가를 정기적으로 실시해야 합니다. 평가 결과에 따라 안전한 공정의 설계, 기술적/행정적 통제, 예방정비, 작업절차서 내 안전 측면 반영, 지속적인 교육 등을 실시해야 하고, 필요한 개인보호구를 근로자에게 제공하며 대상 근로자는 반드시 착용하도록 관리 감독해야 합니다. 3.8 건강검진 및 사후관리: 두산퓨얼셀의 협력회사는 사업을 영위하는 국가별 건강검진 법률에 따라 임직원을 대상으로 일반건강검진 또는 특수건강검진 등을 정기적으로 실시하여야 하며, 건강검진 결과 필요한 경우 작업 장소 변경, 작업 전환, 근로 시간 단축 등의 조치를 실시해야 합니다. 3.9 신체부담 업무: 두산퓨얼셀의 협력회사는 근로자가 무거운 자재를 들어 올리거나 심하게 반복적인 작업, 장시간 서 있는 작업, 체력 소모가 심한 조립 작업 등의 육체적으로 힘든 작업에 노출되는 것을 파악하고 평가하며 통제해야 합니다. 3.10 위생, 식품 및 주거: 두산퓨얼셀의 협력회사는 근로자에게 청결한 화장실과 식수 시설, 위생적인 식품 조리/보관 시설과 식사할 수 있는 장소를 제공해야 합니다. 또한 근로자에게 제공되는 기숙사는 청결하고 안전을 유지해야 하며, 적절한 조명, 비상 탈출시설, 난방, 온수, 환기시설, 개인물품 보관시설 및 적절한 출 ...</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 65;66;67;75
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E6" s="6" t="str">
-        <x:v>Selected Style: governance
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: governance
 Preferred Style Source: template
 Answer Type: governance-organization
 Answer Intent: Explain who is responsible, what they decide or oversee, and how reporting or escalation works.
@@ -514,34 +655,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: Medium: responsibility and decision flow must be clear.</x:v>
-      </x:c>
-      <x:c r="F6" s="6" t="str">
-        <x:v>2023년 4월 3일 두산퓨얼셀㈜ CSHO 박준영 01 02 03 04 05 06 두산퓨얼셀은 안전하고 청결한 작업환경을 임직원, 가족, 사회에 대한 책임이자 핵심가치로 인식하고 있습니다. 안전보건 안전보건관리 중장기 로드맵 수립 두산퓨얼셀은 안전과 보건을 최우선으로 생각하며, 모든 임직원과 지역사회의 안전을 보장하기 위해 최선을 다하고 있습니다. 두산퓨얼셀은 안전보건 중장기 로드맵을 기반으로 KPI(Key Performance Index)를 설정하고 연도별 안전보건추진계획을 수립하여 정기적인 모니터링을 통해 목표 달성 여부 및 실행 효과를 점검하고 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="6" t="str">
-        <x:v>EBX-Q-006</x:v>
-      </x:c>
-      <x:c r="B7" s="6" t="str">
-        <x:v>사회 / 위험 관리 (Risk Management) / 산업안전 리스크 식별 및 예방 활동</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="str">
-        <x:v>[p.62] 인권경영 차별 및 괴롭힘 방지 지침 직장 내 성희롱, 괴롭힘 및 차별 금지 직장 내 성희롱 금지 |  사업주, 관리자 또는 구성원이 직장 내의 지위를 이용하거나 업무 수행과 관련하여 다른 구성원에게 성적인 언동 등으로 성적 굴욕감 또는 혐오감을 느끼게 해서는 안됩니다. 또한 이러한 성적인 언동이나 그 밖의 요구에 따르지 아니하였다는 이유로 근로조건 및 고용에서 불이익을 주는 행위를 해서는 안됩니다. 직장 내 괴롭힘 금지 |  회사 내에서의 지위 또는 관계 등의 우위를 이용하여 업무상 적정 범위를 넘어 다른 구성원에게 신체적, 정신적 고통을 주거나 근무환경을 악화시키는 행위를 해서는 안됩니다. 직장 내 괴롭힘의 행위는 신체적 괴롭힘과 신분적, 업무적, 언어적, 개인적 괴롭힘 및 근무환경의 악화를 포함합니다. 차별 금지 |  임직원의 성별, 인종, 민족, 국적, 종교, 나이, 정치적 견해, 출신 지역에 따라 차별적인 대우를 해서는 안됩니다. 발생 시 조치 신고접수(두산퓨얼셀 인권센터 및 두산그룹 내외부 신고센터) |  직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 알게 된 경우 누구라도 그 내용을 신고할 수 있으며, 신고 접수 시에는 조사 의뢰 등 적절한 방안을 강구하게 됩니다. 조사 및 심의(조사 담당 부서) |  사실 관계 파악을 위해 성희롱, 괴롭힘, 차별 등의 여부를 확인하며, 조사 관련자의 신원에 대해서는 비밀을 유지합니다. 이때, 해결 방식에 대해 피해자의 의견을 청취하고 피해자의 요청이 있을 경우 근무장소의 변경, 휴가의 명령 등 적절한 조치를 취합니다. 조치(인사위원회 주관 부서) |  행위에 의한 피해사실이 확인된 경우에는 지체없이 행위자에 대하여 징계나 그 밖에 이에 준하는 조치를 취합니다. 직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 신고한 직원 또는 피해를 입었거나 피해 발생을 주장하는 직원은 적극적으로 보호합니다. 모니터링(인권센터, HR) |  조치사항의 이행여부와 후속적인 괴롭힘 피해가 없는지 모니터링하며, 피해자에 대한 불리한 처우가 발생하지 않도록 예방합니다. 비밀유지 직장 내 성희롱, 괴롭힘 및 차별 조사 과정에 참여한 임직원은 조사 등으로 알게 된 비밀을 누설하지 않습니다. 재발방지 조치 회 ...
+QA Severity: Medium: responsibility and decision flow must be clear.</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 안전보건 중장기 로드맵을 기반으로 KPI(Key Performance Index)를 설정하고 연도별 안전보건추진계획을 수립하여 정기적인 모니터링을 통해 목표 달성 여부 및 실행 효과를 점검하고 있습니다. 두산퓨얼셀은 임직원 스스로 안전의 중요성을 인식하고 능동적으로 실천하는 안전보건 실행문화를 정착하기 위해 중장기적 관점에서 단계별 세부 목표를 설정하고 지속적으로 개선해나가겠습니다. 두산퓨얼셀은 경영진의 안전보건 실천 의지를 표명하고 안전점검, 회의, 간담회 등 다양한 활동을 통해 EHS 리더십을 적극 실천하고 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-006</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 위험 관리 (Risk Management) / 산업안전 리스크 식별 및 예방 활동</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>[p.62] 인권경영 차별 및 괴롭힘 방지 지침 직장 내 성희롱, 괴롭힘 및 차별 금지 직장 내 성희롱 금지 |  사업주, 관리자 또는 구성원이 직장 내의 지위를 이용하거나 업무 수행과 관련하여 다른 구성원에게 성적인 언동 등으로 성적 굴욕감 또는 혐오감을 느끼게 해서는 안됩니다. 또한 이러한 성적인 언동이나 그 밖의 요구에 따르지 아니하였다는 이유로 근로조건 및 고용에서 불이익을 주는 행위를 해서는 안됩니다. 직장 내 괴롭힘 금지 |  회사 내에서의 지위 또는 관계 등의 우위를 이용하여 업무상 적정 범위를 넘어 다른 구성원에게 신체적, 정신적 고통을 주거나 근무환경을 악화시키는 행위를 해서는 안됩니다. 직장 내 괴롭힘의 행위는 신체적 괴롭힘과 신분적, 업무적, 언어적, 개인적 괴롭힘 및 근무환경의 악화를 포함합니다. 차별 금지 |  임직원의 성별, 인종, 민족, 국적, 종교, 나이, 정치적 견해, 출신 지역에 따라 차별적인 대우를 해서는 안됩니다. 발생 시 조치 신고접수(두산퓨얼셀 인권센터 및 두산그룹 내외부 신고센터) |  직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 알게 된 경우 누구라도 그 내용을 신고할 수 있으며, 신고 접수 시에는 조사 의뢰 등 적절한 방안을 강구하게 됩니다. 조사 및 심의(조사 담당 부서) |  사실 관계 파악을 위해 성희롱, 괴롭힘, 차별 등의 여부를 확인하며, 조사 관련자의 신원에 대해서는 비밀을 유지합니다. 이때, 해결 방식에 대해 피해자의 의견을 청취하고 피해자의 요청이 있을 경우 근무장소의 변경, 휴가의 명령 등 적절한 조치를 취합니다. 조치(인사위원회 주관 부서) |  행위에 의한 피해사실이 확인된 경우에는 지체없이 행위자에 대하여 징계나 그 밖에 이에 준하는 조치를 취합니다. 직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 신고한 직원 또는 피해를 입었거나 피해 발생을 주장하는 직원은 적극적으로 보호합니다. 모니터링(인권센터, HR) |  조치사항의 이행여부와 후속적인 괴롭힘 피해가 없는지 모니터링하며, 피해자에 대한 불리한 처우가 발생하지 않도록 예방합니다. 비밀유지 직장 내 성희롱, 괴롭힘 및 차별 조사 과정에 참여한 임직원은 조사 등으로 알게 된 비밀을 누설하지 않습니다. 재발방지 조치 회 ...
 [p.63] 인권경영 인권정책 인권이슈 제보 채널 두산퓨얼셀은 홈페이지 내 사이버 신고센터를 통해 임직원을 포함한 모든 이해관계자가 인권 침해 및 기타 비윤리적 행위를 제보할 수 있도록 하고 있으며, 비밀보장 원칙에 따라 비공개 신고도 가능합니다. 접수된 제보는 철저히 보호되며, 내부 절차에 따라 신속히 처리됩니다. 또한 인권 관련 문제가 발생한 경우, 피해자 또는 목격자는 내부 신고센터, 직장 내 괴롭힘·성희롱 예방센터, 인권센터 등을 통해 신고할 수 있습니다. 두산퓨얼셀은 임직원 뿐 아니라 경영활동에서 관계를 맺고 있는 모든 이해관계자의 인권을 존중하며, 협력업체 등 제3자를 대상으로 동일한 수준의 인권경영을 권고하고 있습니다. 두산퓨얼셀은 협력사 및 주요 비즈니스 파트너에게 인권보호에 대한 의무이행을 요구하며, 준수 여부를 모니터링 합니다. 두산퓨얼셀은 인권, 노동, 환경과 반부패에 관한 글로벌콤팩트 10대 원칙에 대한 CEO의 지지선언과 함께, ‘세계인권선언(Universal Declaration of Human Rights )’과 ‘유엔 기업과 인권 이행원칙(UN Guiding Principles on Business and Human Rights; Ruggie Framework)’ 등 국제적으로 인정받고 있는 인권원칙을 바탕으로 인권경영 실천 및 실사체계(Due Diligence)를 수립하여 운영하고 있습니다. 고용상의 비차별과 결사 및 단체교섭의 자유 보장 고용과 관련하여 성별, 종교, 장애, 나이, 사회적 신분, 출신 지역 등을 이유로 일체의 부당한 차별을 하지 않으며, 다양성을 포용합니다. 더불어 근로자들의 결사의 자유와 단체 교섭의 자유를 인정하고 노동조합 활동을 이유로 어떠한 불이익도 주지 않습니다. 강제노동 및 아동노동의 금지 사업활동에서 발생할 수 있는 어떠한 형태의 강제노동도 인정하지 않으며 사업 국가가 정한 최소 고용 연령을 준수합니다. 사업 국가의 법규에서 정한 최소고용연령을 준수하고 연소자를 고용한 것을 알게 된 경우, 즉시 구제 조치를 취하는 등 인간 존엄성에 해를 끼치는 모든 잘못된 노동관행을 방지하겠습니다. 산업안전보장 및 책임 있는 공급망 관리 작업환경을 안전하게 유지하며 사업장에 적용되는 환경, 보건 및 안전 ...
 [p.67] 안전보건 안전보건 관리 활동 두산퓨얼셀은 임직원과 협력사 근로자의 안전과 건강을 최우선으로 생각하며 인간 존중 경영을 실천하고 있습니다. EHS와 관련된 위험 요소를 사전에 파악하고 제거하거나 최소화하기 위해 다양한 평가, 점검 및 비상 대응체계를 운영하고 있습 니다. 특히 솔선수범하는 리더십을 바탕으로 임원과 리더 직급의 자율적인 안전보건 활동을 확산시키기 위해 지속적으로 노력하고 있습니다. 또한 매달 EHS 뉴스레터를 발행하여 일상생활에서 유용한 안전 및 건강 정보를 제공하고 있으며, 각 사업장별 이벤트를 통해 임직원의 EHS에 대한 관심과 참여를 유도하고 있습니다. &gt; 안전보건 조직 구축 및 목표 수립 &gt; 안전보건 리더십 활동 &gt; 고객서비스 안전보건관리 두산퓨얼셀은 EHS 방침을 기반으로 전사 및 사업장의 안전보건 목표를 설 정하고 이를 체계적으로 시행하고 있습니다. 또한 안전사고를 예방하고 각 조직의 안전보건 목표를 달성하기 위해 안전보건 전담 부서를 설치, 운영하 고 있습니다. 각 사이트별로 관리 감독자를 선임하고 안전보건 담당자를 지 정하여 효과적으로 운영하고 있습니다. &gt; 임직원 건강 증진 두산퓨얼셀은 임직원의 건강 증진과 직업성 질환 예방을 위해 정기적인 건 강검진을 실시하고 있습니다. 유소견자에 대해서는 지속적인 건강 상담과 추적 관리는 물론, 다양한 건강 증진 프로그램도 함께 운영하고 있습니다. 또한 임직원의 자발적인 건강 관리를 지원하기 위해 체력 측정 이벤트, 금연 프로그램 등도 함께 추진하고 있습니다. 두산퓨얼셀은 경영진의 안전보건 실천 의지를 표명하고 안전점검, 회의, 간담 회 등 다양한 활동을 통해 EHS 리더십을 적극 실천하고 있습니다. 또한 안전보건경영시스템 운영 및 관련 법규 준수 사항에 대해 근로자가 직 접 참여하는 EHS 협의기구를 운영하여, EHS 활동에 대한 책임과 권한을 부 여하고 있습니다. 이를 통해 임직원의 자주적인 안전 활동을 유도하고 안전의 식을 높여, 사업장 내 사고 예방과 지속 가능한 성장에 기여하고 있습니다. &gt; 외주공사 안전관리 및 협력관계 구축 두산퓨얼셀은 사업장에서 발생하는 외주공사 재해예방을 위한 관리규정을 제정하고, 사내 공사 및 유지보수 서비스 현장에 대한 안전관리 프로세 ...
-[p.75] 공급망 ESG 관리 &gt; 3. 안전 및 보건 3.1 산업안전 관리: 두산퓨얼셀의 협력회사는 물리적인 위험 요소를 사전에 제거하고 적절한 설계, 엔지니어링 및 행정적 통제, 예방 정비, 안전한 작업절차를 통해 예방조치를 취해야 합니다. 또한 근로자들이 잠재적 안전 위험 요소(예: 전기 및 기타 에너지원, 화재, 차량, 추락위험)에 노출되지 않도록 하여야 합니다. 이러한 수단으로 위험 요소들을 충분히 통제할 수 없는 경우에는 근로자에게 적절한 개인 보호 장비를 제공해야 합니다. 3.2 기계설비의 안전유지: 두산퓨얼셀의 생산 및 기계설비의 안전 위해 요소를 평가해야 합니다. 근로자가 설비로 인해 상해를 당할 위험이 있을 경우 협력회사는 안전장치, 방호벽, 긴급장치 등을 설치하고 근로자에게 안전 보호구를 지급하여야 합니다. 3.7 위험성 평가: 두산퓨얼셀의 협력회사는 위험 요인에 대한 근로자의 노출 가능성을 파악하고 위험을 사전에 차단하기 위해 위험성 평가를 정기적으로 실시해야 합니다. 평가 결과에 따라 안전한 공정의 설계, 기술적/행정적 통제, 예방정비, 작업절차서 내 안전 측면 반영, 지속적인 교육 등을 실시해야 하고, 필요한 개인보호구를 근로자에게 제공하며 대상 근로자는 반드시 착용하도록 관리 감독해야 합니다. 3.8 건강검진 및 사후관리: 두산퓨얼셀의 협력회사는 사업을 영위하는 국가별 건강검진 법률에 따라 임직원을 대상으로 일반건강검진 또는 특수건강검진 등을 정기적으로 실시하여야 하며, 건강검진 결과 필요한 경우 작업 장소 변경, 작업 전환, 근로 시간 단축 등의 조치를 실시해야 합니다. 3.9 신체부담 업무: 두산퓨얼셀의 협력회사는 근로자가 무거운 자재를 들어 올리거나 심하게 반복적인 작업, 장시간 서 있는 작업, 체력 소모가 심한 조립 작업 등의 육체적으로 힘든 작업에 노출되는 것을 파악하고 평가하며 통제해야 합니다. 3.10 위생, 식품 및 주거: 두산퓨얼셀의 협력회사는 근로자에게 청결한 화장실과 식수 시설, 위생적인 식품 조리/보관 시설과 식사할 수 있는 장소를 제공해야 합니다. 또한 근로자에게 제공되는 기숙사는 청결하고 안전을 유지해야 하며, 적절한 조명, 비상 탈출시설, 난방, 온수, 환기시설, 개인물품 보관시설 및 적절한 출 ...</x:v>
-      </x:c>
-      <x:c r="D7" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.75] 공급망 ESG 관리 &gt; 3. 안전 및 보건 3.1 산업안전 관리: 두산퓨얼셀의 협력회사는 물리적인 위험 요소를 사전에 제거하고 적절한 설계, 엔지니어링 및 행정적 통제, 예방 정비, 안전한 작업절차를 통해 예방조치를 취해야 합니다. 또한 근로자들이 잠재적 안전 위험 요소(예: 전기 및 기타 에너지원, 화재, 차량, 추락위험)에 노출되지 않도록 하여야 합니다. 이러한 수단으로 위험 요소들을 충분히 통제할 수 없는 경우에는 근로자에게 적절한 개인 보호 장비를 제공해야 합니다. 3.2 기계설비의 안전유지: 두산퓨얼셀의 생산 및 기계설비의 안전 위해 요소를 평가해야 합니다. 근로자가 설비로 인해 상해를 당할 위험이 있을 경우 협력회사는 안전장치, 방호벽, 긴급장치 등을 설치하고 근로자에게 안전 보호구를 지급하여야 합니다. 3.7 위험성 평가: 두산퓨얼셀의 협력회사는 위험 요인에 대한 근로자의 노출 가능성을 파악하고 위험을 사전에 차단하기 위해 위험성 평가를 정기적으로 실시해야 합니다. 평가 결과에 따라 안전한 공정의 설계, 기술적/행정적 통제, 예방정비, 작업절차서 내 안전 측면 반영, 지속적인 교육 등을 실시해야 하고, 필요한 개인보호구를 근로자에게 제공하며 대상 근로자는 반드시 착용하도록 관리 감독해야 합니다. 3.8 건강검진 및 사후관리: 두산퓨얼셀의 협력회사는 사업을 영위하는 국가별 건강검진 법률에 따라 임직원을 대상으로 일반건강검진 또는 특수건강검진 등을 정기적으로 실시하여야 하며, 건강검진 결과 필요한 경우 작업 장소 변경, 작업 전환, 근로 시간 단축 등의 조치를 실시해야 합니다. 3.9 신체부담 업무: 두산퓨얼셀의 협력회사는 근로자가 무거운 자재를 들어 올리거나 심하게 반복적인 작업, 장시간 서 있는 작업, 체력 소모가 심한 조립 작업 등의 육체적으로 힘든 작업에 노출되는 것을 파악하고 평가하며 통제해야 합니다. 3.10 위생, 식품 및 주거: 두산퓨얼셀의 협력회사는 근로자에게 청결한 화장실과 식수 시설, 위생적인 식품 조리/보관 시설과 식사할 수 있는 장소를 제공해야 합니다. 또한 근로자에게 제공되는 기숙사는 청결하고 안전을 유지해야 하며, 적절한 조명, 비상 탈출시설, 난방, 온수, 환기시설, 개인물품 보관시설 및 적절한 출 ...</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 62;63;67;75
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>Selected Style: risk-control
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: risk-control
 Preferred Style Source: template
 Answer Type: risk-control
 Answer Intent: Explain the risk/control scope, then prevention, monitoring, and follow-up actions.
@@ -560,33 +713,45 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: High: must include risk/control and monitoring evidence.</x:v>
-      </x:c>
-      <x:c r="F7" s="6" t="str">
-        <x:v>인권경영 인권정책 인권이슈 제보 채널 두산퓨얼셀은 홈페이지 내 사이버 신고센터를 통해 임직원을 포함한 모든 이해관계자가 인권 침해 및 기타 비윤리적 행위를 제보할 수 있도록 하고 있으며, 비밀보장 원칙에 따라 비공개 신고도 가능합니다. 두산퓨얼셀은 임직원 뿐 아니라 경영활동에서 관계를 맺고 있는 모든 이해관계자의 인권을 존중하며, 협력업체 등 제3자를 대상으로 동일한 수준의 인권경영을 권고하고 있습니다. 안전보건 안전보건 관리 활동 두산퓨얼셀은 임직원과 협력사 근로자의 안전과 건강을 최우선으로 생각하며 인간 존중 경영을 실천하고 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="6" t="str">
-        <x:v>EBX-Q-007</x:v>
-      </x:c>
-      <x:c r="B8" s="6" t="str">
-        <x:v>사회 / 지표 (Metrics) / 산업재해 발생 현황 및 안전 성과 지표</x:v>
-      </x:c>
-      <x:c r="C8" s="6" t="str">
-        <x:v>[p.75] 공급망 ESG 관리 &gt; 3. 안전 및 보건 3.1 산업안전 관리: 두산퓨얼셀의 협력회사는 물리적인 위험 요소를 사전에 제거하고 적절한 설계, 엔지니어링 및 행정적 통제, 예방 정비, 안전한 작업절차를 통해 예방조치를 취해야 합니다. 또한 근로자들이 잠재적 안전 위험 요소(예: 전기 및 기타 에너지원, 화재, 차량, 추락위험)에 노출되지 않도록 하여야 합니다. 이러한 수단으로 위험 요소들을 충분히 통제할 수 없는 경우에는 근로자에게 적절한 개인 보호 장비를 제공해야 합니다. 3.2 기계설비의 안전유지: 두산퓨얼셀의 생산 및 기계설비의 안전 위해 요소를 평가해야 합니다. 근로자가 설비로 인해 상해를 당할 위험이 있을 경우 협력회사는 안전장치, 방호벽, 긴급장치 등을 설치하고 근로자에게 안전 보호구를 지급하여야 합니다. 3.7 위험성 평가: 두산퓨얼셀의 협력회사는 위험 요인에 대한 근로자의 노출 가능성을 파악하고 위험을 사전에 차단하기 위해 위험성 평가를 정기적으로 실시해야 합니다. 평가 결과에 따라 안전한 공정의 설계, 기술적/행정적 통제, 예방정비, 작업절차서 내 안전 측면 반영, 지속적인 교육 등을 실시해야 하고, 필요한 개인보호구를 근로자에게 제공하며 대상 근로자는 반드시 착용하도록 관리 감독해야 합니다. 3.8 건강검진 및 사후관리: 두산퓨얼셀의 협력회사는 사업을 영위하는 국가별 건강검진 법률에 따라 임직원을 대상으로 일반건강검진 또는 특수건강검진 등을 정기적으로 실시하여야 하며, 건강검진 결과 필요한 경우 작업 장소 변경, 작업 전환, 근로 시간 단축 등의 조치를 실시해야 합니다. 3.9 신체부담 업무: 두산퓨얼셀의 협력회사는 근로자가 무거운 자재를 들어 올리거나 심하게 반복적인 작업, 장시간 서 있는 작업, 체력 소모가 심한 조립 작업 등의 육체적으로 힘든 작업에 노출되는 것을 파악하고 평가하며 통제해야 합니다. 3.10 위생, 식품 및 주거: 두산퓨얼셀의 협력회사는 근로자에게 청결한 화장실과 식수 시설, 위생적인 식품 조리/보관 시설과 식사할 수 있는 장소를 제공해야 합니다. 또한 근로자에게 제공되는 기숙사는 청결하고 안전을 유지해야 하며, 적절한 조명, 비상 탈출시설, 난방, 온수, 환기시설, 개인물품 보관시설 및 적절한 출 ...
+QA Severity: High: must include risk/control and monitoring evidence.</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 산업안전 리스크 식별 및 예방 활동에서 식별된 위험 요인과 예방 활동을 연결해 관리 수준을 점검하고 있습니다. 인권 관련 문제가 발생한 경우, 피해자 또는 목격자는 내부 신고센터, 직장 내 괴롭힘·성희롱 예방센터, 인권센터 등을 통해 신고할 수 있습니다. 두산퓨얼셀은 임직원뿐 아니라 경영활동에서 관계를 맺고 있는 모든 이해관계자의 인권을 존중하며, 협력업체 등 제3자를 대상으로 동일한 수준의 인권경영을 권고하고 있습니다. 산업안전 리스크 식별 및 예방 활동 관련 공시는 단순한 선언보다 예방, 모니터링, 후속 조치의 연결성을 중심으로 해석할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-007</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 지표 (Metrics) / 산업재해 발생 현황 및 안전 성과 지표</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>[p.75] 공급망 ESG 관리 &gt; 3. 안전 및 보건 3.1 산업안전 관리: 두산퓨얼셀의 협력회사는 물리적인 위험 요소를 사전에 제거하고 적절한 설계, 엔지니어링 및 행정적 통제, 예방 정비, 안전한 작업절차를 통해 예방조치를 취해야 합니다. 또한 근로자들이 잠재적 안전 위험 요소(예: 전기 및 기타 에너지원, 화재, 차량, 추락위험)에 노출되지 않도록 하여야 합니다. 이러한 수단으로 위험 요소들을 충분히 통제할 수 없는 경우에는 근로자에게 적절한 개인 보호 장비를 제공해야 합니다. 3.2 기계설비의 안전유지: 두산퓨얼셀의 생산 및 기계설비의 안전 위해 요소를 평가해야 합니다. 근로자가 설비로 인해 상해를 당할 위험이 있을 경우 협력회사는 안전장치, 방호벽, 긴급장치 등을 설치하고 근로자에게 안전 보호구를 지급하여야 합니다. 3.7 위험성 평가: 두산퓨얼셀의 협력회사는 위험 요인에 대한 근로자의 노출 가능성을 파악하고 위험을 사전에 차단하기 위해 위험성 평가를 정기적으로 실시해야 합니다. 평가 결과에 따라 안전한 공정의 설계, 기술적/행정적 통제, 예방정비, 작업절차서 내 안전 측면 반영, 지속적인 교육 등을 실시해야 하고, 필요한 개인보호구를 근로자에게 제공하며 대상 근로자는 반드시 착용하도록 관리 감독해야 합니다. 3.8 건강검진 및 사후관리: 두산퓨얼셀의 협력회사는 사업을 영위하는 국가별 건강검진 법률에 따라 임직원을 대상으로 일반건강검진 또는 특수건강검진 등을 정기적으로 실시하여야 하며, 건강검진 결과 필요한 경우 작업 장소 변경, 작업 전환, 근로 시간 단축 등의 조치를 실시해야 합니다. 3.9 신체부담 업무: 두산퓨얼셀의 협력회사는 근로자가 무거운 자재를 들어 올리거나 심하게 반복적인 작업, 장시간 서 있는 작업, 체력 소모가 심한 조립 작업 등의 육체적으로 힘든 작업에 노출되는 것을 파악하고 평가하며 통제해야 합니다. 3.10 위생, 식품 및 주거: 두산퓨얼셀의 협력회사는 근로자에게 청결한 화장실과 식수 시설, 위생적인 식품 조리/보관 시설과 식사할 수 있는 장소를 제공해야 합니다. 또한 근로자에게 제공되는 기숙사는 청결하고 안전을 유지해야 하며, 적절한 조명, 비상 탈출시설, 난방, 온수, 환기시설, 개인물품 보관시설 및 적절한 출 ...
 [p.108] 사회 안전보건 임직원 역량 개발 구분 단위 2022 2023 2024 조직에서 업무 및/또는 작업장을 관리하는 근로자 인원 명 61 65 77 비율 % 12.6 13.8 13.5 직장 건강 및 안전 관리 시스템의 적용 대상 근로자(법률과 시스템) 인원 명 485 505 571 비율 % 100 100 100 직장 건강 및 안전 관리 시스템의 적용 대상 근로자(내부감사) 인원 명 226 139 194 비율 % 47.0 29.6 34.0 직장 건강 및 안전 관리 시스템의 적용 대상 근로자(외부감사나 인증) 인원 명 226 139 194 비율 % 47.0 29.6 34.0 산업재해율 % 0.0 0.2 0.2 근로손실재해(L TIFR) 임직원 근로 손실 발생 건수 건 0 1 1 임직원 근로손실재해율 건/백만 시간 0.00 1.01 0.87 협력사 근로 손실 발생 건수 건 0 1 0 협력사 근로손실재해율 건/백만 시간 0 15 0 업무상 질병(OIFR) 1) 임직원 기록가능한 업무관련 질병 발생 건수 건 0 0 0 임직원 업무 관련 질병 발생 비율(OIFR) 건/백만 시간 - - 0 협력사 기록가능한 업무관련 질병 발생 건수 건 - - 0 협력사 업무 관련 질병 발생 비율(OIFR) 건/백만 시간 - - 0 업무상재해(TRIR) 총 기록사고 건수 (임직원) 건 - 9 10 총 기록사고율 (임직원) 1) 건/백만 시간 - 8.95 8.74 업무관련 사망자 수 임직원 명 0 0 0 협력사 명 0 0 0 임직원 비율 % 0 0 0 협력사 비율 % 0 0 0 총 기록 사망률 % 0 0 0 조직에서 업무 및 작업장을 관리하는 근로자(직원 제외) 대상 업무관련 사망자 수 명 0 0 0 기록 가능한 작업 관련 부상자 수 명 0 9 10 비율 % 0 1.89 1.85 근로 손실 일수 일 0 21 31 현장 안전점검(현장당 시행 건수) 건수 18 24 65 연간 총 근로 시간 2) 임직원 시간 - - 1,144,704 협력사 시간 - - 61,248 구분 단위 2022 2023 2024 총 교육 시간 시간 4,053 5,308 5,991 연령별 30세 미만 시간 1,484 1,694 1,063 30세~50세 이하 시간 2,378 3,319 4,776 50세 초과 ...
-[p.117] 주제 코드 회계 지표 범주 측정 단위 보고 페이지 에너지 관리 RR-FC-130a.1 총에너지 소비량 정량적 기가줄(GJ) 101 그리드 전력 비율 정량적 백분율(%) 101 재생가능 비율 정량적 백분율(%) 101 전 종업원 보건 및 안전 RR-FC-320a.1 총기록 재해율(Total Recordable Incident Rate, TRIR) 정량적 비율 108 총기록 사망률 정량적 비율 108 RR-FC-320a.2 종업원의 건강 위험 노출을 평가 및 모니터링하고 감소시키기 위한 노력의 설명 논의 및 분석 해당 없음 65-67 제품 효율 RR-FC-410a.1 제품 용도 및 기술 유형별 산업용 배터리의 평균 저장 용량 정량적 비에너지(Wh/kg) N/A RR-FC-410a.2 제품 용도 및 기술 유형별 전력 효율 정량적 백분율(%) 103 제품 용도 및 기술 유형별 열효율 등 연료 전지의 평균 에너지 효율 정량적 백분율(%) 103 RR-FC-410a.3 제품 용도 및 기술 유형별 쿨롱 효율(Coulombic Efficiency) 등 평균 배터리 효율 정량적 백분율(%) N/A RR-FC-410a.4 제품 용도 및 기술 유형별 연료 전지의 평균 운전 수명 정량적 시간(h) N/A RR-FC-410a.5 제품 용도 및 기술 유형별 배터리의 평균 운전 수명 정량적 주기(cycles) 수 N/A 수명만료 제품관리 RR-FC-410b.1 판매 제품의 재활용 또는 재사용 가능 비율 정량적 중량 기준 백분율(%) N/A RR-FC-410b.2 회수된 수명만료(End Of Life, EOL) 자재 중량 정량적 톤(t) 102 회수된 수명만료(End Of Life, EOL) 자재 재활용 비율 정량적 백분율(%) 102 RR-FC-410b.3 유해물질 사용, 매립 및 폐기 관리에 대한 접근법 설명 논의 및 분석 해당 없음 43-44, 47 자재 조달 RR-FC-440a.1 중요자재(Critical Materials) 사용과 관련된 위험 관리에 대한 설명 논의 및 분석 해당 없음 N/A 활동 지표 코드 범주 측정 단위 보고 페이지 판매 제품 수 RR-FC-000.A 정량적 수 8 판매 전지의 총 저장 용량 RR-FC-000.B 정량적 메가와트(MW) ...</x:v>
-      </x:c>
-      <x:c r="D8" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.117] 주제 코드 회계 지표 범주 측정 단위 보고 페이지 에너지 관리 RR-FC-130a.1 총에너지 소비량 정량적 기가줄(GJ) 101 그리드 전력 비율 정량적 백분율(%) 101 재생가능 비율 정량적 백분율(%) 101 전 종업원 보건 및 안전 RR-FC-320a.1 총기록 재해율(Total Recordable Incident Rate, TRIR) 정량적 비율 108 총기록 사망률 정량적 비율 108 RR-FC-320a.2 종업원의 건강 위험 노출을 평가 및 모니터링하고 감소시키기 위한 노력의 설명 논의 및 분석 해당 없음 65-67 제품 효율 RR-FC-410a.1 제품 용도 및 기술 유형별 산업용 배터리의 평균 저장 용량 정량적 비에너지(Wh/kg) N/A RR-FC-410a.2 제품 용도 및 기술 유형별 전력 효율 정량적 백분율(%) 103 제품 용도 및 기술 유형별 열효율 등 연료 전지의 평균 에너지 효율 정량적 백분율(%) 103 RR-FC-410a.3 제품 용도 및 기술 유형별 쿨롱 효율(Coulombic Efficiency) 등 평균 배터리 효율 정량적 백분율(%) N/A RR-FC-410a.4 제품 용도 및 기술 유형별 연료 전지의 평균 운전 수명 정량적 시간(h) N/A RR-FC-410a.5 제품 용도 및 기술 유형별 배터리의 평균 운전 수명 정량적 주기(cycles) 수 N/A 수명만료 제품관리 RR-FC-410b.1 판매 제품의 재활용 또는 재사용 가능 비율 정량적 중량 기준 백분율(%) N/A RR-FC-410b.2 회수된 수명만료(End Of Life, EOL) 자재 중량 정량적 톤(t) 102 회수된 수명만료(End Of Life, EOL) 자재 재활용 비율 정량적 백분율(%) 102 RR-FC-410b.3 유해물질 사용, 매립 및 폐기 관리에 대한 접근법 설명 논의 및 분석 해당 없음 43-44, 47 자재 조달 RR-FC-440a.1 중요자재(Critical Materials) 사용과 관련된 위험 관리에 대한 설명 논의 및 분석 해당 없음 N/A 활동 지표 코드 범주 측정 단위 보고 페이지 판매 제품 수 RR-FC-000.A 정량적 수 8 판매 전지의 총 저장 용량 RR-FC-000.B 정량적 메가와트(MW) ...</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 75;108;117
 Evidence type: qualitative+quantitative
 Coverage status: SUFFICIENT
-Numeric support: 35 quantitative row(s) in data_dinh_luong.csv are linked to the same source page(s).</x:v>
-      </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>Selected Style: status-performance
+Numeric support: 35 quantitative row(s) in data_dinh_luong.csv are linked to the same source page(s).</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: status-performance
 Preferred Style Source: template
 Answer Type: status-performance
 Answer Intent: Explain the reported status in plain language, then weave figures into the management meaning.
@@ -605,34 +770,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: High: topic-fit figures, non-repetitive opening, no technical metric label.</x:v>
-      </x:c>
-      <x:c r="F8" s="6" t="str">
-        <x:v>두산퓨얼셀는 산업재해 발생 현황 및 안전 성과 지표에 대해 발생 현황과 관리 성과를 함께 확인할 수 있도록 보고하고 있습니다. 회사는 물리적인 위험 요소를 사전에 제거하고 적절한 설계, 엔지니어링 및 행정적 통제, 예방 정비, 안전한 작업절차를 통해 예방조치를 취해야 합니다. 또한 근로자들이 잠재적 안전 위험 요소(예: 전기 및 기타 에너지원, 화재, 차량, 추락위험)에 노출되지 않도록 하여야 합니다. 공개된 수치와 설명은 산업재해 발생 현황 및 안전 성과 지표의 현재 수준을 확인하고 다음 관리 과제를 판단하는 기준이 되며, 전년 수치와 함께 제시될 때 추세 확인에도 활용될 수 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="6" t="str">
-        <x:v>EBX-Q-008</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="str">
-        <x:v>사회 / 전략 (Strategy) / 인권경영 정책 및 목표</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="str">
-        <x:v>[p.62] 인권경영 차별 및 괴롭힘 방지 지침 직장 내 성희롱, 괴롭힘 및 차별 금지 직장 내 성희롱 금지 |  사업주, 관리자 또는 구성원이 직장 내의 지위를 이용하거나 업무 수행과 관련하여 다른 구성원에게 성적인 언동 등으로 성적 굴욕감 또는 혐오감을 느끼게 해서는 안됩니다. 또한 이러한 성적인 언동이나 그 밖의 요구에 따르지 아니하였다는 이유로 근로조건 및 고용에서 불이익을 주는 행위를 해서는 안됩니다. 직장 내 괴롭힘 금지 |  회사 내에서의 지위 또는 관계 등의 우위를 이용하여 업무상 적정 범위를 넘어 다른 구성원에게 신체적, 정신적 고통을 주거나 근무환경을 악화시키는 행위를 해서는 안됩니다. 직장 내 괴롭힘의 행위는 신체적 괴롭힘과 신분적, 업무적, 언어적, 개인적 괴롭힘 및 근무환경의 악화를 포함합니다. 차별 금지 |  임직원의 성별, 인종, 민족, 국적, 종교, 나이, 정치적 견해, 출신 지역에 따라 차별적인 대우를 해서는 안됩니다. 발생 시 조치 신고접수(두산퓨얼셀 인권센터 및 두산그룹 내외부 신고센터) |  직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 알게 된 경우 누구라도 그 내용을 신고할 수 있으며, 신고 접수 시에는 조사 의뢰 등 적절한 방안을 강구하게 됩니다. 조사 및 심의(조사 담당 부서) |  사실 관계 파악을 위해 성희롱, 괴롭힘, 차별 등의 여부를 확인하며, 조사 관련자의 신원에 대해서는 비밀을 유지합니다. 이때, 해결 방식에 대해 피해자의 의견을 청취하고 피해자의 요청이 있을 경우 근무장소의 변경, 휴가의 명령 등 적절한 조치를 취합니다. 조치(인사위원회 주관 부서) |  행위에 의한 피해사실이 확인된 경우에는 지체없이 행위자에 대하여 징계나 그 밖에 이에 준하는 조치를 취합니다. 직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 신고한 직원 또는 피해를 입었거나 피해 발생을 주장하는 직원은 적극적으로 보호합니다. 모니터링(인권센터, HR) |  조치사항의 이행여부와 후속적인 괴롭힘 피해가 없는지 모니터링하며, 피해자에 대한 불리한 처우가 발생하지 않도록 예방합니다. 비밀유지 직장 내 성희롱, 괴롭힘 및 차별 조사 과정에 참여한 임직원은 조사 등으로 알게 된 비밀을 누설하지 않습니다. 재발방지 조치 회 ...
+QA Severity: High: topic-fit figures, non-repetitive opening, no technical metric label.</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 산업재해 발생 현황 및 안전 성과 지표에 대해 발생 현황과 관리 성과를 함께 확인할 수 있도록 보고하고 있습니다. 근로자들이 잠재적 안전 위험 요소(예: 전기 및 기타 에너지원, 화재, 차량, 추락위험)에 노출되지 않도록 하여야 합니다. 회사는 안전장치, 방호벽, 긴급장치 등을 설치하고 근로자에게 안전 보호구를 지급하여야 합니다. 공개된 수치와 설명은 산업재해 발생 현황 및 안전 성과 지표의 현재 수준을 확인하고 다음 관리 과제를 판단하는 기준이 되며, 전년 수치와 함께 제시될 때 추세 확인에도 활용될 수 있습니다. 산업재해 발생 현황 및 안전 성과 지표는 단순한 발생 여부뿐 아니라 접수, 처리, 예방 조치가 관리 체계 안에서 이어지는지를 함께 확인하는 기준으로 활용되며, 공개 범위가 제한될 경우 후속 점검과 내부 관리 보완 여부를 함께 검토할 필요가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-008</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 전략 (Strategy) / 인권경영 정책 및 목표</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>[p.62] 인권경영 차별 및 괴롭힘 방지 지침 직장 내 성희롱, 괴롭힘 및 차별 금지 직장 내 성희롱 금지 |  사업주, 관리자 또는 구성원이 직장 내의 지위를 이용하거나 업무 수행과 관련하여 다른 구성원에게 성적인 언동 등으로 성적 굴욕감 또는 혐오감을 느끼게 해서는 안됩니다. 또한 이러한 성적인 언동이나 그 밖의 요구에 따르지 아니하였다는 이유로 근로조건 및 고용에서 불이익을 주는 행위를 해서는 안됩니다. 직장 내 괴롭힘 금지 |  회사 내에서의 지위 또는 관계 등의 우위를 이용하여 업무상 적정 범위를 넘어 다른 구성원에게 신체적, 정신적 고통을 주거나 근무환경을 악화시키는 행위를 해서는 안됩니다. 직장 내 괴롭힘의 행위는 신체적 괴롭힘과 신분적, 업무적, 언어적, 개인적 괴롭힘 및 근무환경의 악화를 포함합니다. 차별 금지 |  임직원의 성별, 인종, 민족, 국적, 종교, 나이, 정치적 견해, 출신 지역에 따라 차별적인 대우를 해서는 안됩니다. 발생 시 조치 신고접수(두산퓨얼셀 인권센터 및 두산그룹 내외부 신고센터) |  직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 알게 된 경우 누구라도 그 내용을 신고할 수 있으며, 신고 접수 시에는 조사 의뢰 등 적절한 방안을 강구하게 됩니다. 조사 및 심의(조사 담당 부서) |  사실 관계 파악을 위해 성희롱, 괴롭힘, 차별 등의 여부를 확인하며, 조사 관련자의 신원에 대해서는 비밀을 유지합니다. 이때, 해결 방식에 대해 피해자의 의견을 청취하고 피해자의 요청이 있을 경우 근무장소의 변경, 휴가의 명령 등 적절한 조치를 취합니다. 조치(인사위원회 주관 부서) |  행위에 의한 피해사실이 확인된 경우에는 지체없이 행위자에 대하여 징계나 그 밖에 이에 준하는 조치를 취합니다. 직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 신고한 직원 또는 피해를 입었거나 피해 발생을 주장하는 직원은 적극적으로 보호합니다. 모니터링(인권센터, HR) |  조치사항의 이행여부와 후속적인 괴롭힘 피해가 없는지 모니터링하며, 피해자에 대한 불리한 처우가 발생하지 않도록 예방합니다. 비밀유지 직장 내 성희롱, 괴롭힘 및 차별 조사 과정에 참여한 임직원은 조사 등으로 알게 된 비밀을 누설하지 않습니다. 재발방지 조치 회 ...
 [p.63] 인권경영 인권정책 인권이슈 제보 채널 두산퓨얼셀은 홈페이지 내 사이버 신고센터를 통해 임직원을 포함한 모든 이해관계자가 인권 침해 및 기타 비윤리적 행위를 제보할 수 있도록 하고 있으며, 비밀보장 원칙에 따라 비공개 신고도 가능합니다. 접수된 제보는 철저히 보호되며, 내부 절차에 따라 신속히 처리됩니다. 또한 인권 관련 문제가 발생한 경우, 피해자 또는 목격자는 내부 신고센터, 직장 내 괴롭힘·성희롱 예방센터, 인권센터 등을 통해 신고할 수 있습니다. 두산퓨얼셀은 임직원 뿐 아니라 경영활동에서 관계를 맺고 있는 모든 이해관계자의 인권을 존중하며, 협력업체 등 제3자를 대상으로 동일한 수준의 인권경영을 권고하고 있습니다. 두산퓨얼셀은 협력사 및 주요 비즈니스 파트너에게 인권보호에 대한 의무이행을 요구하며, 준수 여부를 모니터링 합니다. 두산퓨얼셀은 인권, 노동, 환경과 반부패에 관한 글로벌콤팩트 10대 원칙에 대한 CEO의 지지선언과 함께, ‘세계인권선언(Universal Declaration of Human Rights )’과 ‘유엔 기업과 인권 이행원칙(UN Guiding Principles on Business and Human Rights; Ruggie Framework)’ 등 국제적으로 인정받고 있는 인권원칙을 바탕으로 인권경영 실천 및 실사체계(Due Diligence)를 수립하여 운영하고 있습니다. 고용상의 비차별과 결사 및 단체교섭의 자유 보장 고용과 관련하여 성별, 종교, 장애, 나이, 사회적 신분, 출신 지역 등을 이유로 일체의 부당한 차별을 하지 않으며, 다양성을 포용합니다. 더불어 근로자들의 결사의 자유와 단체 교섭의 자유를 인정하고 노동조합 활동을 이유로 어떠한 불이익도 주지 않습니다. 강제노동 및 아동노동의 금지 사업활동에서 발생할 수 있는 어떠한 형태의 강제노동도 인정하지 않으며 사업 국가가 정한 최소 고용 연령을 준수합니다. 사업 국가의 법규에서 정한 최소고용연령을 준수하고 연소자를 고용한 것을 알게 된 경우, 즉시 구제 조치를 취하는 등 인간 존엄성에 해를 끼치는 모든 잘못된 노동관행을 방지하겠습니다. 산업안전보장 및 책임 있는 공급망 관리 작업환경을 안전하게 유지하며 사업장에 적용되는 환경, 보건 및 안전 ...
 [p.64] 고용상의 비차별 인권영향평가 프로세스 1) 평가기준 국가인권위원회 인권경영가이드라인 및 򻹧리스트 򻹧리스트 구성 10개 분야 25개 문항 인권경영체계 구축 강제노동의 금지 환경권 보장 산업안전 보장 소비자 인권 보호 결사/단체 교섭 자유보장 책임있는 공급망 관리 존중과 소통 (현지 주민의 인권 보호 제외) 세부 진행절차 01 인권평가 추진계획 수립 02 인권평가 실시 03 인권평가 결과 분석 04 인권리스크 완화 계획 수립 -  인권평가 항목 벤치마킹 (그룹 내 자회자 중심) -  평가대상 확정 -  평가방법 및 절차 수립 - MS Forms 활용 - 주요 인권리스크 확인 -  고위험 대상 인권실사 인터뷰 실시 -  현황 분석 및 리스크 저감 계획 수립 1) 사내 협력사 임직원 포함 인권경영 인권영향평가 인권리스크 완화 계획 &gt; 인권 존중두산퓨얼셀은 인권 이슈로 인한 부정적 영향, 주요 취약 영역을 규명하기 위해 인권영향평가를 시행하고 있습니다. 2024년에 실시한 인권영향평가에는 전체 임직원의 50%가 참여했으며, 중대한 인권 이슈는 발견되지 않았습니다. 다 만 인권경영체계 구축, 존중과 소통, 공급망 관리에 대한 구성원의 긍정 인식률이 상대적으로 낮게 나타나 이를 우선 개선 영역으로 선정했으며, 2025년에는 해당 영역에 대한 개선 조치를 추진할 예정입니다. 고충처리 제도의 운영 절 차 및 연간 처리 실적을 직원에게 안내하여 고충 접수 방법에 대한 이해도를 높이고, 제도의 적극적인 활용을 유도하 는 방법 등을 고려하고 있습니다. 두산퓨얼셀은 2021년 선포한 인권정책선언문을 바탕으로 임직원뿐만 아니라 협력사를 포함한 포괄적 이해관계자들 의 인권을 존중합니다. 회사 내부는 물론 협력사와의 관계에서도 인화의 정신에 위배되는 폭언, 폭력, 성희롱 등 부적 절한 언어나 행동을 용납하지 않으며, 관련 사안은 인권센터 헬프라인, 내부신고센터 등을 통해 신고할 수 있습니다. 인권 침해 발생 시에는 처리 프로세스 및 조치 매뉴얼에 따라 신속하게 조치를 취하고 있으며, 재발방지 및 예방교육 을 지속적으로 시행하여 사업주, 관리자, 구성원 모두가 인권 의식을 높일 수 있도록 노력하고 있습니다. &gt; 인권리스크 완화 조치 두산퓨얼셀은 임직원의 ...
-[p.110] 사회 인권경영 구분 단위 2022 2023 2024 차별 및 괴롭힘 발생 건수 건 2 0 1 임직원 소통 채널을 통해 제기된 불만(고충) 건수 건 - - 1 OECD 다국적 기업용 국가별 연락 창구(NCP)에 접수된 불만 건수 건 - - - 차별 사건 피해로 인한 금전적 손실 원 - - - 인권 교육 시간 시간 1,413 1,265 1,493 참여한 임직원 비율 % 100 98 99 인권검토 또는 인권 영향 평가 인권검토 또는 인권 영향 평가가 시행된 사업장 총 수 개 3 4 4 인권검토 또는 인권 영향 평가가 시행된 사업장 총 비율 % 100 100 100 인권검토 또는 인권 영향 평가가 시행된 협력업체 개 0 0 0 인권검토 또는 인권 영향 평가가 시행된 합작 투자 회사 개 0 0 0 사회공헌 구분 단위 2022 2023 2024 지역사회 참여, 영향 평가 또는 발전 프로그램 운영 사업장 비율 % 100 100 100 사회공헌 비용 지출 백만 원 1,713.0 1,683.8 1,140.6 현금 기부 백만 원 1,076.4 1,643.1 1,120.8 직원 만족도 조사 구분 단위 2022 2023 5) 2024 5) 직원 만족도 1) % 76 - - 직업 만족도 2) 점 68 - - 목적 2) 점 69.7 - - 행복 3) 개 328 - - 스트레스 4) 개 544 - - 데이터 범위 % 75 - - 1) 최고 수준(10점 만점 중 7점 이상)의 만족도를 응답한 직원 비율 2) 전체 응답자 평균점수 3) 인당 3개씩 선택한 ‘최근 일주일 간 가장 많이 경험한 감정’ 키워드 가운데 긍정 키워드 수 4) 인당 3개씩 선택한 ‘최근 일주일 간 가장 많이 경험한 감정’ 키워드 가운데 부정 키워드 수 5) 2023, 2024년도 미시행으로 데이터 공란 고객 만족도 조사 구분 단위 2022 2023 2024 고객 만족도 점수 점 - - 80 고객만족도 실시 목표 업체 수 개 - - 20 고객만족도 실시 업체 수 개 - - 11 고객만족도 실시 고객 수 명 - - 11 리콜 관리 구분 단위 2022 2023 2024 발행된 리콜 수 개 0 0 0 리콜된 제품 수량 개 0 0 0 ESG Data Doosan Fuel Cell Sustainabili ...</x:v>
-      </x:c>
-      <x:c r="D9" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.110] 사회 인권경영 구분 단위 2022 2023 2024 차별 및 괴롭힘 발생 건수 건 2 0 1 임직원 소통 채널을 통해 제기된 불만(고충) 건수 건 - - 1 OECD 다국적 기업용 국가별 연락 창구(NCP)에 접수된 불만 건수 건 - - - 차별 사건 피해로 인한 금전적 손실 원 - - - 인권 교육 시간 시간 1,413 1,265 1,493 참여한 임직원 비율 % 100 98 99 인권검토 또는 인권 영향 평가 인권검토 또는 인권 영향 평가가 시행된 사업장 총 수 개 3 4 4 인권검토 또는 인권 영향 평가가 시행된 사업장 총 비율 % 100 100 100 인권검토 또는 인권 영향 평가가 시행된 협력업체 개 0 0 0 인권검토 또는 인권 영향 평가가 시행된 합작 투자 회사 개 0 0 0 사회공헌 구분 단위 2022 2023 2024 지역사회 참여, 영향 평가 또는 발전 프로그램 운영 사업장 비율 % 100 100 100 사회공헌 비용 지출 백만 원 1,713.0 1,683.8 1,140.6 현금 기부 백만 원 1,076.4 1,643.1 1,120.8 직원 만족도 조사 구분 단위 2022 2023 5) 2024 5) 직원 만족도 1) % 76 - - 직업 만족도 2) 점 68 - - 목적 2) 점 69.7 - - 행복 3) 개 328 - - 스트레스 4) 개 544 - - 데이터 범위 % 75 - - 1) 최고 수준(10점 만점 중 7점 이상)의 만족도를 응답한 직원 비율 2) 전체 응답자 평균점수 3) 인당 3개씩 선택한 ‘최근 일주일 간 가장 많이 경험한 감정’ 키워드 가운데 긍정 키워드 수 4) 인당 3개씩 선택한 ‘최근 일주일 간 가장 많이 경험한 감정’ 키워드 가운데 부정 키워드 수 5) 2023, 2024년도 미시행으로 데이터 공란 고객 만족도 조사 구분 단위 2022 2023 2024 고객 만족도 점수 점 - - 80 고객만족도 실시 목표 업체 수 개 - - 20 고객만족도 실시 업체 수 개 - - 11 고객만족도 실시 고객 수 명 - - 11 리콜 관리 구분 단위 2022 2023 2024 발행된 리콜 수 개 0 0 0 리콜된 제품 수량 개 0 0 0 ESG Data Doosan Fuel Cell Sustainabili ...</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 62;63;64;110
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>Selected Style: narrative
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: narrative
 Preferred Style Source: template
 Answer Type: strategy-policy
 Answer Intent: Explain the policy or strategic direction first, then connect targets, governance, and execution evidence.
@@ -651,34 +828,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: Medium: prose must be natural, evidence-grounded, and non-repetitive.</x:v>
-      </x:c>
-      <x:c r="F9" s="6" t="str">
-        <x:v>인권경영 인권정책 인권이슈 제보 채널 두산퓨얼셀은 홈페이지 내 사이버 신고센터를 통해 임직원을 포함한 모든 이해관계자가 인권 침해 및 기타 비윤리적 행위를 제보할 수 있도록 하고 있으며, 비밀보장 원칙에 따라 비공개 신고도 가능합니다. 두산퓨얼셀은 임직원 뿐 아니라 경영활동에서 관계를 맺고 있는 모든 이해관계자의 인권을 존중하며, 협력업체 등 제3자를 대상으로 동일한 수준의 인권경영을 권고하고 있습니다. 다 만 인권경영체계 구축, 존중과 소통, 공급망 관리에 대한 구성원의 긍정 인식률이 상대적으로 낮게 나타나 이를 우선 개선 영역으로 선정했으며, 2025년에는 해당 영역에 대한 개선 조치를 추진할 예정입니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="6" t="str">
-        <x:v>EBX-Q-009</x:v>
-      </x:c>
-      <x:c r="B10" s="6" t="str">
-        <x:v>사회 / 거버넌스 (Governance) / 노동 및 인권 관리 체계</x:v>
-      </x:c>
-      <x:c r="C10" s="6" t="str">
-        <x:v>[p.63] 인권경영 인권정책 인권이슈 제보 채널 두산퓨얼셀은 홈페이지 내 사이버 신고센터를 통해 임직원을 포함한 모든 이해관계자가 인권 침해 및 기타 비윤리적 행위를 제보할 수 있도록 하고 있으며, 비밀보장 원칙에 따라 비공개 신고도 가능합니다. 접수된 제보는 철저히 보호되며, 내부 절차에 따라 신속히 처리됩니다. 또한 인권 관련 문제가 발생한 경우, 피해자 또는 목격자는 내부 신고센터, 직장 내 괴롭힘·성희롱 예방센터, 인권센터 등을 통해 신고할 수 있습니다. 두산퓨얼셀은 임직원 뿐 아니라 경영활동에서 관계를 맺고 있는 모든 이해관계자의 인권을 존중하며, 협력업체 등 제3자를 대상으로 동일한 수준의 인권경영을 권고하고 있습니다. 두산퓨얼셀은 협력사 및 주요 비즈니스 파트너에게 인권보호에 대한 의무이행을 요구하며, 준수 여부를 모니터링 합니다. 두산퓨얼셀은 인권, 노동, 환경과 반부패에 관한 글로벌콤팩트 10대 원칙에 대한 CEO의 지지선언과 함께, ‘세계인권선언(Universal Declaration of Human Rights )’과 ‘유엔 기업과 인권 이행원칙(UN Guiding Principles on Business and Human Rights; Ruggie Framework)’ 등 국제적으로 인정받고 있는 인권원칙을 바탕으로 인권경영 실천 및 실사체계(Due Diligence)를 수립하여 운영하고 있습니다. 고용상의 비차별과 결사 및 단체교섭의 자유 보장 고용과 관련하여 성별, 종교, 장애, 나이, 사회적 신분, 출신 지역 등을 이유로 일체의 부당한 차별을 하지 않으며, 다양성을 포용합니다. 더불어 근로자들의 결사의 자유와 단체 교섭의 자유를 인정하고 노동조합 활동을 이유로 어떠한 불이익도 주지 않습니다. 강제노동 및 아동노동의 금지 사업활동에서 발생할 수 있는 어떠한 형태의 강제노동도 인정하지 않으며 사업 국가가 정한 최소 고용 연령을 준수합니다. 사업 국가의 법규에서 정한 최소고용연령을 준수하고 연소자를 고용한 것을 알게 된 경우, 즉시 구제 조치를 취하는 등 인간 존엄성에 해를 끼치는 모든 잘못된 노동관행을 방지하겠습니다. 산업안전보장 및 책임 있는 공급망 관리 작업환경을 안전하게 유지하며 사업장에 적용되는 환경, 보건 및 안전 ...
+QA Severity: Medium: prose must be natural, evidence-grounded, and non-repetitive.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 인권경영 정책 및 목표를 중장기 방향과 실행 과제에 연결해 지속가능경영의 방향성을 제시하고 있습니다. 두산퓨얼셀은 임직원뿐 아니라 경영활동에서 관계를 맺고 있는 모든 이해관계자의 인권을 존중하며, 협력업체 등 제3자를 대상으로 동일한 수준의 인권경영을 권고하고 있습니다. 두산퓨얼셀은 협력사 및 주요 비즈니스 파트너에게 인권보호에 대한 의무이행을 요구하며, 준수 여부를 모니터링 합니다. 이러한 내용은 인권경영 정책 및 목표가 선언에 머물지 않고 목표, 조직, 실행 과제로 이어지는 구조임을 보여줍니다. 공개 내용은 인권경영 정책 및 목표가 회사의 전략 방향, 실행 조직, 성과 관리와 연결되어 있음을 보여줍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-009</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 거버넌스 (Governance) / 노동 및 인권 관리 체계</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>[p.63] 인권경영 인권정책 인권이슈 제보 채널 두산퓨얼셀은 홈페이지 내 사이버 신고센터를 통해 임직원을 포함한 모든 이해관계자가 인권 침해 및 기타 비윤리적 행위를 제보할 수 있도록 하고 있으며, 비밀보장 원칙에 따라 비공개 신고도 가능합니다. 접수된 제보는 철저히 보호되며, 내부 절차에 따라 신속히 처리됩니다. 또한 인권 관련 문제가 발생한 경우, 피해자 또는 목격자는 내부 신고센터, 직장 내 괴롭힘·성희롱 예방센터, 인권센터 등을 통해 신고할 수 있습니다. 두산퓨얼셀은 임직원 뿐 아니라 경영활동에서 관계를 맺고 있는 모든 이해관계자의 인권을 존중하며, 협력업체 등 제3자를 대상으로 동일한 수준의 인권경영을 권고하고 있습니다. 두산퓨얼셀은 협력사 및 주요 비즈니스 파트너에게 인권보호에 대한 의무이행을 요구하며, 준수 여부를 모니터링 합니다. 두산퓨얼셀은 인권, 노동, 환경과 반부패에 관한 글로벌콤팩트 10대 원칙에 대한 CEO의 지지선언과 함께, ‘세계인권선언(Universal Declaration of Human Rights )’과 ‘유엔 기업과 인권 이행원칙(UN Guiding Principles on Business and Human Rights; Ruggie Framework)’ 등 국제적으로 인정받고 있는 인권원칙을 바탕으로 인권경영 실천 및 실사체계(Due Diligence)를 수립하여 운영하고 있습니다. 고용상의 비차별과 결사 및 단체교섭의 자유 보장 고용과 관련하여 성별, 종교, 장애, 나이, 사회적 신분, 출신 지역 등을 이유로 일체의 부당한 차별을 하지 않으며, 다양성을 포용합니다. 더불어 근로자들의 결사의 자유와 단체 교섭의 자유를 인정하고 노동조합 활동을 이유로 어떠한 불이익도 주지 않습니다. 강제노동 및 아동노동의 금지 사업활동에서 발생할 수 있는 어떠한 형태의 강제노동도 인정하지 않으며 사업 국가가 정한 최소 고용 연령을 준수합니다. 사업 국가의 법규에서 정한 최소고용연령을 준수하고 연소자를 고용한 것을 알게 된 경우, 즉시 구제 조치를 취하는 등 인간 존엄성에 해를 끼치는 모든 잘못된 노동관행을 방지하겠습니다. 산업안전보장 및 책임 있는 공급망 관리 작업환경을 안전하게 유지하며 사업장에 적용되는 환경, 보건 및 안전 ...
 [p.64] 고용상의 비차별 인권영향평가 프로세스 1) 평가기준 국가인권위원회 인권경영가이드라인 및 򻹧리스트 򻹧리스트 구성 10개 분야 25개 문항 인권경영체계 구축 강제노동의 금지 환경권 보장 산업안전 보장 소비자 인권 보호 결사/단체 교섭 자유보장 책임있는 공급망 관리 존중과 소통 (현지 주민의 인권 보호 제외) 세부 진행절차 01 인권평가 추진계획 수립 02 인권평가 실시 03 인권평가 결과 분석 04 인권리스크 완화 계획 수립 -  인권평가 항목 벤치마킹 (그룹 내 자회자 중심) -  평가대상 확정 -  평가방법 및 절차 수립 - MS Forms 활용 - 주요 인권리스크 확인 -  고위험 대상 인권실사 인터뷰 실시 -  현황 분석 및 리스크 저감 계획 수립 1) 사내 협력사 임직원 포함 인권경영 인권영향평가 인권리스크 완화 계획 &gt; 인권 존중두산퓨얼셀은 인권 이슈로 인한 부정적 영향, 주요 취약 영역을 규명하기 위해 인권영향평가를 시행하고 있습니다. 2024년에 실시한 인권영향평가에는 전체 임직원의 50%가 참여했으며, 중대한 인권 이슈는 발견되지 않았습니다. 다 만 인권경영체계 구축, 존중과 소통, 공급망 관리에 대한 구성원의 긍정 인식률이 상대적으로 낮게 나타나 이를 우선 개선 영역으로 선정했으며, 2025년에는 해당 영역에 대한 개선 조치를 추진할 예정입니다. 고충처리 제도의 운영 절 차 및 연간 처리 실적을 직원에게 안내하여 고충 접수 방법에 대한 이해도를 높이고, 제도의 적극적인 활용을 유도하 는 방법 등을 고려하고 있습니다. 두산퓨얼셀은 2021년 선포한 인권정책선언문을 바탕으로 임직원뿐만 아니라 협력사를 포함한 포괄적 이해관계자들 의 인권을 존중합니다. 회사 내부는 물론 협력사와의 관계에서도 인화의 정신에 위배되는 폭언, 폭력, 성희롱 등 부적 절한 언어나 행동을 용납하지 않으며, 관련 사안은 인권센터 헬프라인, 내부신고센터 등을 통해 신고할 수 있습니다. 인권 침해 발생 시에는 처리 프로세스 및 조치 매뉴얼에 따라 신속하게 조치를 취하고 있으며, 재발방지 및 예방교육 을 지속적으로 시행하여 사업주, 관리자, 구성원 모두가 인권 의식을 높일 수 있도록 노력하고 있습니다. &gt; 인권리스크 완화 조치 두산퓨얼셀은 임직원의 ...
 [p.74] 공급망 ESG 관리 두산퓨얼셀은 신규 협력업체와 계약 시, 윤리경영 실천 서약서와 협력사 ESG 가이드라인 준수 서약을 받고 있습니다. 협력사 ESG 가이드라인(GSSC: Guideline for Sustainable Supply Chains) &gt; 1. 개요 &gt; 2. 노동 및 인권 1.1 목적: 두산퓨얼셀은 윤리적이며 지속가능한 공급망을 구축하기 위해 협력사 가이드라인 GSSC(Guideline for Sustainable Supply Chains, 이하 "가이드라인")을 제정하였습니다. 가이드라인은 두산퓨얼셀에 제품 및 서비스를 공급하는 협력회사들이 지켜야 하는 노동 및 인권, 안전 및 보건, 환경, 윤리 및 공정거래에 대한 요건을 정의하고 있으며, 협력회사는 최소한 해당 협력회사의 1차 공급망에 본 가이드라인의 준수와 실행할 것을 요청해야 합니다. 본 가이드라인은 Responsible Business Alliance(RBA) 행동규범에 기반을 두고 있으며, 국제노동기구 선언(ILO Declaration on Fundamental Principles and Rights at Work), UN 세계인권선언(UN Universal Declaration of Human Rights)을 비롯한 국제적으로 인정되는 기관에서 제정한 글로벌 표준 및 가이드라인은 추가 정보로 활용될 수 있습니다. 본 가이드라인은 협력사가 이행해야 할 사항을 모두 명시한 것은 아니며, 가이드라인은 정기적으로 검토하여 보완 및 개정될 수 있습니다. 1.2 대상: 두산퓨얼셀에 재화와 용역을 제공하거나, 기타 거래를 위해 계약을 체결한 모든 협력사는 본 행동규범을 준수해야 합니다. 본 행동규범의 적용 대상인 모든 협력사는 거래업체(하위 협력사) 등 공급망 전반이 본 행동규범에서 제시하는 사항을 준수하도록 권고해야 합니다. 1.3 협력사 책임과 역할: 두산퓨얼셀의 모든 협력사는 경영의사결정 및 사업 운영 과정에 있어 본 행동강령이 제시하는 사항을 고려해야 합니다. 두산퓨얼셀 및 두산퓨얼셀의 위탁을 받은 제3자 기관은 협력사가 본 행동규범이 제시하는 사항을 준수하고 있는지 법이 허용하는 범위 내에서 점검 및 실사할 수 있습니다. 본 행동규범 준수에 대한 점검 및 실사 결과를 ...
-[p.110] 사회 인권경영 구분 단위 2022 2023 2024 차별 및 괴롭힘 발생 건수 건 2 0 1 임직원 소통 채널을 통해 제기된 불만(고충) 건수 건 - - 1 OECD 다국적 기업용 국가별 연락 창구(NCP)에 접수된 불만 건수 건 - - - 차별 사건 피해로 인한 금전적 손실 원 - - - 인권 교육 시간 시간 1,413 1,265 1,493 참여한 임직원 비율 % 100 98 99 인권검토 또는 인권 영향 평가 인권검토 또는 인권 영향 평가가 시행된 사업장 총 수 개 3 4 4 인권검토 또는 인권 영향 평가가 시행된 사업장 총 비율 % 100 100 100 인권검토 또는 인권 영향 평가가 시행된 협력업체 개 0 0 0 인권검토 또는 인권 영향 평가가 시행된 합작 투자 회사 개 0 0 0 사회공헌 구분 단위 2022 2023 2024 지역사회 참여, 영향 평가 또는 발전 프로그램 운영 사업장 비율 % 100 100 100 사회공헌 비용 지출 백만 원 1,713.0 1,683.8 1,140.6 현금 기부 백만 원 1,076.4 1,643.1 1,120.8 직원 만족도 조사 구분 단위 2022 2023 5) 2024 5) 직원 만족도 1) % 76 - - 직업 만족도 2) 점 68 - - 목적 2) 점 69.7 - - 행복 3) 개 328 - - 스트레스 4) 개 544 - - 데이터 범위 % 75 - - 1) 최고 수준(10점 만점 중 7점 이상)의 만족도를 응답한 직원 비율 2) 전체 응답자 평균점수 3) 인당 3개씩 선택한 ‘최근 일주일 간 가장 많이 경험한 감정’ 키워드 가운데 긍정 키워드 수 4) 인당 3개씩 선택한 ‘최근 일주일 간 가장 많이 경험한 감정’ 키워드 가운데 부정 키워드 수 5) 2023, 2024년도 미시행으로 데이터 공란 고객 만족도 조사 구분 단위 2022 2023 2024 고객 만족도 점수 점 - - 80 고객만족도 실시 목표 업체 수 개 - - 20 고객만족도 실시 업체 수 개 - - 11 고객만족도 실시 고객 수 명 - - 11 리콜 관리 구분 단위 2022 2023 2024 발행된 리콜 수 개 0 0 0 리콜된 제품 수량 개 0 0 0 ESG Data Doosan Fuel Cell Sustainabili ...</x:v>
-      </x:c>
-      <x:c r="D10" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.110] 사회 인권경영 구분 단위 2022 2023 2024 차별 및 괴롭힘 발생 건수 건 2 0 1 임직원 소통 채널을 통해 제기된 불만(고충) 건수 건 - - 1 OECD 다국적 기업용 국가별 연락 창구(NCP)에 접수된 불만 건수 건 - - - 차별 사건 피해로 인한 금전적 손실 원 - - - 인권 교육 시간 시간 1,413 1,265 1,493 참여한 임직원 비율 % 100 98 99 인권검토 또는 인권 영향 평가 인권검토 또는 인권 영향 평가가 시행된 사업장 총 수 개 3 4 4 인권검토 또는 인권 영향 평가가 시행된 사업장 총 비율 % 100 100 100 인권검토 또는 인권 영향 평가가 시행된 협력업체 개 0 0 0 인권검토 또는 인권 영향 평가가 시행된 합작 투자 회사 개 0 0 0 사회공헌 구분 단위 2022 2023 2024 지역사회 참여, 영향 평가 또는 발전 프로그램 운영 사업장 비율 % 100 100 100 사회공헌 비용 지출 백만 원 1,713.0 1,683.8 1,140.6 현금 기부 백만 원 1,076.4 1,643.1 1,120.8 직원 만족도 조사 구분 단위 2022 2023 5) 2024 5) 직원 만족도 1) % 76 - - 직업 만족도 2) 점 68 - - 목적 2) 점 69.7 - - 행복 3) 개 328 - - 스트레스 4) 개 544 - - 데이터 범위 % 75 - - 1) 최고 수준(10점 만점 중 7점 이상)의 만족도를 응답한 직원 비율 2) 전체 응답자 평균점수 3) 인당 3개씩 선택한 ‘최근 일주일 간 가장 많이 경험한 감정’ 키워드 가운데 긍정 키워드 수 4) 인당 3개씩 선택한 ‘최근 일주일 간 가장 많이 경험한 감정’ 키워드 가운데 부정 키워드 수 5) 2023, 2024년도 미시행으로 데이터 공란 고객 만족도 조사 구분 단위 2022 2023 2024 고객 만족도 점수 점 - - 80 고객만족도 실시 목표 업체 수 개 - - 20 고객만족도 실시 업체 수 개 - - 11 고객만족도 실시 고객 수 명 - - 11 리콜 관리 구분 단위 2022 2023 2024 발행된 리콜 수 개 0 0 0 리콜된 제품 수량 개 0 0 0 ESG Data Doosan Fuel Cell Sustainabili ...</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 63;64;74;110
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>Selected Style: governance
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: governance
 Preferred Style Source: template
 Answer Type: governance-organization
 Answer Intent: Explain who is responsible, what they decide or oversee, and how reporting or escalation works.
@@ -697,34 +886,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: Medium: responsibility and decision flow must be clear.</x:v>
-      </x:c>
-      <x:c r="F10" s="6" t="str">
-        <x:v>두산퓨얼셀는 노동 및 인권 관리 체계와 관련해 책임 주체와 의사결정 흐름을 중심으로 관리 체계를 설명하고 있습니다. 두산퓨얼셀은 2021년 선포한 인권정책선언문을 바탕으로 임직원뿐만 아니라 협력사를 포함한 포괄적 이해관계자들 의 인권을 존중합니다. 노동 및 인권 1.1 목적: 두산퓨얼셀은 윤리적이며 지속가능한 공급망을 구축하기 위해 협력사 가이드라인 GSSC(Guideline for Sustainable Supply Chains, 이하 "가이드라인")을 제정하였습니다. 이 구조는 노동 및 인권 관리 체계의 담당 조직, 보고 경로, 감독 역할을 한 문맥에서 확인할 수 있게 합니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="6" t="str">
-        <x:v>EBX-Q-010</x:v>
-      </x:c>
-      <x:c r="B11" s="6" t="str">
-        <x:v>사회 / 위험 관리 (Risk Management) / 인권 리스크 식별 및 대응 활동</x:v>
-      </x:c>
-      <x:c r="C11" s="6" t="str">
-        <x:v>[p.18] ESG 목표 및 성과 Our Goal &amp; Performance 목표 세부 과제 2024년 성과 2025년 계획 친환경 경쟁력 강화 사업장 온실가스 감축 •  익산(PAFC) 공장 및 군산(SOFC) 공장 온실가스 배출량 416.93t 감축 •  익산PAFC 공장 전극 공정 에너지 절감 및 온실가스 배출 저감 활동 실시 •  익산PAFC 공장 제품 생산 원단위 온실가스 배출량 감축 중장기 로드맵 수립 • CCUS 연계형 모델 현장 Set-up 및 실증 완료 •  PAFC 모델 효율 제고 활동 지속 탄소중립 기여 제품/기술 확대 •  수소모델(5CSA PAFC 수소모델) 시제품  KESCO 인증 완료, 양산 시작 •  CCUS(Carbon Capture, Utilization and Storage, 탄소 포집, 활용 및 저장)연계형 모델 개발 및 시운전 완료 •  PAFC 모델 효율 제고 활동 진행 제품 전과정 환경 영향 최소화 •  Non-RCF(Refractory Ceramic Fibers, 내화성세라믹섬유) 부품 설계 진행 •  금속분리판 시제품 도면 설계 •  CSA(Cell Stack Assembly) 재사용/재제조  프로세스 구축 및 실행 •  Resin 재사용으로 자원 순환 활성화 •  Non-RCF 부품 개발 완료 •  금속분리판 시제품 제작 및 안정성 평가 •  CSA 재사용/재제조 수량 확대를 통한 폐기물 감축 •  Resin 재사용 지속 실행 및 사용량 감축 •  전극 비파괴 검사 방법 개발 및 적용으로 폐기물 감축 비재무 리스크 관리 확대 공급망 ESG 관리 확대 •  외부 전문기관 통해 공급망 ESG 평가 진행 •  평가 결과 바탕으로 개선 가이드 제공 •  협력사 대상 ESG 교육 및 평가 결과 제공 •  협력사 On-line 소통채널 구축 및 협력사 총회 /간담회 개최 •  주요 공급망 ESG 평가 진행 •  공급망 ESG 관리 절차서 제정하여 재계약 시 ESG 평가 결과 반영 •  협력사 경영 지원 활동 및 ESG 개선 지원  활동 시행 기후변화 리스크 정보 공개 •  IFRS 지속가능성 보고기준(ISSB)에 따라 기후 변화와 관련된 두산퓨얼셀의 거버넌스, 전략, ...
+QA Severity: Medium: responsibility and decision flow must be clear.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 노동 및 인권 관리 체계와 관련해 책임 주체와 의사결정 흐름을 중심으로 관리 체계를 설명하고 있습니다. 두산퓨얼셀은 협력사 및 주요 비즈니스 파트너에게 인권보호에 대한 의무이행을 요구하며, 준수 여부를 모니터링 합니다. 이 구조는 노동 및 인권 관리 체계의 담당 조직, 보고 경로, 감독 역할을 한 문맥에서 확인할 수 있게 합니다. 공개 내용은 노동 및 인권 관리 체계의 책임 배분과 감독 수준을 함께 보여주며, 의사결정 체계가 실제 운영 구조와 어떻게 연결되는지 파악하는 데 도움이 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-010</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 위험 관리 (Risk Management) / 인권 리스크 식별 및 대응 활동</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>[p.18] ESG 목표 및 성과 Our Goal &amp; Performance 목표 세부 과제 2024년 성과 2025년 계획 친환경 경쟁력 강화 사업장 온실가스 감축 •  익산(PAFC) 공장 및 군산(SOFC) 공장 온실가스 배출량 416.93t 감축 •  익산PAFC 공장 전극 공정 에너지 절감 및 온실가스 배출 저감 활동 실시 •  익산PAFC 공장 제품 생산 원단위 온실가스 배출량 감축 중장기 로드맵 수립 • CCUS 연계형 모델 현장 Set-up 및 실증 완료 •  PAFC 모델 효율 제고 활동 지속 탄소중립 기여 제품/기술 확대 •  수소모델(5CSA PAFC 수소모델) 시제품  KESCO 인증 완료, 양산 시작 •  CCUS(Carbon Capture, Utilization and Storage, 탄소 포집, 활용 및 저장)연계형 모델 개발 및 시운전 완료 •  PAFC 모델 효율 제고 활동 진행 제품 전과정 환경 영향 최소화 •  Non-RCF(Refractory Ceramic Fibers, 내화성세라믹섬유) 부품 설계 진행 •  금속분리판 시제품 도면 설계 •  CSA(Cell Stack Assembly) 재사용/재제조  프로세스 구축 및 실행 •  Resin 재사용으로 자원 순환 활성화 •  Non-RCF 부품 개발 완료 •  금속분리판 시제품 제작 및 안정성 평가 •  CSA 재사용/재제조 수량 확대를 통한 폐기물 감축 •  Resin 재사용 지속 실행 및 사용량 감축 •  전극 비파괴 검사 방법 개발 및 적용으로 폐기물 감축 비재무 리스크 관리 확대 공급망 ESG 관리 확대 •  외부 전문기관 통해 공급망 ESG 평가 진행 •  평가 결과 바탕으로 개선 가이드 제공 •  협력사 대상 ESG 교육 및 평가 결과 제공 •  협력사 On-line 소통채널 구축 및 협력사 총회 /간담회 개최 •  주요 공급망 ESG 평가 진행 •  공급망 ESG 관리 절차서 제정하여 재계약 시 ESG 평가 결과 반영 •  협력사 경영 지원 활동 및 ESG 개선 지원  활동 시행 기후변화 리스크 정보 공개 •  IFRS 지속가능성 보고기준(ISSB)에 따라 기후 변화와 관련된 두산퓨얼셀의 거버넌스, 전략, ...
 [p.63] 인권경영 인권정책 인권이슈 제보 채널 두산퓨얼셀은 홈페이지 내 사이버 신고센터를 통해 임직원을 포함한 모든 이해관계자가 인권 침해 및 기타 비윤리적 행위를 제보할 수 있도록 하고 있으며, 비밀보장 원칙에 따라 비공개 신고도 가능합니다. 접수된 제보는 철저히 보호되며, 내부 절차에 따라 신속히 처리됩니다. 또한 인권 관련 문제가 발생한 경우, 피해자 또는 목격자는 내부 신고센터, 직장 내 괴롭힘·성희롱 예방센터, 인권센터 등을 통해 신고할 수 있습니다. 두산퓨얼셀은 임직원 뿐 아니라 경영활동에서 관계를 맺고 있는 모든 이해관계자의 인권을 존중하며, 협력업체 등 제3자를 대상으로 동일한 수준의 인권경영을 권고하고 있습니다. 두산퓨얼셀은 협력사 및 주요 비즈니스 파트너에게 인권보호에 대한 의무이행을 요구하며, 준수 여부를 모니터링 합니다. 두산퓨얼셀은 인권, 노동, 환경과 반부패에 관한 글로벌콤팩트 10대 원칙에 대한 CEO의 지지선언과 함께, ‘세계인권선언(Universal Declaration of Human Rights )’과 ‘유엔 기업과 인권 이행원칙(UN Guiding Principles on Business and Human Rights; Ruggie Framework)’ 등 국제적으로 인정받고 있는 인권원칙을 바탕으로 인권경영 실천 및 실사체계(Due Diligence)를 수립하여 운영하고 있습니다. 고용상의 비차별과 결사 및 단체교섭의 자유 보장 고용과 관련하여 성별, 종교, 장애, 나이, 사회적 신분, 출신 지역 등을 이유로 일체의 부당한 차별을 하지 않으며, 다양성을 포용합니다. 더불어 근로자들의 결사의 자유와 단체 교섭의 자유를 인정하고 노동조합 활동을 이유로 어떠한 불이익도 주지 않습니다. 강제노동 및 아동노동의 금지 사업활동에서 발생할 수 있는 어떠한 형태의 강제노동도 인정하지 않으며 사업 국가가 정한 최소 고용 연령을 준수합니다. 사업 국가의 법규에서 정한 최소고용연령을 준수하고 연소자를 고용한 것을 알게 된 경우, 즉시 구제 조치를 취하는 등 인간 존엄성에 해를 끼치는 모든 잘못된 노동관행을 방지하겠습니다. 산업안전보장 및 책임 있는 공급망 관리 작업환경을 안전하게 유지하며 사업장에 적용되는 환경, 보건 및 안전 ...
 [p.64] 고용상의 비차별 인권영향평가 프로세스 1) 평가기준 국가인권위원회 인권경영가이드라인 및 򻹧리스트 򻹧리스트 구성 10개 분야 25개 문항 인권경영체계 구축 강제노동의 금지 환경권 보장 산업안전 보장 소비자 인권 보호 결사/단체 교섭 자유보장 책임있는 공급망 관리 존중과 소통 (현지 주민의 인권 보호 제외) 세부 진행절차 01 인권평가 추진계획 수립 02 인권평가 실시 03 인권평가 결과 분석 04 인권리스크 완화 계획 수립 -  인권평가 항목 벤치마킹 (그룹 내 자회자 중심) -  평가대상 확정 -  평가방법 및 절차 수립 - MS Forms 활용 - 주요 인권리스크 확인 -  고위험 대상 인권실사 인터뷰 실시 -  현황 분석 및 리스크 저감 계획 수립 1) 사내 협력사 임직원 포함 인권경영 인권영향평가 인권리스크 완화 계획 &gt; 인권 존중두산퓨얼셀은 인권 이슈로 인한 부정적 영향, 주요 취약 영역을 규명하기 위해 인권영향평가를 시행하고 있습니다. 2024년에 실시한 인권영향평가에는 전체 임직원의 50%가 참여했으며, 중대한 인권 이슈는 발견되지 않았습니다. 다 만 인권경영체계 구축, 존중과 소통, 공급망 관리에 대한 구성원의 긍정 인식률이 상대적으로 낮게 나타나 이를 우선 개선 영역으로 선정했으며, 2025년에는 해당 영역에 대한 개선 조치를 추진할 예정입니다. 고충처리 제도의 운영 절 차 및 연간 처리 실적을 직원에게 안내하여 고충 접수 방법에 대한 이해도를 높이고, 제도의 적극적인 활용을 유도하 는 방법 등을 고려하고 있습니다. 두산퓨얼셀은 2021년 선포한 인권정책선언문을 바탕으로 임직원뿐만 아니라 협력사를 포함한 포괄적 이해관계자들 의 인권을 존중합니다. 회사 내부는 물론 협력사와의 관계에서도 인화의 정신에 위배되는 폭언, 폭력, 성희롱 등 부적 절한 언어나 행동을 용납하지 않으며, 관련 사안은 인권센터 헬프라인, 내부신고센터 등을 통해 신고할 수 있습니다. 인권 침해 발생 시에는 처리 프로세스 및 조치 매뉴얼에 따라 신속하게 조치를 취하고 있으며, 재발방지 및 예방교육 을 지속적으로 시행하여 사업주, 관리자, 구성원 모두가 인권 의식을 높일 수 있도록 노력하고 있습니다. &gt; 인권리스크 완화 조치 두산퓨얼셀은 임직원의 ...
-[p.78] 공급망 ESG 관리 두산퓨얼셀은 공급망의 지속가능성을 평가하기 위해 ESG 진단 전문기관을 선정하여 협력사 ESG 리스크 자가진단 및 실사진단을 진행하고 있습니다. 또한 협력사에 현장방문하여 자가진단 내용을 검증하고, ESG 개선 활동을 지원하는 프로세스를 운영하고 있습니다. 공급망 리스크 관리 평가 및 후속 조치 두산퓨얼셀은 2023년부터 공급망 ESG 관리체계를 구축하고 협력사에 대한 평가를 진행하고 있습니다. 부품 구매 비중, 중요 부품 여부, 대체 가능성, 전문성과 핵심 기술 보유 여부, 조달 기간, 국가 및 지역 리스크, 조직 및 인원 규모 등을 기준으로 협력사를 ‘Critical’, ‘Bottle Neck’, ‘Leverage’, ‘Routine’의 네 가지 유형으로 분류했습니다. 또한 공급망 리스크 진단 전문기관과 협업하여 2024년6월부터 9월까지 전체 1차 부품 협력사(총 34개사)를 대상으로 진단을 실시했으며, 이 중 Critical 및 Leverage 유형의 협력사에 대해서는 독립된 제3자의 현장 실사를 통해 제출 자료의 타당성을 검증하고, One-point Consulting을 통해 개선 방향을 제시하고 있습니다. 최종 평가 결과는 협력사에 결과보고서 및 개선 가이드 형태로 제공하며, 두산퓨얼셀 CEO가 주관하는 ESG 위원회에도 보고하여 지속적으로 관리할 예정입니다. 공급망 ESG 현장 실사 공급망 리스크 평가 이니셔티브 및 방법론 두산퓨얼셀의 공급망 ESG 리스크 평가는 전문성을 갖춘 제3의 기관인 한국평가데이터(KoDATA)을 통해 진행되고 있습니다. 한국평가데이터는 공급업체의 ESG 운영, 정책, 시스템 및 성과를 평가하기 위하여 전문 Auditor를 파견하여 공급업체 현장을 방문하고, 문서 및 기록 검토, 현장 견학은 물론 회사 대표 직원 및 기타 이해관계자와의 인터뷰를 진행합니다. 평가 방법론은 한국평가데이터의 자체 체크리스트로 구성되어 있으며, 자체 체크리스트는 해당 국가의 법률, ISO 14001/26000/37001/45001 등의 국제 표준, RBA 등 인정된 업계 또는 산업 이니셔티브의 방법론 등으로 구성되었습니다. 두산퓨얼셀은 2023년부터 협력사의 ESG 수준 향상을 지원하기 위한 프로그램을 ...</x:v>
-      </x:c>
-      <x:c r="D11" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.78] 공급망 ESG 관리 두산퓨얼셀은 공급망의 지속가능성을 평가하기 위해 ESG 진단 전문기관을 선정하여 협력사 ESG 리스크 자가진단 및 실사진단을 진행하고 있습니다. 또한 협력사에 현장방문하여 자가진단 내용을 검증하고, ESG 개선 활동을 지원하는 프로세스를 운영하고 있습니다. 공급망 리스크 관리 평가 및 후속 조치 두산퓨얼셀은 2023년부터 공급망 ESG 관리체계를 구축하고 협력사에 대한 평가를 진행하고 있습니다. 부품 구매 비중, 중요 부품 여부, 대체 가능성, 전문성과 핵심 기술 보유 여부, 조달 기간, 국가 및 지역 리스크, 조직 및 인원 규모 등을 기준으로 협력사를 ‘Critical’, ‘Bottle Neck’, ‘Leverage’, ‘Routine’의 네 가지 유형으로 분류했습니다. 또한 공급망 리스크 진단 전문기관과 협업하여 2024년6월부터 9월까지 전체 1차 부품 협력사(총 34개사)를 대상으로 진단을 실시했으며, 이 중 Critical 및 Leverage 유형의 협력사에 대해서는 독립된 제3자의 현장 실사를 통해 제출 자료의 타당성을 검증하고, One-point Consulting을 통해 개선 방향을 제시하고 있습니다. 최종 평가 결과는 협력사에 결과보고서 및 개선 가이드 형태로 제공하며, 두산퓨얼셀 CEO가 주관하는 ESG 위원회에도 보고하여 지속적으로 관리할 예정입니다. 공급망 ESG 현장 실사 공급망 리스크 평가 이니셔티브 및 방법론 두산퓨얼셀의 공급망 ESG 리스크 평가는 전문성을 갖춘 제3의 기관인 한국평가데이터(KoDATA)을 통해 진행되고 있습니다. 한국평가데이터는 공급업체의 ESG 운영, 정책, 시스템 및 성과를 평가하기 위하여 전문 Auditor를 파견하여 공급업체 현장을 방문하고, 문서 및 기록 검토, 현장 견학은 물론 회사 대표 직원 및 기타 이해관계자와의 인터뷰를 진행합니다. 평가 방법론은 한국평가데이터의 자체 체크리스트로 구성되어 있으며, 자체 체크리스트는 해당 국가의 법률, ISO 14001/26000/37001/45001 등의 국제 표준, RBA 등 인정된 업계 또는 산업 이니셔티브의 방법론 등으로 구성되었습니다. 두산퓨얼셀은 2023년부터 협력사의 ESG 수준 향상을 지원하기 위한 프로그램을 ...</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 18;63;64;78
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>Selected Style: risk-control
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: risk-control
 Preferred Style Source: template
 Answer Type: risk-control
 Answer Intent: Explain the risk/control scope, then prevention, monitoring, and follow-up actions.
@@ -743,34 +944,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: High: must include risk/control and monitoring evidence.</x:v>
-      </x:c>
-      <x:c r="F11" s="6" t="str">
-        <x:v>두산퓨얼셀는 인권리스크 식별 및 대응 활동에서 식별된 위험 요인과 예방 활동을 연결해 관리 수준을 점검하고 있습니다. 두산퓨얼셀은 2021년 선포한 인권정책선언문을 바탕으로 임직원뿐만 아니라 협력사를 포함한 포괄적 이해관계자들 의 인권을 존중합니다. 공급망 리스크 관리 평가 및 후속 조치 두산퓨얼셀은 2023년부터 공급망 ESG 관리체계를 구축하고 협력사에 대한 평가를 진행하고 있습니다. 따라서 인권리스크 식별 및 대응 활동 관련 공시는 단순한 선언보다 예방, 모니터링, 후속 조치의 연결성을 중심으로 해석할 수 있습니다. 공개 내용은 인권리스크 식별 및 대응 활동의 예방 활동이 일회성 조치가 아니라 운영 과정 안에서 관리되고 있음을 보여줍니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="6" t="str">
-        <x:v>EBX-Q-011</x:v>
-      </x:c>
-      <x:c r="B12" s="6" t="str">
-        <x:v>사회 / 지표 (Metrics) / 인권 관련 고충 및 처리 현황</x:v>
-      </x:c>
-      <x:c r="C12" s="6" t="str">
-        <x:v>[p.62] 인권경영 차별 및 괴롭힘 방지 지침 직장 내 성희롱, 괴롭힘 및 차별 금지 직장 내 성희롱 금지 |  사업주, 관리자 또는 구성원이 직장 내의 지위를 이용하거나 업무 수행과 관련하여 다른 구성원에게 성적인 언동 등으로 성적 굴욕감 또는 혐오감을 느끼게 해서는 안됩니다. 또한 이러한 성적인 언동이나 그 밖의 요구에 따르지 아니하였다는 이유로 근로조건 및 고용에서 불이익을 주는 행위를 해서는 안됩니다. 직장 내 괴롭힘 금지 |  회사 내에서의 지위 또는 관계 등의 우위를 이용하여 업무상 적정 범위를 넘어 다른 구성원에게 신체적, 정신적 고통을 주거나 근무환경을 악화시키는 행위를 해서는 안됩니다. 직장 내 괴롭힘의 행위는 신체적 괴롭힘과 신분적, 업무적, 언어적, 개인적 괴롭힘 및 근무환경의 악화를 포함합니다. 차별 금지 |  임직원의 성별, 인종, 민족, 국적, 종교, 나이, 정치적 견해, 출신 지역에 따라 차별적인 대우를 해서는 안됩니다. 발생 시 조치 신고접수(두산퓨얼셀 인권센터 및 두산그룹 내외부 신고센터) |  직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 알게 된 경우 누구라도 그 내용을 신고할 수 있으며, 신고 접수 시에는 조사 의뢰 등 적절한 방안을 강구하게 됩니다. 조사 및 심의(조사 담당 부서) |  사실 관계 파악을 위해 성희롱, 괴롭힘, 차별 등의 여부를 확인하며, 조사 관련자의 신원에 대해서는 비밀을 유지합니다. 이때, 해결 방식에 대해 피해자의 의견을 청취하고 피해자의 요청이 있을 경우 근무장소의 변경, 휴가의 명령 등 적절한 조치를 취합니다. 조치(인사위원회 주관 부서) |  행위에 의한 피해사실이 확인된 경우에는 지체없이 행위자에 대하여 징계나 그 밖에 이에 준하는 조치를 취합니다. 직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 신고한 직원 또는 피해를 입었거나 피해 발생을 주장하는 직원은 적극적으로 보호합니다. 모니터링(인권센터, HR) |  조치사항의 이행여부와 후속적인 괴롭힘 피해가 없는지 모니터링하며, 피해자에 대한 불리한 처우가 발생하지 않도록 예방합니다. 비밀유지 직장 내 성희롱, 괴롭힘 및 차별 조사 과정에 참여한 임직원은 조사 등으로 알게 된 비밀을 누설하지 않습니다. 재발방지 조치 회 ...
+QA Severity: High: must include risk/control and monitoring evidence.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 인권리스크 식별 및 대응 활동에서 식별된 위험 요인과 예방 활동을 연결해 관리 수준을 점검하고 있습니다. 두산퓨얼셀은 공급망의 지속가능성을 평가하기 위해 ESG 진단 전문기관을 선정하여 협력사 ESG 리스크 자가진단 및 실사진단을 진행하고 있습니다. 인권리스크 식별 및 대응 활동 관련 공시는 단순한 선언보다 예방, 모니터링, 후속 조치의 연결성을 중심으로 해석할 수 있습니다. 공개 내용은 인권리스크 식별 및 대응 활동의 예방 활동이 일회성 조치가 아니라 운영 과정 안에서 관리되고 있음을 보여줍니다. 식별된 위험이 후속 조치와 개선 활동으로 연결되는지 확인할 수 있어 관리 체계의 실행성을 보완합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-011</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 지표 (Metrics) / 인권 관련 고충 및 처리 현황</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>[p.62] 인권경영 차별 및 괴롭힘 방지 지침 직장 내 성희롱, 괴롭힘 및 차별 금지 직장 내 성희롱 금지 |  사업주, 관리자 또는 구성원이 직장 내의 지위를 이용하거나 업무 수행과 관련하여 다른 구성원에게 성적인 언동 등으로 성적 굴욕감 또는 혐오감을 느끼게 해서는 안됩니다. 또한 이러한 성적인 언동이나 그 밖의 요구에 따르지 아니하였다는 이유로 근로조건 및 고용에서 불이익을 주는 행위를 해서는 안됩니다. 직장 내 괴롭힘 금지 |  회사 내에서의 지위 또는 관계 등의 우위를 이용하여 업무상 적정 범위를 넘어 다른 구성원에게 신체적, 정신적 고통을 주거나 근무환경을 악화시키는 행위를 해서는 안됩니다. 직장 내 괴롭힘의 행위는 신체적 괴롭힘과 신분적, 업무적, 언어적, 개인적 괴롭힘 및 근무환경의 악화를 포함합니다. 차별 금지 |  임직원의 성별, 인종, 민족, 국적, 종교, 나이, 정치적 견해, 출신 지역에 따라 차별적인 대우를 해서는 안됩니다. 발생 시 조치 신고접수(두산퓨얼셀 인권센터 및 두산그룹 내외부 신고센터) |  직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 알게 된 경우 누구라도 그 내용을 신고할 수 있으며, 신고 접수 시에는 조사 의뢰 등 적절한 방안을 강구하게 됩니다. 조사 및 심의(조사 담당 부서) |  사실 관계 파악을 위해 성희롱, 괴롭힘, 차별 등의 여부를 확인하며, 조사 관련자의 신원에 대해서는 비밀을 유지합니다. 이때, 해결 방식에 대해 피해자의 의견을 청취하고 피해자의 요청이 있을 경우 근무장소의 변경, 휴가의 명령 등 적절한 조치를 취합니다. 조치(인사위원회 주관 부서) |  행위에 의한 피해사실이 확인된 경우에는 지체없이 행위자에 대하여 징계나 그 밖에 이에 준하는 조치를 취합니다. 직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 신고한 직원 또는 피해를 입었거나 피해 발생을 주장하는 직원은 적극적으로 보호합니다. 모니터링(인권센터, HR) |  조치사항의 이행여부와 후속적인 괴롭힘 피해가 없는지 모니터링하며, 피해자에 대한 불리한 처우가 발생하지 않도록 예방합니다. 비밀유지 직장 내 성희롱, 괴롭힘 및 차별 조사 과정에 참여한 임직원은 조사 등으로 알게 된 비밀을 누설하지 않습니다. 재발방지 조치 회 ...
 [p.63] 인권경영 인권정책 인권이슈 제보 채널 두산퓨얼셀은 홈페이지 내 사이버 신고센터를 통해 임직원을 포함한 모든 이해관계자가 인권 침해 및 기타 비윤리적 행위를 제보할 수 있도록 하고 있으며, 비밀보장 원칙에 따라 비공개 신고도 가능합니다. 접수된 제보는 철저히 보호되며, 내부 절차에 따라 신속히 처리됩니다. 또한 인권 관련 문제가 발생한 경우, 피해자 또는 목격자는 내부 신고센터, 직장 내 괴롭힘·성희롱 예방센터, 인권센터 등을 통해 신고할 수 있습니다. 두산퓨얼셀은 임직원 뿐 아니라 경영활동에서 관계를 맺고 있는 모든 이해관계자의 인권을 존중하며, 협력업체 등 제3자를 대상으로 동일한 수준의 인권경영을 권고하고 있습니다. 두산퓨얼셀은 협력사 및 주요 비즈니스 파트너에게 인권보호에 대한 의무이행을 요구하며, 준수 여부를 모니터링 합니다. 두산퓨얼셀은 인권, 노동, 환경과 반부패에 관한 글로벌콤팩트 10대 원칙에 대한 CEO의 지지선언과 함께, ‘세계인권선언(Universal Declaration of Human Rights )’과 ‘유엔 기업과 인권 이행원칙(UN Guiding Principles on Business and Human Rights; Ruggie Framework)’ 등 국제적으로 인정받고 있는 인권원칙을 바탕으로 인권경영 실천 및 실사체계(Due Diligence)를 수립하여 운영하고 있습니다. 고용상의 비차별과 결사 및 단체교섭의 자유 보장 고용과 관련하여 성별, 종교, 장애, 나이, 사회적 신분, 출신 지역 등을 이유로 일체의 부당한 차별을 하지 않으며, 다양성을 포용합니다. 더불어 근로자들의 결사의 자유와 단체 교섭의 자유를 인정하고 노동조합 활동을 이유로 어떠한 불이익도 주지 않습니다. 강제노동 및 아동노동의 금지 사업활동에서 발생할 수 있는 어떠한 형태의 강제노동도 인정하지 않으며 사업 국가가 정한 최소 고용 연령을 준수합니다. 사업 국가의 법규에서 정한 최소고용연령을 준수하고 연소자를 고용한 것을 알게 된 경우, 즉시 구제 조치를 취하는 등 인간 존엄성에 해를 끼치는 모든 잘못된 노동관행을 방지하겠습니다. 산업안전보장 및 책임 있는 공급망 관리 작업환경을 안전하게 유지하며 사업장에 적용되는 환경, 보건 및 안전 ...
 [p.64] 고용상의 비차별 인권영향평가 프로세스 1) 평가기준 국가인권위원회 인권경영가이드라인 및 򻹧리스트 򻹧리스트 구성 10개 분야 25개 문항 인권경영체계 구축 강제노동의 금지 환경권 보장 산업안전 보장 소비자 인권 보호 결사/단체 교섭 자유보장 책임있는 공급망 관리 존중과 소통 (현지 주민의 인권 보호 제외) 세부 진행절차 01 인권평가 추진계획 수립 02 인권평가 실시 03 인권평가 결과 분석 04 인권리스크 완화 계획 수립 -  인권평가 항목 벤치마킹 (그룹 내 자회자 중심) -  평가대상 확정 -  평가방법 및 절차 수립 - MS Forms 활용 - 주요 인권리스크 확인 -  고위험 대상 인권실사 인터뷰 실시 -  현황 분석 및 리스크 저감 계획 수립 1) 사내 협력사 임직원 포함 인권경영 인권영향평가 인권리스크 완화 계획 &gt; 인권 존중두산퓨얼셀은 인권 이슈로 인한 부정적 영향, 주요 취약 영역을 규명하기 위해 인권영향평가를 시행하고 있습니다. 2024년에 실시한 인권영향평가에는 전체 임직원의 50%가 참여했으며, 중대한 인권 이슈는 발견되지 않았습니다. 다 만 인권경영체계 구축, 존중과 소통, 공급망 관리에 대한 구성원의 긍정 인식률이 상대적으로 낮게 나타나 이를 우선 개선 영역으로 선정했으며, 2025년에는 해당 영역에 대한 개선 조치를 추진할 예정입니다. 고충처리 제도의 운영 절 차 및 연간 처리 실적을 직원에게 안내하여 고충 접수 방법에 대한 이해도를 높이고, 제도의 적극적인 활용을 유도하 는 방법 등을 고려하고 있습니다. 두산퓨얼셀은 2021년 선포한 인권정책선언문을 바탕으로 임직원뿐만 아니라 협력사를 포함한 포괄적 이해관계자들 의 인권을 존중합니다. 회사 내부는 물론 협력사와의 관계에서도 인화의 정신에 위배되는 폭언, 폭력, 성희롱 등 부적 절한 언어나 행동을 용납하지 않으며, 관련 사안은 인권센터 헬프라인, 내부신고센터 등을 통해 신고할 수 있습니다. 인권 침해 발생 시에는 처리 프로세스 및 조치 매뉴얼에 따라 신속하게 조치를 취하고 있으며, 재발방지 및 예방교육 을 지속적으로 시행하여 사업주, 관리자, 구성원 모두가 인권 의식을 높일 수 있도록 노력하고 있습니다. &gt; 인권리스크 완화 조치 두산퓨얼셀은 임직원의 ...
-[p.96] 수집하는 개인정보의 항목 및 수집 방법 1)  고충민원 처리 - 필수항목: 이름, 이메일 주소 2)  서비스 분석 및 서비스 수준 - 서비스 이용기록, 접속로그, 쿠키, 접속IP 정보 3)  채용 전형/결정 - 일반정보: 성명(국문/한자/영문), 생년월일, 성별, 사진, 비밀번호 등 - 민감정보: 장애여부 및 장애구분/장애등급 개인정보의 제3자 제공 정보주체로부터 별도의 동의를 받는 경우 - 법률에 특별한 규정이 있거나 법령상 의무를 준수하기 위하여 불가피한 경우 -  정보주체 또는 그 법정대리인이 의사표시를 할 수 없는 상태에 있거나 주소불명 등으로 사전 동의를 받을 수 없는 경우 개인정보의 수집 이용 목적 1)  고객 관련 -  서비스 분석 및 서비스 수준 제고: 서비스 이용분석을 통해 이용자에게 더 나은 서비스를 제 공하고 본 사이트의 수준 향상(서비스 분석 및 서비스 수준 제고) 등 - 고충·민원 처리: 민원사항 확인, 사실조사를 위한 연락·통지, 처리결과 통보 등 2)  채용 관련 -  채용 전형/결정: 본인 식별 및 실명 확인, 입사 전형 및 지원자와의 연락, 국가유공자법,  장애인고용촉진법 등 관련 사항의 채용상 참고(보훈 대상, 장애 관련 정보 등) 등 개인정보 보호책임자 및 담당자 안내 가.  개인정보 보호책임자 - 성명: 방원조 상무 나.  개인정보 담당부서 - 명칭: 두산퓨얼셀(주) 변화추진/생산관리팀  - 전화번호: 063-831-0717  - 팩스번호: 063-831-0717  - 이메일: daeha.kim@doosan.com 정보보안 및 고객 정보보호 개인정보보호 관리체계 &gt; 개인정보보호 강화 두산퓨얼셀은 개인정보를 안전하게 보호하고 국내외 개인정보보호 법규를 준수하기 위해, 법률 제정 및 변화를 지속적으로 모니터링하여 내부관리계획, 개인정보보호 규정 등에 반영하고, 담당조직에 전파하고 있습니다. 개인정보취급자 및 개인정보처리시스템을 대상으로 매년 이행점검, 위·수탁사 교육 및 점검, 주요 영역 내부감사 등을 진행하고, 도출된 취약점을 개선하여 관리하고 있습니다. •  당사는 개인정보를 수락하는 업체의 개인정보보호 인식 및 관리 수준을 높이기 위해 담당자를 지정하여 연 1회 ...</x:v>
-      </x:c>
-      <x:c r="D12" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.96] 수집하는 개인정보의 항목 및 수집 방법 1)  고충민원 처리 - 필수항목: 이름, 이메일 주소 2)  서비스 분석 및 서비스 수준 - 서비스 이용기록, 접속로그, 쿠키, 접속IP 정보 3)  채용 전형/결정 - 일반정보: 성명(국문/한자/영문), 생년월일, 성별, 사진, 비밀번호 등 - 민감정보: 장애여부 및 장애구분/장애등급 개인정보의 제3자 제공 정보주체로부터 별도의 동의를 받는 경우 - 법률에 특별한 규정이 있거나 법령상 의무를 준수하기 위하여 불가피한 경우 -  정보주체 또는 그 법정대리인이 의사표시를 할 수 없는 상태에 있거나 주소불명 등으로 사전 동의를 받을 수 없는 경우 개인정보의 수집 이용 목적 1)  고객 관련 -  서비스 분석 및 서비스 수준 제고: 서비스 이용분석을 통해 이용자에게 더 나은 서비스를 제 공하고 본 사이트의 수준 향상(서비스 분석 및 서비스 수준 제고) 등 - 고충·민원 처리: 민원사항 확인, 사실조사를 위한 연락·통지, 처리결과 통보 등 2)  채용 관련 -  채용 전형/결정: 본인 식별 및 실명 확인, 입사 전형 및 지원자와의 연락, 국가유공자법,  장애인고용촉진법 등 관련 사항의 채용상 참고(보훈 대상, 장애 관련 정보 등) 등 개인정보 보호책임자 및 담당자 안내 가.  개인정보 보호책임자 - 성명: 방원조 상무 나.  개인정보 담당부서 - 명칭: 두산퓨얼셀(주) 변화추진/생산관리팀  - 전화번호: 063-831-0717  - 팩스번호: 063-831-0717  - 이메일: daeha.kim@doosan.com 정보보안 및 고객 정보보호 개인정보보호 관리체계 &gt; 개인정보보호 강화 두산퓨얼셀은 개인정보를 안전하게 보호하고 국내외 개인정보보호 법규를 준수하기 위해, 법률 제정 및 변화를 지속적으로 모니터링하여 내부관리계획, 개인정보보호 규정 등에 반영하고, 담당조직에 전파하고 있습니다. 개인정보취급자 및 개인정보처리시스템을 대상으로 매년 이행점검, 위·수탁사 교육 및 점검, 주요 영역 내부감사 등을 진행하고, 도출된 취약점을 개선하여 관리하고 있습니다. •  당사는 개인정보를 수락하는 업체의 개인정보보호 인식 및 관리 수준을 높이기 위해 담당자를 지정하여 연 1회 ...</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 62;63;64;96
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E12" s="6" t="str">
-        <x:v>Selected Style: status-performance
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: status-performance
 Preferred Style Source: template
 Answer Type: status-performance
 Answer Intent: Explain the reported status in plain language, then weave figures into the management meaning.
@@ -789,34 +1002,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: High: topic-fit figures, non-repetitive opening, no technical metric label.</x:v>
-      </x:c>
-      <x:c r="F12" s="6" t="str">
-        <x:v>두산퓨얼셀는 인권 관련 고충 및 처리 현황에 대해 발생 현황과 관리 성과를 함께 확인할 수 있도록 보고하고 있습니다. 공개된 수치와 설명은 인권 관련 고충 및 처리 현황의 현재 수준을 확인하고 다음 관리 과제를 판단하는 기준이 되며, 전년 수치와 함께 제시될 때 추세 확인에도 활용될 수 있습니다. 인권 관련 고충 및 처리 현황는 단순한 발생 여부뿐 아니라 접수, 처리, 예방 조치가 관리 체계 안에서 이어지는지를 함께 확인하는 기준으로 활용되며, 공개 범위가 제한될 경우 후속 점검과 내부 관리 보완 여부를 함께 검토할 필요가 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="6" t="str">
-        <x:v>EBX-Q-012</x:v>
-      </x:c>
-      <x:c r="B13" s="6" t="str">
-        <x:v>사회 / 전략 (Strategy) / 제품 안전 및 품질 관리 정책</x:v>
-      </x:c>
-      <x:c r="C13" s="6" t="str">
-        <x:v>[p.5] CEO Message 국내 수소연료전지 1위 기업인 두산퓨얼셀은 국내 발전 시장의 불확실성과 경쟁이 심화될 것으로 전망되는 경영환경 하에서도 CHPS(청정수소 발전 의무화 제도) 입찰시장에서 높은 경쟁우위를 확보하여 국내 연료전지 시장의 리더십을 주도하고 있으며, 미국 데이터센터 시장 진출을 준비하고, 선박용 연료전지 등 신사업 기회를 확대하기 위한 활동도 적극 추진 중에 있습니다. 또한, 제품의 근원적 경쟁력을 강화하기 위해 SOFC(고체산화물 연료전지) 양산 시스템을 구축하여 초도품을 생산하고 PAFC(인산형 연료전지) 품질 역량을 강화하는 등 전 임직원이 ‘수소에너지 Global No.1 Player’ 라는 비전을 달성하기 위한 경영 활동을 지속적으로 실행해 가고 있습니다. 앞으로도 전사 역량을 집중하여 다양한 제품 line-up의 품질과 원가 경쟁력을 강화하고, 해외시장 개척 및 비즈니스 모델 다각화를 통해 중장기 Topline 성장을 꾸준히 확보해 나갈 것입니다. 이러한 경영 전략에 맞추어, 당사는 다음과 같이 비즈니스 가치에 기여하기 위해 필요한 ESG 역량을 강화하여 지속가능성을 높이겠습니다. 첫째, 친환경 경쟁력을 강화하여 탄소중립에 기여하겠습니다. 두산퓨얼셀은 탄소중립에 기여하는 제품과 기술을 개발하는 것과 더불어, 친환경 경영을 위해 온실가스를 줄이기 위한 다양한 방안을 검토하여 추진 중에 있습니다. 에너지 관리 기반 강화, 기저부하 최소화, 폐기물 재활용 등을 통해 사업장 온실가스 배출량을 감축하고 환경 지표를 개선하기 위한 활동을 꾸준히 진행하고 있으며, 향후에도 SOFC 공장 구축에 따른 온실가스 감축, Scope 3 배출량 관리, 재생에너지 도입 등을 통해 사업장 환경 성과를 지속적으로 개선해 나갈 예정입니다. 당사의 비즈니스는 기후변화 대응을 위한 가치 창출로 연결될 수 있는 만큼, 기후정보 공시를 위한 ESG 역량을 보다 강화하고 CDP(탄소정보공개프로젝트) 평가와 지속가능경영보고서 등을 통해 이해관계자와의 소통에도 적극 대응하여 ‘친환경 에너지 Solution Provider’로서의 위상을 적극 알리도록 하겠습니다. 두산퓨얼셀은 제품 설계, 제조, 사용 등 전과정에서 환경적 가치를 높이기 위해 노력하고 있 ...
+QA Severity: High: topic-fit figures, non-repetitive opening, no technical metric label.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 인권 관련 고충 및 처리 현황에 대해 발생 현황과 관리 성과를 함께 확인할 수 있도록 보고하고 있습니다. 두산퓨얼셀은 홈페이지 내 사이버 신고센터를 통해 임직원을 포함한 모든 이해관계자가 인권 침해 및 기타 비윤리적 행위를 제보할 수 있도록 하고 있으며, 비밀보장 원칙에 따라 비공개 신고도 가능합니다. 공개된 수치와 설명은 인권 관련 고충 및 처리 현황의 현재 수준을 확인하고 다음 관리 과제를 판단하는 기준이 되며, 전년 수치와 함께 제시될 때 추세 확인에도 활용될 수 있습니다. 인권 관련 고충 및 처리 현황은 단순한 발생 여부뿐 아니라 접수, 처리, 예방 조치가 관리 체계 안에서 이어지는지를 함께 확인하는 기준으로 활용되며, 공개 범위가 제한될 경우 후속 점검과 내부 관리 보완 여부를 함께 검토할 필요가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-012</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 전략 (Strategy) / 제품 안전 및 품질 관리 정책</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>[p.5] CEO Message 국내 수소연료전지 1위 기업인 두산퓨얼셀은 국내 발전 시장의 불확실성과 경쟁이 심화될 것으로 전망되는 경영환경 하에서도 CHPS(청정수소 발전 의무화 제도) 입찰시장에서 높은 경쟁우위를 확보하여 국내 연료전지 시장의 리더십을 주도하고 있으며, 미국 데이터센터 시장 진출을 준비하고, 선박용 연료전지 등 신사업 기회를 확대하기 위한 활동도 적극 추진 중에 있습니다. 또한, 제품의 근원적 경쟁력을 강화하기 위해 SOFC(고체산화물 연료전지) 양산 시스템을 구축하여 초도품을 생산하고 PAFC(인산형 연료전지) 품질 역량을 강화하는 등 전 임직원이 ‘수소에너지 Global No.1 Player’ 라는 비전을 달성하기 위한 경영 활동을 지속적으로 실행해 가고 있습니다. 앞으로도 전사 역량을 집중하여 다양한 제품 line-up의 품질과 원가 경쟁력을 강화하고, 해외시장 개척 및 비즈니스 모델 다각화를 통해 중장기 Topline 성장을 꾸준히 확보해 나갈 것입니다. 이러한 경영 전략에 맞추어, 당사는 다음과 같이 비즈니스 가치에 기여하기 위해 필요한 ESG 역량을 강화하여 지속가능성을 높이겠습니다. 첫째, 친환경 경쟁력을 강화하여 탄소중립에 기여하겠습니다. 두산퓨얼셀은 탄소중립에 기여하는 제품과 기술을 개발하는 것과 더불어, 친환경 경영을 위해 온실가스를 줄이기 위한 다양한 방안을 검토하여 추진 중에 있습니다. 에너지 관리 기반 강화, 기저부하 최소화, 폐기물 재활용 등을 통해 사업장 온실가스 배출량을 감축하고 환경 지표를 개선하기 위한 활동을 꾸준히 진행하고 있으며, 향후에도 SOFC 공장 구축에 따른 온실가스 감축, Scope 3 배출량 관리, 재생에너지 도입 등을 통해 사업장 환경 성과를 지속적으로 개선해 나갈 예정입니다. 당사의 비즈니스는 기후변화 대응을 위한 가치 창출로 연결될 수 있는 만큼, 기후정보 공시를 위한 ESG 역량을 보다 강화하고 CDP(탄소정보공개프로젝트) 평가와 지속가능경영보고서 등을 통해 이해관계자와의 소통에도 적극 대응하여 ‘친환경 에너지 Solution Provider’로서의 위상을 적극 알리도록 하겠습니다. 두산퓨얼셀은 제품 설계, 제조, 사용 등 전과정에서 환경적 가치를 높이기 위해 노력하고 있 ...
 [p.82] 고객 만족 품질 정책 국제기준에 부합한 설계, 각 분야별 인증 취득 및 주기적인 안전검사, 고효율 발전 및 높은 신뢰성을 가진 제품 생산을 목표로 모든 임직원의 끊임없는 노력을 통해 두산퓨얼셀은 ‘깨끗하고 안정적인 최적의 수소 에너지 솔루션’을 제공고자 힘쓰고 있습니다. 연료전지는 항공우주공학 산업으로 출발하여 모든 산업군 중 가장 엄격한 품질기준을 가지고 있으며, 미국 UTC시절부터 수십년간 안정성과 품질을 바탕으로 연료전지 시장을 선도해 왔습니다. 또한, ‘고객가치 창출’, ‘고효율, 저비용’, ‘지속가능 성장 추구’의 가치를 지켜 나가기 위해 품질 프로세스를 철저히 준수하고 있습니다. 품질경영 추진체계 두산퓨얼셀은 고객이 원하는 요구사항을 반영한 품질 매뉴얼과 제품 설계부터 생산, 서비스까지 모든 업무의 작업을 표준화하여 언제든지 최신본을 열람·활용할 수 있도록 표준문서관리 전산시스템(Spec center)을 운영하고 있습니다. MES(Manufacturing Execution System) 기반의 종합 제조/운영시스템 운영으로 실시간 공정현황 파악을 통한 운영 효율성을 확보하였으며, 실시간 품질현황 모니터링 및 분석을 활용하여 공정불량 발생 가능성을 사전인지하고 예방 및 조치할 수 있는 체계를 운영하고 있습니다. 또한 이를 기반으로 2023년도부터는 공정의 페이퍼리스가 구현되어 적용하고 있습니다. 품질시스템 실행력 강화 품질시스템 실행력 강화를 위해 입고부터 출하까지 전체 공정에 대한 Patrol(PQC) 활동을 주기적으로 실시하고 있습니다. ’23년도 최신 작업기준서의 현장 배포 및 활용과 부적합 개선조치사항의 현장적용 여부 및 유효성 검토를 중점적으로 점검하였고 도출된 보완 필요사항은 관련 부문과 소통하여 지속적으로 개선을 추진하고 있습니다. 2024년도는 공정별 작업기준서 준수여부를 중점적으로 점검하여 작업표준과 현업이 일치하도록 조정했습니다. 품질경영 인증시스템 확대 두산퓨얼셀은 ISO 9001, KGS설계단계 검사, KS 등 품질경영시스템 인증을 바탕으로 지속적인 품질관리를 실시하고 있습니다. 전기안전관리법에 부합되는 품질경영시스템 구축을 위해 연료전지 발전설비 초기검사, 제조시설 등록을 국내 연료전지 회사로는 최초로 ...
 [p.83] 고객 만족 품질 개선 문화 정착 두산퓨얼셀은 고객 만족과 근원적 경쟁력 강화를 위해 전사적인 품질 개선 문화 정착을 위한 활동을 추진하고 있습니다. 기존의 직무역량 강화 활동 등에 더하여 2024년부터는 변경사항 신고제 ‘품질 명탐정 제도’, 품질 소식지 발행, 품질 슬로건 공모 등 전 임직원이 품질 개선을 위한 공감대를 형성하고 참여할 수 있는 교육 및 활동을 진행하고 있습니다. 미국 인증 FC1 취득 연료전지 미국 수출을 위해 연료전지생산공장에 대한 평가인 FC1 초기공장평가(Initial Factory Evaluation)가 CSA그룹에 의해 익산공장에서 실시되었습니다. 품질경영시스템의 운영현황과 요구사항 만족 여부를 점검하였으며, 특히 시험항목의 계측기 관리현황을 중점적으로 점검하였습니다. 요구사항을 만족하여 초기공장평가 합격 및 미국 수출용 연료전지를 생산할 수 있는 인증을 확보하였습니다. 사전 품질 확보 총39.6MW급의 대용량급인 하이창원 연료전지 프로젝트에 대해 2025년5월경, 사전 고객검수를 성공적으로 완료하였습니다. 향후에도 사전 품질확보를 위하여 고객 입회하에 출하 전 고객검수를 진행하여 하이창원 연료전지 프로젝트를 성공적으로 완수할 계획입니다. 기술 교류회 매 짝수 월 첫 주에는 생산과 품질, 각 공정 임직원을 대상으로 기술교류회를 개최하고 있습니다. 이 교류회에서는 주요 부품 기능 설명과 공정 개선 관련 내용을 공유함으로써, 예를 들어 GDL 오염 강화, 전극 Trimming 그을음 현상, 프리신터링 온도 강화 등과 같은 주제를 다루어 업무 이해도와 실무 역량, 전문성을 향상시키고 있습니다. &gt; 직무역량 강화 두산퓨얼셀은 2024년 하반기부터 현재까지 모든 임직원이 자발적으로 품질 문제를 발굴하고 개선하는 품질명탐정 활동을 통해 공정 및 서비스 품질을 향상시켜왔습니다. 또한, 회사의 전반적인 품질 활동과 현황을 전 직원에게 공지하여 품질 수준을 재고하고자, 사무실과 공장에 품질 게시판을 설치하였습니다. 이를 통해 품질 방침, 품질 소식, 이슈 사항, 개선 제안을 공유하여 모든 직원이 품질에 대한 자부심을 갖고 업무에 임할 수 있도록 하고 있습니다. 이러한 일련의 활동들은 두산퓨얼셀의 품질 향상 및 임직원 품질 ...
-[p.84] 고객 만족 고객만족도 평가 지표 개발 및 만족도 조사 &gt; 고객만족도 평가 지표 개발 두산퓨얼셀은 연료전지 운영 사업장과 고객 기반이 점차 확대됨에 따라, 고객의 연료전지 이해도를 높이기 위해 반기별로 맞춤형 교육을 제공하고 있습니다. 또한 운영 과정에서 발생하는 다양한 고객 의견(VOC)을 청취하고, 이를 제품 개선 및 서비스 품질 향상에 지속적으로 반영하고자 고객 만족도 조사(Survey)를 실시하고 있습니다. 해당 조사는 제품 성능 만족도, 서비스 운영 만족도, 대고객 대응 만족도의 세 가지 항목을 중심으로 진행됩니다. 만족도 조사 시행 및 결과 두산퓨얼셀은 2024년 5월, 고객사를 대상으로 서비스만족도 조사를 실시했습니다． 총 20개의 고객사에 이메일을 통해 만족도 조사 안내를 발송했으며, 그 중 11개 고객사의 응답을 바탕으로 아래와 같은 결과를 도출했습니다. 장기 유지보수 계약(LTSA, Long Term Service Agreement) 운영품질에서는 설비의 효율, 정기 실적 보고서, 현장 대응업무에 대해서 긍정적인 의견을 받았으며 고객소통 부문에서는 계약담당자의 친절함, 고객사와의 교류활동에 대한 참여 및 지원에 적극적으로 참여해주었다는 의견 등 전반적으로 매우 긍정적인 응답을 받았습니다. 또한 환경안전보건(EHS) 부문에서도 작업 절차의 준수, 안전장비 착용, 고객사 안전보건협의회 참여에서 높은 만족도를 확인했습니다. 마지막으로 고객사 정기교육에 대해서는 모든 고객사가 높은 참여 의사를 보였고, 교육내용에 관한 다양한 건의사항은 추후 교육에 반영할 것입니다. 만족도 조사 전체 평균 80점 수준으로 확인할 수 있었으며, 2025년에는 고객만족도 측정 설문체계 개선점을 도출하여 운영과 제품 성능 그리고 고객 대응 만족도 향상으로 이어질 수 있게 개선할 계획입니다. 제품 리콜 당사의 제품은 2021년부터 2025년 상반기 현재까지 리콜된 이력이 없습니다. 연료전지는 고객사 납품 후 20년간의 장기 유지보수 계약(LTSA)를 체결하고 본사 직원이 직접 현장에서 제품의 운전과 수리/관리를 책임지고 있습니다. 고객사 Site별 연료전지는 본사 관제센터에서 운전 현황을 24시간 모니터링하고 있으며, 비정상 운전이 파악될 경우 원격 ...</x:v>
-      </x:c>
-      <x:c r="D13" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.84] 고객 만족 고객만족도 평가 지표 개발 및 만족도 조사 &gt; 고객만족도 평가 지표 개발 두산퓨얼셀은 연료전지 운영 사업장과 고객 기반이 점차 확대됨에 따라, 고객의 연료전지 이해도를 높이기 위해 반기별로 맞춤형 교육을 제공하고 있습니다. 또한 운영 과정에서 발생하는 다양한 고객 의견(VOC)을 청취하고, 이를 제품 개선 및 서비스 품질 향상에 지속적으로 반영하고자 고객 만족도 조사(Survey)를 실시하고 있습니다. 해당 조사는 제품 성능 만족도, 서비스 운영 만족도, 대고객 대응 만족도의 세 가지 항목을 중심으로 진행됩니다. 만족도 조사 시행 및 결과 두산퓨얼셀은 2024년 5월, 고객사를 대상으로 서비스만족도 조사를 실시했습니다． 총 20개의 고객사에 이메일을 통해 만족도 조사 안내를 발송했으며, 그 중 11개 고객사의 응답을 바탕으로 아래와 같은 결과를 도출했습니다. 장기 유지보수 계약(LTSA, Long Term Service Agreement) 운영품질에서는 설비의 효율, 정기 실적 보고서, 현장 대응업무에 대해서 긍정적인 의견을 받았으며 고객소통 부문에서는 계약담당자의 친절함, 고객사와의 교류활동에 대한 참여 및 지원에 적극적으로 참여해주었다는 의견 등 전반적으로 매우 긍정적인 응답을 받았습니다. 또한 환경안전보건(EHS) 부문에서도 작업 절차의 준수, 안전장비 착용, 고객사 안전보건협의회 참여에서 높은 만족도를 확인했습니다. 마지막으로 고객사 정기교육에 대해서는 모든 고객사가 높은 참여 의사를 보였고, 교육내용에 관한 다양한 건의사항은 추후 교육에 반영할 것입니다. 만족도 조사 전체 평균 80점 수준으로 확인할 수 있었으며, 2025년에는 고객만족도 측정 설문체계 개선점을 도출하여 운영과 제품 성능 그리고 고객 대응 만족도 향상으로 이어질 수 있게 개선할 계획입니다. 제품 리콜 당사의 제품은 2021년부터 2025년 상반기 현재까지 리콜된 이력이 없습니다. 연료전지는 고객사 납품 후 20년간의 장기 유지보수 계약(LTSA)를 체결하고 본사 직원이 직접 현장에서 제품의 운전과 수리/관리를 책임지고 있습니다. 고객사 Site별 연료전지는 본사 관제센터에서 운전 현황을 24시간 모니터링하고 있으며, 비정상 운전이 파악될 경우 원격 ...</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 5;82;83;84
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E13" s="6" t="str">
-        <x:v>Selected Style: balanced-policy
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: balanced-policy
 Preferred Style Source: template
 Answer Type: policy-management
 Answer Intent: Explain the standard or policy, then show implementation ownership and supporting performance facts.
@@ -835,34 +1060,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: Medium: prose must be natural, evidence-grounded, and non-repetitive.</x:v>
-      </x:c>
-      <x:c r="F13" s="6" t="str">
-        <x:v>또한, 제품의 근원적 경쟁력을 강화하기 위해 SOFC(고체산화물 연료전지) 양산 시스템을 구축하여 초도품을 생산하고 PAFC(인산형 연료전지) 품질 역량을 강화하는 등 전 임직원이 ‘수소에너지 Global No.1 Player’ 라는 비전을 달성하기 위한 경영 활동을 지속적으로 실행해 가고 있습니다. 고객 만족 품질 정책 국제기준에 부합한 설계, 각 분야별 인증 취득 및 주기적인 안전검사, 고효율 발전 및 높은 신뢰성을 가진 제품 생산을 목표로 모든 임직원의 끊임없는 노력을 통해 두산퓨얼셀은 ‘깨끗하고 안정적인 최적의 수소 에너지 솔루션’을 제공고자 힘쓰고 있습니다. 품질경영 추진체계 두산퓨얼셀은 고객이 원하는 요구사항을 반영한 품질 매뉴얼과 제품 설계부터 생산, 서비스까지 모든 업무의 작업을 표준화하여 언제든지 최신본을 열람·활용할 수 있도록 표준문서관리 전산시스템(Spec center)을 운영하고 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="6" t="str">
-        <x:v>EBX-Q-013</x:v>
-      </x:c>
-      <x:c r="B14" s="6" t="str">
-        <x:v>사회 / 거버넌스 (Governance) / 품질 관리 조직 및 책임</x:v>
-      </x:c>
-      <x:c r="C14" s="6" t="str">
-        <x:v>[p.5] CEO Message 국내 수소연료전지 1위 기업인 두산퓨얼셀은 국내 발전 시장의 불확실성과 경쟁이 심화될 것으로 전망되는 경영환경 하에서도 CHPS(청정수소 발전 의무화 제도) 입찰시장에서 높은 경쟁우위를 확보하여 국내 연료전지 시장의 리더십을 주도하고 있으며, 미국 데이터센터 시장 진출을 준비하고, 선박용 연료전지 등 신사업 기회를 확대하기 위한 활동도 적극 추진 중에 있습니다. 또한, 제품의 근원적 경쟁력을 강화하기 위해 SOFC(고체산화물 연료전지) 양산 시스템을 구축하여 초도품을 생산하고 PAFC(인산형 연료전지) 품질 역량을 강화하는 등 전 임직원이 ‘수소에너지 Global No.1 Player’ 라는 비전을 달성하기 위한 경영 활동을 지속적으로 실행해 가고 있습니다. 앞으로도 전사 역량을 집중하여 다양한 제품 line-up의 품질과 원가 경쟁력을 강화하고, 해외시장 개척 및 비즈니스 모델 다각화를 통해 중장기 Topline 성장을 꾸준히 확보해 나갈 것입니다. 이러한 경영 전략에 맞추어, 당사는 다음과 같이 비즈니스 가치에 기여하기 위해 필요한 ESG 역량을 강화하여 지속가능성을 높이겠습니다. 첫째, 친환경 경쟁력을 강화하여 탄소중립에 기여하겠습니다. 두산퓨얼셀은 탄소중립에 기여하는 제품과 기술을 개발하는 것과 더불어, 친환경 경영을 위해 온실가스를 줄이기 위한 다양한 방안을 검토하여 추진 중에 있습니다. 에너지 관리 기반 강화, 기저부하 최소화, 폐기물 재활용 등을 통해 사업장 온실가스 배출량을 감축하고 환경 지표를 개선하기 위한 활동을 꾸준히 진행하고 있으며, 향후에도 SOFC 공장 구축에 따른 온실가스 감축, Scope 3 배출량 관리, 재생에너지 도입 등을 통해 사업장 환경 성과를 지속적으로 개선해 나갈 예정입니다. 당사의 비즈니스는 기후변화 대응을 위한 가치 창출로 연결될 수 있는 만큼, 기후정보 공시를 위한 ESG 역량을 보다 강화하고 CDP(탄소정보공개프로젝트) 평가와 지속가능경영보고서 등을 통해 이해관계자와의 소통에도 적극 대응하여 ‘친환경 에너지 Solution Provider’로서의 위상을 적극 알리도록 하겠습니다. 두산퓨얼셀은 제품 설계, 제조, 사용 등 전과정에서 환경적 가치를 높이기 위해 노력하고 있 ...
+QA Severity: Medium: prose must be natural, evidence-grounded, and non-repetitive.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>제품의 근원적 경쟁력을 강화하기 위해 SOFC(고체산화물 연료전지) 양산 시스템을 구축하여 초도품을 생산하고 PAFC(인산형 연료전지) 품질 역량을 강화하는 등 전 임직원이 ‘수소에너지 Global No.1 Player’라는 비전을 달성하기 위한 경영 활동을 지속적으로 실행해 가고 있습니다. 국제기준에 부합한 설계, 각 분야별 인증 취득 및 주기적인 안전검사, 고효율 발전 및 높은 신뢰성을 가진 제품 생산을 목표로 모든 임직원의 끊임없는 노력을 통해 두산퓨얼셀은 ‘깨끗하고 안정적인 최적의 수소 에너지 솔루션’을 제공하고자 힘쓰고 있습니다. 두산퓨얼셀은 고객이 원하는 요구사항을 반영한 품질 매뉴얼과 제품 설계부터 생산, 서비스까지 모든 업무의 작업을 표준화하여 언제든지 최신본을 열람·활용할 수 있도록 표준문서관리 전산시스템(Spec center)을 운영하고 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-013</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 거버넌스 (Governance) / 품질 관리 조직 및 책임</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>[p.5] CEO Message 국내 수소연료전지 1위 기업인 두산퓨얼셀은 국내 발전 시장의 불확실성과 경쟁이 심화될 것으로 전망되는 경영환경 하에서도 CHPS(청정수소 발전 의무화 제도) 입찰시장에서 높은 경쟁우위를 확보하여 국내 연료전지 시장의 리더십을 주도하고 있으며, 미국 데이터센터 시장 진출을 준비하고, 선박용 연료전지 등 신사업 기회를 확대하기 위한 활동도 적극 추진 중에 있습니다. 또한, 제품의 근원적 경쟁력을 강화하기 위해 SOFC(고체산화물 연료전지) 양산 시스템을 구축하여 초도품을 생산하고 PAFC(인산형 연료전지) 품질 역량을 강화하는 등 전 임직원이 ‘수소에너지 Global No.1 Player’ 라는 비전을 달성하기 위한 경영 활동을 지속적으로 실행해 가고 있습니다. 앞으로도 전사 역량을 집중하여 다양한 제품 line-up의 품질과 원가 경쟁력을 강화하고, 해외시장 개척 및 비즈니스 모델 다각화를 통해 중장기 Topline 성장을 꾸준히 확보해 나갈 것입니다. 이러한 경영 전략에 맞추어, 당사는 다음과 같이 비즈니스 가치에 기여하기 위해 필요한 ESG 역량을 강화하여 지속가능성을 높이겠습니다. 첫째, 친환경 경쟁력을 강화하여 탄소중립에 기여하겠습니다. 두산퓨얼셀은 탄소중립에 기여하는 제품과 기술을 개발하는 것과 더불어, 친환경 경영을 위해 온실가스를 줄이기 위한 다양한 방안을 검토하여 추진 중에 있습니다. 에너지 관리 기반 강화, 기저부하 최소화, 폐기물 재활용 등을 통해 사업장 온실가스 배출량을 감축하고 환경 지표를 개선하기 위한 활동을 꾸준히 진행하고 있으며, 향후에도 SOFC 공장 구축에 따른 온실가스 감축, Scope 3 배출량 관리, 재생에너지 도입 등을 통해 사업장 환경 성과를 지속적으로 개선해 나갈 예정입니다. 당사의 비즈니스는 기후변화 대응을 위한 가치 창출로 연결될 수 있는 만큼, 기후정보 공시를 위한 ESG 역량을 보다 강화하고 CDP(탄소정보공개프로젝트) 평가와 지속가능경영보고서 등을 통해 이해관계자와의 소통에도 적극 대응하여 ‘친환경 에너지 Solution Provider’로서의 위상을 적극 알리도록 하겠습니다. 두산퓨얼셀은 제품 설계, 제조, 사용 등 전과정에서 환경적 가치를 높이기 위해 노력하고 있 ...
 [p.82] 고객 만족 품질 정책 국제기준에 부합한 설계, 각 분야별 인증 취득 및 주기적인 안전검사, 고효율 발전 및 높은 신뢰성을 가진 제품 생산을 목표로 모든 임직원의 끊임없는 노력을 통해 두산퓨얼셀은 ‘깨끗하고 안정적인 최적의 수소 에너지 솔루션’을 제공고자 힘쓰고 있습니다. 연료전지는 항공우주공학 산업으로 출발하여 모든 산업군 중 가장 엄격한 품질기준을 가지고 있으며, 미국 UTC시절부터 수십년간 안정성과 품질을 바탕으로 연료전지 시장을 선도해 왔습니다. 또한, ‘고객가치 창출’, ‘고효율, 저비용’, ‘지속가능 성장 추구’의 가치를 지켜 나가기 위해 품질 프로세스를 철저히 준수하고 있습니다. 품질경영 추진체계 두산퓨얼셀은 고객이 원하는 요구사항을 반영한 품질 매뉴얼과 제품 설계부터 생산, 서비스까지 모든 업무의 작업을 표준화하여 언제든지 최신본을 열람·활용할 수 있도록 표준문서관리 전산시스템(Spec center)을 운영하고 있습니다. MES(Manufacturing Execution System) 기반의 종합 제조/운영시스템 운영으로 실시간 공정현황 파악을 통한 운영 효율성을 확보하였으며, 실시간 품질현황 모니터링 및 분석을 활용하여 공정불량 발생 가능성을 사전인지하고 예방 및 조치할 수 있는 체계를 운영하고 있습니다. 또한 이를 기반으로 2023년도부터는 공정의 페이퍼리스가 구현되어 적용하고 있습니다. 품질시스템 실행력 강화 품질시스템 실행력 강화를 위해 입고부터 출하까지 전체 공정에 대한 Patrol(PQC) 활동을 주기적으로 실시하고 있습니다. ’23년도 최신 작업기준서의 현장 배포 및 활용과 부적합 개선조치사항의 현장적용 여부 및 유효성 검토를 중점적으로 점검하였고 도출된 보완 필요사항은 관련 부문과 소통하여 지속적으로 개선을 추진하고 있습니다. 2024년도는 공정별 작업기준서 준수여부를 중점적으로 점검하여 작업표준과 현업이 일치하도록 조정했습니다. 품질경영 인증시스템 확대 두산퓨얼셀은 ISO 9001, KGS설계단계 검사, KS 등 품질경영시스템 인증을 바탕으로 지속적인 품질관리를 실시하고 있습니다. 전기안전관리법에 부합되는 품질경영시스템 구축을 위해 연료전지 발전설비 초기검사, 제조시설 등록을 국내 연료전지 회사로는 최초로 ...
 [p.83] 고객 만족 품질 개선 문화 정착 두산퓨얼셀은 고객 만족과 근원적 경쟁력 강화를 위해 전사적인 품질 개선 문화 정착을 위한 활동을 추진하고 있습니다. 기존의 직무역량 강화 활동 등에 더하여 2024년부터는 변경사항 신고제 ‘품질 명탐정 제도’, 품질 소식지 발행, 품질 슬로건 공모 등 전 임직원이 품질 개선을 위한 공감대를 형성하고 참여할 수 있는 교육 및 활동을 진행하고 있습니다. 미국 인증 FC1 취득 연료전지 미국 수출을 위해 연료전지생산공장에 대한 평가인 FC1 초기공장평가(Initial Factory Evaluation)가 CSA그룹에 의해 익산공장에서 실시되었습니다. 품질경영시스템의 운영현황과 요구사항 만족 여부를 점검하였으며, 특히 시험항목의 계측기 관리현황을 중점적으로 점검하였습니다. 요구사항을 만족하여 초기공장평가 합격 및 미국 수출용 연료전지를 생산할 수 있는 인증을 확보하였습니다. 사전 품질 확보 총39.6MW급의 대용량급인 하이창원 연료전지 프로젝트에 대해 2025년5월경, 사전 고객검수를 성공적으로 완료하였습니다. 향후에도 사전 품질확보를 위하여 고객 입회하에 출하 전 고객검수를 진행하여 하이창원 연료전지 프로젝트를 성공적으로 완수할 계획입니다. 기술 교류회 매 짝수 월 첫 주에는 생산과 품질, 각 공정 임직원을 대상으로 기술교류회를 개최하고 있습니다. 이 교류회에서는 주요 부품 기능 설명과 공정 개선 관련 내용을 공유함으로써, 예를 들어 GDL 오염 강화, 전극 Trimming 그을음 현상, 프리신터링 온도 강화 등과 같은 주제를 다루어 업무 이해도와 실무 역량, 전문성을 향상시키고 있습니다. &gt; 직무역량 강화 두산퓨얼셀은 2024년 하반기부터 현재까지 모든 임직원이 자발적으로 품질 문제를 발굴하고 개선하는 품질명탐정 활동을 통해 공정 및 서비스 품질을 향상시켜왔습니다. 또한, 회사의 전반적인 품질 활동과 현황을 전 직원에게 공지하여 품질 수준을 재고하고자, 사무실과 공장에 품질 게시판을 설치하였습니다. 이를 통해 품질 방침, 품질 소식, 이슈 사항, 개선 제안을 공유하여 모든 직원이 품질에 대한 자부심을 갖고 업무에 임할 수 있도록 하고 있습니다. 이러한 일련의 활동들은 두산퓨얼셀의 품질 향상 및 임직원 품질 ...
-[p.84] 고객 만족 고객만족도 평가 지표 개발 및 만족도 조사 &gt; 고객만족도 평가 지표 개발 두산퓨얼셀은 연료전지 운영 사업장과 고객 기반이 점차 확대됨에 따라, 고객의 연료전지 이해도를 높이기 위해 반기별로 맞춤형 교육을 제공하고 있습니다. 또한 운영 과정에서 발생하는 다양한 고객 의견(VOC)을 청취하고, 이를 제품 개선 및 서비스 품질 향상에 지속적으로 반영하고자 고객 만족도 조사(Survey)를 실시하고 있습니다. 해당 조사는 제품 성능 만족도, 서비스 운영 만족도, 대고객 대응 만족도의 세 가지 항목을 중심으로 진행됩니다. 만족도 조사 시행 및 결과 두산퓨얼셀은 2024년 5월, 고객사를 대상으로 서비스만족도 조사를 실시했습니다． 총 20개의 고객사에 이메일을 통해 만족도 조사 안내를 발송했으며, 그 중 11개 고객사의 응답을 바탕으로 아래와 같은 결과를 도출했습니다. 장기 유지보수 계약(LTSA, Long Term Service Agreement) 운영품질에서는 설비의 효율, 정기 실적 보고서, 현장 대응업무에 대해서 긍정적인 의견을 받았으며 고객소통 부문에서는 계약담당자의 친절함, 고객사와의 교류활동에 대한 참여 및 지원에 적극적으로 참여해주었다는 의견 등 전반적으로 매우 긍정적인 응답을 받았습니다. 또한 환경안전보건(EHS) 부문에서도 작업 절차의 준수, 안전장비 착용, 고객사 안전보건협의회 참여에서 높은 만족도를 확인했습니다. 마지막으로 고객사 정기교육에 대해서는 모든 고객사가 높은 참여 의사를 보였고, 교육내용에 관한 다양한 건의사항은 추후 교육에 반영할 것입니다. 만족도 조사 전체 평균 80점 수준으로 확인할 수 있었으며, 2025년에는 고객만족도 측정 설문체계 개선점을 도출하여 운영과 제품 성능 그리고 고객 대응 만족도 향상으로 이어질 수 있게 개선할 계획입니다. 제품 리콜 당사의 제품은 2021년부터 2025년 상반기 현재까지 리콜된 이력이 없습니다. 연료전지는 고객사 납품 후 20년간의 장기 유지보수 계약(LTSA)를 체결하고 본사 직원이 직접 현장에서 제품의 운전과 수리/관리를 책임지고 있습니다. 고객사 Site별 연료전지는 본사 관제센터에서 운전 현황을 24시간 모니터링하고 있으며, 비정상 운전이 파악될 경우 원격 ...</x:v>
-      </x:c>
-      <x:c r="D14" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.84] 고객 만족 고객만족도 평가 지표 개발 및 만족도 조사 &gt; 고객만족도 평가 지표 개발 두산퓨얼셀은 연료전지 운영 사업장과 고객 기반이 점차 확대됨에 따라, 고객의 연료전지 이해도를 높이기 위해 반기별로 맞춤형 교육을 제공하고 있습니다. 또한 운영 과정에서 발생하는 다양한 고객 의견(VOC)을 청취하고, 이를 제품 개선 및 서비스 품질 향상에 지속적으로 반영하고자 고객 만족도 조사(Survey)를 실시하고 있습니다. 해당 조사는 제품 성능 만족도, 서비스 운영 만족도, 대고객 대응 만족도의 세 가지 항목을 중심으로 진행됩니다. 만족도 조사 시행 및 결과 두산퓨얼셀은 2024년 5월, 고객사를 대상으로 서비스만족도 조사를 실시했습니다． 총 20개의 고객사에 이메일을 통해 만족도 조사 안내를 발송했으며, 그 중 11개 고객사의 응답을 바탕으로 아래와 같은 결과를 도출했습니다. 장기 유지보수 계약(LTSA, Long Term Service Agreement) 운영품질에서는 설비의 효율, 정기 실적 보고서, 현장 대응업무에 대해서 긍정적인 의견을 받았으며 고객소통 부문에서는 계약담당자의 친절함, 고객사와의 교류활동에 대한 참여 및 지원에 적극적으로 참여해주었다는 의견 등 전반적으로 매우 긍정적인 응답을 받았습니다. 또한 환경안전보건(EHS) 부문에서도 작업 절차의 준수, 안전장비 착용, 고객사 안전보건협의회 참여에서 높은 만족도를 확인했습니다. 마지막으로 고객사 정기교육에 대해서는 모든 고객사가 높은 참여 의사를 보였고, 교육내용에 관한 다양한 건의사항은 추후 교육에 반영할 것입니다. 만족도 조사 전체 평균 80점 수준으로 확인할 수 있었으며, 2025년에는 고객만족도 측정 설문체계 개선점을 도출하여 운영과 제품 성능 그리고 고객 대응 만족도 향상으로 이어질 수 있게 개선할 계획입니다. 제품 리콜 당사의 제품은 2021년부터 2025년 상반기 현재까지 리콜된 이력이 없습니다. 연료전지는 고객사 납품 후 20년간의 장기 유지보수 계약(LTSA)를 체결하고 본사 직원이 직접 현장에서 제품의 운전과 수리/관리를 책임지고 있습니다. 고객사 Site별 연료전지는 본사 관제센터에서 운전 현황을 24시간 모니터링하고 있으며, 비정상 운전이 파악될 경우 원격 ...</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 5;82;83;84
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E14" s="6" t="str">
-        <x:v>Selected Style: governance
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: governance
 Preferred Style Source: template
 Answer Type: governance-organization
 Answer Intent: Explain who is responsible, what they decide or oversee, and how reporting or escalation works.
@@ -881,34 +1118,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: Medium: responsibility and decision flow must be clear.</x:v>
-      </x:c>
-      <x:c r="F14" s="6" t="str">
-        <x:v>고객 만족 품질 정책 국제기준에 부합한 설계, 각 분야별 인증 취득 및 주기적인 안전검사, 고효율 발전 및 높은 신뢰성을 가진 제품 생산을 목표로 모든 임직원의 끊임없는 노력을 통해 두산퓨얼셀은 ‘깨끗하고 안정적인 최적의 수소 에너지 솔루션’을 제공고자 힘쓰고 있습니다. 품질경영 추진체계 두산퓨얼셀은 고객이 원하는 요구사항을 반영한 품질 매뉴얼과 제품 설계부터 생산, 서비스까지 모든 업무의 작업을 표준화하여 언제든지 최신본을 열람·활용할 수 있도록 표준문서관리 전산시스템(Spec center)을 운영하고 있습니다. 품질경영 인증시스템 확대 두산퓨얼셀은 ISO 9001, KGS설계단계 검사, KS 등 품질경영시스템 인증을 바탕으로 지속적인 품질관리를 실시하고 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="6" t="str">
-        <x:v>EBX-Q-014</x:v>
-      </x:c>
-      <x:c r="B15" s="6" t="str">
-        <x:v>사회 / 위험 관리 (Risk Management) / 제품 품질 및 안전 리스크 관리</x:v>
-      </x:c>
-      <x:c r="C15" s="6" t="str">
-        <x:v>[p.7] 회사 개요 경영전략 두산퓨얼셀을 둘러싼 글로벌 환경과 국내 정책 상황의 불확실성은 높을 것으로 예상됩니다. 미국의 트럼프 2기를 중심으로 격변하는 세계 관세 무역 환경과 러시아-우크라이나 전쟁, 중동 분쟁에 따른 지정학적 위기로 에너지 시장의 불안정은 지속되고 있습니다. 또한 금융 시장과 원자재 가격의 변동성이 크게 확대되고 있어 연료전지 사업의 여건은 우호적이지 않은 상황입니다. 다만, 당사는 불확실한 경영환경에도 불구하고 기술 개발과 생산 효율화를 통해 경쟁력을 강화하고 있으며, 친환경 에너지 전환을 가속화하기 위한 활동을 지속적으로 확대하고 있습니다. 국내 환경적 측면에서 2023년부터 개설된 수소발전 입찰 시장에 따라 발전단가 인하, 분산전원 확대, 국내산업 기여 측면에서 긍정적인 결과를 만들고 있으며, 해외 환경적 측면으로는 미국 AI 데이터 센터에서 기인한 전력수요 증가로 연료전지에 대한 관심이 증가하고 있습니다. 당사는 미국 인증 등을 통해 미국 데이터 센터로의 수출을 본격 추진 중에 있으며, ㈜두산의 미국 소재 수소사업 자회사 HyAxiom은 데이터 센터 주요 고객을 대상으로 영업활동을 강화하고 있으므로 미국 데이터 센터 납품 등의 시너지 효과가 기대됩니다. 그 외 해외시장은 수소연료전지에 대한 검증 및 실증 단계이며, 친환경 발전원의 중요성 확대에 따라 점진적으로 시장이 확대될 것으로 기대합니다. 추진 방향 두산퓨얼셀은 시장 경쟁력을 강화함으로써 불안정한 경영환경을 극복하고, 친환경 기술과 청정 에너지 솔루션을 바탕으로 탄소중립 실현과 지속가능한 미래를 가속화하기 위한 사업 모델을 전개하고 있습니다. 연료전지를 활용할 수 있는 다양한 사업모델을 개발하는 한편, 수소에너지에 대한 관심이 높아지고 있는 해외 시장에서의 사업기회 확대도 추진하고 있으며, 발전용 및 선박용 SOFC(고체산화물 연료전지) 등 미래 성장을 위한 신규 사업을 추진하고 있습니다. 앞으로도 적극적인 사업개발, 원가 및 품질 경쟁력 강화를 통해 기존 사업의 경쟁력을 공고히 하는 한편, 수소 관련 신사업 추진을 본격화하여 사업 포트폴리오를 확장할 계획입니다. Flexible system integration for a variety of applicatio ...
+QA Severity: Medium: responsibility and decision flow must be clear.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>국내 수소연료전지 1위 기업인 두산퓨얼셀은 국내 발전 시장의 불확실성과 경쟁이 심화될 것으로 전망되는 경영환경 하에서도 CHPS(청정수소 발전 의무화 제도) 입찰시장에서 높은 경쟁우위를 확보하여 국내 연료전지 시장의 리더십을 주도하고 있으며, 미국 데이터센터 시장 진출을 준비하고, 선박용 연료전지 등 신사업 기회를 확대하기 위한 활동도 적극 추진 중에 있습니다. 두산퓨얼셀은 고객이 원하는 요구사항을 반영한 품질 매뉴얼과 제품 설계부터 생산, 서비스까지 모든 업무의 작업을 표준화하여 언제든지 최신본을 열람·활용할 수 있도록 표준문서관리 전산시스템(Spec center)을 운영하고 있습니다. 품질경영 인증시스템 확대 두산퓨얼셀은 ISO 9001, KGS설계단계 검사, KS 등 품질경영시스템 인증을 바탕으로 지속적인 품질관리를 실시하고 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-014</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 위험 관리 (Risk Management) / 제품 품질 및 안전 리스크 관리</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>[p.7] 회사 개요 경영전략 두산퓨얼셀을 둘러싼 글로벌 환경과 국내 정책 상황의 불확실성은 높을 것으로 예상됩니다. 미국의 트럼프 2기를 중심으로 격변하는 세계 관세 무역 환경과 러시아-우크라이나 전쟁, 중동 분쟁에 따른 지정학적 위기로 에너지 시장의 불안정은 지속되고 있습니다. 또한 금융 시장과 원자재 가격의 변동성이 크게 확대되고 있어 연료전지 사업의 여건은 우호적이지 않은 상황입니다. 다만, 당사는 불확실한 경영환경에도 불구하고 기술 개발과 생산 효율화를 통해 경쟁력을 강화하고 있으며, 친환경 에너지 전환을 가속화하기 위한 활동을 지속적으로 확대하고 있습니다. 국내 환경적 측면에서 2023년부터 개설된 수소발전 입찰 시장에 따라 발전단가 인하, 분산전원 확대, 국내산업 기여 측면에서 긍정적인 결과를 만들고 있으며, 해외 환경적 측면으로는 미국 AI 데이터 센터에서 기인한 전력수요 증가로 연료전지에 대한 관심이 증가하고 있습니다. 당사는 미국 인증 등을 통해 미국 데이터 센터로의 수출을 본격 추진 중에 있으며, ㈜두산의 미국 소재 수소사업 자회사 HyAxiom은 데이터 센터 주요 고객을 대상으로 영업활동을 강화하고 있으므로 미국 데이터 센터 납품 등의 시너지 효과가 기대됩니다. 그 외 해외시장은 수소연료전지에 대한 검증 및 실증 단계이며, 친환경 발전원의 중요성 확대에 따라 점진적으로 시장이 확대될 것으로 기대합니다. 추진 방향 두산퓨얼셀은 시장 경쟁력을 강화함으로써 불안정한 경영환경을 극복하고, 친환경 기술과 청정 에너지 솔루션을 바탕으로 탄소중립 실현과 지속가능한 미래를 가속화하기 위한 사업 모델을 전개하고 있습니다. 연료전지를 활용할 수 있는 다양한 사업모델을 개발하는 한편, 수소에너지에 대한 관심이 높아지고 있는 해외 시장에서의 사업기회 확대도 추진하고 있으며, 발전용 및 선박용 SOFC(고체산화물 연료전지) 등 미래 성장을 위한 신규 사업을 추진하고 있습니다. 앞으로도 적극적인 사업개발, 원가 및 품질 경쟁력 강화를 통해 기존 사업의 경쟁력을 공고히 하는 한편, 수소 관련 신사업 추진을 본격화하여 사업 포트폴리오를 확장할 계획입니다. Flexible system integration for a variety of applicatio ...
 [p.45] 생물다양성 보존 활동 두산퓨얼셀은 군산 공장이 위치한 전북 군산시 새만금 일대 생물다양성 보존을 위하여 2024년 국립생태원 멸종위기종복원센터와 업무협약을 체결하고, 멸종위기식물 Ⅱ급 ‘석곡’의 국내 최북단 자생지인 군산시 고군산군도 일대에 석곡 이식 및 서식지 보전을 위한 활동을 진행하고 있습니다. 멸종위기야생생물 보전 사업 주요 환경영향 및 관리항목 리스트 주요환경영향 관리항목 관련기록 관리주기 담당자 번호 위해요소 환경측면 1 액상 폐기물 누출 수질, 대기, 토양 환경운영 일상관리 환경일상운영관리 결과 매분기 제조EHS팀 방재장비함 점검 방재장비LIST 점검결과 매월 제조EHS팀 비상시 연락체계 구축 비상연락기준 변경시 제조EHS팀 2 오수(Overflow) 오수(Overflow) 일일 순찰 일일 순찰 일지 매일 경비실 오수 맨홀 상태 점검 오수 및 정화조 점검표 매월 관리지원팀 비상시 연락체계 구축 비상연락기준 변경시 제조EHS팀 구분 사업내용 사업기간 2024년9월~ 사업장소 전북특별자치도 군산시 고군산군도 내 대장도 사업재원 두산퓨얼셀 기부금 3,000만원 사업단계 두산퓨얼셀 임직원 대상 멸종위기야생생물 보전의 필요성 등 생태 전반에 관한 교육 진행 3. 멸종위기야생생물 보전교육 이식 후 모니터링 데이터를 통해 위협요인, 생육환경 등 도출 4. 석곡 이식지 연구 수행 지속적인 협업을 통한 멸종위기식물 관리 5.  석곡 등 멸종위기식물 증식 및 유지ㆍ관리 2-1. 이식 후보지 탐색 및 선정 2-2. 이식 후 모니터링 2-3. 이식 후 개체 및 서식지 관리 무인비행기(드론) 조사를 통해 고군산군도 내 암석에 서식하는 석곡 서식지 탐색 1. 석곡 신규서식지 발굴 2. 대체서식지 내 이식 고군산군도 내 석곡 개체 이식 및 서식지 복원 활동내역 업무협약 체결 ('24.10) 석곡 증식 연구 지원 (‘24.10~) 석곡 200개체 이식 (‘25.4) 이식 후 서식지 관리 (‘25.5~) 상황 시나리오대본내용 역할및 행동내용 글리콜 저장소 방유제 펌핑 작업 1.글리콜저장소 방제활동 실시 "소화활동으로 화재진압이 완료되었지만, 글리콜저장소 방유제에 균열이 발생하여 유출될 가능성이 있으므로 신속하게 방제활동을 실시하기 바랍니다." 2. 소 ...
 [p.84] 고객 만족 고객만족도 평가 지표 개발 및 만족도 조사 &gt; 고객만족도 평가 지표 개발 두산퓨얼셀은 연료전지 운영 사업장과 고객 기반이 점차 확대됨에 따라, 고객의 연료전지 이해도를 높이기 위해 반기별로 맞춤형 교육을 제공하고 있습니다. 또한 운영 과정에서 발생하는 다양한 고객 의견(VOC)을 청취하고, 이를 제품 개선 및 서비스 품질 향상에 지속적으로 반영하고자 고객 만족도 조사(Survey)를 실시하고 있습니다. 해당 조사는 제품 성능 만족도, 서비스 운영 만족도, 대고객 대응 만족도의 세 가지 항목을 중심으로 진행됩니다. 만족도 조사 시행 및 결과 두산퓨얼셀은 2024년 5월, 고객사를 대상으로 서비스만족도 조사를 실시했습니다． 총 20개의 고객사에 이메일을 통해 만족도 조사 안내를 발송했으며, 그 중 11개 고객사의 응답을 바탕으로 아래와 같은 결과를 도출했습니다. 장기 유지보수 계약(LTSA, Long Term Service Agreement) 운영품질에서는 설비의 효율, 정기 실적 보고서, 현장 대응업무에 대해서 긍정적인 의견을 받았으며 고객소통 부문에서는 계약담당자의 친절함, 고객사와의 교류활동에 대한 참여 및 지원에 적극적으로 참여해주었다는 의견 등 전반적으로 매우 긍정적인 응답을 받았습니다. 또한 환경안전보건(EHS) 부문에서도 작업 절차의 준수, 안전장비 착용, 고객사 안전보건협의회 참여에서 높은 만족도를 확인했습니다. 마지막으로 고객사 정기교육에 대해서는 모든 고객사가 높은 참여 의사를 보였고, 교육내용에 관한 다양한 건의사항은 추후 교육에 반영할 것입니다. 만족도 조사 전체 평균 80점 수준으로 확인할 수 있었으며, 2025년에는 고객만족도 측정 설문체계 개선점을 도출하여 운영과 제품 성능 그리고 고객 대응 만족도 향상으로 이어질 수 있게 개선할 계획입니다. 제품 리콜 당사의 제품은 2021년부터 2025년 상반기 현재까지 리콜된 이력이 없습니다. 연료전지는 고객사 납품 후 20년간의 장기 유지보수 계약(LTSA)를 체결하고 본사 직원이 직접 현장에서 제품의 운전과 수리/관리를 책임지고 있습니다. 고객사 Site별 연료전지는 본사 관제센터에서 운전 현황을 24시간 모니터링하고 있으며, 비정상 운전이 파악될 경우 원격 ...
-[p.88] 우편 서울특별시 중구 장충단로 275 두산타워 17층 두산퓨얼셀 이메일 inhye.jo@doosan.com 주관부서 두산퓨얼셀㈜ Legal/Compliance팀 윤리경영 윤리규범 서문 HELP DESK 운영 회사의 윤리경영 정책 및 윤리규범 세부내용, 기타 신고 및 제보 등과 관련된 궁금한 사항이나 문의에 대하여 상담, 안내할 수 있는 청구인 Help Desk를 두어 회사 홈페이지에 게재하였으며, 이를 통해 두산퓨얼셀㈜ 윤리경영 원칙과 업무 수행방침에 대해 두산퓨얼셀 내부 임직원은 물론 외부 이해관계자들의 이해를 향상시켰습니다. 사이버신고센터 운영방침 •  두산퓨얼셀 사이버신고센터는 임직원과 외부인 모두에게 열려 있으 며, 법령, 두산퓨얼셀 Credo 및 윤리규범 등 내부규정 위반행위, 기타 부당한 행위를 신고대상으로 합니다. •  신고는 익명 또는 실명으로 하실 수 있습니다. 다만, 회사는 구체적인 증거가 제시되지 않은 익명신고 등에 대하여 조사하지 않을 수 있습 니다. •  회사는 신고자의 신원 및 신고내용 등에 대한 비밀을 보장하며, 선의 의 신고자에 대한 불이익을 금지합니다. •  임직원의 신고에는 회사의 내부신고제도 운영규정이 적용되며, 본 규 정은 두드림 또는 주관부서를 통하여 안내 받으실 수 있습니다. •  회사는 사이버신고센터 이외에도 우편, 전화, 팩스, 이메일, 주관부서 방문 등 다양한 경로를 통하여 신고를 받고 있습니다. 접수 채널 윤리규범 및 윤리규범 위반과 관련한 문의사항이나 도움이 필요한 경우 두산퓨얼셀은 지속적인 성장을 위하여 인화, 고객 중심의 경영 철학과 함께 투명한 경영 및 혁신을 기반으로 기업의 경쟁력을 높이고 사회적 책임을 성실히 이행하고자 합니다. 이에 따라 윤리규범을 제정하여 임직원이 업무 수행 시 준수해야 할 행동 원칙으로 삼고 있습니다. 이 윤리규범은 두산퓨얼셀의 임직원(이하 "두산인")에게 적용되며, 두산퓨얼셀과 거래하는 협력업체 등 제3자도 함께 준수할 것을 권장합니다. 두산인은 관련법령과 윤리규범을 포함한 내부규정을 올바르게 이해하고 준수할 책임이 있습니다. Legal/Compliance팀은 윤리규범에서 명시되지 않았거나 구체적 해석이 필요한 사항에 대해 별도의 세부 규정을 마련 ...</x:v>
-      </x:c>
-      <x:c r="D15" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.88] 우편 서울특별시 중구 장충단로 275 두산타워 17층 두산퓨얼셀 이메일 inhye.jo@doosan.com 주관부서 두산퓨얼셀㈜ Legal/Compliance팀 윤리경영 윤리규범 서문 HELP DESK 운영 회사의 윤리경영 정책 및 윤리규범 세부내용, 기타 신고 및 제보 등과 관련된 궁금한 사항이나 문의에 대하여 상담, 안내할 수 있는 청구인 Help Desk를 두어 회사 홈페이지에 게재하였으며, 이를 통해 두산퓨얼셀㈜ 윤리경영 원칙과 업무 수행방침에 대해 두산퓨얼셀 내부 임직원은 물론 외부 이해관계자들의 이해를 향상시켰습니다. 사이버신고센터 운영방침 •  두산퓨얼셀 사이버신고센터는 임직원과 외부인 모두에게 열려 있으 며, 법령, 두산퓨얼셀 Credo 및 윤리규범 등 내부규정 위반행위, 기타 부당한 행위를 신고대상으로 합니다. •  신고는 익명 또는 실명으로 하실 수 있습니다. 다만, 회사는 구체적인 증거가 제시되지 않은 익명신고 등에 대하여 조사하지 않을 수 있습 니다. •  회사는 신고자의 신원 및 신고내용 등에 대한 비밀을 보장하며, 선의 의 신고자에 대한 불이익을 금지합니다. •  임직원의 신고에는 회사의 내부신고제도 운영규정이 적용되며, 본 규 정은 두드림 또는 주관부서를 통하여 안내 받으실 수 있습니다. •  회사는 사이버신고센터 이외에도 우편, 전화, 팩스, 이메일, 주관부서 방문 등 다양한 경로를 통하여 신고를 받고 있습니다. 접수 채널 윤리규범 및 윤리규범 위반과 관련한 문의사항이나 도움이 필요한 경우 두산퓨얼셀은 지속적인 성장을 위하여 인화, 고객 중심의 경영 철학과 함께 투명한 경영 및 혁신을 기반으로 기업의 경쟁력을 높이고 사회적 책임을 성실히 이행하고자 합니다. 이에 따라 윤리규범을 제정하여 임직원이 업무 수행 시 준수해야 할 행동 원칙으로 삼고 있습니다. 이 윤리규범은 두산퓨얼셀의 임직원(이하 "두산인")에게 적용되며, 두산퓨얼셀과 거래하는 협력업체 등 제3자도 함께 준수할 것을 권장합니다. 두산인은 관련법령과 윤리규범을 포함한 내부규정을 올바르게 이해하고 준수할 책임이 있습니다. Legal/Compliance팀은 윤리규범에서 명시되지 않았거나 구체적 해석이 필요한 사항에 대해 별도의 세부 규정을 마련 ...</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 7;45;84;88
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E15" s="6" t="str">
-        <x:v>Selected Style: risk-control
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: risk-control
 Preferred Style Source: template
 Answer Type: risk-control
 Answer Intent: Explain the risk/control scope, then prevention, monitoring, and follow-up actions.
@@ -927,34 +1176,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: High: must include risk/control and monitoring evidence.</x:v>
-      </x:c>
-      <x:c r="F15" s="6" t="str">
-        <x:v>추진 방향 두산퓨얼셀은 시장 경쟁력을 강화함으로써 불안정한 경영환경을 극복하고, 친환경 기술과 청정 에너지 솔루션을 바탕으로 탄소중립 실현과 지속가능한 미래를 가속화하기 위한 사업 모델을 전개하고 있습니다. 또한 운영 과정에서 발생하는 다양한 고객 의견(VOC)을 청취하고, 이를 제품 개선 및 서비스 품질 향상에 지속적으로 반영하고자 고객 만족도 조사(Survey)를 실시하고 있습니다. 이를 통해 두산퓨얼셀㈜ 윤리경영 원칙과 업무 수행방침에 대해 두산퓨얼셀 내부 임직원은 물론 외부 이해관계자들의 이해를 향상시켰습니다. 두산퓨얼셀는 제품 품질 및 안전 리스크 관리에서 식별된 위험 요인과 예방 활동을 연결해 관리 수준을 점검하고 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="6" t="str">
-        <x:v>EBX-Q-015</x:v>
-      </x:c>
-      <x:c r="B16" s="6" t="str">
-        <x:v>사회 / 지표 (Metrics) / 제품 안전 및 품질 관련 사고 현황</x:v>
-      </x:c>
-      <x:c r="C16" s="6" t="str">
-        <x:v>[p.18] ESG 목표 및 성과 Our Goal &amp; Performance 목표 세부 과제 2024년 성과 2025년 계획 친환경 경쟁력 강화 사업장 온실가스 감축 •  익산(PAFC) 공장 및 군산(SOFC) 공장 온실가스 배출량 416.93t 감축 •  익산PAFC 공장 전극 공정 에너지 절감 및 온실가스 배출 저감 활동 실시 •  익산PAFC 공장 제품 생산 원단위 온실가스 배출량 감축 중장기 로드맵 수립 • CCUS 연계형 모델 현장 Set-up 및 실증 완료 •  PAFC 모델 효율 제고 활동 지속 탄소중립 기여 제품/기술 확대 •  수소모델(5CSA PAFC 수소모델) 시제품  KESCO 인증 완료, 양산 시작 •  CCUS(Carbon Capture, Utilization and Storage, 탄소 포집, 활용 및 저장)연계형 모델 개발 및 시운전 완료 •  PAFC 모델 효율 제고 활동 진행 제품 전과정 환경 영향 최소화 •  Non-RCF(Refractory Ceramic Fibers, 내화성세라믹섬유) 부품 설계 진행 •  금속분리판 시제품 도면 설계 •  CSA(Cell Stack Assembly) 재사용/재제조  프로세스 구축 및 실행 •  Resin 재사용으로 자원 순환 활성화 •  Non-RCF 부품 개발 완료 •  금속분리판 시제품 제작 및 안정성 평가 •  CSA 재사용/재제조 수량 확대를 통한 폐기물 감축 •  Resin 재사용 지속 실행 및 사용량 감축 •  전극 비파괴 검사 방법 개발 및 적용으로 폐기물 감축 비재무 리스크 관리 확대 공급망 ESG 관리 확대 •  외부 전문기관 통해 공급망 ESG 평가 진행 •  평가 결과 바탕으로 개선 가이드 제공 •  협력사 대상 ESG 교육 및 평가 결과 제공 •  협력사 On-line 소통채널 구축 및 협력사 총회 /간담회 개최 •  주요 공급망 ESG 평가 진행 •  공급망 ESG 관리 절차서 제정하여 재계약 시 ESG 평가 결과 반영 •  협력사 경영 지원 활동 및 ESG 개선 지원  활동 시행 기후변화 리스크 정보 공개 •  IFRS 지속가능성 보고기준(ISSB)에 따라 기후 변화와 관련된 두산퓨얼셀의 거버넌스, 전략, ...
+QA Severity: High: must include risk/control and monitoring evidence.</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 시장 경쟁력을 강화함으로써 불안정한 경영환경을 극복하고, 친환경 기술과 청정 에너지 솔루션을 바탕으로 탄소중립 실현과 지속가능한 미래를 가속화하기 위한 사업 모델을 전개하고 있습니다. 운영 과정에서 발생하는 다양한 고객 의견(VOC)을 청취하고, 이를 제품 개선 및 서비스 품질 향상에 지속적으로 반영하고자 고객 만족도 조사(Survey)를 실시하고 있습니다. 두산퓨얼셀 사이버신고센터는 임직원과 외부인 모두에게 열려 있으며, 법령, 두산퓨얼셀 Credo 및 윤리규범 등 내부규정 위반행위, 기타 부당한 행위를 신고대상으로 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-015</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 지표 (Metrics) / 제품 안전 및 품질 관련 사고 현황</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>[p.18] ESG 목표 및 성과 Our Goal &amp; Performance 목표 세부 과제 2024년 성과 2025년 계획 친환경 경쟁력 강화 사업장 온실가스 감축 •  익산(PAFC) 공장 및 군산(SOFC) 공장 온실가스 배출량 416.93t 감축 •  익산PAFC 공장 전극 공정 에너지 절감 및 온실가스 배출 저감 활동 실시 •  익산PAFC 공장 제품 생산 원단위 온실가스 배출량 감축 중장기 로드맵 수립 • CCUS 연계형 모델 현장 Set-up 및 실증 완료 •  PAFC 모델 효율 제고 활동 지속 탄소중립 기여 제품/기술 확대 •  수소모델(5CSA PAFC 수소모델) 시제품  KESCO 인증 완료, 양산 시작 •  CCUS(Carbon Capture, Utilization and Storage, 탄소 포집, 활용 및 저장)연계형 모델 개발 및 시운전 완료 •  PAFC 모델 효율 제고 활동 진행 제품 전과정 환경 영향 최소화 •  Non-RCF(Refractory Ceramic Fibers, 내화성세라믹섬유) 부품 설계 진행 •  금속분리판 시제품 도면 설계 •  CSA(Cell Stack Assembly) 재사용/재제조  프로세스 구축 및 실행 •  Resin 재사용으로 자원 순환 활성화 •  Non-RCF 부품 개발 완료 •  금속분리판 시제품 제작 및 안정성 평가 •  CSA 재사용/재제조 수량 확대를 통한 폐기물 감축 •  Resin 재사용 지속 실행 및 사용량 감축 •  전극 비파괴 검사 방법 개발 및 적용으로 폐기물 감축 비재무 리스크 관리 확대 공급망 ESG 관리 확대 •  외부 전문기관 통해 공급망 ESG 평가 진행 •  평가 결과 바탕으로 개선 가이드 제공 •  협력사 대상 ESG 교육 및 평가 결과 제공 •  협력사 On-line 소통채널 구축 및 협력사 총회 /간담회 개최 •  주요 공급망 ESG 평가 진행 •  공급망 ESG 관리 절차서 제정하여 재계약 시 ESG 평가 결과 반영 •  협력사 경영 지원 활동 및 ESG 개선 지원  활동 시행 기후변화 리스크 정보 공개 •  IFRS 지속가능성 보고기준(ISSB)에 따라 기후 변화와 관련된 두산퓨얼셀의 거버넌스, 전략, ...
 [p.45] 생물다양성 보존 활동 두산퓨얼셀은 군산 공장이 위치한 전북 군산시 새만금 일대 생물다양성 보존을 위하여 2024년 국립생태원 멸종위기종복원센터와 업무협약을 체결하고, 멸종위기식물 Ⅱ급 ‘석곡’의 국내 최북단 자생지인 군산시 고군산군도 일대에 석곡 이식 및 서식지 보전을 위한 활동을 진행하고 있습니다. 멸종위기야생생물 보전 사업 주요 환경영향 및 관리항목 리스트 주요환경영향 관리항목 관련기록 관리주기 담당자 번호 위해요소 환경측면 1 액상 폐기물 누출 수질, 대기, 토양 환경운영 일상관리 환경일상운영관리 결과 매분기 제조EHS팀 방재장비함 점검 방재장비LIST 점검결과 매월 제조EHS팀 비상시 연락체계 구축 비상연락기준 변경시 제조EHS팀 2 오수(Overflow) 오수(Overflow) 일일 순찰 일일 순찰 일지 매일 경비실 오수 맨홀 상태 점검 오수 및 정화조 점검표 매월 관리지원팀 비상시 연락체계 구축 비상연락기준 변경시 제조EHS팀 구분 사업내용 사업기간 2024년9월~ 사업장소 전북특별자치도 군산시 고군산군도 내 대장도 사업재원 두산퓨얼셀 기부금 3,000만원 사업단계 두산퓨얼셀 임직원 대상 멸종위기야생생물 보전의 필요성 등 생태 전반에 관한 교육 진행 3. 멸종위기야생생물 보전교육 이식 후 모니터링 데이터를 통해 위협요인, 생육환경 등 도출 4. 석곡 이식지 연구 수행 지속적인 협업을 통한 멸종위기식물 관리 5.  석곡 등 멸종위기식물 증식 및 유지ㆍ관리 2-1. 이식 후보지 탐색 및 선정 2-2. 이식 후 모니터링 2-3. 이식 후 개체 및 서식지 관리 무인비행기(드론) 조사를 통해 고군산군도 내 암석에 서식하는 석곡 서식지 탐색 1. 석곡 신규서식지 발굴 2. 대체서식지 내 이식 고군산군도 내 석곡 개체 이식 및 서식지 복원 활동내역 업무협약 체결 ('24.10) 석곡 증식 연구 지원 (‘24.10~) 석곡 200개체 이식 (‘25.4) 이식 후 서식지 관리 (‘25.5~) 상황 시나리오대본내용 역할및 행동내용 글리콜 저장소 방유제 펌핑 작업 1.글리콜저장소 방제활동 실시 "소화활동으로 화재진압이 완료되었지만, 글리콜저장소 방유제에 균열이 발생하여 유출될 가능성이 있으므로 신속하게 방제활동을 실시하기 바랍니다." 2. 소 ...
 [p.67] 안전보건 안전보건 관리 활동 두산퓨얼셀은 임직원과 협력사 근로자의 안전과 건강을 최우선으로 생각하며 인간 존중 경영을 실천하고 있습니다. EHS와 관련된 위험 요소를 사전에 파악하고 제거하거나 최소화하기 위해 다양한 평가, 점검 및 비상 대응체계를 운영하고 있습 니다. 특히 솔선수범하는 리더십을 바탕으로 임원과 리더 직급의 자율적인 안전보건 활동을 확산시키기 위해 지속적으로 노력하고 있습니다. 또한 매달 EHS 뉴스레터를 발행하여 일상생활에서 유용한 안전 및 건강 정보를 제공하고 있으며, 각 사업장별 이벤트를 통해 임직원의 EHS에 대한 관심과 참여를 유도하고 있습니다. &gt; 안전보건 조직 구축 및 목표 수립 &gt; 안전보건 리더십 활동 &gt; 고객서비스 안전보건관리 두산퓨얼셀은 EHS 방침을 기반으로 전사 및 사업장의 안전보건 목표를 설 정하고 이를 체계적으로 시행하고 있습니다. 또한 안전사고를 예방하고 각 조직의 안전보건 목표를 달성하기 위해 안전보건 전담 부서를 설치, 운영하 고 있습니다. 각 사이트별로 관리 감독자를 선임하고 안전보건 담당자를 지 정하여 효과적으로 운영하고 있습니다. &gt; 임직원 건강 증진 두산퓨얼셀은 임직원의 건강 증진과 직업성 질환 예방을 위해 정기적인 건 강검진을 실시하고 있습니다. 유소견자에 대해서는 지속적인 건강 상담과 추적 관리는 물론, 다양한 건강 증진 프로그램도 함께 운영하고 있습니다. 또한 임직원의 자발적인 건강 관리를 지원하기 위해 체력 측정 이벤트, 금연 프로그램 등도 함께 추진하고 있습니다. 두산퓨얼셀은 경영진의 안전보건 실천 의지를 표명하고 안전점검, 회의, 간담 회 등 다양한 활동을 통해 EHS 리더십을 적극 실천하고 있습니다. 또한 안전보건경영시스템 운영 및 관련 법규 준수 사항에 대해 근로자가 직 접 참여하는 EHS 협의기구를 운영하여, EHS 활동에 대한 책임과 권한을 부 여하고 있습니다. 이를 통해 임직원의 자주적인 안전 활동을 유도하고 안전의 식을 높여, 사업장 내 사고 예방과 지속 가능한 성장에 기여하고 있습니다. &gt; 외주공사 안전관리 및 협력관계 구축 두산퓨얼셀은 사업장에서 발생하는 외주공사 재해예방을 위한 관리규정을 제정하고, 사내 공사 및 유지보수 서비스 현장에 대한 안전관리 프로세 ...
-[p.95] 보안사고 후속 조치 ❶  보안사고에 대한 재발방지 대책이 요구되는 경우 보안 사고 대상 부서의 책임자 등은 사고처리 결과를 통보받은 날로부터 2주 이내에 재발방지에 대한 조치 또는 조치계획을 수립하여 보안담당부서에 보고해야 한다. ❷  보안담당부서원은 요구된 재발방지 대책에 대하여 보안사고 대상 부서의 책임자 등이 적절한 조치를 취했는지 확인해야 한다. 단, 해당 조치의 확인시기는 긴급성과 중요성 등을 고려하여 차등적으로 결정할 수 있다. ❸  회사는 보안사고 조사결과에 따라 관련 임직원 및 책임자를 징계, 처벌할 수 있으며, 필요한 경우 법적 조치를 취할 수 있다. 사고조사 및 대응 ❶  보안담당부서 또는 긴급 사고대응 조직은 초기대응 완료 후 수집한 증거 및 증적의 법적 증거력이 훼손되지 않도록 해당 보안사고에 대한 조사를 실시하며, 필요할 경우 대외기관에 협조를 요청할 수 있다. ❷ 사고조사 중에도 필요한 경우 피해가 확산되지 않도록 선 조치를 취할 수 있다. ❸  보안담당부서 또는 긴급 사고대응 조직은 사고 조사 완료 후 다음의 각 호에 대한 결과를 보고서로 작성하여 사고의 경중에 따라 보안담당 임원 등에게 보고하여야 한다. 단, 필요시에는 조사 중에도 보안담당 임원 등에게 이를 보고할 수 있다.  1) 사고 주체 및 인적사항 2) 사고발생 일시 및 장소 3) 사고내용 및 경위 4) 조사 결과에 대한 판단 5) 사후조치 및 개선 권고사항 ❹ 보안사고에 대한 내용은 조사가 종료되기 전까지 공개하지 않으며, 조사결과는 관련당사자인 임직원과 보안 담당 임원 및 최고 경영진 외에는 공개를 제한한다. 초기대응 ❶  임직원은 임의적 대응을 자제하고 즉시 보안담당부서에 신고한 후 보안담당부서의 지시를 따른다. 단, 랜섬웨어와 같이 회사의 네트워크를 통한 피해 확산이 우려 되는 경우에는 해당 전산장비를 회사의 유무선 네트워크로부터 분리시킨 후, 보안담당부서에 즉시 신고하여야 한다. ❷  보안담당부서는 각 영역별 정보시스템 관리부서, 운영 부서 및 유관부서 등에 보안사고 또는 위험을 알리고 피해가 확산되지 않도록 초동 조치를 취하게 한 후 사고의 경중을 평가하여야 한다. 보안담당부서는 사고의 경중을 판단하여 보안담당 임원에게 이를 ...</x:v>
-      </x:c>
-      <x:c r="D16" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.95] 보안사고 후속 조치 ❶  보안사고에 대한 재발방지 대책이 요구되는 경우 보안 사고 대상 부서의 책임자 등은 사고처리 결과를 통보받은 날로부터 2주 이내에 재발방지에 대한 조치 또는 조치계획을 수립하여 보안담당부서에 보고해야 한다. ❷  보안담당부서원은 요구된 재발방지 대책에 대하여 보안사고 대상 부서의 책임자 등이 적절한 조치를 취했는지 확인해야 한다. 단, 해당 조치의 확인시기는 긴급성과 중요성 등을 고려하여 차등적으로 결정할 수 있다. ❸  회사는 보안사고 조사결과에 따라 관련 임직원 및 책임자를 징계, 처벌할 수 있으며, 필요한 경우 법적 조치를 취할 수 있다. 사고조사 및 대응 ❶  보안담당부서 또는 긴급 사고대응 조직은 초기대응 완료 후 수집한 증거 및 증적의 법적 증거력이 훼손되지 않도록 해당 보안사고에 대한 조사를 실시하며, 필요할 경우 대외기관에 협조를 요청할 수 있다. ❷ 사고조사 중에도 필요한 경우 피해가 확산되지 않도록 선 조치를 취할 수 있다. ❸  보안담당부서 또는 긴급 사고대응 조직은 사고 조사 완료 후 다음의 각 호에 대한 결과를 보고서로 작성하여 사고의 경중에 따라 보안담당 임원 등에게 보고하여야 한다. 단, 필요시에는 조사 중에도 보안담당 임원 등에게 이를 보고할 수 있다.  1) 사고 주체 및 인적사항 2) 사고발생 일시 및 장소 3) 사고내용 및 경위 4) 조사 결과에 대한 판단 5) 사후조치 및 개선 권고사항 ❹ 보안사고에 대한 내용은 조사가 종료되기 전까지 공개하지 않으며, 조사결과는 관련당사자인 임직원과 보안 담당 임원 및 최고 경영진 외에는 공개를 제한한다. 초기대응 ❶  임직원은 임의적 대응을 자제하고 즉시 보안담당부서에 신고한 후 보안담당부서의 지시를 따른다. 단, 랜섬웨어와 같이 회사의 네트워크를 통한 피해 확산이 우려 되는 경우에는 해당 전산장비를 회사의 유무선 네트워크로부터 분리시킨 후, 보안담당부서에 즉시 신고하여야 한다. ❷  보안담당부서는 각 영역별 정보시스템 관리부서, 운영 부서 및 유관부서 등에 보안사고 또는 위험을 알리고 피해가 확산되지 않도록 초동 조치를 취하게 한 후 사고의 경중을 평가하여야 한다. 보안담당부서는 사고의 경중을 판단하여 보안담당 임원에게 이를 ...</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 18;45;67;95
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E16" s="6" t="str">
-        <x:v>Selected Style: status-performance
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: status-performance
 Preferred Style Source: template
 Answer Type: status-performance
 Answer Intent: Explain the reported status in plain language, then weave figures into the management meaning.
@@ -973,34 +1234,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: High: topic-fit figures, non-repetitive opening, no technical metric label.</x:v>
-      </x:c>
-      <x:c r="F16" s="6" t="str">
-        <x:v>두산퓨얼셀는 제품 안전 및 품질 관련 사고 현황에 대해 발생 현황과 관리 성과를 함께 확인할 수 있도록 보고하고 있습니다. 특히 솔선수범하는 리더십을 바탕으로 임원과 리더 직급의 자율적인 안전보건 활동을 확산시키기 위해 지속적으로 노력하고 있습니다. 공개된 수치와 설명은 제품 안전 및 품질 관련 사고 현황의 현재 수준을 확인하고 다음 관리 과제를 판단하는 기준이 되며, 전년 수치와 함께 제시될 때 추세 확인에도 활용될 수 있습니다. 제품 안전 및 품질 관련 사고 현황는 단순한 발생 여부뿐 아니라 접수, 처리, 예방 조치가 관리 체계 안에서 이어지는지를 함께 확인하는 기준으로 활용되며, 공개 범위가 제한될 경우 후속 점검과 내부 관리 보완 여부를 함께 검토할 필요가 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="6" t="str">
-        <x:v>EBX-Q-016</x:v>
-      </x:c>
-      <x:c r="B17" s="6" t="str">
-        <x:v>사회 / 전략 (Strategy) / 정보보안 및 개인정보 보호 정책</x:v>
-      </x:c>
-      <x:c r="C17" s="6" t="str">
-        <x:v>[p.76] 공급망 ESG 관리 &gt; 4. 환경 &gt; 5. 윤리 및 공정거래 5.1 투명경영 및 반부패: 모든 비즈니스 관계에 있어 최고 수준의 윤리 기준이 요구됩니다. 모든 형태의 부패나 갈취, 횡령, 뇌물 수수, 상납, 향응 등의 비윤리적 행위는 엄격히 금지하는 무관용 정책을 표방해야 합니다. 두산퓨얼셀의 협력회사는 이러한 비윤리적 행위에 대한 감시 및 단속 절차를 이행하여 자율적 윤리 준수를 실천하고 반부패 법령을 준수하기 위해 감시, 기록 관리, 집행 절차를 실행해야 합니다. 5.2 공정거래 준수: 두산퓨얼셀의 협력회사는 사업상에서 부당하거나 부적절한 거래를 통해 이익을 취하는 수단을 제공하거나 수락하는 행위를 금지해야 합니다. 공정거래와 관련한 법규와 규정을 준수하여야 하며, 불공정한 거래 관행 등 공정한 거래 질서를 저해하는 행위를 하여서는 안 됩니다. 또한 상품 또는 용역의 가격, 공급량, 거래 지역, 거래조건 등에 관해 다른 사업자와 부당하게 경쟁을 제한하는 행위를 합의해서는 안 되며 회사, 경쟁업체, 협력업체, 제3자로부터 부정하게 정보를 획득하거나 획득한 정보를 사용 또는 공개해서는 안됩니다. 5.3 투명한 정보공개: 두산퓨얼셀의 협력회사는 관련법과 규정을 준수하여, 사업 활동과 재정 상황, 사업성과 등에 대한 정보를 거짓 없이 공개해야 합니다. 모든 업무 거래를 투명하게 실행하고 협력회사의 사업 장부와 기록에 정확히 반영해야 합니다. 협력회사의 노동, 보건과 안전, 환경관리 실태, 사업 활동, 구조, 재무 현황 및 성과에 관한 정보를 관련 일반적인 산업계 관행에 따라 공개해야 합니다. 공급망 내 관련 분야 실태 및 관행에 대한 기록 위조나 부실 표기는 용인될 수 없습니다. 5.4 지적재산권 보호: 두산퓨얼셀의 협력회사는 사업상 타인의 특허, 소프트웨어, 디자인, 상표 등과 같은 지적 재산을 침해하거나 불법적으로 사용하지 않습니다. 지적재산권을 존중하며 기술 및 노하우의 이전은 해당 권리를 보호하는 방식으로 이루어져야 합니다. 5.5 개인정보보호: 두산퓨얼셀의 협력회사는 모든 이해관계자(협력회사, 고객사, 임직원 등)의 개인정보를 체계적으로 관리 및 보호해야 하며, 개인정보의 수집, 저장, 이용, 제공, 파기 등 처리 시 관련 법규를 ...
+QA Severity: High: topic-fit figures, non-repetitive opening, no technical metric label.</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 제품 안전 및 품질 관련 사고 현황에 대해 발생 현황과 관리 성과를 함께 확인할 수 있도록 보고하고 있습니다. 두산퓨얼셀은 임직원과 협력사 근로자의 안전과 건강을 최우선으로 생각하며 인간 존중 경영을 실천하고 있습니다. 매달 EHS 뉴스레터를 발행하여 일상생활에서 유용한 안전 및 건강 정보를 제공하고 있으며, 각 사업장별 이벤트를 통해 임직원의 EHS에 대한 관심과 참여를 유도하고 있습니다. 공개된 수치와 설명은 제품 안전 및 품질 관련 사고 현황의 현재 수준을 확인하고 다음 관리 과제를 판단하는 기준이 되며, 전년 수치와 함께 제시될 때 추세 확인에도 활용될 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-016</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 전략 (Strategy) / 정보보안 및 개인정보 보호 정책</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>[p.76] 공급망 ESG 관리 &gt; 4. 환경 &gt; 5. 윤리 및 공정거래 5.1 투명경영 및 반부패: 모든 비즈니스 관계에 있어 최고 수준의 윤리 기준이 요구됩니다. 모든 형태의 부패나 갈취, 횡령, 뇌물 수수, 상납, 향응 등의 비윤리적 행위는 엄격히 금지하는 무관용 정책을 표방해야 합니다. 두산퓨얼셀의 협력회사는 이러한 비윤리적 행위에 대한 감시 및 단속 절차를 이행하여 자율적 윤리 준수를 실천하고 반부패 법령을 준수하기 위해 감시, 기록 관리, 집행 절차를 실행해야 합니다. 5.2 공정거래 준수: 두산퓨얼셀의 협력회사는 사업상에서 부당하거나 부적절한 거래를 통해 이익을 취하는 수단을 제공하거나 수락하는 행위를 금지해야 합니다. 공정거래와 관련한 법규와 규정을 준수하여야 하며, 불공정한 거래 관행 등 공정한 거래 질서를 저해하는 행위를 하여서는 안 됩니다. 또한 상품 또는 용역의 가격, 공급량, 거래 지역, 거래조건 등에 관해 다른 사업자와 부당하게 경쟁을 제한하는 행위를 합의해서는 안 되며 회사, 경쟁업체, 협력업체, 제3자로부터 부정하게 정보를 획득하거나 획득한 정보를 사용 또는 공개해서는 안됩니다. 5.3 투명한 정보공개: 두산퓨얼셀의 협력회사는 관련법과 규정을 준수하여, 사업 활동과 재정 상황, 사업성과 등에 대한 정보를 거짓 없이 공개해야 합니다. 모든 업무 거래를 투명하게 실행하고 협력회사의 사업 장부와 기록에 정확히 반영해야 합니다. 협력회사의 노동, 보건과 안전, 환경관리 실태, 사업 활동, 구조, 재무 현황 및 성과에 관한 정보를 관련 일반적인 산업계 관행에 따라 공개해야 합니다. 공급망 내 관련 분야 실태 및 관행에 대한 기록 위조나 부실 표기는 용인될 수 없습니다. 5.4 지적재산권 보호: 두산퓨얼셀의 협력회사는 사업상 타인의 특허, 소프트웨어, 디자인, 상표 등과 같은 지적 재산을 침해하거나 불법적으로 사용하지 않습니다. 지적재산권을 존중하며 기술 및 노하우의 이전은 해당 권리를 보호하는 방식으로 이루어져야 합니다. 5.5 개인정보보호: 두산퓨얼셀의 협력회사는 모든 이해관계자(협력회사, 고객사, 임직원 등)의 개인정보를 체계적으로 관리 및 보호해야 하며, 개인정보의 수집, 저장, 이용, 제공, 파기 등 처리 시 관련 법규를 ...
 [p.93] 중요 영업비밀에 대한 법적 보호 및 보안관리를 위해 영업비밀 목록을 구축하여 매년 업데이트하고 있으며, 외부 반출 이력을 탐지 및 차단하는 정책을 적용하여 영업비밀 유·노출 위험을 최소화하고 있습니다. 부서 내 보안의식을 전파하고, 보안사고 또는 징후가 있을 경우 보안담당부서와 협업할 수 있도록 부서별 보안책임자 및 담당자를 지정했습니다. 정보보안 및 고객 정보보호 정보보안 운영체계 두산퓨얼셀은 국가핵심기술(수소, '23.4월 지정) 취급사로서, 「산업기술의 유출방지 및 보호에 관한 법률」 과 「산업기술보호지침」 등에 따라 관계 국가기관으로부터 정기적인 보안관리 체계, 정보시스템 관리, 보안취약점 점검 등을 감사받고 있습니다. 당사는 정보 보안 문제를 감독하는 임원급 책임자인 정보보호최고책임자(CISO)와 개인정보보호 최고 책임자(CPO)를 지정하고 산하의 보안담당부서를 중심으로 국가핵심기술 보호를 위한 조치/관리 활동을 추진하고 있으며, 사내 IT/OT 시스템, 애플리케이션, 네트워크 인프라 등의 취약성을 점검하고 정보 보안 시스템을 지속적으로 개선해 내/외부의 보안 위협으로부터 회사의 자산을 보호하고 있습니다. 보안 총괄부서는 국가핵심기술 유출사고 예방을 위한 모니터링 및 유해 트래픽 감시를 담당하고, 개인정보를 다루는 관련 부서 간 효율적인 업무 추진 및 소통을 위하여 정기적으로 보안 협의회를 운영하고 있습니다. 보안 이상 문제 발생 시, 보안 협의회를 통해 조치 방안을 수립 및 실행하고 재발방지 대책을 논의하고 있습니다. 두산퓨얼셀은 두산 그룹의 계열사로서 ㈜두산에서 정보보안외부 인증인 ISMS를 획득했고, 제3자 취약점 분석의 일환으로 ㈜두산에서 주최한 모의해커훈련에 참여하여 정보보안 강화에 힘쓰고 있습니다. CISO 생산/운영 정보보호책임자 (익산/군산) 정보보호책임자 정보보호책임자 (서울) 정보보호담당자 (익산/군산) 정보보호담당자 정보보호담당자 (서울) 연구소 전사 정보보호책임자 전사 정보보호담당자 서비스부문 2020년 보안규정(HR&amp;협력사, IT시스템, 보안감사, 보안관리, 보안사고대응, 시설보안, 영업비밀보호, 정보자산 및 정보기기, 클라우드 보안정책) 제정 후 매년 검토하여 필요시 개정하고 있으며, 보안정책은 사내 ...
 [p.94] 정보보안 및 고객 정보보호 정보보호 인식 제고 두산퓨얼셀은 전 임직원을 대상으로 정보유출 예방, 영업비밀 보호, 정보기기 관리, 개인정보보호 등을 내용으로 하는 정보보호 교육을 연 1회 필수 과정으로 운영하고 있습니다. 계정 탈취 목적의 피싱 이메일(Phishing Email)을 이용한 랜섬웨어 유포, 송금사기, 정보유출 피해를 예방하기 위하여 분기별로(연 4회) 모의 훈련을 실시(해킹메일 모의 훈련 3회, 개인정보보호 유출 대응 모의 훈련 1회)하고, 후속 캠페인을 통해 해킹메일 구별과 신고 방법을 교육해 임직원의 대응 역량을 향상시켰습니다(보안 이슈 신고서, 처리 보고서 작성, 담당부서 신고 및 사후 처리 등). 보안진단의 날을 연 4회 지정하여 보안 관련 뉴스 및 주요 공지를 전달하고, 임직원이 보안 관리 상태를 자가 점검할 수 있도록 체크리스트와 가이드를 제공하고 있습니다. 목적 내용 대상 보안 점검/조치 PC DI 생활보안 개인 정보시스템 부서 영업비밀문서 시설구역출입 보안담당중점 보안관리 의식 강화 보안 Newsletter 교육 및 훈련 활동명 내용 대상 주기 임직원 보안/개인정보보호 교육 보안 준수사항 안내 전 임직원 연 1회 신입/경력사원 정보보호 교육 보안규정 및 프로세스 안내 신입/경력사원 입사 시 부서별 보안담당자/책임자 교육 보안규정 및 프로세스 안내 부서별 보안담당자·책임자 연 1회 협력사 보안 교육 협력업체 정보보호 준수 사항 안내 협력회사 직원 연 1회 해킹 모의훈련 해킹메일 대응, 개인정보보호 유출 대응 전 임직원 연 4회 보안진단의 날 임직원 보안의식 제고(보안 뉴스 등) 전 임직원 연 4회 정보보안 및 고객정보보호를 위한 주요 활동 보안진단의 날 점검 사항 정보보안 관련 게시물 Doosan Fuel Cell Sustainability Report 2025 Company Overview Materiality ESG Strategy ESG Performance Appendix Social 인재경영 인권경영 안전보건 사회공헌 공급망 ESG 관리 고객 만족 Governance 지배구조 윤리경영 혁신경영 정보보안 및 고객 정보보호 리스크 관리 협회 및 단체활동 Environmental 환경경영 사업장 환경 성과 ...
-[p.96] 수집하는 개인정보의 항목 및 수집 방법 1)  고충민원 처리 - 필수항목: 이름, 이메일 주소 2)  서비스 분석 및 서비스 수준 - 서비스 이용기록, 접속로그, 쿠키, 접속IP 정보 3)  채용 전형/결정 - 일반정보: 성명(국문/한자/영문), 생년월일, 성별, 사진, 비밀번호 등 - 민감정보: 장애여부 및 장애구분/장애등급 개인정보의 제3자 제공 정보주체로부터 별도의 동의를 받는 경우 - 법률에 특별한 규정이 있거나 법령상 의무를 준수하기 위하여 불가피한 경우 -  정보주체 또는 그 법정대리인이 의사표시를 할 수 없는 상태에 있거나 주소불명 등으로 사전 동의를 받을 수 없는 경우 개인정보의 수집 이용 목적 1)  고객 관련 -  서비스 분석 및 서비스 수준 제고: 서비스 이용분석을 통해 이용자에게 더 나은 서비스를 제 공하고 본 사이트의 수준 향상(서비스 분석 및 서비스 수준 제고) 등 - 고충·민원 처리: 민원사항 확인, 사실조사를 위한 연락·통지, 처리결과 통보 등 2)  채용 관련 -  채용 전형/결정: 본인 식별 및 실명 확인, 입사 전형 및 지원자와의 연락, 국가유공자법,  장애인고용촉진법 등 관련 사항의 채용상 참고(보훈 대상, 장애 관련 정보 등) 등 개인정보 보호책임자 및 담당자 안내 가.  개인정보 보호책임자 - 성명: 방원조 상무 나.  개인정보 담당부서 - 명칭: 두산퓨얼셀(주) 변화추진/생산관리팀  - 전화번호: 063-831-0717  - 팩스번호: 063-831-0717  - 이메일: daeha.kim@doosan.com 정보보안 및 고객 정보보호 개인정보보호 관리체계 &gt; 개인정보보호 강화 두산퓨얼셀은 개인정보를 안전하게 보호하고 국내외 개인정보보호 법규를 준수하기 위해, 법률 제정 및 변화를 지속적으로 모니터링하여 내부관리계획, 개인정보보호 규정 등에 반영하고, 담당조직에 전파하고 있습니다. 개인정보취급자 및 개인정보처리시스템을 대상으로 매년 이행점검, 위·수탁사 교육 및 점검, 주요 영역 내부감사 등을 진행하고, 도출된 취약점을 개선하여 관리하고 있습니다. •  당사는 개인정보를 수락하는 업체의 개인정보보호 인식 및 관리 수준을 높이기 위해 담당자를 지정하여 연 1회 ...</x:v>
-      </x:c>
-      <x:c r="D17" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.96] 수집하는 개인정보의 항목 및 수집 방법 1)  고충민원 처리 - 필수항목: 이름, 이메일 주소 2)  서비스 분석 및 서비스 수준 - 서비스 이용기록, 접속로그, 쿠키, 접속IP 정보 3)  채용 전형/결정 - 일반정보: 성명(국문/한자/영문), 생년월일, 성별, 사진, 비밀번호 등 - 민감정보: 장애여부 및 장애구분/장애등급 개인정보의 제3자 제공 정보주체로부터 별도의 동의를 받는 경우 - 법률에 특별한 규정이 있거나 법령상 의무를 준수하기 위하여 불가피한 경우 -  정보주체 또는 그 법정대리인이 의사표시를 할 수 없는 상태에 있거나 주소불명 등으로 사전 동의를 받을 수 없는 경우 개인정보의 수집 이용 목적 1)  고객 관련 -  서비스 분석 및 서비스 수준 제고: 서비스 이용분석을 통해 이용자에게 더 나은 서비스를 제 공하고 본 사이트의 수준 향상(서비스 분석 및 서비스 수준 제고) 등 - 고충·민원 처리: 민원사항 확인, 사실조사를 위한 연락·통지, 처리결과 통보 등 2)  채용 관련 -  채용 전형/결정: 본인 식별 및 실명 확인, 입사 전형 및 지원자와의 연락, 국가유공자법,  장애인고용촉진법 등 관련 사항의 채용상 참고(보훈 대상, 장애 관련 정보 등) 등 개인정보 보호책임자 및 담당자 안내 가.  개인정보 보호책임자 - 성명: 방원조 상무 나.  개인정보 담당부서 - 명칭: 두산퓨얼셀(주) 변화추진/생산관리팀  - 전화번호: 063-831-0717  - 팩스번호: 063-831-0717  - 이메일: daeha.kim@doosan.com 정보보안 및 고객 정보보호 개인정보보호 관리체계 &gt; 개인정보보호 강화 두산퓨얼셀은 개인정보를 안전하게 보호하고 국내외 개인정보보호 법규를 준수하기 위해, 법률 제정 및 변화를 지속적으로 모니터링하여 내부관리계획, 개인정보보호 규정 등에 반영하고, 담당조직에 전파하고 있습니다. 개인정보취급자 및 개인정보처리시스템을 대상으로 매년 이행점검, 위·수탁사 교육 및 점검, 주요 영역 내부감사 등을 진행하고, 도출된 취약점을 개선하여 관리하고 있습니다. •  당사는 개인정보를 수락하는 업체의 개인정보보호 인식 및 관리 수준을 높이기 위해 담당자를 지정하여 연 1회 ...</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 76;93;94;96
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E17" s="6" t="str">
-        <x:v>Selected Style: narrative
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: narrative
 Preferred Style Source: template
 Answer Type: strategy-policy
 Answer Intent: Explain the policy or strategic direction first, then connect targets, governance, and execution evidence.
@@ -1019,32 +1292,44 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: Medium: prose must be natural, evidence-grounded, and non-repetitive.</x:v>
-      </x:c>
-      <x:c r="F17" s="6" t="str">
-        <x:v>당사는 정보 보안 문제를 감독하는 임원급 책임자인 정보보호최고책임자(CISO)와 개인정보보호 최고 책임자(CPO)를 지정하고 산하의 보안담당부서를 중심으로 국가핵심기술 보호를 위한 조치/관리 활동을 추진하고 있으며, 사내 IT/OT 시스템, 애플리케이션, 네트워크 인프라 등의 취약성을 점검하고 정보 보안 시스템을 지속적으로 개선해 내/외부의 보안 위협으로부터 회사의 자산을 보호하고 있습니다. 정보보안 및 고객 정보보호 정보보호 인식 제고 두산퓨얼셀은 전 임직원을 대상으로 정보유출 예방, 영업비밀 보호, 정보기기 관리, 개인정보보호 등을 내용으로 하는 정보보호 교육을 연 1회 필수 과정으로 운영하고 있습니다. 이러한 내용은 정보보안 및 개인정보 보호 정책가 선언에 머물지 않고 목표, 조직, 실행 과제로 이어지는 구조임을 보여줍니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="6" t="str">
-        <x:v>EBX-Q-017</x:v>
-      </x:c>
-      <x:c r="B18" s="6" t="str">
-        <x:v>사회 / 거버넌스 (Governance) / 정보보호 관리 조직</x:v>
-      </x:c>
-      <x:c r="C18" s="6" t="str">
-        <x:v>[p.93] 중요 영업비밀에 대한 법적 보호 및 보안관리를 위해 영업비밀 목록을 구축하여 매년 업데이트하고 있으며, 외부 반출 이력을 탐지 및 차단하는 정책을 적용하여 영업비밀 유·노출 위험을 최소화하고 있습니다. 부서 내 보안의식을 전파하고, 보안사고 또는 징후가 있을 경우 보안담당부서와 협업할 수 있도록 부서별 보안책임자 및 담당자를 지정했습니다. 정보보안 및 고객 정보보호 정보보안 운영체계 두산퓨얼셀은 국가핵심기술(수소, '23.4월 지정) 취급사로서, 「산업기술의 유출방지 및 보호에 관한 법률」 과 「산업기술보호지침」 등에 따라 관계 국가기관으로부터 정기적인 보안관리 체계, 정보시스템 관리, 보안취약점 점검 등을 감사받고 있습니다. 당사는 정보 보안 문제를 감독하는 임원급 책임자인 정보보호최고책임자(CISO)와 개인정보보호 최고 책임자(CPO)를 지정하고 산하의 보안담당부서를 중심으로 국가핵심기술 보호를 위한 조치/관리 활동을 추진하고 있으며, 사내 IT/OT 시스템, 애플리케이션, 네트워크 인프라 등의 취약성을 점검하고 정보 보안 시스템을 지속적으로 개선해 내/외부의 보안 위협으로부터 회사의 자산을 보호하고 있습니다. 보안 총괄부서는 국가핵심기술 유출사고 예방을 위한 모니터링 및 유해 트래픽 감시를 담당하고, 개인정보를 다루는 관련 부서 간 효율적인 업무 추진 및 소통을 위하여 정기적으로 보안 협의회를 운영하고 있습니다. 보안 이상 문제 발생 시, 보안 협의회를 통해 조치 방안을 수립 및 실행하고 재발방지 대책을 논의하고 있습니다. 두산퓨얼셀은 두산 그룹의 계열사로서 ㈜두산에서 정보보안외부 인증인 ISMS를 획득했고, 제3자 취약점 분석의 일환으로 ㈜두산에서 주최한 모의해커훈련에 참여하여 정보보안 강화에 힘쓰고 있습니다. CISO 생산/운영 정보보호책임자 (익산/군산) 정보보호책임자 정보보호책임자 (서울) 정보보호담당자 (익산/군산) 정보보호담당자 정보보호담당자 (서울) 연구소 전사 정보보호책임자 전사 정보보호담당자 서비스부문 2020년 보안규정(HR&amp;협력사, IT시스템, 보안감사, 보안관리, 보안사고대응, 시설보안, 영업비밀보호, 정보자산 및 정보기기, 클라우드 보안정책) 제정 후 매년 검토하여 필요시 개정하고 있으며, 보안정책은 사내 ...
-[p.97] 2차 방어선 (2nd line of defence) 리스크 관리 리스크 관리 거버넌스 두산퓨얼셀은 체계적이고 전사적인 리스크 관리 활동을 통해 영업의 효율성, 재무보고의 신뢰성, 법규 및 규정 준수 등의 조직 목표를 효과적 ㆍ 효율적으로 달성하기 위하여 적절한 내부통제 체계를 갖추고 있습니다. 제품 제조 ㆍ 생산 ㆍ 공급하는데 직접적으로 관여하는 부서는 일상적인 운영에서 1차적으로 리스크를 관리하고 모니터링할 책임이 있으며, 리스크 모니터링 전담 부서와 기능적으로 분할된 관련 부서들이 2차적으로 리스크를 관리 ㆍ 감독하고 있습니다. 마지막으로 두산퓨얼셀은 상법 제542조의13 등 관련 규정에 의거하여 준법지원인을 선임하였으며, 준법지원인은 위험 관리 및 규정 준수 프로세스의 효과에 대한 독립적인 보증을 제공하는 내부 감사 기능을 수행합니다. 잠재 리스크 및 대응 활동 잠재 리스크 연료전지 시장 다각화(혁신기술 개발 요구) 인공지능(AI) 기술의 발전에 따른 보안 위협 설명 연료전지 시장이 다각화 됨에 따라 혁신기술 개발 요구가 증대되고 있습니다. 기업은 빠르게 변화하는 시장 환경에서 고객의 니즈에 부합하는 기술 개발을 위해 자원과 역량을 투입해야 합니다. AI 기술의 발전은 기업의 생산성 향상에 기여하는 한편, 악용 사례로 인한 사이버 보안 위협도 함께 증가시키고 있습니다. 기업은 기존 보안 시스템으로 대응이 어려운 신규 보안 위협 요인에 대비가 필요합니다. 영향 혁신기술을 적시에 개발하지 못하거나 성공적으로 상용화하지 못할 경우, 기술 개발 투자에서 기대했던 이익이 실현되지 않아 회사의 수익성과 매출에 부정적인 영향을 미칠 수 있습니다. 두산퓨얼셀은 국가핵심기술 취급사로서, 국내외 시장에서 차지하는 기술적·경제적 가치가 높아 관련 정보가 유출될 경우 당사의 기술 경쟁력 뿐만 아니라 국가 안보와 국민경제의 발전에 중대한 악영향을 미칠 수 있습니다. 대응 두산퓨얼셀은국내 최초 상용화 한 SOFC(고체산화물 연료전지) 기술을 바탕으로 한 선박용 연료전지 시장 진출을 위해 기술 확보 및 생산설비를 구축하고, 선사, 조선사 등과 함께 선박용 연료전지 실증사업을 추진하고 있습니다. 두산퓨얼셀은 정보보호최고책임자(CISO)와 개인정보보호 최고 책 ...</x:v>
-      </x:c>
-      <x:c r="D18" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+QA Severity: Medium: prose must be natural, evidence-grounded, and non-repetitive.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>당사는 정보 보안 문제를 감독하는 임원급 책임자인 정보보호최고책임자(CISO)와 개인정보보호 최고 책임자(CPO)를 지정하고 산하의 보안담당부서를 중심으로 국가핵심기술 보호를 위한 조치/관리 활동을 추진하고 있으며, 사내 IT/OT 시스템, 애플리케이션, 네트워크 인프라 등의 취약성을 점검하고 정보 보안 시스템을 지속적으로 개선해 내외부의 보안 위협으로부터 회사의 자산을 보호하고 있습니다. 두산퓨얼셀은 전 임직원을 대상으로 정보유출 예방, 영업비밀 보호, 정보기기 관리, 개인정보보호 등을 내용으로 하는 정보보호 교육을 연 1회 필수 과정으로 운영하고 있습니다. 이러한 내용은 정보보안 및 개인정보 보호 정책이 선언에 머물지 않고 목표, 조직, 실행 과제로 이어지는 구조임을 보여줍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-017</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 거버넌스 (Governance) / 정보보호 관리 조직</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>[p.93] 중요 영업비밀에 대한 법적 보호 및 보안관리를 위해 영업비밀 목록을 구축하여 매년 업데이트하고 있으며, 외부 반출 이력을 탐지 및 차단하는 정책을 적용하여 영업비밀 유·노출 위험을 최소화하고 있습니다. 부서 내 보안의식을 전파하고, 보안사고 또는 징후가 있을 경우 보안담당부서와 협업할 수 있도록 부서별 보안책임자 및 담당자를 지정했습니다. 정보보안 및 고객 정보보호 정보보안 운영체계 두산퓨얼셀은 국가핵심기술(수소, '23.4월 지정) 취급사로서, 「산업기술의 유출방지 및 보호에 관한 법률」 과 「산업기술보호지침」 등에 따라 관계 국가기관으로부터 정기적인 보안관리 체계, 정보시스템 관리, 보안취약점 점검 등을 감사받고 있습니다. 당사는 정보 보안 문제를 감독하는 임원급 책임자인 정보보호최고책임자(CISO)와 개인정보보호 최고 책임자(CPO)를 지정하고 산하의 보안담당부서를 중심으로 국가핵심기술 보호를 위한 조치/관리 활동을 추진하고 있으며, 사내 IT/OT 시스템, 애플리케이션, 네트워크 인프라 등의 취약성을 점검하고 정보 보안 시스템을 지속적으로 개선해 내/외부의 보안 위협으로부터 회사의 자산을 보호하고 있습니다. 보안 총괄부서는 국가핵심기술 유출사고 예방을 위한 모니터링 및 유해 트래픽 감시를 담당하고, 개인정보를 다루는 관련 부서 간 효율적인 업무 추진 및 소통을 위하여 정기적으로 보안 협의회를 운영하고 있습니다. 보안 이상 문제 발생 시, 보안 협의회를 통해 조치 방안을 수립 및 실행하고 재발방지 대책을 논의하고 있습니다. 두산퓨얼셀은 두산 그룹의 계열사로서 ㈜두산에서 정보보안외부 인증인 ISMS를 획득했고, 제3자 취약점 분석의 일환으로 ㈜두산에서 주최한 모의해커훈련에 참여하여 정보보안 강화에 힘쓰고 있습니다. CISO 생산/운영 정보보호책임자 (익산/군산) 정보보호책임자 정보보호책임자 (서울) 정보보호담당자 (익산/군산) 정보보호담당자 정보보호담당자 (서울) 연구소 전사 정보보호책임자 전사 정보보호담당자 서비스부문 2020년 보안규정(HR&amp;협력사, IT시스템, 보안감사, 보안관리, 보안사고대응, 시설보안, 영업비밀보호, 정보자산 및 정보기기, 클라우드 보안정책) 제정 후 매년 검토하여 필요시 개정하고 있으며, 보안정책은 사내 ...
+[p.97] 2차 방어선 (2nd line of defence) 리스크 관리 리스크 관리 거버넌스 두산퓨얼셀은 체계적이고 전사적인 리스크 관리 활동을 통해 영업의 효율성, 재무보고의 신뢰성, 법규 및 규정 준수 등의 조직 목표를 효과적 ㆍ 효율적으로 달성하기 위하여 적절한 내부통제 체계를 갖추고 있습니다. 제품 제조 ㆍ 생산 ㆍ 공급하는데 직접적으로 관여하는 부서는 일상적인 운영에서 1차적으로 리스크를 관리하고 모니터링할 책임이 있으며, 리스크 모니터링 전담 부서와 기능적으로 분할된 관련 부서들이 2차적으로 리스크를 관리 ㆍ 감독하고 있습니다. 마지막으로 두산퓨얼셀은 상법 제542조의13 등 관련 규정에 의거하여 준법지원인을 선임하였으며, 준법지원인은 위험 관리 및 규정 준수 프로세스의 효과에 대한 독립적인 보증을 제공하는 내부 감사 기능을 수행합니다. 잠재 리스크 및 대응 활동 잠재 리스크 연료전지 시장 다각화(혁신기술 개발 요구) 인공지능(AI) 기술의 발전에 따른 보안 위협 설명 연료전지 시장이 다각화 됨에 따라 혁신기술 개발 요구가 증대되고 있습니다. 기업은 빠르게 변화하는 시장 환경에서 고객의 니즈에 부합하는 기술 개발을 위해 자원과 역량을 투입해야 합니다. AI 기술의 발전은 기업의 생산성 향상에 기여하는 한편, 악용 사례로 인한 사이버 보안 위협도 함께 증가시키고 있습니다. 기업은 기존 보안 시스템으로 대응이 어려운 신규 보안 위협 요인에 대비가 필요합니다. 영향 혁신기술을 적시에 개발하지 못하거나 성공적으로 상용화하지 못할 경우, 기술 개발 투자에서 기대했던 이익이 실현되지 않아 회사의 수익성과 매출에 부정적인 영향을 미칠 수 있습니다. 두산퓨얼셀은 국가핵심기술 취급사로서, 국내외 시장에서 차지하는 기술적·경제적 가치가 높아 관련 정보가 유출될 경우 당사의 기술 경쟁력 뿐만 아니라 국가 안보와 국민경제의 발전에 중대한 악영향을 미칠 수 있습니다. 대응 두산퓨얼셀은국내 최초 상용화 한 SOFC(고체산화물 연료전지) 기술을 바탕으로 한 선박용 연료전지 시장 진출을 위해 기술 확보 및 생산설비를 구축하고, 선사, 조선사 등과 함께 선박용 연료전지 실증사업을 추진하고 있습니다. 두산퓨얼셀은 정보보호최고책임자(CISO)와 개인정보보호 최고 책 ...</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 93;97
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E18" s="6" t="str">
-        <x:v>Selected Style: governance
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: governance
 Preferred Style Source: template
 Answer Type: governance-organization
 Answer Intent: Explain who is responsible, what they decide or oversee, and how reporting or escalation works.
@@ -1063,32 +1348,44 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: Medium: responsibility and decision flow must be clear.</x:v>
-      </x:c>
-      <x:c r="F18" s="6" t="str">
-        <x:v>중요 영업비밀에 대한 법적 보호 및 보안관리를 위해 영업비밀 목록을 구축하여 매년 업데이트하고 있으며, 외부 반출 이력을 탐지 및 차단하는 정책을 적용하여 영업비밀 유·노출 위험을 최소화하고 있습니다. 당사는 정보 보안 문제를 감독하는 임원급 책임자인 정보보호최고책임자(CISO)와 개인정보보호 최고 책임자(CPO)를 지정하고 산하의 보안담당부서를 중심으로 국가핵심기술 보호를 위한 조치/관리 활동을 추진하고 있으며, 사내 IT/OT 시스템, 애플리케이션, 네트워크 인프라 등의 취약성을 점검하고 정보 보안 시스템을 지속적으로 개선해 내/외부의 보안 위협으로부터 회사의 자산을 보호하고 있습니다. 두산퓨얼셀은 두산 그룹의 계열사로서 ㈜두산에서 정보보안외부 인증인 ISMS를 획득했고, 제3자 취약점 분석의 일환으로 ㈜두산에서 주최한 모의해커훈련에 참여하여 정보보안 강화에 힘쓰고 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="6" t="str">
-        <x:v>EBX-Q-018</x:v>
-      </x:c>
-      <x:c r="B19" s="6" t="str">
-        <x:v>사회 / 위험 관리 (Risk Management) / 정보보안 및 개인정보 보호 리스크 관리</x:v>
-      </x:c>
-      <x:c r="C19" s="6" t="str">
-        <x:v>[p.98] 리스크 관리 리스크 관리 활동 두산퓨얼셀은 기업 경영과 전략에 영향을 미칠 수 있는 리스크 유형을 분류하고 리스크 관리 프로세스에 따라 연 1회 이상 리스크를 검토하고 식별된 리스크에 대한 대응활동을 체계적으로 진행하고 있습니다. 특히, 리스크 관리 문화 조성을 위 하여 모든 임원 및 사외이사를 대상으로 연 1회 이상 리스크 관리 교육을 실시하고 있습니다. 리스크 유형 예상 리스크 관리 활동 리스크 유형 예상 리스크 관리활동 사업 리스크 수주 계약 조건 및  계약 이행 관련 리스크 - 제반 계약 조건에 대한 유관부서 내부 검토 - 계열체결에 대한 경영진 보고와 품의 품질 리스크 품질/생산 및 서비스 관련 리스크 -  전사적인 품질 이슈 발굴 및 개선 제도 시행 -  사무실과 공장에 품질 게시판 신설 -  격월 생산과 품질부서 기술교류회 개최 외환 리스크 국제적 영업활동 영위에 따른 환율변동 위험에 노출 -  수출과 수입통화 대응을 통한 Hedge로 환율변동 노출금액 상쇄 -  환위험관리규정에 따라 선물환 등 파생산품 이용하여 환율변동위험 관리 -  환율 10% 인상/인하에 따른 민감도 분석 공급망 리스크 부품 협력사의 비즈니스  연속성 측면의 리스크 -  비즈니스 영향과 구매 위험에 따른 1차 부품 협력사 Grouping -  Group별 ESG 평가 지표 개발과 자가진단 및 현장 실사 실시 - 자가진단 결과에 따른 개선 지원 이자율 리스크 이자율 변동위험에 노출된 변동금리부 금융자산 및 부채 리스크 -  변동금리부 금융자산 및 금융부채의 이자율 100bp 변동시 세전순손익에 미치는 민감도 분석 정보 보안 리스크 정보 유출 위험 - IT 권한 모니터링 실시하여 업무별 권한 최소화 - 연 4회 정보유출 피해 예방 모의 훈련 실시 신용 리스크 금융상품의 당사자 중 일방이 의무를 이행하지 않아 발생하는 재무손실 -  신규 거래처 계약시 재무정보와 신용평가기관 정보를 이용해 신용도를 평가하고 신용거래한도를 결정하며 담보 또는 지급보증 제공 받음 -  주기적인 거래처 신용도 재평가 및 신용거래한도 재조정 인적 리스크 우수인재 확보와 유지 및  유출로 인한 위험 -  전사 사업전략과 연계하여 전략적 인력계획 수립 - ...</x:v>
-      </x:c>
-      <x:c r="D19" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+QA Severity: Medium: responsibility and decision flow must be clear.</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>중요 영업비밀에 대한 법적 보호 및 보안관리를 위해 영업비밀 목록을 구축하여 매년 업데이트하고 있으며, 외부 반출 이력을 탐지 및 차단하는 정책을 적용하여 영업비밀 유·노출 위험을 최소화하고 있습니다. 당사는 정보 보안 문제를 감독하는 임원급 책임자인 정보보호최고책임자(CISO)와 개인정보보호 최고 책임자(CPO)를 지정하고 산하의 보안담당부서를 중심으로 국가핵심기술 보호를 위한 조치/관리 활동을 추진하고 있으며, 사내 IT/OT 시스템, 애플리케이션, 네트워크 인프라 등의 취약성을 점검하고 정보 보안 시스템을 지속적으로 개선해 내외부의 보안 위협으로부터 회사의 자산을 보호하고 있습니다. 두산퓨얼셀은 두산 그룹의 계열사로서 ㈜두산에서 정보보안외부 인증인 ISMS를 획득했고, 제3자 취약점 분석의 일환으로 ㈜두산에서 주최한 모의해커훈련에 참여하여 정보보안 강화에 힘쓰고 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-018</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 위험 관리 (Risk Management) / 정보보안 및 개인정보 보호 리스크 관리</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>[p.98] 리스크 관리 리스크 관리 활동 두산퓨얼셀은 기업 경영과 전략에 영향을 미칠 수 있는 리스크 유형을 분류하고 리스크 관리 프로세스에 따라 연 1회 이상 리스크를 검토하고 식별된 리스크에 대한 대응활동을 체계적으로 진행하고 있습니다. 특히, 리스크 관리 문화 조성을 위 하여 모든 임원 및 사외이사를 대상으로 연 1회 이상 리스크 관리 교육을 실시하고 있습니다. 리스크 유형 예상 리스크 관리 활동 리스크 유형 예상 리스크 관리활동 사업 리스크 수주 계약 조건 및  계약 이행 관련 리스크 - 제반 계약 조건에 대한 유관부서 내부 검토 - 계열체결에 대한 경영진 보고와 품의 품질 리스크 품질/생산 및 서비스 관련 리스크 -  전사적인 품질 이슈 발굴 및 개선 제도 시행 -  사무실과 공장에 품질 게시판 신설 -  격월 생산과 품질부서 기술교류회 개최 외환 리스크 국제적 영업활동 영위에 따른 환율변동 위험에 노출 -  수출과 수입통화 대응을 통한 Hedge로 환율변동 노출금액 상쇄 -  환위험관리규정에 따라 선물환 등 파생산품 이용하여 환율변동위험 관리 -  환율 10% 인상/인하에 따른 민감도 분석 공급망 리스크 부품 협력사의 비즈니스  연속성 측면의 리스크 -  비즈니스 영향과 구매 위험에 따른 1차 부품 협력사 Grouping -  Group별 ESG 평가 지표 개발과 자가진단 및 현장 실사 실시 - 자가진단 결과에 따른 개선 지원 이자율 리스크 이자율 변동위험에 노출된 변동금리부 금융자산 및 부채 리스크 -  변동금리부 금융자산 및 금융부채의 이자율 100bp 변동시 세전순손익에 미치는 민감도 분석 정보 보안 리스크 정보 유출 위험 - IT 권한 모니터링 실시하여 업무별 권한 최소화 - 연 4회 정보유출 피해 예방 모의 훈련 실시 신용 리스크 금융상품의 당사자 중 일방이 의무를 이행하지 않아 발생하는 재무손실 -  신규 거래처 계약시 재무정보와 신용평가기관 정보를 이용해 신용도를 평가하고 신용거래한도를 결정하며 담보 또는 지급보증 제공 받음 -  주기적인 거래처 신용도 재평가 및 신용거래한도 재조정 인적 리스크 우수인재 확보와 유지 및  유출로 인한 위험 -  전사 사업전략과 연계하여 전략적 인력계획 수립 - ...</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 98
 Evidence type: qualitative
 Coverage status: PARTIAL
 Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.
-Gap or reviewer note: Limited direct evidence found by automated keyword extraction; review manually against the PDF.</x:v>
-      </x:c>
-      <x:c r="E19" s="6" t="str">
-        <x:v>Selected Style: risk-control
+Gap or reviewer note: Limited direct evidence found by automated keyword extraction; review manually against the PDF.</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: risk-control
 Preferred Style Source: template
 Answer Type: risk-control
 Answer Intent: Explain the risk/control scope, then prevention, monitoring, and follow-up actions.
@@ -1107,32 +1404,44 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: High: must include risk/control and monitoring evidence.</x:v>
-      </x:c>
-      <x:c r="F19" s="6" t="str">
-        <x:v>리스크 관리 리스크 관리 활동 두산퓨얼셀은 기업 경영과 전략에 영향을 미칠 수 있는 리스크 유형을 분류하고 리스크 관리 프로세스에 따라 연 1회 이상 리스크를 검토하고 식별된 리스크에 대한 대응활동을 체계적으로 진행하고 있습니다. 특히, 리스크 관리 문화 조성을 위 하여 모든 임원 및 사외이사를 대상으로 연 1회 이상 리스크 관리 교육을 실시하고 있습니다. 두산퓨얼셀의 정보보안 및 개인정보 보호 리스크 관리 공시는 확인 가능한 제도와 활동을 중심으로 구성되어 있으며, 일부 세부 수치나 사건 현황은 공개 범위에서 제한적으로 제시되어 추가 보완 여지가 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="6" t="str">
-        <x:v>EBX-Q-019</x:v>
-      </x:c>
-      <x:c r="B20" s="6" t="str">
-        <x:v>사회 / 지표 (Metrics) / 개인정보 침해 및 정보보안 사고 현황</x:v>
-      </x:c>
-      <x:c r="C20" s="6" t="str">
-        <x:v>[p.94] 정보보안 및 고객 정보보호 정보보호 인식 제고 두산퓨얼셀은 전 임직원을 대상으로 정보유출 예방, 영업비밀 보호, 정보기기 관리, 개인정보보호 등을 내용으로 하는 정보보호 교육을 연 1회 필수 과정으로 운영하고 있습니다. 계정 탈취 목적의 피싱 이메일(Phishing Email)을 이용한 랜섬웨어 유포, 송금사기, 정보유출 피해를 예방하기 위하여 분기별로(연 4회) 모의 훈련을 실시(해킹메일 모의 훈련 3회, 개인정보보호 유출 대응 모의 훈련 1회)하고, 후속 캠페인을 통해 해킹메일 구별과 신고 방법을 교육해 임직원의 대응 역량을 향상시켰습니다(보안 이슈 신고서, 처리 보고서 작성, 담당부서 신고 및 사후 처리 등). 보안진단의 날을 연 4회 지정하여 보안 관련 뉴스 및 주요 공지를 전달하고, 임직원이 보안 관리 상태를 자가 점검할 수 있도록 체크리스트와 가이드를 제공하고 있습니다. 목적 내용 대상 보안 점검/조치 PC DI 생활보안 개인 정보시스템 부서 영업비밀문서 시설구역출입 보안담당중점 보안관리 의식 강화 보안 Newsletter 교육 및 훈련 활동명 내용 대상 주기 임직원 보안/개인정보보호 교육 보안 준수사항 안내 전 임직원 연 1회 신입/경력사원 정보보호 교육 보안규정 및 프로세스 안내 신입/경력사원 입사 시 부서별 보안담당자/책임자 교육 보안규정 및 프로세스 안내 부서별 보안담당자·책임자 연 1회 협력사 보안 교육 협력업체 정보보호 준수 사항 안내 협력회사 직원 연 1회 해킹 모의훈련 해킹메일 대응, 개인정보보호 유출 대응 전 임직원 연 4회 보안진단의 날 임직원 보안의식 제고(보안 뉴스 등) 전 임직원 연 4회 정보보안 및 고객정보보호를 위한 주요 활동 보안진단의 날 점검 사항 정보보안 관련 게시물 Doosan Fuel Cell Sustainability Report 2025 Company Overview Materiality ESG Strategy ESG Performance Appendix Social 인재경영 인권경영 안전보건 사회공헌 공급망 ESG 관리 고객 만족 Governance 지배구조 윤리경영 혁신경영 정보보안 및 고객 정보보호 리스크 관리 협회 및 단체활동 Environmental 환경경영 사업장 환경 성과 ...</x:v>
-      </x:c>
-      <x:c r="D20" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+QA Severity: High: must include risk/control and monitoring evidence.</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 기업 경영과 전략에 영향을 미칠 수 있는 리스크 유형을 분류하고 리스크 관리 프로세스에 따라 연 1회 이상 리스크를 검토하고 식별된 리스크에 대한 대응활동을 체계적으로 진행하고 있습니다. 리스크 관리 문화 조성을 위하여 모든 임원 및 사외이사를 대상으로 연 1회 이상 리스크 관리 교육을 실시하고 있습니다. 두산퓨얼셀의 정보보안 및 개인정보 보호 리스크 관리 공시는 확인 가능한 제도와 활동을 중심으로 구성되어 있으며, 일부 세부 수치나 사건 현황은 공개 범위에서 제한적으로 제시되어 추가 보완 여지가 있습니다. 두산퓨얼셀은 정보보안 및 개인정보 보호 리스크 관리에서 식별된 위험 요인과 예방 활동을 연결해 관리 수준을 점검하고 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-019</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>사회 / 지표 (Metrics) / 개인정보 침해 및 정보보안 사고 현황</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>[p.94] 정보보안 및 고객 정보보호 정보보호 인식 제고 두산퓨얼셀은 전 임직원을 대상으로 정보유출 예방, 영업비밀 보호, 정보기기 관리, 개인정보보호 등을 내용으로 하는 정보보호 교육을 연 1회 필수 과정으로 운영하고 있습니다. 계정 탈취 목적의 피싱 이메일(Phishing Email)을 이용한 랜섬웨어 유포, 송금사기, 정보유출 피해를 예방하기 위하여 분기별로(연 4회) 모의 훈련을 실시(해킹메일 모의 훈련 3회, 개인정보보호 유출 대응 모의 훈련 1회)하고, 후속 캠페인을 통해 해킹메일 구별과 신고 방법을 교육해 임직원의 대응 역량을 향상시켰습니다(보안 이슈 신고서, 처리 보고서 작성, 담당부서 신고 및 사후 처리 등). 보안진단의 날을 연 4회 지정하여 보안 관련 뉴스 및 주요 공지를 전달하고, 임직원이 보안 관리 상태를 자가 점검할 수 있도록 체크리스트와 가이드를 제공하고 있습니다. 목적 내용 대상 보안 점검/조치 PC DI 생활보안 개인 정보시스템 부서 영업비밀문서 시설구역출입 보안담당중점 보안관리 의식 강화 보안 Newsletter 교육 및 훈련 활동명 내용 대상 주기 임직원 보안/개인정보보호 교육 보안 준수사항 안내 전 임직원 연 1회 신입/경력사원 정보보호 교육 보안규정 및 프로세스 안내 신입/경력사원 입사 시 부서별 보안담당자/책임자 교육 보안규정 및 프로세스 안내 부서별 보안담당자·책임자 연 1회 협력사 보안 교육 협력업체 정보보호 준수 사항 안내 협력회사 직원 연 1회 해킹 모의훈련 해킹메일 대응, 개인정보보호 유출 대응 전 임직원 연 4회 보안진단의 날 임직원 보안의식 제고(보안 뉴스 등) 전 임직원 연 4회 정보보안 및 고객정보보호를 위한 주요 활동 보안진단의 날 점검 사항 정보보안 관련 게시물 Doosan Fuel Cell Sustainability Report 2025 Company Overview Materiality ESG Strategy ESG Performance Appendix Social 인재경영 인권경영 안전보건 사회공헌 공급망 ESG 관리 고객 만족 Governance 지배구조 윤리경영 혁신경영 정보보안 및 고객 정보보호 리스크 관리 협회 및 단체활동 Environmental 환경경영 사업장 환경 성과 ...</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 94
 Evidence type: qualitative
 Coverage status: PARTIAL
 Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.
-Gap or reviewer note: Limited direct evidence found by automated keyword extraction; review manually against the PDF.</x:v>
-      </x:c>
-      <x:c r="E20" s="6" t="str">
-        <x:v>Selected Style: status-performance
+Gap or reviewer note: Limited direct evidence found by automated keyword extraction; review manually against the PDF.</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: status-performance
 Preferred Style Source: template
 Answer Type: status-performance
 Answer Intent: Explain the reported status in plain language, then weave figures into the management meaning.
@@ -1151,34 +1460,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: High: topic-fit figures, non-repetitive opening, no technical metric label.</x:v>
-      </x:c>
-      <x:c r="F20" s="6" t="str">
-        <x:v>두산퓨얼셀는 개인정보 침해 및 정보보안 사고 현황에 대해 발생 현황과 관리 성과를 함께 확인할 수 있도록 보고하고 있습니다. 정보보안 및 고객 정보보호 정보보호 인식 제고 두산퓨얼셀은 전 임직원을 대상으로 정보유출 예방, 영업비밀 보호, 정보기기 관리, 개인정보보호 등을 내용으로 하는 정보보호 교육을 연 1회 필수 과정으로 운영하고 있습니다. 보안진단의 날을 연 4회 지정하여 보안 관련 뉴스 및 주요 공지를 전달하고, 임직원이 보안 관리 상태를 자가 점검할 수 있도록 체크리스트와 가이드를 제공하고 있습니다. 두산퓨얼셀의 개인정보 침해 및 정보보안 사고 현황 공시는 확인 가능한 제도와 활동을 중심으로 구성되어 있으며, 일부 세부 수치나 사건 현황은 공개 범위에서 제한적으로 제시되어 추가 보완 여지가 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="6" t="str">
-        <x:v>EBX-Q-020</x:v>
-      </x:c>
-      <x:c r="B21" s="6" t="str">
-        <x:v>환경 / 전략 (Strategy) / 환경경영 정책 및 목표</x:v>
-      </x:c>
-      <x:c r="C21" s="6" t="str">
-        <x:v>[p.42] 환경경영 방침 환경경영 &gt; 환경경영 조직 &gt; 환경경영 방침 환경경영 정책 두산퓨얼셀은 친환경적이며 쾌적하고 안전한 사업장을 만들어 나가기 위해 조직 내 최고 EHS(Environment, Health &amp; Safety) 경영책임자(CSHO)를 임명하여 환경과 안전, 보건에 관한 사항을 총괄 운영하고 있습니다. 또한 EHS 경영책임자 산하에 전담 EHS 관리 조직을 구성하여 제조, 연구소, 서 비스 현장을 관리하고 있습니다. 부서 별로는 EHS 관리감독자, 담당자를 지 정하고 각 조직이 스스로 EHS 활동을 실행할 수 있도록 EHS 관련 교육과 점검을 통해 임직원의 EHS 인식 제고 및 역량강화에 노력을 기울이고 있습 니다. 한편, ESG 위원회를 중심으로 기후변화 대응과 관련된 위험과 기회 요인의 중대성을 분석하고, 중장기 대응전략을 수립하여 기후 재무정보와 경영전략을 통합적으로 관리하고 있습니다. 두산퓨얼셀은 안전하고 청결한 환경을 우리 모두와 가족, 사회에 대한 책임 이자 핵심가치로 인식하고 있습니다. 이에 따라 EHS경영체계를 구축하고 환 경경영 방침을 제정하여 CSHO의 승인을 받아 단기, 중장기 환경성과 개선 을 위한 세부목표를 수립하여 실천하고 있습니다. 앞으로도 환경영향을 최소 화하고 Global Standard를 준수하기 위해 지속적으로 노력하겠습니다. 환경경영 조직도 CSHO 1) EHS부문 생산/운영 EHS총괄책임자 EHS 위원회 EHS 관리책임자 관리감독자 근로자/협력사 연구소 EHS관리책임자 연구소 EHS 위원회 연구소 책임자 연구원 서비스부문 EHS 관리책임자 EHS 협의체 관리감독자 근로자/협력사 EHS팀 제조EHS팀 환경경영 목표 환경경영 전략 1) CSHO(Chief Safety and Health Officer, 최고 EHS 경영책임자) 환경경영 목표 환경사고 ‘ZERO’ 환경법규 준수 환경 법규위반 ‘Zero’ 에너지 사용 절감 연간 목표대비 90% 이상 달성 비상사태 예방/대응 각 본부별 1건 이상 실행 환경 오염 물질 배출시설 및 방지시설 적정 모니터링(점검, 측정) 및 유지관리 주기적인 법규 준수평가 및 개정 법규 모니터링 실시 환경 사고 예방/대응을 위한 환경영향평가 및 비상훈련 실시 환경경영체제 ...
+QA Severity: High: topic-fit figures, non-repetitive opening, no technical metric label.</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 개인정보 침해 및 정보보안 사고 현황에 대해 발생 현황과 관리 성과를 함께 확인할 수 있도록 보고하고 있습니다. 두산퓨얼셀은 전 임직원을 대상으로 정보유출 예방, 영업비밀 보호, 정보기기 관리, 개인정보보호 등을 내용으로 하는 정보보호 교육을 연 1회 필수 과정으로 운영하고 있습니다. 보안진단의 날을 연 4회 지정하여 보안 관련 뉴스 및 주요 공지를 전달하고, 임직원이 보안 관리 상태를 자가 점검할 수 있도록 체크리스트와 가이드를 제공하고 있습니다. 두산퓨얼셀의 개인정보 침해 및 정보보안 사고 현황 공시는 확인 가능한 제도와 활동을 중심으로 구성되어 있으며, 일부 세부 수치나 사건 현황은 공개 범위에서 제한적으로 제시되어 추가 보완 여지가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-020</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>환경 / 전략 (Strategy) / 환경경영 정책 및 목표</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>[p.42] 환경경영 방침 환경경영 &gt; 환경경영 조직 &gt; 환경경영 방침 환경경영 정책 두산퓨얼셀은 친환경적이며 쾌적하고 안전한 사업장을 만들어 나가기 위해 조직 내 최고 EHS(Environment, Health &amp; Safety) 경영책임자(CSHO)를 임명하여 환경과 안전, 보건에 관한 사항을 총괄 운영하고 있습니다. 또한 EHS 경영책임자 산하에 전담 EHS 관리 조직을 구성하여 제조, 연구소, 서 비스 현장을 관리하고 있습니다. 부서 별로는 EHS 관리감독자, 담당자를 지 정하고 각 조직이 스스로 EHS 활동을 실행할 수 있도록 EHS 관련 교육과 점검을 통해 임직원의 EHS 인식 제고 및 역량강화에 노력을 기울이고 있습 니다. 한편, ESG 위원회를 중심으로 기후변화 대응과 관련된 위험과 기회 요인의 중대성을 분석하고, 중장기 대응전략을 수립하여 기후 재무정보와 경영전략을 통합적으로 관리하고 있습니다. 두산퓨얼셀은 안전하고 청결한 환경을 우리 모두와 가족, 사회에 대한 책임 이자 핵심가치로 인식하고 있습니다. 이에 따라 EHS경영체계를 구축하고 환 경경영 방침을 제정하여 CSHO의 승인을 받아 단기, 중장기 환경성과 개선 을 위한 세부목표를 수립하여 실천하고 있습니다. 앞으로도 환경영향을 최소 화하고 Global Standard를 준수하기 위해 지속적으로 노력하겠습니다. 환경경영 조직도 CSHO 1) EHS부문 생산/운영 EHS총괄책임자 EHS 위원회 EHS 관리책임자 관리감독자 근로자/협력사 연구소 EHS관리책임자 연구소 EHS 위원회 연구소 책임자 연구원 서비스부문 EHS 관리책임자 EHS 협의체 관리감독자 근로자/협력사 EHS팀 제조EHS팀 환경경영 목표 환경경영 전략 1) CSHO(Chief Safety and Health Officer, 최고 EHS 경영책임자) 환경경영 목표 환경사고 ‘ZERO’ 환경법규 준수 환경 법규위반 ‘Zero’ 에너지 사용 절감 연간 목표대비 90% 이상 달성 비상사태 예방/대응 각 본부별 1건 이상 실행 환경 오염 물질 배출시설 및 방지시설 적정 모니터링(점검, 측정) 및 유지관리 주기적인 법규 준수평가 및 개정 법규 모니터링 실시 환경 사고 예방/대응을 위한 환경영향평가 및 비상훈련 실시 환경경영체제 ...
 [p.43] 환경경영 &gt; 환경규제 대응 및 모니터링 &gt; 생물다양성 방침 &gt; 친환경 구매 기준 수립 환경경영 프로그램 국내 ㆍ 외에서 환경경영의 중요성이 부각되고 환경 영향에 대한 관심이 높아짐에 따라, 두산퓨얼셀은 환경경영체계를 구축하고 기업 활동으로 인한 환경 영향을 최소화하기 위해 노력하고 있습니다. 또한 환경규제 및 동향을 상시 모니터링하고 신규 설비 설치 등과 관련하여 발생가능한 리스크를 사전에 검토하여 선제적으로 대응하고 있습니다. &gt; 폐기물 관리 체계 두산퓨얼셀은 폐기물 발생을 최소화하고 자원 순환을 실현하기 위해 다양한 노력을 기울이고 있습니다. 성능이 저하된 주요 설비는 회수 후 수리하여 재사용하고 있으며, 사업장에서 발생하는 폐기물은 우선적으로 재활용 처리함으로써 소각 및 매립량을 줄이고 있습니다. 또한 발생 단계부터 철저하게 분리·보관·배출하고 있으며, 관련 법규를 준수하여 체계적으로 관리하고 있습니다. 재활용률을 높이기 위해 매년 신규 업체를 발굴하고 재입찰을 통해 폐기물 배출 계약을 체결하고 있습니다. 이 과정에서 적법한 처리가 가능한 위탁업체만을 선정할 수 있도록 사전 평가를 실시하고, 일정 기준을 충족한 업체만 입찰에 참여할 수 있도록 제한하고 있습니다. 전 임직원을 대상으로 폐기물 교육을 실시하고, 팀 단위로 감량 목표를 설정해 실질적인 저감 활동을 추진하고 있습니다. 앞으로도 폐기물 발생을 줄이고 재활용률을 지속적으로 높이기 위해 더욱 적극적으로 대응해 나가겠습니다. 두산퓨얼셀은 생물다양성 보전을 기후변화 대응의 핵심 과제로 인식하고 있으며, 사업장 인근 지역의 환경 영향을 최소화하기 위해 생물다양성 방침을 수립했습니다. 이에 따라 생물다양성 보호를 위한 다양한 활동을 진행하고 있습니다. 두산퓨얼셀은 친환경 제품을 정의하고 친환경제품의 실적 집계와 구매 확대를 위하여 아래와 같이 친환경 구매 기준을 수립하고 업무 기준을 제시하고 있습니다. 신규 프로젝트 수행 시 생물다양성에 미칠 영향을 사전에 다각도로 평가하고 위협요소과 요인을 예방할 수 있도록 노력하겠습니다. 또한, 국제 협약(World Heritage areas,  IUCN Category I-Ⅳ protected areas)이 적용되는 국가 및 지방의 법적 요건 ...
 [p.44] 환경법규 준수 두산퓨얼셀은 EHS(환경보건안전)와 관련된 전반적인 법규를 정기적으로 모니터링하며, 제·개정 사항을 사내 규정에 반영하고 있습니다. 또한, 새로운 내용을 사내 게시판을 통해 임직원과 공유하고, 사업장별 준수 평가를 통해 법규 위반 여부를 확인하고 있습니다. 아울러 원자재와 설비 등의 신규 구매 또는 변경 시 사전 EHS 평가를 통해 법규 리스크를 사전에 점검하여 법규 위반 리스크를 제거하고 있습니다. 2024년에는 환경 법규 위반이 없었습니다. 환경영향평가 두산퓨얼셀은 사업 활동이 미치는 직간접적인 환경 영향을 사전에 식별하고 체계적으로 관리하기 위해 환경영향평가를 실시하고 있습니다. 평가 결과는 사업장의 세부 목표에 반영되며, 이를 기반으로 실행 성과를 점검하고 환경 리스크를 관리하고 있습니다. 환경영향평가 프로세스 환경 교육 두산퓨얼셀은 임직원의 환경경영 인식 제고와 역량 강화를 위해 매년 정기적으로 교육을 실시하고 있습니다. 2024년에는 총 4회(402명)에 걸쳐 분기별로 교육을 실시했으며, 화학물질 취급 요령과 주요 환경 법규 위반 사례에 대한 교육을 신규로 추가해 운영했습니다. 사업장 폐기물 배출량 절감과 재활용률 향상을 위한 폐기물 관리 요령 교육을 마친 후에는 분리수거 캠페인도 함께 진행했습니다. 또한 환경기술인 교육과 부서별 EHS 담당자는 ISO 내부 심사 양성 교육 등 외부 교육을 이수했습니다. 환경 교육 이수 현장 폐기물 발생 카드 작성법 환경경영시스템 인증 두산퓨얼셀은 사업장에서 발생할 수 있는 환경 영향을 최소화하기 위해 2022년에 국제 표준인 환경경영시스템(ISO 14001) 인증을 취득했고 2024년에는 사후심사를 완료했습니다. 환경경영시스템의 지속적인 개선을 위해 전사 차원의 목표를 바탕으로 각 사업장별 세부 목표를 수립하고, 환경 성과 향상을 위한 활동을 수행하고 있습니다. 또한 실무자 중심의 운영을 통해 환경경영시스템의 고도화를 추진하고 있으며, 현재 양산체계를 구축 중인 SOFC 군산공장도 추후 환경경영시스템 인증을 받을 예정입니다. 환경영향평가 단계 단계별 수행 내용 환경영향평가 대상 선정 • 공정, 설비, 원재료, 건축물 등에 대해 2년 단위로 환경영향평가 실시 • 최초 평가 혹은 ...
-[p.54] 탄소중립 기여 제품·기술 확대 탄소포집 연계형 연료전지 시스템 개발로 청정발전 가속화 수소는 생산 공정과 이용 원료에 따라 다양하게 분류되지만 이산화탄소 배출 여부에 따라 크게 그린수소, 블루수소, 그레이수소로 구분되고 있습니다. 국제에너지기구(IEA)에 따르면 전세계 수소 생산량 중 그레이수소가 81%를 차지할만큼 대다수의 비중을 차지하며, 천연가스와 석유를 통해 생산되는 그레이수소는 CCUS(Carbon Capture Utilization and Storage)를 통해 이산화탄소를 포집하는 단계를 거치면 블루수소 사용과 동일한 탄소저감 효과를 낼 수 있습니다. 순수소를 활용한 청정 발전 인프라의 과도기적 단계로 두산퓨얼셀은 현재 도시가스 인프라 기반 연료전지 발전 시 수소를 활용하고, 잔여 이산화탄소를 포집하는 기술 개발에 성공하였습니다. 2024년에 한국수력원자력과 체결한 공동 기술 개발과 1년 간의 실증을 거쳐 2025년 연료전지 발전 시 90% 이상 CO 2를 회수하는 실증을 완료하고 청정에너지 발전과 보급이 가속화될 것으로 기대하고 있습니다. 또한 기존 연료전지 발전소에 분리막 CO2 포집 설비와 연계한 기술 적용을 통해 이산화탄소 배출이 없는 친환경 발전소로 전환하여 탄소중립 실현에 기여할 것으로 예상됩니다. 두산퓨얼셀은 순수 수소를 통한 모델 뿐만 아니라 기존 NG 인프라를 활용한 발전으로도 청정에너지 사회를 앞당기기 위해 노력하고 있습니다. PAFC 연료전지 탄소포집기술 시연회 에너지 자원 유연화 기술 협력 두산퓨얼셀은 2025년4월17일, 한국남부발전 신세종빛드림본부, 두산에너빌리티와 ‘에너지 자원 유연화 기술협력’을 위한 업무협약(MOU)를 체결하고 친환경 발전소 구축을 위한 협력에 나섰습니다. 이번 협약은 신세종본부의 에너지 자원을 이용, 열과 전력을 병행하는 열병합모드 운전의 전력 자원 유연성 확보, 그리고 LNG 직도입을 활용한 연료전지 등 신규 전원 및 열 공급 최적화 방안 도출을 위해 추진되었습니다. 두산퓨얼셀은 이번 협약을 통해 기존 액화천연가스(LNG)를 주 연료로 하는 열병합발전소에 최대 40MW 규모의 수소연료전지를 활용해 최적의 종합효율을 낼 수 있는 열병합모드를 개발하고, 전력계통 안정화를 위한 ...</x:v>
-      </x:c>
-      <x:c r="D21" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.54] 탄소중립 기여 제품·기술 확대 탄소포집 연계형 연료전지 시스템 개발로 청정발전 가속화 수소는 생산 공정과 이용 원료에 따라 다양하게 분류되지만 이산화탄소 배출 여부에 따라 크게 그린수소, 블루수소, 그레이수소로 구분되고 있습니다. 국제에너지기구(IEA)에 따르면 전세계 수소 생산량 중 그레이수소가 81%를 차지할만큼 대다수의 비중을 차지하며, 천연가스와 석유를 통해 생산되는 그레이수소는 CCUS(Carbon Capture Utilization and Storage)를 통해 이산화탄소를 포집하는 단계를 거치면 블루수소 사용과 동일한 탄소저감 효과를 낼 수 있습니다. 순수소를 활용한 청정 발전 인프라의 과도기적 단계로 두산퓨얼셀은 현재 도시가스 인프라 기반 연료전지 발전 시 수소를 활용하고, 잔여 이산화탄소를 포집하는 기술 개발에 성공하였습니다. 2024년에 한국수력원자력과 체결한 공동 기술 개발과 1년 간의 실증을 거쳐 2025년 연료전지 발전 시 90% 이상 CO 2를 회수하는 실증을 완료하고 청정에너지 발전과 보급이 가속화될 것으로 기대하고 있습니다. 또한 기존 연료전지 발전소에 분리막 CO2 포집 설비와 연계한 기술 적용을 통해 이산화탄소 배출이 없는 친환경 발전소로 전환하여 탄소중립 실현에 기여할 것으로 예상됩니다. 두산퓨얼셀은 순수 수소를 통한 모델 뿐만 아니라 기존 NG 인프라를 활용한 발전으로도 청정에너지 사회를 앞당기기 위해 노력하고 있습니다. PAFC 연료전지 탄소포집기술 시연회 에너지 자원 유연화 기술 협력 두산퓨얼셀은 2025년4월17일, 한국남부발전 신세종빛드림본부, 두산에너빌리티와 ‘에너지 자원 유연화 기술협력’을 위한 업무협약(MOU)를 체결하고 친환경 발전소 구축을 위한 협력에 나섰습니다. 이번 협약은 신세종본부의 에너지 자원을 이용, 열과 전력을 병행하는 열병합모드 운전의 전력 자원 유연성 확보, 그리고 LNG 직도입을 활용한 연료전지 등 신규 전원 및 열 공급 최적화 방안 도출을 위해 추진되었습니다. 두산퓨얼셀은 이번 협약을 통해 기존 액화천연가스(LNG)를 주 연료로 하는 열병합발전소에 최대 40MW 규모의 수소연료전지를 활용해 최적의 종합효율을 낼 수 있는 열병합모드를 개발하고, 전력계통 안정화를 위한 ...</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 42;43;44;54
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E21" s="6" t="str">
-        <x:v>Selected Style: narrative
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: narrative
 Preferred Style Source: template
 Answer Type: strategy-policy
 Answer Intent: Explain the policy or strategic direction first, then connect targets, governance, and execution evidence.
@@ -1197,34 +1518,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: Medium: prose must be natural, evidence-grounded, and non-repetitive.</x:v>
-      </x:c>
-      <x:c r="F21" s="6" t="str">
-        <x:v>두산퓨얼셀은 생물다양성 보전을 기후변화 대응의 핵심 과제로 인식하고 있으며, 사업장 인근 지역의 환경 영향을 최소화하기 위해 생물다양성 방침을 수립했습니다. 환경영향평가 프로세스 환경 교육 두산퓨얼셀은 임직원의 환경경영 인식 제고와 역량 강화를 위해 매년 정기적으로 교육을 실시하고 있습니다. 환경 교육 이수 현장 폐기물 발생 카드 작성법 환경경영시스템 인증 두산퓨얼셀은 사업장에서 발생할 수 있는 환경 영향을 최소화하기 위해 두산퓨얼셀는 환경경영 정책 및 목표를 중장기 방향과 실행 과제에 연결해 지속가능경영의 방향성을 제시하고 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="6" t="str">
-        <x:v>EBX-Q-021</x:v>
-      </x:c>
-      <x:c r="B22" s="6" t="str">
-        <x:v>환경 / 거버넌스 (Governance) / 환경경영 조직 및 책임</x:v>
-      </x:c>
-      <x:c r="C22" s="6" t="str">
-        <x:v>[p.44] 환경법규 준수 두산퓨얼셀은 EHS(환경보건안전)와 관련된 전반적인 법규를 정기적으로 모니터링하며, 제·개정 사항을 사내 규정에 반영하고 있습니다. 또한, 새로운 내용을 사내 게시판을 통해 임직원과 공유하고, 사업장별 준수 평가를 통해 법규 위반 여부를 확인하고 있습니다. 아울러 원자재와 설비 등의 신규 구매 또는 변경 시 사전 EHS 평가를 통해 법규 리스크를 사전에 점검하여 법규 위반 리스크를 제거하고 있습니다. 2024년에는 환경 법규 위반이 없었습니다. 환경영향평가 두산퓨얼셀은 사업 활동이 미치는 직간접적인 환경 영향을 사전에 식별하고 체계적으로 관리하기 위해 환경영향평가를 실시하고 있습니다. 평가 결과는 사업장의 세부 목표에 반영되며, 이를 기반으로 실행 성과를 점검하고 환경 리스크를 관리하고 있습니다. 환경영향평가 프로세스 환경 교육 두산퓨얼셀은 임직원의 환경경영 인식 제고와 역량 강화를 위해 매년 정기적으로 교육을 실시하고 있습니다. 2024년에는 총 4회(402명)에 걸쳐 분기별로 교육을 실시했으며, 화학물질 취급 요령과 주요 환경 법규 위반 사례에 대한 교육을 신규로 추가해 운영했습니다. 사업장 폐기물 배출량 절감과 재활용률 향상을 위한 폐기물 관리 요령 교육을 마친 후에는 분리수거 캠페인도 함께 진행했습니다. 또한 환경기술인 교육과 부서별 EHS 담당자는 ISO 내부 심사 양성 교육 등 외부 교육을 이수했습니다. 환경 교육 이수 현장 폐기물 발생 카드 작성법 환경경영시스템 인증 두산퓨얼셀은 사업장에서 발생할 수 있는 환경 영향을 최소화하기 위해 2022년에 국제 표준인 환경경영시스템(ISO 14001) 인증을 취득했고 2024년에는 사후심사를 완료했습니다. 환경경영시스템의 지속적인 개선을 위해 전사 차원의 목표를 바탕으로 각 사업장별 세부 목표를 수립하고, 환경 성과 향상을 위한 활동을 수행하고 있습니다. 또한 실무자 중심의 운영을 통해 환경경영시스템의 고도화를 추진하고 있으며, 현재 양산체계를 구축 중인 SOFC 군산공장도 추후 환경경영시스템 인증을 받을 예정입니다. 환경영향평가 단계 단계별 수행 내용 환경영향평가 대상 선정 • 공정, 설비, 원재료, 건축물 등에 대해 2년 단위로 환경영향평가 실시 • 최초 평가 혹은 ...
+QA Severity: Medium: prose must be natural, evidence-grounded, and non-repetitive.</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 생물다양성 보전을 기후변화 대응의 핵심 과제로 인식하고 있으며, 사업장 인근 지역의 환경 영향을 최소화하기 위해 생물다양성 방침을 수립했습니다. 두산퓨얼셀은 친환경 제품을 정의하고 친환경제품의 실적 집계와 구매 확대를 위하여 아래와 같이 친환경 구매 기준을 수립하고 업무 기준을 제시하고 있습니다. 두산퓨얼셀은 EHS(환경보건안전)와 관련된 전반적인 법규를 정기적으로 모니터링하며, 제·개정 사항을 사내 규정에 반영하고 있습니다. 두산퓨얼셀은 환경경영 정책 및 목표를 중장기 방향과 실행 과제에 연결해 지속가능경영의 방향성을 제시하고 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-021</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>환경 / 거버넌스 (Governance) / 환경경영 조직 및 책임</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>[p.44] 환경법규 준수 두산퓨얼셀은 EHS(환경보건안전)와 관련된 전반적인 법규를 정기적으로 모니터링하며, 제·개정 사항을 사내 규정에 반영하고 있습니다. 또한, 새로운 내용을 사내 게시판을 통해 임직원과 공유하고, 사업장별 준수 평가를 통해 법규 위반 여부를 확인하고 있습니다. 아울러 원자재와 설비 등의 신규 구매 또는 변경 시 사전 EHS 평가를 통해 법규 리스크를 사전에 점검하여 법규 위반 리스크를 제거하고 있습니다. 2024년에는 환경 법규 위반이 없었습니다. 환경영향평가 두산퓨얼셀은 사업 활동이 미치는 직간접적인 환경 영향을 사전에 식별하고 체계적으로 관리하기 위해 환경영향평가를 실시하고 있습니다. 평가 결과는 사업장의 세부 목표에 반영되며, 이를 기반으로 실행 성과를 점검하고 환경 리스크를 관리하고 있습니다. 환경영향평가 프로세스 환경 교육 두산퓨얼셀은 임직원의 환경경영 인식 제고와 역량 강화를 위해 매년 정기적으로 교육을 실시하고 있습니다. 2024년에는 총 4회(402명)에 걸쳐 분기별로 교육을 실시했으며, 화학물질 취급 요령과 주요 환경 법규 위반 사례에 대한 교육을 신규로 추가해 운영했습니다. 사업장 폐기물 배출량 절감과 재활용률 향상을 위한 폐기물 관리 요령 교육을 마친 후에는 분리수거 캠페인도 함께 진행했습니다. 또한 환경기술인 교육과 부서별 EHS 담당자는 ISO 내부 심사 양성 교육 등 외부 교육을 이수했습니다. 환경 교육 이수 현장 폐기물 발생 카드 작성법 환경경영시스템 인증 두산퓨얼셀은 사업장에서 발생할 수 있는 환경 영향을 최소화하기 위해 2022년에 국제 표준인 환경경영시스템(ISO 14001) 인증을 취득했고 2024년에는 사후심사를 완료했습니다. 환경경영시스템의 지속적인 개선을 위해 전사 차원의 목표를 바탕으로 각 사업장별 세부 목표를 수립하고, 환경 성과 향상을 위한 활동을 수행하고 있습니다. 또한 실무자 중심의 운영을 통해 환경경영시스템의 고도화를 추진하고 있으며, 현재 양산체계를 구축 중인 SOFC 군산공장도 추후 환경경영시스템 인증을 받을 예정입니다. 환경영향평가 단계 단계별 수행 내용 환경영향평가 대상 선정 • 공정, 설비, 원재료, 건축물 등에 대해 2년 단위로 환경영향평가 실시 • 최초 평가 혹은 ...
 [p.49] 온실가스 관리 SCOPE 3 배출량 관리 점차 의무화되는 기후공시를 사전 준비하고 제품 전과정 친환경성 강화를 위하여 단계적으로 온실가스 Scope 3 배출량을 산정 및 관리하는 계획을 수립하였습니다. 2024년도에는 카테고리 5~7번을 산정하였으며, 향후 산정 범위를 확대하고 평가 방법론 및 배출계수를 고도화해 정확성을 높여 개선 활동에 활용할 예정입니다. Scope 3 산정 결과 1) 카테고리 배출량 비고 5. 폐기물 발생/처리 232.66tCO2eq • 산정 방식 : 종류별 폐기방식 기반 • 활동 자료 : 폐기물 배출 및 처리 실적 보고서 • 배출 계수 : 한국환경산업기술원 환경성적표지 평가계수 등 활용 6. 임직원 출장 394.60tCO2eq • 산정 방식 : 비용 기반 • 활동 자료 : 여비교통비_시내/해외/출장비 원장 •  배출 계수 : 미국 환경산업연관계수(USEEIO) 등 활용 7. 임직원 통근 567.40tCO2eq • 산정 방식 : 거리 기반 • 활동 자료 : 임직원 샘플링 설문 조사 결과 • 배출 계수 : 환경부 고시 2021년 국가 온실가스 배출계수 합계 1,194.66tCO2eq - 내부 탄소 가격 두산퓨얼셀은 온실가스 목표관리제 및 배출권거래제 대상 사업장은 아니지만 온실가스 배출량 확인 및 에너지 감축활동을 촉진하기 위해 내부 탄소 가격을 설정하고, 이를 경제성 평가와 내부 포상 제도 등에 활용하여 임직원의 에너지 감축활동을 유도하고 있습니다. 2) 한국거래소 KAU24 1월2일 종가 기준 내부탄소가격 2) 적용 방안 임직원의 적극적인 에너지 절감 활동을 유도하기 위해 매년 원가 절감 포상 제도의 평가항목으로 온실가스 절감 실적을 추가하여 평가를 진행하고 있습니다. 온실가스 절감 실적에 대한 개인포상 반영 두산퓨얼셀 자체 온실가스 계산기 및 연료 비교표를 활용하여 온실가스 절감계획을 수립할 때 절감량을 예측하고 연료 종류별 경제성 비교를 통해 시설 개선 및 연료 변경 시에도 온실가스 감축을 고려하고 있습니다. 연료 종류별 경제성 비교 매년 온실가스 절감 활동의 결과에 내부 탄소가격을 적용하여 공개함으로써, 임직원들이 온실가스 감축에 대한 의식을 높이고 다양한 에너지 절감 활동에 적극 참여하도록 유도하고 있습 ...
 [p.78] 공급망 ESG 관리 두산퓨얼셀은 공급망의 지속가능성을 평가하기 위해 ESG 진단 전문기관을 선정하여 협력사 ESG 리스크 자가진단 및 실사진단을 진행하고 있습니다. 또한 협력사에 현장방문하여 자가진단 내용을 검증하고, ESG 개선 활동을 지원하는 프로세스를 운영하고 있습니다. 공급망 리스크 관리 평가 및 후속 조치 두산퓨얼셀은 2023년부터 공급망 ESG 관리체계를 구축하고 협력사에 대한 평가를 진행하고 있습니다. 부품 구매 비중, 중요 부품 여부, 대체 가능성, 전문성과 핵심 기술 보유 여부, 조달 기간, 국가 및 지역 리스크, 조직 및 인원 규모 등을 기준으로 협력사를 ‘Critical’, ‘Bottle Neck’, ‘Leverage’, ‘Routine’의 네 가지 유형으로 분류했습니다. 또한 공급망 리스크 진단 전문기관과 협업하여 2024년6월부터 9월까지 전체 1차 부품 협력사(총 34개사)를 대상으로 진단을 실시했으며, 이 중 Critical 및 Leverage 유형의 협력사에 대해서는 독립된 제3자의 현장 실사를 통해 제출 자료의 타당성을 검증하고, One-point Consulting을 통해 개선 방향을 제시하고 있습니다. 최종 평가 결과는 협력사에 결과보고서 및 개선 가이드 형태로 제공하며, 두산퓨얼셀 CEO가 주관하는 ESG 위원회에도 보고하여 지속적으로 관리할 예정입니다. 공급망 ESG 현장 실사 공급망 리스크 평가 이니셔티브 및 방법론 두산퓨얼셀의 공급망 ESG 리스크 평가는 전문성을 갖춘 제3의 기관인 한국평가데이터(KoDATA)을 통해 진행되고 있습니다. 한국평가데이터는 공급업체의 ESG 운영, 정책, 시스템 및 성과를 평가하기 위하여 전문 Auditor를 파견하여 공급업체 현장을 방문하고, 문서 및 기록 검토, 현장 견학은 물론 회사 대표 직원 및 기타 이해관계자와의 인터뷰를 진행합니다. 평가 방법론은 한국평가데이터의 자체 체크리스트로 구성되어 있으며, 자체 체크리스트는 해당 국가의 법률, ISO 14001/26000/37001/45001 등의 국제 표준, RBA 등 인정된 업계 또는 산업 이니셔티브의 방법론 등으로 구성되었습니다. 두산퓨얼셀은 2023년부터 협력사의 ESG 수준 향상을 지원하기 위한 프로그램을 ...
-[p.104] 환경 원료 사용량 구분 단위 2022 2023 2024 총 사용량 ton 4,183 2,226 3,112 비재생원료 사용량 % 100 100 100 재생원료 1) 사용량 % - - - 환경 교육 구분 단위 2022 2023 2024 교육 참여 임직원 수 1) 명 117 440 402 인당 교육시간 2) 시간 4 4 4 1) 연 4회 대면교육 중 2) 교육주기: 분기1회, 교육시간: 1시간/회, 연간 평균 근로자 기준 1) 「자원의 절약과 재활용 촉진에 관한 법률」 제2조, 제33조의2 , 「순환경제사회 전환 촉진법 시행령」 제2조에서 정의하는 원료 환경 경영 구분 단위 2022 2023 2024 환경 법규 위반 위반 건수 건 - - - 벌금/과태료 금액 백만 원 - - - 연말에 발생한 환경 책임 백만 원 - - - 환경 경영 및 친환경 제품 인증 전체 생산 사업장 수 개 1 1 1 ISO 14001 인증 사업장 수 개 1 1 1 ISO 14001 인증 사업장 비율 1) % 100 100 100 환경 투자 자본 투자액 % 408.1 0.0 87.3 운영 비용 백만 원 200.7 70.9 90.3 총 비용 백만 원 608.8 70.9 177.6 비용 절감 (수익, 세금 혜택) 백만 원 8,920 7,785 7,704 1) 사업장별 매출액 대비 ISO 14001 인증 사업장 매출액이 차지하는 비중 ESG Data Doosan Fuel Cell Sustainability Report 2025 Company Overview ESG Strategy Appendix Materiality ESG Performance ESG Data GRI Index SASB Index TCFD Index UN SDGs 협회 · 단체 가입 현황 제3자 검증의견서 온실가스 검증의견서 104</x:v>
-      </x:c>
-      <x:c r="D22" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.104] 환경 원료 사용량 구분 단위 2022 2023 2024 총 사용량 ton 4,183 2,226 3,112 비재생원료 사용량 % 100 100 100 재생원료 1) 사용량 % - - - 환경 교육 구분 단위 2022 2023 2024 교육 참여 임직원 수 1) 명 117 440 402 인당 교육시간 2) 시간 4 4 4 1) 연 4회 대면교육 중 2) 교육주기: 분기1회, 교육시간: 1시간/회, 연간 평균 근로자 기준 1) 「자원의 절약과 재활용 촉진에 관한 법률」 제2조, 제33조의2 , 「순환경제사회 전환 촉진법 시행령」 제2조에서 정의하는 원료 환경 경영 구분 단위 2022 2023 2024 환경 법규 위반 위반 건수 건 - - - 벌금/과태료 금액 백만 원 - - - 연말에 발생한 환경 책임 백만 원 - - - 환경 경영 및 친환경 제품 인증 전체 생산 사업장 수 개 1 1 1 ISO 14001 인증 사업장 수 개 1 1 1 ISO 14001 인증 사업장 비율 1) % 100 100 100 환경 투자 자본 투자액 % 408.1 0.0 87.3 운영 비용 백만 원 200.7 70.9 90.3 총 비용 백만 원 608.8 70.9 177.6 비용 절감 (수익, 세금 혜택) 백만 원 8,920 7,785 7,704 1) 사업장별 매출액 대비 ISO 14001 인증 사업장 매출액이 차지하는 비중 ESG Data Doosan Fuel Cell Sustainability Report 2025 Company Overview ESG Strategy Appendix Materiality ESG Performance ESG Data GRI Index SASB Index TCFD Index UN SDGs 협회 · 단체 가입 현황 제3자 검증의견서 온실가스 검증의견서 104</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 44;49;78;104
 Evidence type: qualitative+quantitative
 Coverage status: SUFFICIENT
-Numeric support: 12 quantitative row(s) in data_dinh_luong.csv are linked to the same source page(s).</x:v>
-      </x:c>
-      <x:c r="E22" s="6" t="str">
-        <x:v>Selected Style: governance
+Numeric support: 12 quantitative row(s) in data_dinh_luong.csv are linked to the same source page(s).</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: governance
 Preferred Style Source: template
 Answer Type: governance-organization
 Answer Intent: Explain who is responsible, what they decide or oversee, and how reporting or escalation works.
@@ -1243,34 +1576,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: Medium: responsibility and decision flow must be clear.</x:v>
-      </x:c>
-      <x:c r="F22" s="6" t="str">
-        <x:v>환경법규 준수 두산퓨얼셀은 EHS(환경보건안전)와 관련된 전반적인 법규를 정기적으로 모니터링하며, 제·개정 사항을 사내 규정에 반영하고 있습니다. 환경영향평가 두산퓨얼셀은 사업 활동이 미치는 직간접적인 환경 영향을 사전에 식별하고 체계적으로 관리하기 위해 환경영향평가를 실시하고 있습니다. 환경영향평가 프로세스 환경 교육 두산퓨얼셀은 임직원의 환경경영 인식 제고와 역량 강화를 위해 매년 정기적으로 교육을 실시하고 있습니다. 두산퓨얼셀는 환경경영 조직 및 책임과 관련해 책임 주체와 의사결정 흐름을 중심으로 관리 체계를 설명하고 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="6" t="str">
-        <x:v>EBX-Q-022</x:v>
-      </x:c>
-      <x:c r="B23" s="6" t="str">
-        <x:v>환경 / 위험 관리 (Risk Management) / 환경 영향 및 환경 리스크 관리</x:v>
-      </x:c>
-      <x:c r="C23" s="6" t="str">
-        <x:v>[p.25] &gt; 최고 경영진의 역할과 책임 지배구조 두산퓨얼셀은 기후변화 관련 위험과 기회를 관리 및 감독하기 위하여 경영진 의사결정 기구인 ESG위원회를 중심으로 거버넌스를 구축하고 있습니다. ESG위원회는 연 2회 개최하며, 상반기에는 기후변화 관련 위험과 기회를 보고받고 대응 전략과 목표를 결정하며, 하반기에는 성과를 점검하고 차기 연도 방향성을 수립합니다. 또한, ESG를 총괄하는 경영지원본부장이 필요에 따라 수시로 기후변화 관련 위험 분석과 모니터링 및 대응 전략을 검토하고 있습니다. 한편, 기후변화 관련 주요 전략 및 과제는 연 1회 이상 이사회에 보고하고 있습니다. &gt; 기후변화 관련 위험과 기회를 의사결정에 고려하는 방법 정부는 탄소중립 이행을 위하여 정책적으로 수소산업을 육성하고 있습니다. 그 일환으로 일반수소발전 입찰시장(RPS)과 함께 2024년부터 청정수소발전 의무화제도(CHPS)를 운영하고 있으며, RPS와 CHPS 입찰 시장 규모를 합하면 2024년 기준 약 7,800GWh 규모입니다. 두산퓨얼셀은 수소발전 입찰시장이 커짐에 따라 사업기회가 확대될 것으로 기대하고 있습니다. 한편, CHPS의 도입으로 연료전지 사업자뿐만 아니라 석탄-암모니아 혼소, 수소전소터빈 등 신규 사업자와의 경쟁이 심화될 것으로 예상됩니다. 이에 따라 당사는 경쟁력 제고를 위해 제품 효율 개선을 통한 균등화발전원가(LCOE) 저감과 품질 개선을 통한 장기유지보수(LTSA) 비용 저감 등의 투자를 진행하고 있습니다. &gt; 경영진의 기후변화 감독을 지원하기 위한 통제 및 절차 두산퓨얼셀은 매년 중대성 평가 시, 기후변화와 관련된 영향, 위험 및 기회요인(IRO)을 도출하여 유관부서 실무자를  대상으로 설문조사를 실시하여 환경/사회적 영향과 재무적 영향의 규모, 범위, 발생 가능성을 파악합니다. 결과는 경영진 주관의 ESG위원회에 보고되어 대응 방안의 수립과 목표를 의사결정 받는데 활용됩니다. 특히, 최고전략책임자(CSO)를 겸하고 있는 CEO는 사업전략 수립에, ESG를 총괄하는 경영지원본부장은 사업장 환경 및 안전/보건 전략 수립에  기후변화에 따른 위험과 기회 분석 결과를 반영하고 있습니다. &gt; 최고 경영진 교육 현황 두산퓨얼셀은 법률, 재무/회계, ...
+QA Severity: Medium: responsibility and decision flow must be clear.</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 EHS(환경보건안전)와 관련된 전반적인 법규를 정기적으로 모니터링하며, 제·개정 사항을 사내 규정에 반영하고 있습니다. 두산퓨얼셀은 사업 활동이 미치는 직간접적인 환경 영향을 사전에 식별하고 체계적으로 관리하기 위해 환경영향평가를 실시하고 있습니다. 두산퓨얼셀은 임직원의 환경경영 인식 제고와 역량 강화를 위해 매년 정기적으로 교육을 실시하고 있습니다. 두산퓨얼셀은 환경경영 조직 및 책임과 관련해 책임 주체와 의사결정 흐름을 중심으로 관리 체계를 설명하고 있습니다. 이 구조는 환경경영 조직 및 책임의 담당 조직, 보고 경로, 감독 역할을 한 문맥에서 확인할 수 있게 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-022</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>환경 / 위험 관리 (Risk Management) / 환경 영향 및 환경 리스크 관리</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>[p.25] &gt; 최고 경영진의 역할과 책임 지배구조 두산퓨얼셀은 기후변화 관련 위험과 기회를 관리 및 감독하기 위하여 경영진 의사결정 기구인 ESG위원회를 중심으로 거버넌스를 구축하고 있습니다. ESG위원회는 연 2회 개최하며, 상반기에는 기후변화 관련 위험과 기회를 보고받고 대응 전략과 목표를 결정하며, 하반기에는 성과를 점검하고 차기 연도 방향성을 수립합니다. 또한, ESG를 총괄하는 경영지원본부장이 필요에 따라 수시로 기후변화 관련 위험 분석과 모니터링 및 대응 전략을 검토하고 있습니다. 한편, 기후변화 관련 주요 전략 및 과제는 연 1회 이상 이사회에 보고하고 있습니다. &gt; 기후변화 관련 위험과 기회를 의사결정에 고려하는 방법 정부는 탄소중립 이행을 위하여 정책적으로 수소산업을 육성하고 있습니다. 그 일환으로 일반수소발전 입찰시장(RPS)과 함께 2024년부터 청정수소발전 의무화제도(CHPS)를 운영하고 있으며, RPS와 CHPS 입찰 시장 규모를 합하면 2024년 기준 약 7,800GWh 규모입니다. 두산퓨얼셀은 수소발전 입찰시장이 커짐에 따라 사업기회가 확대될 것으로 기대하고 있습니다. 한편, CHPS의 도입으로 연료전지 사업자뿐만 아니라 석탄-암모니아 혼소, 수소전소터빈 등 신규 사업자와의 경쟁이 심화될 것으로 예상됩니다. 이에 따라 당사는 경쟁력 제고를 위해 제품 효율 개선을 통한 균등화발전원가(LCOE) 저감과 품질 개선을 통한 장기유지보수(LTSA) 비용 저감 등의 투자를 진행하고 있습니다. &gt; 경영진의 기후변화 감독을 지원하기 위한 통제 및 절차 두산퓨얼셀은 매년 중대성 평가 시, 기후변화와 관련된 영향, 위험 및 기회요인(IRO)을 도출하여 유관부서 실무자를  대상으로 설문조사를 실시하여 환경/사회적 영향과 재무적 영향의 규모, 범위, 발생 가능성을 파악합니다. 결과는 경영진 주관의 ESG위원회에 보고되어 대응 방안의 수립과 목표를 의사결정 받는데 활용됩니다. 특히, 최고전략책임자(CSO)를 겸하고 있는 CEO는 사업전략 수립에, ESG를 총괄하는 경영지원본부장은 사업장 환경 및 안전/보건 전략 수립에  기후변화에 따른 위험과 기회 분석 결과를 반영하고 있습니다. &gt; 최고 경영진 교육 현황 두산퓨얼셀은 법률, 재무/회계, ...
 [p.29] 기후변화 대응 MATERIAL TOPIC #1. &gt; 기후변화 시나리오 분석을 통한 기후 회복력 평가 두산퓨얼셀은 기후변화가 당사에 미치는 영향을 평가하기 위하여 기후변화 시나리오 분석을 수행하였습니다.  기후리스크를 탄소중립 또는 탄소저감정책에 따른 비용 상승 등의 전환리스크와 급성 또는 만성적으로 영향을 미치는 이상기후현상 등의 물리적리스크로 구분하여 기후변화 시나리오 분석을 실시하고 해당 리스크가 두산퓨얼셀의 사업 활동 및 재무적으로 미치는 영향을 분석하였습니다. 기후변화 시나리오 분석은 2021년 말 대내 ㆍ 외 경영 환경을 기준으로 2050년까지의 영향을 분석하였으며, 전환리스크는 에너지 산업군에서 널리 활용하는 IEA(국제에너지기구)의 NZE2050 시나리오와 STEPS 시나리오를 활용하여 저탄소  경제로 전환하는 과정에서 발생하는 탄소 비용 증가, 수주 경쟁력 약화, 규제 대응 비용 증가 규모를 분석하였고,  물리적 리스크는 IPCC에서 제시하는 SSP 시나리오를 활용하여 이상기후현상에 따른 재무적 영향(영업이익)을 분석 하였습니다. &gt; 전환 리스크 시나리오 분석 두산퓨얼셀은 IEA의 기후변화 시나리오 가운데 2050년까지 전 세계가 순배출 제로 경로를 달성하고, 기온 상승폭을 1.5℃에서 유지하는 것을 전제로 하는 NZE2050 기후변화 시나리오와 각 부문 ㆍ 국가 ㆍ 지역에서 이미 추진하고 있는  정책과 조치에 더하여 현재까지 발표된 감축목표, 이미 확정된 계획 등을 기반으로 전망하는 STEPS 시나리오를 활용 하였습니다. 이는 현재 시장 형성 초기로서 정부 정책에 따라 수요 변동폭이 큰 수소연료전지 시장의 특성을 가장 적절 하게 반영하기 위해서입니다. NZE2050 시나리오에서는 탄소가격이 2030년 90USD에서 2040년 160USD, 2050년 200USD까지 상승하고, SPS 시나리오에서는 2030년까지 56USD, 2040년까지 73USD, 2050년까지 89USD까지 상승 할 것으로 예측되었습니다. 구분 시나리오 전환  리스크 물리적 리스크 급성 만성 폭염 호우 강수량 수자원 평균기온 상승 IEA NZE2050 1.5℃ 2050년 전 세계적으로 탄소중립을 달성하고 평균기온 상승폭을 1.5℃ 이하로 ...
 [p.46] 사업장 환경 성과 개선 용수 관리 폐기물 관리 화학물질 관리 두산퓨얼셀은 누출점 확인 및 조치를 위해 용수 배관의 일일점검을 진행하고 있으며, 용수 사용량 절감을 위한 활동을 진행하고 있습니다. 2024년도 용수 사용량은 18,512톤으로, 목표치인 21,900톤 대비 18% 가량 절감하는 성과를 달성했습니다. 2025년에는 2024년 용수사용량 대비 5% 절감계획을 가지고 있으며, 향후 계속적으로 매년 5% 절감하는 것을 목표로 하고 있습니다. 또한 2025년에는 폐수 처리 시스템 개선을 완료하여 정화 품질의 개선을 기대하고 있습니다. 발생한 폐수는 폐수 위탁처리 업체 및 폐수 종말 처리장을 통해 처리하고 있습니다. 폐수 위탁업체는 투명하고 공정한 내부 기준에 따라 선정하고 관련 인허가 서류와 현장 폐수 처리시설을 직접 확인하여 폐수를 적법하게 처리할 수 있는지 평가합니다. 두산퓨얼셀은 사업장에서 배출되는 폐기물을 최소화하기 위해 노력하고 있습니다. 주요 설비 및 부품 재이용을 실시하고 있으며, 배출된 폐기물에 대해서는 우선적으로 재활용하여 소각하거나 매립하는 폐기물의 종류를 최소화하고 있습니다. 2024년에는 기존에 소각 처리하던 품목 1종을 소각과 함께 재활용도 병행 처리하고 있습니다. 폐기물 위탁처리 업체는 투명하고 공정한 계약을 위해 매년 인허가 사항, 법규 위반 여부 등 관련 서류를 검토하고, 보관 및 처리시설에 대한 현장점검을 통해 객관적인 평가를 실시하여 적합 기준 이상의 업체만 선별하고 있습니다. 또한 폐기물 배출량은 ‘올바로 시스템’을 통해 명확하게 관리되고 있습니다. 두산퓨얼셀은 2024년 전극 공장 인수 및 생산량 증가에 따라 일반 폐기물 발생량이 859.83톤으로, 목표치인 674톤 대비 약 27.6% 초과하였습니다. 반면, 위험폐기물 발생량은 248.66톤으로, 목표치인 275톤 대비 약 9.6% 절감하는 성과를 보였습니다. 한편, 폐기물 배출량 목표관리를 하고 있는 익산 공장의 총 폐기물 재활용률은 2023년 41.8%에서 49.8%로 증가하는 성과가 있었습니다. 앞으로도 각 사업장에서는 공정 단계부터 폐기물 발생을 줄이고 재이용률을 높이는 한편, 재질 개선과 신규 위탁업체 발굴을 통해 재활용률 향상을 위해 ...
-[p.118] TCFD Index TCFD 권고안 보고 페이지 지배구조 a) 기후변화 관련 위험과 기회에 대한 이사회의 감독 설명 25 b) 기후변화와 관련된 위험과 기회를 평가하고 관리하는 경영진의 역할 설명 25 전략 a) 단기, 중기 및 장기적 측면의 기후변화 위험과 기회 설명 26 b) 기후변화 위험과 기회가 조직의 사업, 전략 및 재무 계획에 미치는 영향 설명 27-28 c) 2˚C 이하의 시나리오를 포함하여 다양한 기후변화 관련 시나리오를 고려한 전략의 회복 탄력성 설명 29-32 위험관리 a) 기후변화 관련 위험을 식별하고 평가하기 위한 조직의 프로세스 설명 33 b) 기후변화 관련 위험을 관리하기 위한 조직의 프로세스 설명 33 c) 기후변화 관련 위험을 식별, 평가 및 관리하는 프로세스가 조직의 전반적인 위험 관리에 통합되는 방법 설명 33 지표 및 목표 a) 조직이 전략 및 위험관리 프로세스에 따라 기후변화와 관련된 위험과 기회를 평가하기 위해 사용한 지표 33 b) Scope 1, Scope 2, 그리고 해당되는 경우 Scope 3 온실가스 배출량 및 관련 위험 33 c) 기후변화 관련 위험, 기회 및 목표 대비 성과를 관리하기 위해 조직이 사용하는 목표 33 Doosan Fuel Cell Sustainability Report 2025 Company Overview ESG Strategy Appendix Materiality ESG Performance ESG Data GRI Index SASB Index TCFD Index UN SDGs 협회 · 단체 가입 현황 제3자 검증의견서 온실가스 검증의견서 118</x:v>
-      </x:c>
-      <x:c r="D23" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.118] TCFD Index TCFD 권고안 보고 페이지 지배구조 a) 기후변화 관련 위험과 기회에 대한 이사회의 감독 설명 25 b) 기후변화와 관련된 위험과 기회를 평가하고 관리하는 경영진의 역할 설명 25 전략 a) 단기, 중기 및 장기적 측면의 기후변화 위험과 기회 설명 26 b) 기후변화 위험과 기회가 조직의 사업, 전략 및 재무 계획에 미치는 영향 설명 27-28 c) 2˚C 이하의 시나리오를 포함하여 다양한 기후변화 관련 시나리오를 고려한 전략의 회복 탄력성 설명 29-32 위험관리 a) 기후변화 관련 위험을 식별하고 평가하기 위한 조직의 프로세스 설명 33 b) 기후변화 관련 위험을 관리하기 위한 조직의 프로세스 설명 33 c) 기후변화 관련 위험을 식별, 평가 및 관리하는 프로세스가 조직의 전반적인 위험 관리에 통합되는 방법 설명 33 지표 및 목표 a) 조직이 전략 및 위험관리 프로세스에 따라 기후변화와 관련된 위험과 기회를 평가하기 위해 사용한 지표 33 b) Scope 1, Scope 2, 그리고 해당되는 경우 Scope 3 온실가스 배출량 및 관련 위험 33 c) 기후변화 관련 위험, 기회 및 목표 대비 성과를 관리하기 위해 조직이 사용하는 목표 33 Doosan Fuel Cell Sustainability Report 2025 Company Overview ESG Strategy Appendix Materiality ESG Performance ESG Data GRI Index SASB Index TCFD Index UN SDGs 협회 · 단체 가입 현황 제3자 검증의견서 온실가스 검증의견서 118</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 25;29;46;118
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E23" s="6" t="str">
-        <x:v>Selected Style: risk-control
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: risk-control
 Preferred Style Source: template
 Answer Type: risk-control
 Answer Intent: Explain the risk/control scope, then prevention, monitoring, and follow-up actions.
@@ -1289,34 +1634,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: High: must include risk/control and monitoring evidence.</x:v>
-      </x:c>
-      <x:c r="F23" s="6" t="str">
-        <x:v> 기후리스크를 탄소중립 또는 탄소저감정책에 따른 비용 상승 등의 전환리스크와 급성 또는 만성적으로 영향을 미치는 이상기후현상 등의 물리적리스크로 구분하여 기후변화 시나리오 분석을 실시하고 해당 리스크가 두산퓨얼셀의 사업 활동 및 재무적으로 미치는 영향을 분석하였습니다. 기후변화 시나리오 분석은 2021년 말 대내 ㆍ 외 경영 환경을 기준으로 2050년까지의 영향을 분석하였으며, 전환리스크는 에너지 산업군에서 널리 활용하는 IEA(국제에너지기구)의 NZE2050 시나리오와 STEPS 시나리오를 활용하여 저탄소  경제로 전환하는 과정에서 발생하는 탄소 비용 증가, 수주 경쟁력 약화, 규제 대응 비용 증가 규모를 분석하였고,  물리적 리스크는 IPCC에서 제시하는 SSP 시나리오를 활용하여 이상기후현상에 따른 재무적 영향(영업이익)을 분석 하였습니다. 따라서 환경 영향 및 환경 리스크 관리 관련 공시는 단순한 선언보다 예방, 모니터링, 후속 조치의 연결성을 중심으로 해석할 수 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="6" t="str">
-        <x:v>EBX-Q-023</x:v>
-      </x:c>
-      <x:c r="B24" s="6" t="str">
-        <x:v>환경 / 지표 (Metrics) / 환경 성과 지표 및 환경 사고 현황</x:v>
-      </x:c>
-      <x:c r="C24" s="6" t="str">
-        <x:v>[p.28] 기후변화 대응 MATERIAL TOPIC #1. &gt; 대응 전략 실행을 위한 자원 조달 두산퓨얼셀은 식별된 기후 관련 기회와 위험에 대응하기 위하여 신규 생산설비 구축 및 연구개발을 위한 투자를 진행 하고 있습니다. 관련된 자금 조달은 당사의 제6기(2024년 회계연도) 사업보고서 내 Ⅲ. 재무에 관한 사항 7-2 증권의 발행을 통해 조달된 자금의 사용 실적 공시 사항을 참조하시기 바랍니다. &gt; 기후 관련 전환 계획, 주요 가정, 의존 요소 및 목표 달성을 위한 기업의 계획 두산퓨얼셀은 2030년까지 익산공장의 온실가스 배출량 Scope1&amp;2를 BAU(배출예상량)대비 16% 감축하는 계획을 보유하고 있습니다. 당사의 공정에서는 전기 사용량이 에너지 사용량의 80% 이상을 차지하고 있어, 온실가스 배출 저감에는 전기 사용량 감축과 재생에너지 도입을 가장 효과적인 방안으로 판단하고 있습니다. 이에 따라 국내 온실가스 배출 관련 규제와 산업용 전력 단가 및 태양광 등 재생에너지 전력 단가에 대한 전망을 기반으로 감축 목표 로드맵을 수립하였습니다. 향후에도 관련 동향을 정기적으로 모니터링하고 당사의 중장기 사업계획을 반영하여 목표 달성 계획을 유연하게 조정할 예정입니다. 현재의 가정 및 의존 요소를 고려한 목표 달성 계획은 아래와 같습니다. 두산퓨얼셀은 ’24년 말 온실가스 배출량이 업체기준 50,000tCO2eq, 사업장 기준 15,000tCO2eq 이상에 해당하지 않으므로, 목표관리제나 배출권 거래제 대상에 해당하지 않습니다. 그러나 ’22년 3월부터 에너지 사용량 기준이 삭제되면서 대상이 확대되었고, 공공부문을 중심으로 목표관리제 대상이 아닌 지방자치단체 출자기관이나 출연기관까지 감축 의무를 확대하고 있습니다. 또한, ’25년 6월부터는 목표관리제 감축 목표가 배출예상량 기준에서 기준연도대비 절대량 기준으로 강화되는 등 제도가 점차 강화되는 추세에 있습니다. 따라서 당사는 2030년까지 온실가스 배출량 감축 로드맵을 수립하고 기저부하 저감, 단기 에너지 절감 활동 및 장기적으로는 고효율 설비 투자와 재생에너지 도입을 검토하고 있습니다. 온실가스 배출규제 전망 에너지경제연구원의 보고서 1) 에 따르면 1MW규모의 LCOE(균등화 발전비용)는 ...
+QA Severity: High: must include risk/control and monitoring evidence.</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>기후리스크를 탄소중립 또는 탄소저감정책에 따른 비용 상승 등의 전환리스크와 급성 또는 만성적으로 영향을 미치는 이상기후현상 등의 물리적 리스크로 구분하여 기후변화 시나리오 분석을 실시하고 해당 리스크가 두산퓨얼셀의 사업 활동 및 재무적으로 미치는 영향을 분석하였습니다. 기후변화 시나리오 분석은 2021년 말 대내외 경영 환경을 기준으로 2050년까지의 영향을 분석하였으며, 전환리스크는 에너지 산업군에서 널리 활용하는 IEA(국제에너지기구)의 NZE2050 시나리오와 STEPS 시나리오를 활용하여 저탄소 경제로 전환하는 과정에서 발생하는 탄소 비용 증가, 수주 경쟁력 약화, 규제 대응 비용 증가 규모를 분석하였고, 물리적 리스크는 IPCC에서 제시하는 SSP 시나리오를 활용하여 이상기후현상에 따른 재무적 영향(영업이익)을 분석하였습니다. 환경 영향 및 환경 리스크 관리 관련 공시는 단순한 선언보다 예방, 모니터링, 후속 조치의 연결성을 중심으로 해석할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-023</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>환경 / 지표 (Metrics) / 환경 성과 지표 및 환경 사고 현황</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>[p.28] 기후변화 대응 MATERIAL TOPIC #1. &gt; 대응 전략 실행을 위한 자원 조달 두산퓨얼셀은 식별된 기후 관련 기회와 위험에 대응하기 위하여 신규 생산설비 구축 및 연구개발을 위한 투자를 진행 하고 있습니다. 관련된 자금 조달은 당사의 제6기(2024년 회계연도) 사업보고서 내 Ⅲ. 재무에 관한 사항 7-2 증권의 발행을 통해 조달된 자금의 사용 실적 공시 사항을 참조하시기 바랍니다. &gt; 기후 관련 전환 계획, 주요 가정, 의존 요소 및 목표 달성을 위한 기업의 계획 두산퓨얼셀은 2030년까지 익산공장의 온실가스 배출량 Scope1&amp;2를 BAU(배출예상량)대비 16% 감축하는 계획을 보유하고 있습니다. 당사의 공정에서는 전기 사용량이 에너지 사용량의 80% 이상을 차지하고 있어, 온실가스 배출 저감에는 전기 사용량 감축과 재생에너지 도입을 가장 효과적인 방안으로 판단하고 있습니다. 이에 따라 국내 온실가스 배출 관련 규제와 산업용 전력 단가 및 태양광 등 재생에너지 전력 단가에 대한 전망을 기반으로 감축 목표 로드맵을 수립하였습니다. 향후에도 관련 동향을 정기적으로 모니터링하고 당사의 중장기 사업계획을 반영하여 목표 달성 계획을 유연하게 조정할 예정입니다. 현재의 가정 및 의존 요소를 고려한 목표 달성 계획은 아래와 같습니다. 두산퓨얼셀은 ’24년 말 온실가스 배출량이 업체기준 50,000tCO2eq, 사업장 기준 15,000tCO2eq 이상에 해당하지 않으므로, 목표관리제나 배출권 거래제 대상에 해당하지 않습니다. 그러나 ’22년 3월부터 에너지 사용량 기준이 삭제되면서 대상이 확대되었고, 공공부문을 중심으로 목표관리제 대상이 아닌 지방자치단체 출자기관이나 출연기관까지 감축 의무를 확대하고 있습니다. 또한, ’25년 6월부터는 목표관리제 감축 목표가 배출예상량 기준에서 기준연도대비 절대량 기준으로 강화되는 등 제도가 점차 강화되는 추세에 있습니다. 따라서 당사는 2030년까지 온실가스 배출량 감축 로드맵을 수립하고 기저부하 저감, 단기 에너지 절감 활동 및 장기적으로는 고효율 설비 투자와 재생에너지 도입을 검토하고 있습니다. 온실가스 배출규제 전망 에너지경제연구원의 보고서 1) 에 따르면 1MW규모의 LCOE(균등화 발전비용)는 ...
 [p.47] 16% 온실가스 관리 온실가스 배출 현황 온실가스 감축 로드맵 수립 두산퓨얼셀은 기후변화 대응과 탄소중립의 핵심 요소로 온실가스 관리와 온실가스 감축의 필요성을 인지하고 있습니다. 온실가스 목표관리제 및 배출권거래제 대상 사업장은 아니지만 배출량의 정확한 관리와 저감 목표 수립을 위해 IPCC 가이드라인과 국가별 관리 지침에 따라 자발적으로 제3자 온실가스 배출량을 검증하고 관련 정보를 공시하고 있습니다. 특히 2025년부터는 CDP(탄소정보공개프로젝트)에 참여하여 보다 투명하고 체계적으로 온실가스 관련 정보를 공개할 예정입니다. 두산퓨얼셀은 중장기 계획 생산량 변경에 따라 2030 온실가스 감축 로드맵을 재수립하였습니다. 2024년 말 현재 전사 온실가스 배출량의 94%를 차지하는 익산공장을 대상으로 온실가스 감축 로드맵을 수립하였으며, 2025년 양산 예정인 군산공장(SOFC)을 포함한 로드맵은 2025년 이후 수립할 계획입니다. 온실가스 및 에너지 배출량 목표 설정 2024년 익산공장 에너지 사용 목표량은 118.29TJ이었으나, 전극동의 생산설비를 인수하여 익산공장에서 생산함에 따라 에너지 사용량이 120.35TJ로 증가하였습니다. 그 결과 주요 에너지 사용 및 온실가스 배출원인 익산공장의 경우 2024년 온실가스 배출량이 목표였던 5,639tCO2eq에서 약 2.6% 초과한 5,785.541tCO 2eq으로 증가하였습니다. 그러나 Inverter와 Fan 제어 최적화, 폐열을 활용한 Heater Off 등 다양한 에너지 절감 활동을 통해서 온실가스 91.22tCO2eq을 절감하는 등 온실가스 배출 증가를 억제하였습니다. 온실가스 감축 로드맵(익산공장) &gt; 전극 내재화에 따른 로드맵 재수립 2024년8월부터 전극 내재화가 진행되고 있으며, 2025년에는 제조 공정의 Shift가 변경되어 운영하고 있습니다. 이러한 제조 공정의 변화로 인해 배출량 전망에 큰 변화가 발생할 것으로 예상됩니다. 매년 생산량이 증가함에 따라 변화가 발생할 것으로 예상되므로 기존 배출량 데이터를 기반으로 각 공정의 특성을 면밀히 분석한 후, 이를 반영하여 목표 배출량 원단위를 설정할 계획입니다. 이러한 과정을 통해 온실가스 배출량을 효과적으로 관리할 수 ...
 [p.49] 온실가스 관리 SCOPE 3 배출량 관리 점차 의무화되는 기후공시를 사전 준비하고 제품 전과정 친환경성 강화를 위하여 단계적으로 온실가스 Scope 3 배출량을 산정 및 관리하는 계획을 수립하였습니다. 2024년도에는 카테고리 5~7번을 산정하였으며, 향후 산정 범위를 확대하고 평가 방법론 및 배출계수를 고도화해 정확성을 높여 개선 활동에 활용할 예정입니다. Scope 3 산정 결과 1) 카테고리 배출량 비고 5. 폐기물 발생/처리 232.66tCO2eq • 산정 방식 : 종류별 폐기방식 기반 • 활동 자료 : 폐기물 배출 및 처리 실적 보고서 • 배출 계수 : 한국환경산업기술원 환경성적표지 평가계수 등 활용 6. 임직원 출장 394.60tCO2eq • 산정 방식 : 비용 기반 • 활동 자료 : 여비교통비_시내/해외/출장비 원장 •  배출 계수 : 미국 환경산업연관계수(USEEIO) 등 활용 7. 임직원 통근 567.40tCO2eq • 산정 방식 : 거리 기반 • 활동 자료 : 임직원 샘플링 설문 조사 결과 • 배출 계수 : 환경부 고시 2021년 국가 온실가스 배출계수 합계 1,194.66tCO2eq - 내부 탄소 가격 두산퓨얼셀은 온실가스 목표관리제 및 배출권거래제 대상 사업장은 아니지만 온실가스 배출량 확인 및 에너지 감축활동을 촉진하기 위해 내부 탄소 가격을 설정하고, 이를 경제성 평가와 내부 포상 제도 등에 활용하여 임직원의 에너지 감축활동을 유도하고 있습니다. 2) 한국거래소 KAU24 1월2일 종가 기준 내부탄소가격 2) 적용 방안 임직원의 적극적인 에너지 절감 활동을 유도하기 위해 매년 원가 절감 포상 제도의 평가항목으로 온실가스 절감 실적을 추가하여 평가를 진행하고 있습니다. 온실가스 절감 실적에 대한 개인포상 반영 두산퓨얼셀 자체 온실가스 계산기 및 연료 비교표를 활용하여 온실가스 절감계획을 수립할 때 절감량을 예측하고 연료 종류별 경제성 비교를 통해 시설 개선 및 연료 변경 시에도 온실가스 감축을 고려하고 있습니다. 연료 종류별 경제성 비교 매년 온실가스 절감 활동의 결과에 내부 탄소가격을 적용하여 공개함으로써, 임직원들이 온실가스 감축에 대한 의식을 높이고 다양한 에너지 절감 활동에 적극 참여하도록 유도하고 있습 ...
-[p.102] ESG Data 환경 일반 폐기물 지정 폐기물 2) 구분 단위 2022 2023 2024 총 지정 폐기물 발생량 ton 8.66 249.32 248.66 처리량 ton 8.95 249.42 248.35 재활용된 지정 폐기물 재활용/재사용된 지정 폐기물 총량 ton 6.34 247.36 246.74 지정 폐기물 재활용률 1) % 73.24 99.22 99.23 폐기된  지정 폐기물 폐기된 지정 폐기물 총량 ton 2.61 2.06 1.61 매립된 지정 폐기물 ton - - - 에너지 회수와 함께 소각된 지정 폐기물 ton - - - 에너지 회수 없이 소각된 지정 폐기물 ton 1.65 1.58 0.89 다른 방식으로 처리된 지정 폐기물(현장저장) ton 0.96 0.48 0.72 폐기 방법을 알 수 없는 지정 폐기물 ton - - - 데이터 범위 % 100 100 100 구분 단위 2022 2023 2024 총 일반 폐기물 발생량 ton 929.25 724.59 859.83 처리량 ton 923.24 705.28 821.33 재활용된 일반 폐기물 재활용/재사용된 일반 폐기물 총량 ton 444.37 301.80 430.86 일반 폐기물 재활용률 1) % 47.82 41.65 50.11 폐기된  일반 폐기물 폐기된 일반 폐기물 총량 ton 478.87 403.48 390.47 매립된 일반 폐기물 ton 405.92 336.50 363.65 에너지 회수와 함께 소각된 일반 폐기물 ton - - - 에너지 회수 없이 소각된 일반 폐기물 ton 72.95 66.98 26.82 다른 방식으로 처리된 일반 폐기물(현장저장) ton - - - 폐기 방법을 알 수 없는 일반 폐기물 ton - - - 데이터 범위 % 100 100 100 2) 전년도 이월된 폐기물 처리에 따라 발생량 대비 처리율이 100%를 넘을 수 있음1) 2024년부터 처리량이 아닌 발생량 기준으로 산정함에 따라 2022~2023년 수치도 동일한 기준으로 조정 Doosan Fuel Cell Sustainability Report 2025 Company Overview ESG Strategy Appendix Materiality ESG Performance ESG Data GR ...</x:v>
-      </x:c>
-      <x:c r="D24" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.102] ESG Data 환경 일반 폐기물 지정 폐기물 2) 구분 단위 2022 2023 2024 총 지정 폐기물 발생량 ton 8.66 249.32 248.66 처리량 ton 8.95 249.42 248.35 재활용된 지정 폐기물 재활용/재사용된 지정 폐기물 총량 ton 6.34 247.36 246.74 지정 폐기물 재활용률 1) % 73.24 99.22 99.23 폐기된  지정 폐기물 폐기된 지정 폐기물 총량 ton 2.61 2.06 1.61 매립된 지정 폐기물 ton - - - 에너지 회수와 함께 소각된 지정 폐기물 ton - - - 에너지 회수 없이 소각된 지정 폐기물 ton 1.65 1.58 0.89 다른 방식으로 처리된 지정 폐기물(현장저장) ton 0.96 0.48 0.72 폐기 방법을 알 수 없는 지정 폐기물 ton - - - 데이터 범위 % 100 100 100 구분 단위 2022 2023 2024 총 일반 폐기물 발생량 ton 929.25 724.59 859.83 처리량 ton 923.24 705.28 821.33 재활용된 일반 폐기물 재활용/재사용된 일반 폐기물 총량 ton 444.37 301.80 430.86 일반 폐기물 재활용률 1) % 47.82 41.65 50.11 폐기된  일반 폐기물 폐기된 일반 폐기물 총량 ton 478.87 403.48 390.47 매립된 일반 폐기물 ton 405.92 336.50 363.65 에너지 회수와 함께 소각된 일반 폐기물 ton - - - 에너지 회수 없이 소각된 일반 폐기물 ton 72.95 66.98 26.82 다른 방식으로 처리된 일반 폐기물(현장저장) ton - - - 폐기 방법을 알 수 없는 일반 폐기물 ton - - - 데이터 범위 % 100 100 100 2) 전년도 이월된 폐기물 처리에 따라 발생량 대비 처리율이 100%를 넘을 수 있음1) 2024년부터 처리량이 아닌 발생량 기준으로 산정함에 따라 2022~2023년 수치도 동일한 기준으로 조정 Doosan Fuel Cell Sustainability Report 2025 Company Overview ESG Strategy Appendix Materiality ESG Performance ESG Data GR ...</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 28;47;49;102
 Evidence type: qualitative+quantitative
 Coverage status: SUFFICIENT
-Numeric support: 15 quantitative row(s) in data_dinh_luong.csv are linked to the same source page(s).</x:v>
-      </x:c>
-      <x:c r="E24" s="6" t="str">
-        <x:v>Selected Style: status-performance
+Numeric support: 15 quantitative row(s) in data_dinh_luong.csv are linked to the same source page(s).</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: status-performance
 Preferred Style Source: template
 Answer Type: status-performance
 Answer Intent: Explain the reported status in plain language, then weave figures into the management meaning.
@@ -1335,34 +1692,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: High: topic-fit figures, non-repetitive opening, no technical metric label.</x:v>
-      </x:c>
-      <x:c r="F24" s="6" t="str">
-        <x:v>두산퓨얼셀는 환경 성과 지표 및 환경 사고 현황에 대해 발생 현황과 관리 성과를 함께 확인할 수 있도록 보고하고 있습니다. 두산퓨얼셀은 ’24년 말 온실가스 배출량이 업체기준 50,000tCO2eq, 사업장 기준 15,000tCO2eq 이상에 해당하지 않으므로, 목표관리제나 배출권 거래제 대상에 해당하지 않습니다. 온실가스 관리 SCOPE 3 배출량 관리 점차 의무화되는 기후공시를 사전 준비하고 제품 전과정 친환경성 강화를 위하여 단계적으로 온실가스 Scope 3 배출량을 산정 및 관리하는 계획을 수립하였습니다. 공개된 수치와 설명은 환경 성과 지표 및 환경 사고 현황의 현재 수준을 확인하고 다음 관리 과제를 판단하는 기준이 되며, 전년 수치와 함께 제시될 때 추세 확인에도 활용될 수 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="6" t="str">
-        <x:v>EBX-Q-024</x:v>
-      </x:c>
-      <x:c r="B25" s="6" t="str">
-        <x:v>거버넌스 / 전략 (Strategy) / 윤리경영 정책 및 목표</x:v>
-      </x:c>
-      <x:c r="C25" s="6" t="str">
-        <x:v>[p.76] 공급망 ESG 관리 &gt; 4. 환경 &gt; 5. 윤리 및 공정거래 5.1 투명경영 및 반부패: 모든 비즈니스 관계에 있어 최고 수준의 윤리 기준이 요구됩니다. 모든 형태의 부패나 갈취, 횡령, 뇌물 수수, 상납, 향응 등의 비윤리적 행위는 엄격히 금지하는 무관용 정책을 표방해야 합니다. 두산퓨얼셀의 협력회사는 이러한 비윤리적 행위에 대한 감시 및 단속 절차를 이행하여 자율적 윤리 준수를 실천하고 반부패 법령을 준수하기 위해 감시, 기록 관리, 집행 절차를 실행해야 합니다. 5.2 공정거래 준수: 두산퓨얼셀의 협력회사는 사업상에서 부당하거나 부적절한 거래를 통해 이익을 취하는 수단을 제공하거나 수락하는 행위를 금지해야 합니다. 공정거래와 관련한 법규와 규정을 준수하여야 하며, 불공정한 거래 관행 등 공정한 거래 질서를 저해하는 행위를 하여서는 안 됩니다. 또한 상품 또는 용역의 가격, 공급량, 거래 지역, 거래조건 등에 관해 다른 사업자와 부당하게 경쟁을 제한하는 행위를 합의해서는 안 되며 회사, 경쟁업체, 협력업체, 제3자로부터 부정하게 정보를 획득하거나 획득한 정보를 사용 또는 공개해서는 안됩니다. 5.3 투명한 정보공개: 두산퓨얼셀의 협력회사는 관련법과 규정을 준수하여, 사업 활동과 재정 상황, 사업성과 등에 대한 정보를 거짓 없이 공개해야 합니다. 모든 업무 거래를 투명하게 실행하고 협력회사의 사업 장부와 기록에 정확히 반영해야 합니다. 협력회사의 노동, 보건과 안전, 환경관리 실태, 사업 활동, 구조, 재무 현황 및 성과에 관한 정보를 관련 일반적인 산업계 관행에 따라 공개해야 합니다. 공급망 내 관련 분야 실태 및 관행에 대한 기록 위조나 부실 표기는 용인될 수 없습니다. 5.4 지적재산권 보호: 두산퓨얼셀의 협력회사는 사업상 타인의 특허, 소프트웨어, 디자인, 상표 등과 같은 지적 재산을 침해하거나 불법적으로 사용하지 않습니다. 지적재산권을 존중하며 기술 및 노하우의 이전은 해당 권리를 보호하는 방식으로 이루어져야 합니다. 5.5 개인정보보호: 두산퓨얼셀의 협력회사는 모든 이해관계자(협력회사, 고객사, 임직원 등)의 개인정보를 체계적으로 관리 및 보호해야 하며, 개인정보의 수집, 저장, 이용, 제공, 파기 등 처리 시 관련 법규를 ...
+QA Severity: High: topic-fit figures, non-repetitive opening, no technical metric label.</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 환경 성과 지표 및 환경 사고 현황에 대해 발생 현황과 관리 성과를 함께 확인할 수 있도록 보고하고 있습니다. 두산퓨얼셀은 ’24년 말 온실가스 배출량이 업체기준 50,000tCO2eq, 사업장 기준 15,000tCO2eq 이상에 해당하지 않으므로, 목표관리제나 배출권 거래제 대상에 해당하지 않습니다. 점차 의무화되는 기후공시를 사전 준비하고 제품 전과정 친환경성 강화를 위하여 단계적으로 온실가스 Scope 3 배출량을 산정 및 관리하는 계획을 수립하였습니다. 공개된 수치와 설명은 환경 성과 지표 및 환경 사고 현황의 현재 수준을 확인하고 다음 관리 과제를 판단하는 기준이 되며, 전년 수치와 함께 제시될 때 추세 확인에도 활용될 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-024</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>거버넌스 / 전략 (Strategy) / 윤리경영 정책 및 목표</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>[p.76] 공급망 ESG 관리 &gt; 4. 환경 &gt; 5. 윤리 및 공정거래 5.1 투명경영 및 반부패: 모든 비즈니스 관계에 있어 최고 수준의 윤리 기준이 요구됩니다. 모든 형태의 부패나 갈취, 횡령, 뇌물 수수, 상납, 향응 등의 비윤리적 행위는 엄격히 금지하는 무관용 정책을 표방해야 합니다. 두산퓨얼셀의 협력회사는 이러한 비윤리적 행위에 대한 감시 및 단속 절차를 이행하여 자율적 윤리 준수를 실천하고 반부패 법령을 준수하기 위해 감시, 기록 관리, 집행 절차를 실행해야 합니다. 5.2 공정거래 준수: 두산퓨얼셀의 협력회사는 사업상에서 부당하거나 부적절한 거래를 통해 이익을 취하는 수단을 제공하거나 수락하는 행위를 금지해야 합니다. 공정거래와 관련한 법규와 규정을 준수하여야 하며, 불공정한 거래 관행 등 공정한 거래 질서를 저해하는 행위를 하여서는 안 됩니다. 또한 상품 또는 용역의 가격, 공급량, 거래 지역, 거래조건 등에 관해 다른 사업자와 부당하게 경쟁을 제한하는 행위를 합의해서는 안 되며 회사, 경쟁업체, 협력업체, 제3자로부터 부정하게 정보를 획득하거나 획득한 정보를 사용 또는 공개해서는 안됩니다. 5.3 투명한 정보공개: 두산퓨얼셀의 협력회사는 관련법과 규정을 준수하여, 사업 활동과 재정 상황, 사업성과 등에 대한 정보를 거짓 없이 공개해야 합니다. 모든 업무 거래를 투명하게 실행하고 협력회사의 사업 장부와 기록에 정확히 반영해야 합니다. 협력회사의 노동, 보건과 안전, 환경관리 실태, 사업 활동, 구조, 재무 현황 및 성과에 관한 정보를 관련 일반적인 산업계 관행에 따라 공개해야 합니다. 공급망 내 관련 분야 실태 및 관행에 대한 기록 위조나 부실 표기는 용인될 수 없습니다. 5.4 지적재산권 보호: 두산퓨얼셀의 협력회사는 사업상 타인의 특허, 소프트웨어, 디자인, 상표 등과 같은 지적 재산을 침해하거나 불법적으로 사용하지 않습니다. 지적재산권을 존중하며 기술 및 노하우의 이전은 해당 권리를 보호하는 방식으로 이루어져야 합니다. 5.5 개인정보보호: 두산퓨얼셀의 협력회사는 모든 이해관계자(협력회사, 고객사, 임직원 등)의 개인정보를 체계적으로 관리 및 보호해야 하며, 개인정보의 수집, 저장, 이용, 제공, 파기 등 처리 시 관련 법규를 ...
 [p.88] 우편 서울특별시 중구 장충단로 275 두산타워 17층 두산퓨얼셀 이메일 inhye.jo@doosan.com 주관부서 두산퓨얼셀㈜ Legal/Compliance팀 윤리경영 윤리규범 서문 HELP DESK 운영 회사의 윤리경영 정책 및 윤리규범 세부내용, 기타 신고 및 제보 등과 관련된 궁금한 사항이나 문의에 대하여 상담, 안내할 수 있는 청구인 Help Desk를 두어 회사 홈페이지에 게재하였으며, 이를 통해 두산퓨얼셀㈜ 윤리경영 원칙과 업무 수행방침에 대해 두산퓨얼셀 내부 임직원은 물론 외부 이해관계자들의 이해를 향상시켰습니다. 사이버신고센터 운영방침 •  두산퓨얼셀 사이버신고센터는 임직원과 외부인 모두에게 열려 있으 며, 법령, 두산퓨얼셀 Credo 및 윤리규범 등 내부규정 위반행위, 기타 부당한 행위를 신고대상으로 합니다. •  신고는 익명 또는 실명으로 하실 수 있습니다. 다만, 회사는 구체적인 증거가 제시되지 않은 익명신고 등에 대하여 조사하지 않을 수 있습 니다. •  회사는 신고자의 신원 및 신고내용 등에 대한 비밀을 보장하며, 선의 의 신고자에 대한 불이익을 금지합니다. •  임직원의 신고에는 회사의 내부신고제도 운영규정이 적용되며, 본 규 정은 두드림 또는 주관부서를 통하여 안내 받으실 수 있습니다. •  회사는 사이버신고센터 이외에도 우편, 전화, 팩스, 이메일, 주관부서 방문 등 다양한 경로를 통하여 신고를 받고 있습니다. 접수 채널 윤리규범 및 윤리규범 위반과 관련한 문의사항이나 도움이 필요한 경우 두산퓨얼셀은 지속적인 성장을 위하여 인화, 고객 중심의 경영 철학과 함께 투명한 경영 및 혁신을 기반으로 기업의 경쟁력을 높이고 사회적 책임을 성실히 이행하고자 합니다. 이에 따라 윤리규범을 제정하여 임직원이 업무 수행 시 준수해야 할 행동 원칙으로 삼고 있습니다. 이 윤리규범은 두산퓨얼셀의 임직원(이하 "두산인")에게 적용되며, 두산퓨얼셀과 거래하는 협력업체 등 제3자도 함께 준수할 것을 권장합니다. 두산인은 관련법령과 윤리규범을 포함한 내부규정을 올바르게 이해하고 준수할 책임이 있습니다. Legal/Compliance팀은 윤리규범에서 명시되지 않았거나 구체적 해석이 필요한 사항에 대해 별도의 세부 규정을 마련 ...
 [p.89] 윤리경영 두산퓨얼셀의 모든 임직원은 윤리경영에 대한 인식 수준을 함양하고자 매년 온라인 및 대면방식 윤리규범 교육을 수강하고 있습니다. 모든 임직원은 윤리규범준수서약서와 이해관계서술서를 제출함으로써 윤리적 가치를 준수하고 정직·투명하게 업무를 수행하려는 의지를 표명하고 있습니다. 또한 모든 임직원들에게 CEO의 메시지를 통해 윤리규범에 대한 실천 및 준수를 당부하고 있습니다. 특히, 명절 등 선물이 오가는 시기에는 정직과 투명성 실천 및 법규준수를 강조하는 CEO Announcement를 매년 진행하여 임직원들의 경각심을 고취하고 있습니다. 반부패 및 윤리규범 교육 협력사 및 임직원 반부패 설문 두산퓨얼셀은 임직원과 협력사를 대상으로 매년 설문조사를 실시하여 윤리경영에 대한 임직원의 인식 수준을 확인하고 의견을 청취하고 있습니다. 설문조사 결과는 부정 방지 대안 수립, 부족한 부분에 대한 개선방안 도출 등의 윤리경영 활동 계획 수립에 활용하고 있습니다. 2024년 시행된 임직원 설문은 투명하고 적극적인 응답을 위하여 무기명으로 실시되었으며, 서술형을 포함하여 임직원 24개 항목, 협력사 21개 문항을 조사했습니다. 반부패 설문 구성 진단영역 문항수 기본정보(소속/직위) 2개 윤리경영 제도 및 시스템 6개 건전한 조직문화 4개 정직과 투명성 5개 공정한 경쟁 4개 종업원 관계 3개 설문은 매우 그렇지 않다(0점)-그렇지 않다(25점)-보통이다(50점)-그렇다(75점)-매우 그렇다(100점)의 척도로 조사하였으며 설문 결과 임직원 평균 76점, 협력사 평균 86점으로 그렇다(75점)와 매우 그렇다(100점)의 사잇값이 나와 비교적 윤리경영이 잘 지켜지는 것으로 조사되었습니다. 두산퓨얼셀은 평균값 이하가 나온 취약항목에 대해 개선대책을 마련하고 시행할 계획입니다. 윤리경영 위반 및 조치 2024년에는 2건의 제보가 접수되었으며 1건의 징계 처분(경고)이 이루어졌습니다. 고용노동부의 ‘개인정보보호 가이드’에 따라, 윤리규범 위반 건이 발생하면 개인정보를 제외한 구성원의 비윤리 행위 사례에 대해 백서제도, 윤리교육 사례전파, 윤리경영 Letter 형식으로 공개하는 등 관련 사항의 정보 공유를 통해 유사 사례의 재발을 방지하고 있습니다. 여기에 ...
-[p.99] 협회 및 단체활동 UNGC 활동 협회 및 단체 활동 두산퓨얼셀은 2023년 6월 유엔글로벌콤팩트에 가입하여 10대 원칙에 대한 지지를 선언했습니다. 2024년에는 최초로 이행성과보고서(CoP, Communication on Progress)를 통해 4대 영역 10대 원칙에 대한 활동 경과를 보고하였으며, 매년 이행성과보고서를 통해 활동 경과를 보고할 예정입니다. 또한 가입 이후 UNGC의 10대 원칙과 ESG 활동의  내재화를 위해 각 실무진들이 다양한 실무그룹과 엑셀러레이터 프로그램, 세미나에 참여하고 있습니다. 2024년에는 총 10명의 실무자가 ESG/환경/인권/반부패/지속가능금융 실무그룹 및 기업과 인권, 기후앰비션 엑셀러레이터, Target Gender Equality 프로그램에 참석하여 수료했습니다. 2025년에는 사회공헌 실무그룹을 포함한 6개의 실무그룹과 2개의 엑셀러레이터 프로그램에 참여하여 주요 현안을 파악하고 ESG T rend에 대해 논의할 예정으로, 끊임없이 역량 강화를 위해 노력하고 있습니다. 두산퓨얼셀은 파리기후협약 이행과 탄소중립에 기여하기 위해 수소 및 신재생 산업에 관련된 다양한 협회 및 단체 활동에 적극 참여하고 있습니다. 특히 두산퓨얼셀㈜ 대표이사는 한국수소연료전지산업협회 회장으로서 수소산업 생태계의 이해관계자들과 적극적으로 소통하면서 수소산업 발전에 커다란 관심을 갖고 활동하고 있습니다. 또한 기후위기를 해결하고 신재생에너지 산업 촉진과 생태계 조성을 위하여 재생에너지 및 무탄소 전원과 관련된 제도 지원, 기술 개발과 보급 확대, 인력양성을 위한 ‘RE100 ㆍ CF100 에너지솔루션 얼라이언스’에 참여하고 있습니다. 참여/가입 연도 협회/단체명 2024년 RE100ㆍCF100 에너지솔루션 얼라이언스 2023년 수소도시 융합포럼 2022년 한국수소연료전지산업협회 2021년 에너지얼라이언스 청정 암모니아 협의체 에너지미래포럼 에너지전환포럼 2017년 한국수소연합 2016년 연료전지산업발전협의회 2003년 한국신재생에너지협회 ESG내재화 실무그룹 운영 환경 실무그룹 세계적으로 강화되는 환경 관련 기업 규제 대응역량을 강화하고 저탄소 에너지 전환 전략을 공유 지속가능금융 실무그룹 임팩트 투자, ESG ...</x:v>
-      </x:c>
-      <x:c r="D25" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.99] 협회 및 단체활동 UNGC 활동 협회 및 단체 활동 두산퓨얼셀은 2023년 6월 유엔글로벌콤팩트에 가입하여 10대 원칙에 대한 지지를 선언했습니다. 2024년에는 최초로 이행성과보고서(CoP, Communication on Progress)를 통해 4대 영역 10대 원칙에 대한 활동 경과를 보고하였으며, 매년 이행성과보고서를 통해 활동 경과를 보고할 예정입니다. 또한 가입 이후 UNGC의 10대 원칙과 ESG 활동의  내재화를 위해 각 실무진들이 다양한 실무그룹과 엑셀러레이터 프로그램, 세미나에 참여하고 있습니다. 2024년에는 총 10명의 실무자가 ESG/환경/인권/반부패/지속가능금융 실무그룹 및 기업과 인권, 기후앰비션 엑셀러레이터, Target Gender Equality 프로그램에 참석하여 수료했습니다. 2025년에는 사회공헌 실무그룹을 포함한 6개의 실무그룹과 2개의 엑셀러레이터 프로그램에 참여하여 주요 현안을 파악하고 ESG T rend에 대해 논의할 예정으로, 끊임없이 역량 강화를 위해 노력하고 있습니다. 두산퓨얼셀은 파리기후협약 이행과 탄소중립에 기여하기 위해 수소 및 신재생 산업에 관련된 다양한 협회 및 단체 활동에 적극 참여하고 있습니다. 특히 두산퓨얼셀㈜ 대표이사는 한국수소연료전지산업협회 회장으로서 수소산업 생태계의 이해관계자들과 적극적으로 소통하면서 수소산업 발전에 커다란 관심을 갖고 활동하고 있습니다. 또한 기후위기를 해결하고 신재생에너지 산업 촉진과 생태계 조성을 위하여 재생에너지 및 무탄소 전원과 관련된 제도 지원, 기술 개발과 보급 확대, 인력양성을 위한 ‘RE100 ㆍ CF100 에너지솔루션 얼라이언스’에 참여하고 있습니다. 참여/가입 연도 협회/단체명 2024년 RE100ㆍCF100 에너지솔루션 얼라이언스 2023년 수소도시 융합포럼 2022년 한국수소연료전지산업협회 2021년 에너지얼라이언스 청정 암모니아 협의체 에너지미래포럼 에너지전환포럼 2017년 한국수소연합 2016년 연료전지산업발전협의회 2003년 한국신재생에너지협회 ESG내재화 실무그룹 운영 환경 실무그룹 세계적으로 강화되는 환경 관련 기업 규제 대응역량을 강화하고 저탄소 에너지 전환 전략을 공유 지속가능금융 실무그룹 임팩트 투자, ESG ...</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 76;88;89;99
 Evidence type: qualitative+quantitative
 Coverage status: SUFFICIENT
-Numeric support: 2 quantitative row(s) in data_dinh_luong.csv are linked to the same source page(s).</x:v>
-      </x:c>
-      <x:c r="E25" s="6" t="str">
-        <x:v>Selected Style: narrative
+Numeric support: 2 quantitative row(s) in data_dinh_luong.csv are linked to the same source page(s).</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: narrative
 Preferred Style Source: template
 Answer Type: strategy-policy
 Answer Intent: Explain the policy or strategic direction first, then connect targets, governance, and execution evidence.
@@ -1381,34 +1750,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: Medium: prose must be natural, evidence-grounded, and non-repetitive.</x:v>
-      </x:c>
-      <x:c r="F25" s="6" t="str">
-        <x:v>이를 통해 두산퓨얼셀㈜ 윤리경영 원칙과 업무 수행방침에 대해 두산퓨얼셀 내부 임직원은 물론 외부 이해관계자들의 이해를 향상시켰습니다. 이 윤리규범은 두산퓨얼셀의 임직원(이하 "두산인")에게 적용되며, 두산퓨얼셀과 거래하는 협력업체 등 제3자도 함께 준수할 것을 권장합니다. 윤리경영 두산퓨얼셀의 모든 임직원은 윤리경영에 대한 인식 수준을 함양하고자 매년 온라인 및 대면방식 윤리규범 교육을 수강하고 있습니다. 두산퓨얼셀는 윤리경영 정책 및 목표를 중장기 방향과 실행 과제에 연결해 지속가능경영의 방향성을 제시하고 있습니다. 이러한 내용은 윤리경영 정책 및 목표가 선언에 머물지 않고 목표, 조직, 실행 과제로 이어지는 구조임을 보여줍니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="6" t="str">
-        <x:v>EBX-Q-025</x:v>
-      </x:c>
-      <x:c r="B26" s="6" t="str">
-        <x:v>거버넌스 / 거버넌스 (Governance) / 윤리경영 조직 및 운영 체계</x:v>
-      </x:c>
-      <x:c r="C26" s="6" t="str">
-        <x:v>[p.62] 인권경영 차별 및 괴롭힘 방지 지침 직장 내 성희롱, 괴롭힘 및 차별 금지 직장 내 성희롱 금지 |  사업주, 관리자 또는 구성원이 직장 내의 지위를 이용하거나 업무 수행과 관련하여 다른 구성원에게 성적인 언동 등으로 성적 굴욕감 또는 혐오감을 느끼게 해서는 안됩니다. 또한 이러한 성적인 언동이나 그 밖의 요구에 따르지 아니하였다는 이유로 근로조건 및 고용에서 불이익을 주는 행위를 해서는 안됩니다. 직장 내 괴롭힘 금지 |  회사 내에서의 지위 또는 관계 등의 우위를 이용하여 업무상 적정 범위를 넘어 다른 구성원에게 신체적, 정신적 고통을 주거나 근무환경을 악화시키는 행위를 해서는 안됩니다. 직장 내 괴롭힘의 행위는 신체적 괴롭힘과 신분적, 업무적, 언어적, 개인적 괴롭힘 및 근무환경의 악화를 포함합니다. 차별 금지 |  임직원의 성별, 인종, 민족, 국적, 종교, 나이, 정치적 견해, 출신 지역에 따라 차별적인 대우를 해서는 안됩니다. 발생 시 조치 신고접수(두산퓨얼셀 인권센터 및 두산그룹 내외부 신고센터) |  직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 알게 된 경우 누구라도 그 내용을 신고할 수 있으며, 신고 접수 시에는 조사 의뢰 등 적절한 방안을 강구하게 됩니다. 조사 및 심의(조사 담당 부서) |  사실 관계 파악을 위해 성희롱, 괴롭힘, 차별 등의 여부를 확인하며, 조사 관련자의 신원에 대해서는 비밀을 유지합니다. 이때, 해결 방식에 대해 피해자의 의견을 청취하고 피해자의 요청이 있을 경우 근무장소의 변경, 휴가의 명령 등 적절한 조치를 취합니다. 조치(인사위원회 주관 부서) |  행위에 의한 피해사실이 확인된 경우에는 지체없이 행위자에 대하여 징계나 그 밖에 이에 준하는 조치를 취합니다. 직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 신고한 직원 또는 피해를 입었거나 피해 발생을 주장하는 직원은 적극적으로 보호합니다. 모니터링(인권센터, HR) |  조치사항의 이행여부와 후속적인 괴롭힘 피해가 없는지 모니터링하며, 피해자에 대한 불리한 처우가 발생하지 않도록 예방합니다. 비밀유지 직장 내 성희롱, 괴롭힘 및 차별 조사 과정에 참여한 임직원은 조사 등으로 알게 된 비밀을 누설하지 않습니다. 재발방지 조치 회 ...
+QA Severity: Medium: prose must be natural, evidence-grounded, and non-repetitive.</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀 윤리경영 원칙과 업무 수행방침에 대해 두산퓨얼셀 내부 임직원은 물론 외부 이해관계자들의 이해를 향상시켰습니다. 이 윤리규범은 두산퓨얼셀의 임직원(이하 "두산인")에게 적용되며, 두산퓨얼셀과 거래하는 협력업체 등 제3자도 함께 준수할 것을 권장합니다. 두산퓨얼셀의 모든 임직원은 윤리경영에 대한 인식 수준을 함양하고자 매년 온라인 및 대면방식 윤리규범 교육을 수강하고 있습니다. 두산퓨얼셀은 윤리경영 정책 및 목표를 중장기 방향과 실행 과제에 연결해 지속가능경영의 방향성을 제시하고 있습니다. 이러한 내용은 윤리경영 정책 및 목표가 선언에 머물지 않고 목표, 조직, 실행 과제로 이어지는 구조임을 보여줍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-025</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>거버넌스 / 거버넌스 (Governance) / 윤리경영 조직 및 운영 체계</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>[p.62] 인권경영 차별 및 괴롭힘 방지 지침 직장 내 성희롱, 괴롭힘 및 차별 금지 직장 내 성희롱 금지 |  사업주, 관리자 또는 구성원이 직장 내의 지위를 이용하거나 업무 수행과 관련하여 다른 구성원에게 성적인 언동 등으로 성적 굴욕감 또는 혐오감을 느끼게 해서는 안됩니다. 또한 이러한 성적인 언동이나 그 밖의 요구에 따르지 아니하였다는 이유로 근로조건 및 고용에서 불이익을 주는 행위를 해서는 안됩니다. 직장 내 괴롭힘 금지 |  회사 내에서의 지위 또는 관계 등의 우위를 이용하여 업무상 적정 범위를 넘어 다른 구성원에게 신체적, 정신적 고통을 주거나 근무환경을 악화시키는 행위를 해서는 안됩니다. 직장 내 괴롭힘의 행위는 신체적 괴롭힘과 신분적, 업무적, 언어적, 개인적 괴롭힘 및 근무환경의 악화를 포함합니다. 차별 금지 |  임직원의 성별, 인종, 민족, 국적, 종교, 나이, 정치적 견해, 출신 지역에 따라 차별적인 대우를 해서는 안됩니다. 발생 시 조치 신고접수(두산퓨얼셀 인권센터 및 두산그룹 내외부 신고센터) |  직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 알게 된 경우 누구라도 그 내용을 신고할 수 있으며, 신고 접수 시에는 조사 의뢰 등 적절한 방안을 강구하게 됩니다. 조사 및 심의(조사 담당 부서) |  사실 관계 파악을 위해 성희롱, 괴롭힘, 차별 등의 여부를 확인하며, 조사 관련자의 신원에 대해서는 비밀을 유지합니다. 이때, 해결 방식에 대해 피해자의 의견을 청취하고 피해자의 요청이 있을 경우 근무장소의 변경, 휴가의 명령 등 적절한 조치를 취합니다. 조치(인사위원회 주관 부서) |  행위에 의한 피해사실이 확인된 경우에는 지체없이 행위자에 대하여 징계나 그 밖에 이에 준하는 조치를 취합니다. 직장 내 성희롱, 괴롭힘 및 차별 발생 사실을 신고한 직원 또는 피해를 입었거나 피해 발생을 주장하는 직원은 적극적으로 보호합니다. 모니터링(인권센터, HR) |  조치사항의 이행여부와 후속적인 괴롭힘 피해가 없는지 모니터링하며, 피해자에 대한 불리한 처우가 발생하지 않도록 예방합니다. 비밀유지 직장 내 성희롱, 괴롭힘 및 차별 조사 과정에 참여한 임직원은 조사 등으로 알게 된 비밀을 누설하지 않습니다. 재발방지 조치 회 ...
 [p.63] 인권경영 인권정책 인권이슈 제보 채널 두산퓨얼셀은 홈페이지 내 사이버 신고센터를 통해 임직원을 포함한 모든 이해관계자가 인권 침해 및 기타 비윤리적 행위를 제보할 수 있도록 하고 있으며, 비밀보장 원칙에 따라 비공개 신고도 가능합니다. 접수된 제보는 철저히 보호되며, 내부 절차에 따라 신속히 처리됩니다. 또한 인권 관련 문제가 발생한 경우, 피해자 또는 목격자는 내부 신고센터, 직장 내 괴롭힘·성희롱 예방센터, 인권센터 등을 통해 신고할 수 있습니다. 두산퓨얼셀은 임직원 뿐 아니라 경영활동에서 관계를 맺고 있는 모든 이해관계자의 인권을 존중하며, 협력업체 등 제3자를 대상으로 동일한 수준의 인권경영을 권고하고 있습니다. 두산퓨얼셀은 협력사 및 주요 비즈니스 파트너에게 인권보호에 대한 의무이행을 요구하며, 준수 여부를 모니터링 합니다. 두산퓨얼셀은 인권, 노동, 환경과 반부패에 관한 글로벌콤팩트 10대 원칙에 대한 CEO의 지지선언과 함께, ‘세계인권선언(Universal Declaration of Human Rights )’과 ‘유엔 기업과 인권 이행원칙(UN Guiding Principles on Business and Human Rights; Ruggie Framework)’ 등 국제적으로 인정받고 있는 인권원칙을 바탕으로 인권경영 실천 및 실사체계(Due Diligence)를 수립하여 운영하고 있습니다. 고용상의 비차별과 결사 및 단체교섭의 자유 보장 고용과 관련하여 성별, 종교, 장애, 나이, 사회적 신분, 출신 지역 등을 이유로 일체의 부당한 차별을 하지 않으며, 다양성을 포용합니다. 더불어 근로자들의 결사의 자유와 단체 교섭의 자유를 인정하고 노동조합 활동을 이유로 어떠한 불이익도 주지 않습니다. 강제노동 및 아동노동의 금지 사업활동에서 발생할 수 있는 어떠한 형태의 강제노동도 인정하지 않으며 사업 국가가 정한 최소 고용 연령을 준수합니다. 사업 국가의 법규에서 정한 최소고용연령을 준수하고 연소자를 고용한 것을 알게 된 경우, 즉시 구제 조치를 취하는 등 인간 존엄성에 해를 끼치는 모든 잘못된 노동관행을 방지하겠습니다. 산업안전보장 및 책임 있는 공급망 관리 작업환경을 안전하게 유지하며 사업장에 적용되는 환경, 보건 및 안전 ...
 [p.88] 우편 서울특별시 중구 장충단로 275 두산타워 17층 두산퓨얼셀 이메일 inhye.jo@doosan.com 주관부서 두산퓨얼셀㈜ Legal/Compliance팀 윤리경영 윤리규범 서문 HELP DESK 운영 회사의 윤리경영 정책 및 윤리규범 세부내용, 기타 신고 및 제보 등과 관련된 궁금한 사항이나 문의에 대하여 상담, 안내할 수 있는 청구인 Help Desk를 두어 회사 홈페이지에 게재하였으며, 이를 통해 두산퓨얼셀㈜ 윤리경영 원칙과 업무 수행방침에 대해 두산퓨얼셀 내부 임직원은 물론 외부 이해관계자들의 이해를 향상시켰습니다. 사이버신고센터 운영방침 •  두산퓨얼셀 사이버신고센터는 임직원과 외부인 모두에게 열려 있으 며, 법령, 두산퓨얼셀 Credo 및 윤리규범 등 내부규정 위반행위, 기타 부당한 행위를 신고대상으로 합니다. •  신고는 익명 또는 실명으로 하실 수 있습니다. 다만, 회사는 구체적인 증거가 제시되지 않은 익명신고 등에 대하여 조사하지 않을 수 있습 니다. •  회사는 신고자의 신원 및 신고내용 등에 대한 비밀을 보장하며, 선의 의 신고자에 대한 불이익을 금지합니다. •  임직원의 신고에는 회사의 내부신고제도 운영규정이 적용되며, 본 규 정은 두드림 또는 주관부서를 통하여 안내 받으실 수 있습니다. •  회사는 사이버신고센터 이외에도 우편, 전화, 팩스, 이메일, 주관부서 방문 등 다양한 경로를 통하여 신고를 받고 있습니다. 접수 채널 윤리규범 및 윤리규범 위반과 관련한 문의사항이나 도움이 필요한 경우 두산퓨얼셀은 지속적인 성장을 위하여 인화, 고객 중심의 경영 철학과 함께 투명한 경영 및 혁신을 기반으로 기업의 경쟁력을 높이고 사회적 책임을 성실히 이행하고자 합니다. 이에 따라 윤리규범을 제정하여 임직원이 업무 수행 시 준수해야 할 행동 원칙으로 삼고 있습니다. 이 윤리규범은 두산퓨얼셀의 임직원(이하 "두산인")에게 적용되며, 두산퓨얼셀과 거래하는 협력업체 등 제3자도 함께 준수할 것을 권장합니다. 두산인은 관련법령과 윤리규범을 포함한 내부규정을 올바르게 이해하고 준수할 책임이 있습니다. Legal/Compliance팀은 윤리규범에서 명시되지 않았거나 구체적 해석이 필요한 사항에 대해 별도의 세부 규정을 마련 ...
-[p.97] 2차 방어선 (2nd line of defence) 리스크 관리 리스크 관리 거버넌스 두산퓨얼셀은 체계적이고 전사적인 리스크 관리 활동을 통해 영업의 효율성, 재무보고의 신뢰성, 법규 및 규정 준수 등의 조직 목표를 효과적 ㆍ 효율적으로 달성하기 위하여 적절한 내부통제 체계를 갖추고 있습니다. 제품 제조 ㆍ 생산 ㆍ 공급하는데 직접적으로 관여하는 부서는 일상적인 운영에서 1차적으로 리스크를 관리하고 모니터링할 책임이 있으며, 리스크 모니터링 전담 부서와 기능적으로 분할된 관련 부서들이 2차적으로 리스크를 관리 ㆍ 감독하고 있습니다. 마지막으로 두산퓨얼셀은 상법 제542조의13 등 관련 규정에 의거하여 준법지원인을 선임하였으며, 준법지원인은 위험 관리 및 규정 준수 프로세스의 효과에 대한 독립적인 보증을 제공하는 내부 감사 기능을 수행합니다. 잠재 리스크 및 대응 활동 잠재 리스크 연료전지 시장 다각화(혁신기술 개발 요구) 인공지능(AI) 기술의 발전에 따른 보안 위협 설명 연료전지 시장이 다각화 됨에 따라 혁신기술 개발 요구가 증대되고 있습니다. 기업은 빠르게 변화하는 시장 환경에서 고객의 니즈에 부합하는 기술 개발을 위해 자원과 역량을 투입해야 합니다. AI 기술의 발전은 기업의 생산성 향상에 기여하는 한편, 악용 사례로 인한 사이버 보안 위협도 함께 증가시키고 있습니다. 기업은 기존 보안 시스템으로 대응이 어려운 신규 보안 위협 요인에 대비가 필요합니다. 영향 혁신기술을 적시에 개발하지 못하거나 성공적으로 상용화하지 못할 경우, 기술 개발 투자에서 기대했던 이익이 실현되지 않아 회사의 수익성과 매출에 부정적인 영향을 미칠 수 있습니다. 두산퓨얼셀은 국가핵심기술 취급사로서, 국내외 시장에서 차지하는 기술적·경제적 가치가 높아 관련 정보가 유출될 경우 당사의 기술 경쟁력 뿐만 아니라 국가 안보와 국민경제의 발전에 중대한 악영향을 미칠 수 있습니다. 대응 두산퓨얼셀은국내 최초 상용화 한 SOFC(고체산화물 연료전지) 기술을 바탕으로 한 선박용 연료전지 시장 진출을 위해 기술 확보 및 생산설비를 구축하고, 선사, 조선사 등과 함께 선박용 연료전지 실증사업을 추진하고 있습니다. 두산퓨얼셀은 정보보호최고책임자(CISO)와 개인정보보호 최고 책 ...</x:v>
-      </x:c>
-      <x:c r="D26" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.97] 2차 방어선 (2nd line of defence) 리스크 관리 리스크 관리 거버넌스 두산퓨얼셀은 체계적이고 전사적인 리스크 관리 활동을 통해 영업의 효율성, 재무보고의 신뢰성, 법규 및 규정 준수 등의 조직 목표를 효과적 ㆍ 효율적으로 달성하기 위하여 적절한 내부통제 체계를 갖추고 있습니다. 제품 제조 ㆍ 생산 ㆍ 공급하는데 직접적으로 관여하는 부서는 일상적인 운영에서 1차적으로 리스크를 관리하고 모니터링할 책임이 있으며, 리스크 모니터링 전담 부서와 기능적으로 분할된 관련 부서들이 2차적으로 리스크를 관리 ㆍ 감독하고 있습니다. 마지막으로 두산퓨얼셀은 상법 제542조의13 등 관련 규정에 의거하여 준법지원인을 선임하였으며, 준법지원인은 위험 관리 및 규정 준수 프로세스의 효과에 대한 독립적인 보증을 제공하는 내부 감사 기능을 수행합니다. 잠재 리스크 및 대응 활동 잠재 리스크 연료전지 시장 다각화(혁신기술 개발 요구) 인공지능(AI) 기술의 발전에 따른 보안 위협 설명 연료전지 시장이 다각화 됨에 따라 혁신기술 개발 요구가 증대되고 있습니다. 기업은 빠르게 변화하는 시장 환경에서 고객의 니즈에 부합하는 기술 개발을 위해 자원과 역량을 투입해야 합니다. AI 기술의 발전은 기업의 생산성 향상에 기여하는 한편, 악용 사례로 인한 사이버 보안 위협도 함께 증가시키고 있습니다. 기업은 기존 보안 시스템으로 대응이 어려운 신규 보안 위협 요인에 대비가 필요합니다. 영향 혁신기술을 적시에 개발하지 못하거나 성공적으로 상용화하지 못할 경우, 기술 개발 투자에서 기대했던 이익이 실현되지 않아 회사의 수익성과 매출에 부정적인 영향을 미칠 수 있습니다. 두산퓨얼셀은 국가핵심기술 취급사로서, 국내외 시장에서 차지하는 기술적·경제적 가치가 높아 관련 정보가 유출될 경우 당사의 기술 경쟁력 뿐만 아니라 국가 안보와 국민경제의 발전에 중대한 악영향을 미칠 수 있습니다. 대응 두산퓨얼셀은국내 최초 상용화 한 SOFC(고체산화물 연료전지) 기술을 바탕으로 한 선박용 연료전지 시장 진출을 위해 기술 확보 및 생산설비를 구축하고, 선사, 조선사 등과 함께 선박용 연료전지 실증사업을 추진하고 있습니다. 두산퓨얼셀은 정보보호최고책임자(CISO)와 개인정보보호 최고 책 ...</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 62;63;88;97
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E26" s="6" t="str">
-        <x:v>Selected Style: governance
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: governance
 Preferred Style Source: template
 Answer Type: governance-organization
 Answer Intent: Explain who is responsible, what they decide or oversee, and how reporting or escalation works.
@@ -1427,34 +1808,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: Medium: responsibility and decision flow must be clear.</x:v>
-      </x:c>
-      <x:c r="F26" s="6" t="str">
-        <x:v>두산퓨얼셀는 윤리경영 조직 및 운영 체계와 관련해 책임 주체와 의사결정 흐름을 중심으로 관리 체계를 설명하고 있습니다. 사이버신고센터 운영방침 •  두산퓨얼셀 사이버신고센터는 임직원과 외부인 모두에게 열려 있으 며, 법령, 두산퓨얼셀 Credo 및 윤리규범 등 내부규정 위반행위, 기타 부당한 행위를 신고대상으로 합니다. 이 구조는 윤리경영 조직 및 운영 체계의 담당 조직, 보고 경로, 감독 역할을 한 문맥에서 확인할 수 있게 합니다. 공개 내용은 윤리경영 조직 및 운영 체계의 책임 배분과 감독 수준을 함께 보여주며, 의사결정 체계가 실제 운영 구조와 어떻게 연결되는지 파악하는 데 도움이 됩니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="6" t="str">
-        <x:v>EBX-Q-026</x:v>
-      </x:c>
-      <x:c r="B27" s="6" t="str">
-        <x:v>거버넌스 / 위험 관리 (Risk Management) / 윤리 및 준법 리스크 관리</x:v>
-      </x:c>
-      <x:c r="C27" s="6" t="str">
-        <x:v>[p.18] ESG 목표 및 성과 Our Goal &amp; Performance 목표 세부 과제 2024년 성과 2025년 계획 친환경 경쟁력 강화 사업장 온실가스 감축 •  익산(PAFC) 공장 및 군산(SOFC) 공장 온실가스 배출량 416.93t 감축 •  익산PAFC 공장 전극 공정 에너지 절감 및 온실가스 배출 저감 활동 실시 •  익산PAFC 공장 제품 생산 원단위 온실가스 배출량 감축 중장기 로드맵 수립 • CCUS 연계형 모델 현장 Set-up 및 실증 완료 •  PAFC 모델 효율 제고 활동 지속 탄소중립 기여 제품/기술 확대 •  수소모델(5CSA PAFC 수소모델) 시제품  KESCO 인증 완료, 양산 시작 •  CCUS(Carbon Capture, Utilization and Storage, 탄소 포집, 활용 및 저장)연계형 모델 개발 및 시운전 완료 •  PAFC 모델 효율 제고 활동 진행 제품 전과정 환경 영향 최소화 •  Non-RCF(Refractory Ceramic Fibers, 내화성세라믹섬유) 부품 설계 진행 •  금속분리판 시제품 도면 설계 •  CSA(Cell Stack Assembly) 재사용/재제조  프로세스 구축 및 실행 •  Resin 재사용으로 자원 순환 활성화 •  Non-RCF 부품 개발 완료 •  금속분리판 시제품 제작 및 안정성 평가 •  CSA 재사용/재제조 수량 확대를 통한 폐기물 감축 •  Resin 재사용 지속 실행 및 사용량 감축 •  전극 비파괴 검사 방법 개발 및 적용으로 폐기물 감축 비재무 리스크 관리 확대 공급망 ESG 관리 확대 •  외부 전문기관 통해 공급망 ESG 평가 진행 •  평가 결과 바탕으로 개선 가이드 제공 •  협력사 대상 ESG 교육 및 평가 결과 제공 •  협력사 On-line 소통채널 구축 및 협력사 총회 /간담회 개최 •  주요 공급망 ESG 평가 진행 •  공급망 ESG 관리 절차서 제정하여 재계약 시 ESG 평가 결과 반영 •  협력사 경영 지원 활동 및 ESG 개선 지원  활동 시행 기후변화 리스크 정보 공개 •  IFRS 지속가능성 보고기준(ISSB)에 따라 기후 변화와 관련된 두산퓨얼셀의 거버넌스, 전략, ...
+QA Severity: Medium: responsibility and decision flow must be clear.</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 윤리경영 조직 및 운영 체계와 관련해 책임 주체와 의사결정 흐름을 중심으로 관리 체계를 설명하고 있습니다. 두산퓨얼셀 윤리경영 원칙과 업무 수행방침에 대해 두산퓨얼셀 내부 임직원은 물론 외부 이해관계자들의 이해를 향상시켰습니다. 이 구조는 윤리경영 조직 및 운영 체계의 담당 조직, 보고 경로, 감독 역할을 한 문맥에서 확인할 수 있게 합니다. 공개 내용은 윤리경영 조직 및 운영 체계의 책임 배분과 감독 수준을 함께 보여주며, 의사결정 체계가 실제 운영 구조와 어떻게 연결되는지 파악하는 데 도움이 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-026</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>거버넌스 / 위험 관리 (Risk Management) / 윤리 및 준법 리스크 관리</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>[p.18] ESG 목표 및 성과 Our Goal &amp; Performance 목표 세부 과제 2024년 성과 2025년 계획 친환경 경쟁력 강화 사업장 온실가스 감축 •  익산(PAFC) 공장 및 군산(SOFC) 공장 온실가스 배출량 416.93t 감축 •  익산PAFC 공장 전극 공정 에너지 절감 및 온실가스 배출 저감 활동 실시 •  익산PAFC 공장 제품 생산 원단위 온실가스 배출량 감축 중장기 로드맵 수립 • CCUS 연계형 모델 현장 Set-up 및 실증 완료 •  PAFC 모델 효율 제고 활동 지속 탄소중립 기여 제품/기술 확대 •  수소모델(5CSA PAFC 수소모델) 시제품  KESCO 인증 완료, 양산 시작 •  CCUS(Carbon Capture, Utilization and Storage, 탄소 포집, 활용 및 저장)연계형 모델 개발 및 시운전 완료 •  PAFC 모델 효율 제고 활동 진행 제품 전과정 환경 영향 최소화 •  Non-RCF(Refractory Ceramic Fibers, 내화성세라믹섬유) 부품 설계 진행 •  금속분리판 시제품 도면 설계 •  CSA(Cell Stack Assembly) 재사용/재제조  프로세스 구축 및 실행 •  Resin 재사용으로 자원 순환 활성화 •  Non-RCF 부품 개발 완료 •  금속분리판 시제품 제작 및 안정성 평가 •  CSA 재사용/재제조 수량 확대를 통한 폐기물 감축 •  Resin 재사용 지속 실행 및 사용량 감축 •  전극 비파괴 검사 방법 개발 및 적용으로 폐기물 감축 비재무 리스크 관리 확대 공급망 ESG 관리 확대 •  외부 전문기관 통해 공급망 ESG 평가 진행 •  평가 결과 바탕으로 개선 가이드 제공 •  협력사 대상 ESG 교육 및 평가 결과 제공 •  협력사 On-line 소통채널 구축 및 협력사 총회 /간담회 개최 •  주요 공급망 ESG 평가 진행 •  공급망 ESG 관리 절차서 제정하여 재계약 시 ESG 평가 결과 반영 •  협력사 경영 지원 활동 및 ESG 개선 지원  활동 시행 기후변화 리스크 정보 공개 •  IFRS 지속가능성 보고기준(ISSB)에 따라 기후 변화와 관련된 두산퓨얼셀의 거버넌스, 전략, ...
 [p.76] 공급망 ESG 관리 &gt; 4. 환경 &gt; 5. 윤리 및 공정거래 5.1 투명경영 및 반부패: 모든 비즈니스 관계에 있어 최고 수준의 윤리 기준이 요구됩니다. 모든 형태의 부패나 갈취, 횡령, 뇌물 수수, 상납, 향응 등의 비윤리적 행위는 엄격히 금지하는 무관용 정책을 표방해야 합니다. 두산퓨얼셀의 협력회사는 이러한 비윤리적 행위에 대한 감시 및 단속 절차를 이행하여 자율적 윤리 준수를 실천하고 반부패 법령을 준수하기 위해 감시, 기록 관리, 집행 절차를 실행해야 합니다. 5.2 공정거래 준수: 두산퓨얼셀의 협력회사는 사업상에서 부당하거나 부적절한 거래를 통해 이익을 취하는 수단을 제공하거나 수락하는 행위를 금지해야 합니다. 공정거래와 관련한 법규와 규정을 준수하여야 하며, 불공정한 거래 관행 등 공정한 거래 질서를 저해하는 행위를 하여서는 안 됩니다. 또한 상품 또는 용역의 가격, 공급량, 거래 지역, 거래조건 등에 관해 다른 사업자와 부당하게 경쟁을 제한하는 행위를 합의해서는 안 되며 회사, 경쟁업체, 협력업체, 제3자로부터 부정하게 정보를 획득하거나 획득한 정보를 사용 또는 공개해서는 안됩니다. 5.3 투명한 정보공개: 두산퓨얼셀의 협력회사는 관련법과 규정을 준수하여, 사업 활동과 재정 상황, 사업성과 등에 대한 정보를 거짓 없이 공개해야 합니다. 모든 업무 거래를 투명하게 실행하고 협력회사의 사업 장부와 기록에 정확히 반영해야 합니다. 협력회사의 노동, 보건과 안전, 환경관리 실태, 사업 활동, 구조, 재무 현황 및 성과에 관한 정보를 관련 일반적인 산업계 관행에 따라 공개해야 합니다. 공급망 내 관련 분야 실태 및 관행에 대한 기록 위조나 부실 표기는 용인될 수 없습니다. 5.4 지적재산권 보호: 두산퓨얼셀의 협력회사는 사업상 타인의 특허, 소프트웨어, 디자인, 상표 등과 같은 지적 재산을 침해하거나 불법적으로 사용하지 않습니다. 지적재산권을 존중하며 기술 및 노하우의 이전은 해당 권리를 보호하는 방식으로 이루어져야 합니다. 5.5 개인정보보호: 두산퓨얼셀의 협력회사는 모든 이해관계자(협력회사, 고객사, 임직원 등)의 개인정보를 체계적으로 관리 및 보호해야 하며, 개인정보의 수집, 저장, 이용, 제공, 파기 등 처리 시 관련 법규를 ...
 [p.90] 윤리경영 &gt; 공정거래 가이드라인 배포 공정거래 주요 활동 두산퓨얼셀은 구성원이 업무를 수행하면서 변화하는 규제 환경을 인식하고 의도치 않게 관련 법규를 위반하는 것을 방지하기 위해 노력하고 있습니다. 이를 위해, 하도급 부당특약금지 위반 예방을 위한 가이드라인과 부당지원 및 일감 몰아주기 예방을 위한 가이드라인을 수립했습니다. 하도급 업체에 자료 요청 시에는 기술자료제공 동의서 및 비밀유지계약서 작성, 교부 가이드라인을 배포하였습니다. 또한 대외 무역 제재 사항을 준수하기 위해 해외 업체와의 거래 시 실사 설문지를 배포하여 관련 위험을 예방하고 있습니다. &gt; 납품대금 연동제 실시 2023년 10월 4일부터 '납품대금 연동제'가 시행됨에 따라 사내 공지를 통해 관련 정보를 제공하여 법규를 준수할 수 있도록 노력하고 있습니다. &gt; 공정거래 교육 운영 두산퓨얼셀은 구성원이 공정거래 관련 법규 및 가이드라인을 실제 업무 수행에 적용할 수 있도록 다양한 교육 프로그램을 운영하고 있습니다. 이를 위해, 관련 부서 담당자를 대상으로 하도급법 주요 내용에 대한 온라인 교육과 부당지원 및 일감 몰아주기 예방 가이드라인에 대한 온라인 설명회를 진행했습니다. 또한, 최근 제정된 하도급대금 연동제 준수를 위해 구매팀 등 밀접하게 관련된 유관 부서에게 법의 주요 내용과 하도급대금 연동 의무 위반 시의 제재 사항을 설명하고, 해당 법의 준수를 위해 유의해야 할 고려사항을 교육했습니다. 뿐만 아니라, 비밀정보 유출 방지를 위해 정기적으로 IP 교육을 실시하여 위험성과 적절한 관리 및 보호 방법에 대한 교육을 통해 불공정 거래를 예방하고 있습니다. 교육과 설명회 진행 시에는 별도의 질의응답 세션을 마련하여 일방적인 지식 전달을 지양하고, 실무 담당자들이 실제 업무에서 참조할 수 있는 사례를 공유하여 시행착오를 최소화하고자 노력하고 있습니다. &gt; 공정거래 내부 모니터링 강화 두산퓨얼셀은 공정거래법을 준수하기 위해 계열사 내부 거래 시 결제 선에 법무 담당자를 포함시키고 계약 전 이사회 승인을 받아 부당지원 여부를 사전에 검토함으로써 법 위반 사항이 발생하지 않도록 하고 있습니다. 또한 하도급법을 준수하기 위해 지주 동반 성장팀과 함께 서울사무소, 연구소, 익산 및 ...
-[p.98] 리스크 관리 리스크 관리 활동 두산퓨얼셀은 기업 경영과 전략에 영향을 미칠 수 있는 리스크 유형을 분류하고 리스크 관리 프로세스에 따라 연 1회 이상 리스크를 검토하고 식별된 리스크에 대한 대응활동을 체계적으로 진행하고 있습니다. 특히, 리스크 관리 문화 조성을 위 하여 모든 임원 및 사외이사를 대상으로 연 1회 이상 리스크 관리 교육을 실시하고 있습니다. 리스크 유형 예상 리스크 관리 활동 리스크 유형 예상 리스크 관리활동 사업 리스크 수주 계약 조건 및  계약 이행 관련 리스크 - 제반 계약 조건에 대한 유관부서 내부 검토 - 계열체결에 대한 경영진 보고와 품의 품질 리스크 품질/생산 및 서비스 관련 리스크 -  전사적인 품질 이슈 발굴 및 개선 제도 시행 -  사무실과 공장에 품질 게시판 신설 -  격월 생산과 품질부서 기술교류회 개최 외환 리스크 국제적 영업활동 영위에 따른 환율변동 위험에 노출 -  수출과 수입통화 대응을 통한 Hedge로 환율변동 노출금액 상쇄 -  환위험관리규정에 따라 선물환 등 파생산품 이용하여 환율변동위험 관리 -  환율 10% 인상/인하에 따른 민감도 분석 공급망 리스크 부품 협력사의 비즈니스  연속성 측면의 리스크 -  비즈니스 영향과 구매 위험에 따른 1차 부품 협력사 Grouping -  Group별 ESG 평가 지표 개발과 자가진단 및 현장 실사 실시 - 자가진단 결과에 따른 개선 지원 이자율 리스크 이자율 변동위험에 노출된 변동금리부 금융자산 및 부채 리스크 -  변동금리부 금융자산 및 금융부채의 이자율 100bp 변동시 세전순손익에 미치는 민감도 분석 정보 보안 리스크 정보 유출 위험 - IT 권한 모니터링 실시하여 업무별 권한 최소화 - 연 4회 정보유출 피해 예방 모의 훈련 실시 신용 리스크 금융상품의 당사자 중 일방이 의무를 이행하지 않아 발생하는 재무손실 -  신규 거래처 계약시 재무정보와 신용평가기관 정보를 이용해 신용도를 평가하고 신용거래한도를 결정하며 담보 또는 지급보증 제공 받음 -  주기적인 거래처 신용도 재평가 및 신용거래한도 재조정 인적 리스크 우수인재 확보와 유지 및  유출로 인한 위험 -  전사 사업전략과 연계하여 전략적 인력계획 수립 - ...</x:v>
-      </x:c>
-      <x:c r="D27" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.98] 리스크 관리 리스크 관리 활동 두산퓨얼셀은 기업 경영과 전략에 영향을 미칠 수 있는 리스크 유형을 분류하고 리스크 관리 프로세스에 따라 연 1회 이상 리스크를 검토하고 식별된 리스크에 대한 대응활동을 체계적으로 진행하고 있습니다. 특히, 리스크 관리 문화 조성을 위 하여 모든 임원 및 사외이사를 대상으로 연 1회 이상 리스크 관리 교육을 실시하고 있습니다. 리스크 유형 예상 리스크 관리 활동 리스크 유형 예상 리스크 관리활동 사업 리스크 수주 계약 조건 및  계약 이행 관련 리스크 - 제반 계약 조건에 대한 유관부서 내부 검토 - 계열체결에 대한 경영진 보고와 품의 품질 리스크 품질/생산 및 서비스 관련 리스크 -  전사적인 품질 이슈 발굴 및 개선 제도 시행 -  사무실과 공장에 품질 게시판 신설 -  격월 생산과 품질부서 기술교류회 개최 외환 리스크 국제적 영업활동 영위에 따른 환율변동 위험에 노출 -  수출과 수입통화 대응을 통한 Hedge로 환율변동 노출금액 상쇄 -  환위험관리규정에 따라 선물환 등 파생산품 이용하여 환율변동위험 관리 -  환율 10% 인상/인하에 따른 민감도 분석 공급망 리스크 부품 협력사의 비즈니스  연속성 측면의 리스크 -  비즈니스 영향과 구매 위험에 따른 1차 부품 협력사 Grouping -  Group별 ESG 평가 지표 개발과 자가진단 및 현장 실사 실시 - 자가진단 결과에 따른 개선 지원 이자율 리스크 이자율 변동위험에 노출된 변동금리부 금융자산 및 부채 리스크 -  변동금리부 금융자산 및 금융부채의 이자율 100bp 변동시 세전순손익에 미치는 민감도 분석 정보 보안 리스크 정보 유출 위험 - IT 권한 모니터링 실시하여 업무별 권한 최소화 - 연 4회 정보유출 피해 예방 모의 훈련 실시 신용 리스크 금융상품의 당사자 중 일방이 의무를 이행하지 않아 발생하는 재무손실 -  신규 거래처 계약시 재무정보와 신용평가기관 정보를 이용해 신용도를 평가하고 신용거래한도를 결정하며 담보 또는 지급보증 제공 받음 -  주기적인 거래처 신용도 재평가 및 신용거래한도 재조정 인적 리스크 우수인재 확보와 유지 및  유출로 인한 위험 -  전사 사업전략과 연계하여 전략적 인력계획 수립 - ...</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 18;76;90;98
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E27" s="6" t="str">
-        <x:v>Selected Style: risk-control
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: risk-control
 Preferred Style Source: template
 Answer Type: risk-control
 Answer Intent: Explain the risk/control scope, then prevention, monitoring, and follow-up actions.
@@ -1473,34 +1866,46 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: High: must include risk/control and monitoring evidence.</x:v>
-      </x:c>
-      <x:c r="F27" s="6" t="str">
-        <x:v>모든 형태의 부패나 갈취, 횡령, 뇌물 수수, 상납, 향응 등의 비윤리적 행위는 엄격히 금지하는 무관용 정책을 표방해야 합니다. 회사는 이러한 비윤리적 행위에 대한 감시 및 단속 절차를 이행하여 자율적 윤리 준수를 실천하고 반부패 법령을 준수하기 위해 감시, 기록 관리, 집행 절차를 실행해야 합니다. 리스크 관리 리스크 관리 활동 두산퓨얼셀은 기업 경영과 전략에 영향을 미칠 수 있는 리스크 유형을 분류하고 리스크 관리 프로세스에 따라 연 1회 이상 리스크를 검토하고 식별된 리스크에 대한 대응활동을 체계적으로 진행하고 있습니다. 두산퓨얼셀는 윤리 및 준법 리스크 관리에서 식별된 위험 요인과 예방 활동을 연결해 관리 수준을 점검하고 있습니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="6" t="str">
-        <x:v>EBX-Q-027</x:v>
-      </x:c>
-      <x:c r="B28" s="6" t="str">
-        <x:v>거버넌스 / 지표 (Metrics) / 윤리 위반 및 준법 관련 사건 현황</x:v>
-      </x:c>
-      <x:c r="C28" s="6" t="str">
-        <x:v>[p.44] 환경법규 준수 두산퓨얼셀은 EHS(환경보건안전)와 관련된 전반적인 법규를 정기적으로 모니터링하며, 제·개정 사항을 사내 규정에 반영하고 있습니다. 또한, 새로운 내용을 사내 게시판을 통해 임직원과 공유하고, 사업장별 준수 평가를 통해 법규 위반 여부를 확인하고 있습니다. 아울러 원자재와 설비 등의 신규 구매 또는 변경 시 사전 EHS 평가를 통해 법규 리스크를 사전에 점검하여 법규 위반 리스크를 제거하고 있습니다. 2024년에는 환경 법규 위반이 없었습니다. 환경영향평가 두산퓨얼셀은 사업 활동이 미치는 직간접적인 환경 영향을 사전에 식별하고 체계적으로 관리하기 위해 환경영향평가를 실시하고 있습니다. 평가 결과는 사업장의 세부 목표에 반영되며, 이를 기반으로 실행 성과를 점검하고 환경 리스크를 관리하고 있습니다. 환경영향평가 프로세스 환경 교육 두산퓨얼셀은 임직원의 환경경영 인식 제고와 역량 강화를 위해 매년 정기적으로 교육을 실시하고 있습니다. 2024년에는 총 4회(402명)에 걸쳐 분기별로 교육을 실시했으며, 화학물질 취급 요령과 주요 환경 법규 위반 사례에 대한 교육을 신규로 추가해 운영했습니다. 사업장 폐기물 배출량 절감과 재활용률 향상을 위한 폐기물 관리 요령 교육을 마친 후에는 분리수거 캠페인도 함께 진행했습니다. 또한 환경기술인 교육과 부서별 EHS 담당자는 ISO 내부 심사 양성 교육 등 외부 교육을 이수했습니다. 환경 교육 이수 현장 폐기물 발생 카드 작성법 환경경영시스템 인증 두산퓨얼셀은 사업장에서 발생할 수 있는 환경 영향을 최소화하기 위해 2022년에 국제 표준인 환경경영시스템(ISO 14001) 인증을 취득했고 2024년에는 사후심사를 완료했습니다. 환경경영시스템의 지속적인 개선을 위해 전사 차원의 목표를 바탕으로 각 사업장별 세부 목표를 수립하고, 환경 성과 향상을 위한 활동을 수행하고 있습니다. 또한 실무자 중심의 운영을 통해 환경경영시스템의 고도화를 추진하고 있으며, 현재 양산체계를 구축 중인 SOFC 군산공장도 추후 환경경영시스템 인증을 받을 예정입니다. 환경영향평가 단계 단계별 수행 내용 환경영향평가 대상 선정 • 공정, 설비, 원재료, 건축물 등에 대해 2년 단위로 환경영향평가 실시 • 최초 평가 혹은 ...
+QA Severity: High: must include risk/control and monitoring evidence.</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>비밀정보 유출 방지를 위해 정기적으로 IP 교육을 실시하여 위험성과 적절한 관리 및 보호 방법에 대한 교육을 통해 불공정 거래를 예방하고 있습니다. 두산퓨얼셀은 기업 경영과 전략에 영향을 미칠 수 있는 리스크 유형을 분류하고 리스크 관리 프로세스에 따라 연 1회 이상 리스크를 검토하고 식별된 리스크에 대한 대응활동을 체계적으로 진행하고 있습니다. 윤리 및 준법 리스크 관리 관련 공시는 단순한 선언보다 예방, 모니터링, 후속 조치의 연결성을 중심으로 해석할 수 있습니다. 두산퓨얼셀은 윤리 및 준법 리스크 관리에서 식별된 위험 요인과 예방 활동을 연결해 관리 수준을 점검하고 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>EBX-Q-027</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>거버넌스 / 지표 (Metrics) / 윤리 위반 및 준법 관련 사건 현황</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[p.44] 환경법규 준수 두산퓨얼셀은 EHS(환경보건안전)와 관련된 전반적인 법규를 정기적으로 모니터링하며, 제·개정 사항을 사내 규정에 반영하고 있습니다. 또한, 새로운 내용을 사내 게시판을 통해 임직원과 공유하고, 사업장별 준수 평가를 통해 법규 위반 여부를 확인하고 있습니다. 아울러 원자재와 설비 등의 신규 구매 또는 변경 시 사전 EHS 평가를 통해 법규 리스크를 사전에 점검하여 법규 위반 리스크를 제거하고 있습니다. 2024년에는 환경 법규 위반이 없었습니다. 환경영향평가 두산퓨얼셀은 사업 활동이 미치는 직간접적인 환경 영향을 사전에 식별하고 체계적으로 관리하기 위해 환경영향평가를 실시하고 있습니다. 평가 결과는 사업장의 세부 목표에 반영되며, 이를 기반으로 실행 성과를 점검하고 환경 리스크를 관리하고 있습니다. 환경영향평가 프로세스 환경 교육 두산퓨얼셀은 임직원의 환경경영 인식 제고와 역량 강화를 위해 매년 정기적으로 교육을 실시하고 있습니다. 2024년에는 총 4회(402명)에 걸쳐 분기별로 교육을 실시했으며, 화학물질 취급 요령과 주요 환경 법규 위반 사례에 대한 교육을 신규로 추가해 운영했습니다. 사업장 폐기물 배출량 절감과 재활용률 향상을 위한 폐기물 관리 요령 교육을 마친 후에는 분리수거 캠페인도 함께 진행했습니다. 또한 환경기술인 교육과 부서별 EHS 담당자는 ISO 내부 심사 양성 교육 등 외부 교육을 이수했습니다. 환경 교육 이수 현장 폐기물 발생 카드 작성법 환경경영시스템 인증 두산퓨얼셀은 사업장에서 발생할 수 있는 환경 영향을 최소화하기 위해 2022년에 국제 표준인 환경경영시스템(ISO 14001) 인증을 취득했고 2024년에는 사후심사를 완료했습니다. 환경경영시스템의 지속적인 개선을 위해 전사 차원의 목표를 바탕으로 각 사업장별 세부 목표를 수립하고, 환경 성과 향상을 위한 활동을 수행하고 있습니다. 또한 실무자 중심의 운영을 통해 환경경영시스템의 고도화를 추진하고 있으며, 현재 양산체계를 구축 중인 SOFC 군산공장도 추후 환경경영시스템 인증을 받을 예정입니다. 환경영향평가 단계 단계별 수행 내용 환경영향평가 대상 선정 • 공정, 설비, 원재료, 건축물 등에 대해 2년 단위로 환경영향평가 실시 • 최초 평가 혹은 ...
 [p.88] 우편 서울특별시 중구 장충단로 275 두산타워 17층 두산퓨얼셀 이메일 inhye.jo@doosan.com 주관부서 두산퓨얼셀㈜ Legal/Compliance팀 윤리경영 윤리규범 서문 HELP DESK 운영 회사의 윤리경영 정책 및 윤리규범 세부내용, 기타 신고 및 제보 등과 관련된 궁금한 사항이나 문의에 대하여 상담, 안내할 수 있는 청구인 Help Desk를 두어 회사 홈페이지에 게재하였으며, 이를 통해 두산퓨얼셀㈜ 윤리경영 원칙과 업무 수행방침에 대해 두산퓨얼셀 내부 임직원은 물론 외부 이해관계자들의 이해를 향상시켰습니다. 사이버신고센터 운영방침 •  두산퓨얼셀 사이버신고센터는 임직원과 외부인 모두에게 열려 있으 며, 법령, 두산퓨얼셀 Credo 및 윤리규범 등 내부규정 위반행위, 기타 부당한 행위를 신고대상으로 합니다. •  신고는 익명 또는 실명으로 하실 수 있습니다. 다만, 회사는 구체적인 증거가 제시되지 않은 익명신고 등에 대하여 조사하지 않을 수 있습 니다. •  회사는 신고자의 신원 및 신고내용 등에 대한 비밀을 보장하며, 선의 의 신고자에 대한 불이익을 금지합니다. •  임직원의 신고에는 회사의 내부신고제도 운영규정이 적용되며, 본 규 정은 두드림 또는 주관부서를 통하여 안내 받으실 수 있습니다. •  회사는 사이버신고센터 이외에도 우편, 전화, 팩스, 이메일, 주관부서 방문 등 다양한 경로를 통하여 신고를 받고 있습니다. 접수 채널 윤리규범 및 윤리규범 위반과 관련한 문의사항이나 도움이 필요한 경우 두산퓨얼셀은 지속적인 성장을 위하여 인화, 고객 중심의 경영 철학과 함께 투명한 경영 및 혁신을 기반으로 기업의 경쟁력을 높이고 사회적 책임을 성실히 이행하고자 합니다. 이에 따라 윤리규범을 제정하여 임직원이 업무 수행 시 준수해야 할 행동 원칙으로 삼고 있습니다. 이 윤리규범은 두산퓨얼셀의 임직원(이하 "두산인")에게 적용되며, 두산퓨얼셀과 거래하는 협력업체 등 제3자도 함께 준수할 것을 권장합니다. 두산인은 관련법령과 윤리규범을 포함한 내부규정을 올바르게 이해하고 준수할 책임이 있습니다. Legal/Compliance팀은 윤리규범에서 명시되지 않았거나 구체적 해석이 필요한 사항에 대해 별도의 세부 규정을 마련 ...
 [p.89] 윤리경영 두산퓨얼셀의 모든 임직원은 윤리경영에 대한 인식 수준을 함양하고자 매년 온라인 및 대면방식 윤리규범 교육을 수강하고 있습니다. 모든 임직원은 윤리규범준수서약서와 이해관계서술서를 제출함으로써 윤리적 가치를 준수하고 정직·투명하게 업무를 수행하려는 의지를 표명하고 있습니다. 또한 모든 임직원들에게 CEO의 메시지를 통해 윤리규범에 대한 실천 및 준수를 당부하고 있습니다. 특히, 명절 등 선물이 오가는 시기에는 정직과 투명성 실천 및 법규준수를 강조하는 CEO Announcement를 매년 진행하여 임직원들의 경각심을 고취하고 있습니다. 반부패 및 윤리규범 교육 협력사 및 임직원 반부패 설문 두산퓨얼셀은 임직원과 협력사를 대상으로 매년 설문조사를 실시하여 윤리경영에 대한 임직원의 인식 수준을 확인하고 의견을 청취하고 있습니다. 설문조사 결과는 부정 방지 대안 수립, 부족한 부분에 대한 개선방안 도출 등의 윤리경영 활동 계획 수립에 활용하고 있습니다. 2024년 시행된 임직원 설문은 투명하고 적극적인 응답을 위하여 무기명으로 실시되었으며, 서술형을 포함하여 임직원 24개 항목, 협력사 21개 문항을 조사했습니다. 반부패 설문 구성 진단영역 문항수 기본정보(소속/직위) 2개 윤리경영 제도 및 시스템 6개 건전한 조직문화 4개 정직과 투명성 5개 공정한 경쟁 4개 종업원 관계 3개 설문은 매우 그렇지 않다(0점)-그렇지 않다(25점)-보통이다(50점)-그렇다(75점)-매우 그렇다(100점)의 척도로 조사하였으며 설문 결과 임직원 평균 76점, 협력사 평균 86점으로 그렇다(75점)와 매우 그렇다(100점)의 사잇값이 나와 비교적 윤리경영이 잘 지켜지는 것으로 조사되었습니다. 두산퓨얼셀은 평균값 이하가 나온 취약항목에 대해 개선대책을 마련하고 시행할 계획입니다. 윤리경영 위반 및 조치 2024년에는 2건의 제보가 접수되었으며 1건의 징계 처분(경고)이 이루어졌습니다. 고용노동부의 ‘개인정보보호 가이드’에 따라, 윤리규범 위반 건이 발생하면 개인정보를 제외한 구성원의 비윤리 행위 사례에 대해 백서제도, 윤리교육 사례전파, 윤리경영 Letter 형식으로 공개하는 등 관련 사항의 정보 공유를 통해 유사 사례의 재발을 방지하고 있습니다. 여기에 ...
-[p.90] 윤리경영 &gt; 공정거래 가이드라인 배포 공정거래 주요 활동 두산퓨얼셀은 구성원이 업무를 수행하면서 변화하는 규제 환경을 인식하고 의도치 않게 관련 법규를 위반하는 것을 방지하기 위해 노력하고 있습니다. 이를 위해, 하도급 부당특약금지 위반 예방을 위한 가이드라인과 부당지원 및 일감 몰아주기 예방을 위한 가이드라인을 수립했습니다. 하도급 업체에 자료 요청 시에는 기술자료제공 동의서 및 비밀유지계약서 작성, 교부 가이드라인을 배포하였습니다. 또한 대외 무역 제재 사항을 준수하기 위해 해외 업체와의 거래 시 실사 설문지를 배포하여 관련 위험을 예방하고 있습니다. &gt; 납품대금 연동제 실시 2023년 10월 4일부터 '납품대금 연동제'가 시행됨에 따라 사내 공지를 통해 관련 정보를 제공하여 법규를 준수할 수 있도록 노력하고 있습니다. &gt; 공정거래 교육 운영 두산퓨얼셀은 구성원이 공정거래 관련 법규 및 가이드라인을 실제 업무 수행에 적용할 수 있도록 다양한 교육 프로그램을 운영하고 있습니다. 이를 위해, 관련 부서 담당자를 대상으로 하도급법 주요 내용에 대한 온라인 교육과 부당지원 및 일감 몰아주기 예방 가이드라인에 대한 온라인 설명회를 진행했습니다. 또한, 최근 제정된 하도급대금 연동제 준수를 위해 구매팀 등 밀접하게 관련된 유관 부서에게 법의 주요 내용과 하도급대금 연동 의무 위반 시의 제재 사항을 설명하고, 해당 법의 준수를 위해 유의해야 할 고려사항을 교육했습니다. 뿐만 아니라, 비밀정보 유출 방지를 위해 정기적으로 IP 교육을 실시하여 위험성과 적절한 관리 및 보호 방법에 대한 교육을 통해 불공정 거래를 예방하고 있습니다. 교육과 설명회 진행 시에는 별도의 질의응답 세션을 마련하여 일방적인 지식 전달을 지양하고, 실무 담당자들이 실제 업무에서 참조할 수 있는 사례를 공유하여 시행착오를 최소화하고자 노력하고 있습니다. &gt; 공정거래 내부 모니터링 강화 두산퓨얼셀은 공정거래법을 준수하기 위해 계열사 내부 거래 시 결제 선에 법무 담당자를 포함시키고 계약 전 이사회 승인을 받아 부당지원 여부를 사전에 검토함으로써 법 위반 사항이 발생하지 않도록 하고 있습니다. 또한 하도급법을 준수하기 위해 지주 동반 성장팀과 함께 서울사무소, 연구소, 익산 및 ...</x:v>
-      </x:c>
-      <x:c r="D28" s="6" t="str">
-        <x:v>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
+[p.90] 윤리경영 &gt; 공정거래 가이드라인 배포 공정거래 주요 활동 두산퓨얼셀은 구성원이 업무를 수행하면서 변화하는 규제 환경을 인식하고 의도치 않게 관련 법규를 위반하는 것을 방지하기 위해 노력하고 있습니다. 이를 위해, 하도급 부당특약금지 위반 예방을 위한 가이드라인과 부당지원 및 일감 몰아주기 예방을 위한 가이드라인을 수립했습니다. 하도급 업체에 자료 요청 시에는 기술자료제공 동의서 및 비밀유지계약서 작성, 교부 가이드라인을 배포하였습니다. 또한 대외 무역 제재 사항을 준수하기 위해 해외 업체와의 거래 시 실사 설문지를 배포하여 관련 위험을 예방하고 있습니다. &gt; 납품대금 연동제 실시 2023년 10월 4일부터 '납품대금 연동제'가 시행됨에 따라 사내 공지를 통해 관련 정보를 제공하여 법규를 준수할 수 있도록 노력하고 있습니다. &gt; 공정거래 교육 운영 두산퓨얼셀은 구성원이 공정거래 관련 법규 및 가이드라인을 실제 업무 수행에 적용할 수 있도록 다양한 교육 프로그램을 운영하고 있습니다. 이를 위해, 관련 부서 담당자를 대상으로 하도급법 주요 내용에 대한 온라인 교육과 부당지원 및 일감 몰아주기 예방 가이드라인에 대한 온라인 설명회를 진행했습니다. 또한, 최근 제정된 하도급대금 연동제 준수를 위해 구매팀 등 밀접하게 관련된 유관 부서에게 법의 주요 내용과 하도급대금 연동 의무 위반 시의 제재 사항을 설명하고, 해당 법의 준수를 위해 유의해야 할 고려사항을 교육했습니다. 뿐만 아니라, 비밀정보 유출 방지를 위해 정기적으로 IP 교육을 실시하여 위험성과 적절한 관리 및 보호 방법에 대한 교육을 통해 불공정 거래를 예방하고 있습니다. 교육과 설명회 진행 시에는 별도의 질의응답 세션을 마련하여 일방적인 지식 전달을 지양하고, 실무 담당자들이 실제 업무에서 참조할 수 있는 사례를 공유하여 시행착오를 최소화하고자 노력하고 있습니다. &gt; 공정거래 내부 모니터링 강화 두산퓨얼셀은 공정거래법을 준수하기 위해 계열사 내부 거래 시 결제 선에 법무 담당자를 포함시키고 계약 전 이사회 승인을 받아 부당지원 여부를 사전에 검토함으로써 법 위반 사항이 발생하지 않도록 하고 있습니다. 또한 하도급법을 준수하기 위해 지주 동반 성장팀과 함께 서울사무소, 연구소, 익산 및 ...</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Source PDF: esg_report/20250630_20250630000947_두산퓨얼셀.pdf
 Source pages: 44;88;89;90
 Evidence type: qualitative
 Coverage status: SUFFICIENT
-Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</x:v>
-      </x:c>
-      <x:c r="E28" s="6" t="str">
-        <x:v>Selected Style: status-performance
+Numeric support: No directly linked quantitative row found by automated extraction; use qualitative evidence and review PDF tables if needed.</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Selected Style: status-performance
 Preferred Style Source: template
 Answer Type: status-performance
 Answer Intent: Explain the reported status in plain language, then weave figures into the management meaning.
@@ -1519,13 +1924,16 @@
 Do not keep OCR/table headings such as Corporate Governance, 구분, 추진체계와 주요성과, 코드 공시 항목.
 For ethics/compliance incident rows, use plain words such as report intake, actions, training completions, or committee/self-check activity when supported.
 QA Rules: {"requireKorean":true,"minSentences":3,"minCharsWarn":270,"forbidTechnicalMetricWording":true,"forbidEbxCode":true,"forbidSourceTrace":true,"forbidOcrArtifacts":true,"forbidGenericV6FallbackGrammar":true,"requireMetricNumberWhenMetricExpected":true}
-QA Severity: High: topic-fit figures, non-repetitive opening, no technical metric label.</x:v>
-      </x:c>
-      <x:c r="F28" s="6" t="str">
-        <x:v>두산퓨얼셀는 윤리 위반 및 준법 관련 사건 현황에 대해 발생 현황과 관리 성과를 함께 확인할 수 있도록 보고하고 있습니다. 사이버신고센터 운영방침 •  두산퓨얼셀 사이버신고센터는 임직원과 외부인 모두에게 열려 있으 며, 법령, 두산퓨얼셀 Credo 및 윤리규범 등 내부규정 위반행위, 기타 부당한 행위를 신고대상으로 합니다. 공개된 수치와 설명은 윤리 위반 및 준법 관련 사건 현황의 현재 수준을 확인하고 다음 관리 과제를 판단하는 기준이 되며, 전년 수치와 함께 제시될 때 추세 확인에도 활용될 수 있습니다. 윤리 위반 및 준법 관련 사건 현황는 단순한 발생 여부뿐 아니라 접수, 처리, 예방 조치가 관리 체계 안에서 이어지는지를 함께 확인하는 기준으로 활용되며, 공개 범위가 제한될 경우 후속 점검과 내부 관리 보완 여부를 함께 검토할 필요가 있습니다.</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+QA Severity: High: topic-fit figures, non-repetitive opening, no technical metric label.</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀은 윤리 위반 및 준법 관련 사건 현황에 대해 발생 현황과 관리 성과를 함께 확인할 수 있도록 보고하고 있습니다. 두산퓨얼셀 사이버신고센터는 임직원과 외부인 모두에게 열려 있으며, 법령, 두산퓨얼셀 Credo 및 윤리규범 등 내부규정 위반행위, 기타 부당한 행위를 신고대상으로 합니다. 이 윤리규범은 두산퓨얼셀의 임직원(이하 "두산인")에게 적용되며, 두산퓨얼셀과 거래하는 협력업체 등 제3자도 함께 준수할 것을 권장합니다. 공개된 수치와 설명은 윤리 위반 및 준법 관련 사건 현황의 현재 수준을 확인하고 다음 관리 과제를 판단하는 기준이 되며, 전년 수치와 함께 제시될 때 추세 확인에도 활용될 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>